--- a/results/cluster_ga/UAVs10_GRID13/revenue/UAVs10_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs10_GRID13/revenue/UAVs10_GRID13_Greedy.xlsx
@@ -677,34 +677,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.30714727526846</v>
+        <v>31.22054674250523</v>
       </c>
       <c r="C2" t="n">
-        <v>44.86681877882872</v>
+        <v>47.13537731549437</v>
       </c>
       <c r="D2" t="n">
-        <v>32.88437940302424</v>
+        <v>49.78331449788804</v>
       </c>
       <c r="E2" t="n">
-        <v>45.01328633658119</v>
+        <v>34.33743365166012</v>
       </c>
       <c r="F2" t="n">
-        <v>50.01484822420323</v>
+        <v>45.19396748058821</v>
       </c>
       <c r="G2" t="n">
-        <v>33.51240678474331</v>
+        <v>47.41547461077329</v>
       </c>
       <c r="H2" t="n">
-        <v>33.40880157348553</v>
+        <v>42.95655358612392</v>
       </c>
       <c r="I2" t="n">
-        <v>42.31385563957796</v>
+        <v>42.56280719900322</v>
       </c>
       <c r="J2" t="n">
-        <v>50.18154965762346</v>
+        <v>47.58366512449121</v>
       </c>
       <c r="K2" t="n">
-        <v>52.46955988520482</v>
+        <v>35.95565757234522</v>
       </c>
     </row>
   </sheetData>
@@ -783,34 +783,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.12169451413843</v>
+        <v>47.47413593477366</v>
       </c>
       <c r="C2" t="n">
-        <v>32.83950686672293</v>
+        <v>44.99785474437438</v>
       </c>
       <c r="D2" t="n">
-        <v>26.13773547668585</v>
+        <v>37.04262602419476</v>
       </c>
       <c r="E2" t="n">
-        <v>39.75310243778492</v>
+        <v>34.74622546539155</v>
       </c>
       <c r="F2" t="n">
-        <v>39.10739882408387</v>
+        <v>43.41816092648317</v>
       </c>
       <c r="G2" t="n">
-        <v>48.69846322826078</v>
+        <v>48.76954253186084</v>
       </c>
       <c r="H2" t="n">
-        <v>39.46709605516204</v>
+        <v>32.59833204356726</v>
       </c>
       <c r="I2" t="n">
-        <v>37.32709332577886</v>
+        <v>46.16448615552773</v>
       </c>
       <c r="J2" t="n">
-        <v>44.84632026065009</v>
+        <v>43.06132202010377</v>
       </c>
       <c r="K2" t="n">
-        <v>52.54025615758653</v>
+        <v>47.24352628621109</v>
       </c>
     </row>
   </sheetData>
@@ -889,34 +889,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>46.36689043990847</v>
+        <v>39.66702684899588</v>
       </c>
       <c r="C2" t="n">
-        <v>53.13167194119694</v>
+        <v>64.27975386542074</v>
       </c>
       <c r="D2" t="n">
-        <v>30.90579490707897</v>
+        <v>60.72033156928761</v>
       </c>
       <c r="E2" t="n">
-        <v>36.38549685963606</v>
+        <v>41.89115696264947</v>
       </c>
       <c r="F2" t="n">
-        <v>47.22288070906843</v>
+        <v>35.47430181194961</v>
       </c>
       <c r="G2" t="n">
-        <v>47.76023275968667</v>
+        <v>42.28691129136051</v>
       </c>
       <c r="H2" t="n">
-        <v>37.24842646956743</v>
+        <v>33.40879419160696</v>
       </c>
       <c r="I2" t="n">
-        <v>28.56200654260003</v>
+        <v>36.92182801320267</v>
       </c>
       <c r="J2" t="n">
-        <v>40.20722236951708</v>
+        <v>54.99610356420734</v>
       </c>
       <c r="K2" t="n">
-        <v>41.79814399845775</v>
+        <v>30.55587791082006</v>
       </c>
     </row>
   </sheetData>
@@ -995,34 +995,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.70337235730315</v>
+        <v>47.28838048412923</v>
       </c>
       <c r="C2" t="n">
-        <v>40.73103426708246</v>
+        <v>44.51290460420543</v>
       </c>
       <c r="D2" t="n">
-        <v>37.33653945535946</v>
+        <v>37.58628440288663</v>
       </c>
       <c r="E2" t="n">
-        <v>42.24775009147997</v>
+        <v>38.65083345808363</v>
       </c>
       <c r="F2" t="n">
-        <v>35.0130012756109</v>
+        <v>54.95240662898911</v>
       </c>
       <c r="G2" t="n">
-        <v>49.69993785561249</v>
+        <v>31.16610861883115</v>
       </c>
       <c r="H2" t="n">
-        <v>41.48519446064615</v>
+        <v>50.91148802419979</v>
       </c>
       <c r="I2" t="n">
-        <v>25.71140919150717</v>
+        <v>46.826817941585</v>
       </c>
       <c r="J2" t="n">
-        <v>38.61846053533621</v>
+        <v>48.62605872767271</v>
       </c>
       <c r="K2" t="n">
-        <v>40.78613203262123</v>
+        <v>41.2924568799679</v>
       </c>
     </row>
   </sheetData>
@@ -1101,34 +1101,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.47028779553473</v>
+        <v>39.96126383869292</v>
       </c>
       <c r="C2" t="n">
-        <v>82.38156546007539</v>
+        <v>40.49998712398559</v>
       </c>
       <c r="D2" t="n">
-        <v>14.67704199575992</v>
+        <v>35.43089737023864</v>
       </c>
       <c r="E2" t="n">
-        <v>44.82832607416794</v>
+        <v>38.41181171515289</v>
       </c>
       <c r="F2" t="n">
-        <v>22.67011204613729</v>
+        <v>35.52073151719247</v>
       </c>
       <c r="G2" t="n">
-        <v>15.86090468790871</v>
+        <v>39.07236935757475</v>
       </c>
       <c r="H2" t="n">
-        <v>41.65383194183386</v>
+        <v>35.89617998715928</v>
       </c>
       <c r="I2" t="n">
-        <v>30.83680721187164</v>
+        <v>41.11904719874104</v>
       </c>
       <c r="J2" t="n">
-        <v>41.62721249423125</v>
+        <v>44.42927825367948</v>
       </c>
       <c r="K2" t="n">
-        <v>70.32628659104486</v>
+        <v>38.21833697702134</v>
       </c>
     </row>
   </sheetData>
@@ -1207,34 +1207,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.78831258198327</v>
+        <v>32.87661870122341</v>
       </c>
       <c r="C2" t="n">
-        <v>26.61812645647843</v>
+        <v>38.60900599166548</v>
       </c>
       <c r="D2" t="n">
-        <v>17.35990963774774</v>
+        <v>44.69156201624779</v>
       </c>
       <c r="E2" t="n">
-        <v>51.68839690678967</v>
+        <v>36.74773874837947</v>
       </c>
       <c r="F2" t="n">
-        <v>36.33726470502014</v>
+        <v>36.12566965103361</v>
       </c>
       <c r="G2" t="n">
-        <v>33.84004787434122</v>
+        <v>54.18227951753921</v>
       </c>
       <c r="H2" t="n">
-        <v>44.54091868423163</v>
+        <v>36.65471063727109</v>
       </c>
       <c r="I2" t="n">
-        <v>52.63609464823446</v>
+        <v>58.42294955663275</v>
       </c>
       <c r="J2" t="n">
-        <v>53.36037670373592</v>
+        <v>36.87151086453157</v>
       </c>
       <c r="K2" t="n">
-        <v>44.65531474507184</v>
+        <v>44.00874551730823</v>
       </c>
     </row>
   </sheetData>
@@ -1313,34 +1313,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.97294181367977</v>
+        <v>40.96190280387582</v>
       </c>
       <c r="C2" t="n">
-        <v>30.82070182780532</v>
+        <v>35.00518718708187</v>
       </c>
       <c r="D2" t="n">
-        <v>30.97924791057401</v>
+        <v>43.82085994750273</v>
       </c>
       <c r="E2" t="n">
-        <v>32.53741767155352</v>
+        <v>41.45988859005467</v>
       </c>
       <c r="F2" t="n">
-        <v>36.23342397655907</v>
+        <v>40.98889182368539</v>
       </c>
       <c r="G2" t="n">
-        <v>47.60105886625133</v>
+        <v>30.50049735499833</v>
       </c>
       <c r="H2" t="n">
-        <v>32.70729926576708</v>
+        <v>39.7707961566695</v>
       </c>
       <c r="I2" t="n">
-        <v>29.62462113037672</v>
+        <v>40.84410180567031</v>
       </c>
       <c r="J2" t="n">
-        <v>47.1030050091779</v>
+        <v>38.151529436796</v>
       </c>
       <c r="K2" t="n">
-        <v>49.99320021448407</v>
+        <v>45.3322220479571</v>
       </c>
     </row>
   </sheetData>
@@ -1419,34 +1419,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.42289956759405</v>
+        <v>37.69446731865425</v>
       </c>
       <c r="C2" t="n">
-        <v>38.47027234997699</v>
+        <v>43.40517342192121</v>
       </c>
       <c r="D2" t="n">
-        <v>29.95887835194664</v>
+        <v>40.3977985260758</v>
       </c>
       <c r="E2" t="n">
-        <v>29.45173824827131</v>
+        <v>38.08985833823472</v>
       </c>
       <c r="F2" t="n">
-        <v>46.80102312431617</v>
+        <v>30.84453396645617</v>
       </c>
       <c r="G2" t="n">
-        <v>31.00446497255505</v>
+        <v>39.55416162908715</v>
       </c>
       <c r="H2" t="n">
-        <v>48.8890924950508</v>
+        <v>25.048134627472</v>
       </c>
       <c r="I2" t="n">
-        <v>33.06595589288075</v>
+        <v>41.12394705977808</v>
       </c>
       <c r="J2" t="n">
-        <v>43.36661084750901</v>
+        <v>54.72450252025798</v>
       </c>
       <c r="K2" t="n">
-        <v>43.88407391083004</v>
+        <v>31.24589482821547</v>
       </c>
     </row>
   </sheetData>
@@ -1525,34 +1525,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.72983358188753</v>
+        <v>32.05302780717292</v>
       </c>
       <c r="C2" t="n">
-        <v>41.01170656111913</v>
+        <v>42.4147766481991</v>
       </c>
       <c r="D2" t="n">
-        <v>40.22127116182529</v>
+        <v>35.74139005600755</v>
       </c>
       <c r="E2" t="n">
-        <v>29.10284825187362</v>
+        <v>38.50197263710912</v>
       </c>
       <c r="F2" t="n">
-        <v>39.86096208515708</v>
+        <v>39.64013794736233</v>
       </c>
       <c r="G2" t="n">
-        <v>36.58112206694441</v>
+        <v>34.91618969114703</v>
       </c>
       <c r="H2" t="n">
-        <v>33.96121787643492</v>
+        <v>35.83564868741291</v>
       </c>
       <c r="I2" t="n">
-        <v>23.57361806673444</v>
+        <v>31.05150373919422</v>
       </c>
       <c r="J2" t="n">
-        <v>32.87433290310521</v>
+        <v>46.77464738798059</v>
       </c>
       <c r="K2" t="n">
-        <v>50.81906426562867</v>
+        <v>37.14068454956692</v>
       </c>
     </row>
   </sheetData>
@@ -1631,34 +1631,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.82522638176467</v>
+        <v>38.75239973143557</v>
       </c>
       <c r="C2" t="n">
-        <v>35.71252632847668</v>
+        <v>42.14718780005419</v>
       </c>
       <c r="D2" t="n">
-        <v>34.53512170081682</v>
+        <v>40.66917821824581</v>
       </c>
       <c r="E2" t="n">
-        <v>31.84347131305311</v>
+        <v>39.42052575083034</v>
       </c>
       <c r="F2" t="n">
-        <v>46.57409780052414</v>
+        <v>30.86615637823669</v>
       </c>
       <c r="G2" t="n">
-        <v>38.05613834707555</v>
+        <v>48.99387362716348</v>
       </c>
       <c r="H2" t="n">
-        <v>33.21149856561575</v>
+        <v>48.97376844795187</v>
       </c>
       <c r="I2" t="n">
-        <v>47.27940058153285</v>
+        <v>37.86190967773713</v>
       </c>
       <c r="J2" t="n">
-        <v>24.96659828188149</v>
+        <v>21.15390139315879</v>
       </c>
       <c r="K2" t="n">
-        <v>49.72352730752321</v>
+        <v>41.33318175806497</v>
       </c>
     </row>
   </sheetData>
@@ -1737,34 +1737,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.05168738905435</v>
+        <v>26.8656968851218</v>
       </c>
       <c r="C2" t="n">
-        <v>41.19431614458434</v>
+        <v>38.15991539214507</v>
       </c>
       <c r="D2" t="n">
-        <v>33.67439254730644</v>
+        <v>33.8192535335007</v>
       </c>
       <c r="E2" t="n">
-        <v>31.92017068104115</v>
+        <v>36.75190905661479</v>
       </c>
       <c r="F2" t="n">
-        <v>28.78760738095177</v>
+        <v>37.27137638900321</v>
       </c>
       <c r="G2" t="n">
-        <v>48.69018961776521</v>
+        <v>44.57990035064138</v>
       </c>
       <c r="H2" t="n">
-        <v>37.80526561216754</v>
+        <v>46.56825268170559</v>
       </c>
       <c r="I2" t="n">
-        <v>35.31435933153113</v>
+        <v>41.18496161803617</v>
       </c>
       <c r="J2" t="n">
-        <v>52.54531920076288</v>
+        <v>40.89327529033706</v>
       </c>
       <c r="K2" t="n">
-        <v>27.46108253353105</v>
+        <v>42.01395998779685</v>
       </c>
     </row>
   </sheetData>
@@ -1843,34 +1843,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.90908473672605</v>
+        <v>33.38094189065064</v>
       </c>
       <c r="C2" t="n">
-        <v>37.91356461346212</v>
+        <v>35.95887682871085</v>
       </c>
       <c r="D2" t="n">
-        <v>38.87961174801613</v>
+        <v>76.59213892637473</v>
       </c>
       <c r="E2" t="n">
-        <v>47.26252943857337</v>
+        <v>46.11466869853995</v>
       </c>
       <c r="F2" t="n">
-        <v>30.95539545557353</v>
+        <v>50.70736435153716</v>
       </c>
       <c r="G2" t="n">
-        <v>48.71407939056265</v>
+        <v>35.05456331358639</v>
       </c>
       <c r="H2" t="n">
-        <v>62.50270095462523</v>
+        <v>42.41896195021718</v>
       </c>
       <c r="I2" t="n">
-        <v>34.02166767617422</v>
+        <v>43.6314528429649</v>
       </c>
       <c r="J2" t="n">
-        <v>31.14330090285512</v>
+        <v>31.36972740476186</v>
       </c>
       <c r="K2" t="n">
-        <v>49.5178782354371</v>
+        <v>43.90532799993767</v>
       </c>
     </row>
   </sheetData>
@@ -1949,34 +1949,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.35463571182104</v>
+        <v>47.36138851684815</v>
       </c>
       <c r="C2" t="n">
-        <v>29.77859580893599</v>
+        <v>31.57289082854294</v>
       </c>
       <c r="D2" t="n">
-        <v>33.5808419374973</v>
+        <v>39.22008535843139</v>
       </c>
       <c r="E2" t="n">
-        <v>38.89586735701565</v>
+        <v>51.78977258675314</v>
       </c>
       <c r="F2" t="n">
-        <v>37.58145186532042</v>
+        <v>47.3763883659119</v>
       </c>
       <c r="G2" t="n">
-        <v>35.37397931609796</v>
+        <v>45.62412166172545</v>
       </c>
       <c r="H2" t="n">
-        <v>29.64568990180741</v>
+        <v>40.98851500928482</v>
       </c>
       <c r="I2" t="n">
-        <v>36.02931157956204</v>
+        <v>37.37908286071018</v>
       </c>
       <c r="J2" t="n">
-        <v>36.48349320578714</v>
+        <v>53.39476066988799</v>
       </c>
       <c r="K2" t="n">
-        <v>46.1238977423433</v>
+        <v>29.65524337227733</v>
       </c>
     </row>
   </sheetData>
@@ -2055,34 +2055,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49.65970030767433</v>
+        <v>38.3364372375513</v>
       </c>
       <c r="C2" t="n">
-        <v>53.77269506938157</v>
+        <v>69.66414708321319</v>
       </c>
       <c r="D2" t="n">
-        <v>31.24496193817578</v>
+        <v>38.98422473848584</v>
       </c>
       <c r="E2" t="n">
-        <v>23.2552558385527</v>
+        <v>46.11601164469906</v>
       </c>
       <c r="F2" t="n">
-        <v>44.24316556828373</v>
+        <v>45.18815805297924</v>
       </c>
       <c r="G2" t="n">
-        <v>48.26394558698304</v>
+        <v>42.35412938566437</v>
       </c>
       <c r="H2" t="n">
-        <v>31.2834174327944</v>
+        <v>46.37733586615874</v>
       </c>
       <c r="I2" t="n">
-        <v>46.19637305376353</v>
+        <v>38.47392564690981</v>
       </c>
       <c r="J2" t="n">
-        <v>31.8156048043331</v>
+        <v>54.13194382302652</v>
       </c>
       <c r="K2" t="n">
-        <v>31.63620543354925</v>
+        <v>37.11099569803235</v>
       </c>
     </row>
   </sheetData>
@@ -2161,34 +2161,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.72329295488765</v>
+        <v>34.51643856977994</v>
       </c>
       <c r="C2" t="n">
-        <v>46.50805754117804</v>
+        <v>35.95988933554765</v>
       </c>
       <c r="D2" t="n">
-        <v>30.86651087503429</v>
+        <v>35.28063601910251</v>
       </c>
       <c r="E2" t="n">
-        <v>29.87729258646482</v>
+        <v>38.56698584874431</v>
       </c>
       <c r="F2" t="n">
-        <v>33.16652847937278</v>
+        <v>45.26372001385469</v>
       </c>
       <c r="G2" t="n">
-        <v>33.78588300997994</v>
+        <v>39.24371932088233</v>
       </c>
       <c r="H2" t="n">
-        <v>39.05650348330923</v>
+        <v>36.08024126297677</v>
       </c>
       <c r="I2" t="n">
-        <v>45.84403914637715</v>
+        <v>45.77976246871073</v>
       </c>
       <c r="J2" t="n">
-        <v>36.91599485419459</v>
+        <v>40.29177441427662</v>
       </c>
       <c r="K2" t="n">
-        <v>24.6929466109434</v>
+        <v>35.49033631701352</v>
       </c>
     </row>
   </sheetData>
@@ -2267,34 +2267,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.3724455210821</v>
+        <v>39.28152768111533</v>
       </c>
       <c r="C2" t="n">
-        <v>27.31866436184827</v>
+        <v>34.79479143339783</v>
       </c>
       <c r="D2" t="n">
-        <v>23.45160681880684</v>
+        <v>32.93019003136016</v>
       </c>
       <c r="E2" t="n">
-        <v>32.43223457768874</v>
+        <v>29.85582831035061</v>
       </c>
       <c r="F2" t="n">
-        <v>34.75322043540638</v>
+        <v>37.71742812902641</v>
       </c>
       <c r="G2" t="n">
-        <v>27.19032643800393</v>
+        <v>41.40108872704344</v>
       </c>
       <c r="H2" t="n">
-        <v>10.94010315173358</v>
+        <v>42.45889724318218</v>
       </c>
       <c r="I2" t="n">
-        <v>47.10530853658194</v>
+        <v>42.71434875290915</v>
       </c>
       <c r="J2" t="n">
-        <v>43.84570227700266</v>
+        <v>27.57077425792699</v>
       </c>
       <c r="K2" t="n">
-        <v>5715.704906703524</v>
+        <v>33.69543820480887</v>
       </c>
     </row>
   </sheetData>
@@ -2373,34 +2373,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.94405775256797</v>
+        <v>29.14538727955615</v>
       </c>
       <c r="C2" t="n">
-        <v>37.31011392610583</v>
+        <v>43.87891956372281</v>
       </c>
       <c r="D2" t="n">
-        <v>31.05922461141933</v>
+        <v>40.6074463207006</v>
       </c>
       <c r="E2" t="n">
-        <v>31.71384285070691</v>
+        <v>30.83676910793844</v>
       </c>
       <c r="F2" t="n">
-        <v>39.81341076679477</v>
+        <v>44.00669156207945</v>
       </c>
       <c r="G2" t="n">
-        <v>44.58604795838213</v>
+        <v>34.00314795628655</v>
       </c>
       <c r="H2" t="n">
-        <v>36.74915165471721</v>
+        <v>36.8109779555072</v>
       </c>
       <c r="I2" t="n">
-        <v>26.73417359932917</v>
+        <v>30.63623006975062</v>
       </c>
       <c r="J2" t="n">
-        <v>26.31910363182246</v>
+        <v>41.65047837599344</v>
       </c>
       <c r="K2" t="n">
-        <v>36.25820796773016</v>
+        <v>33.80143045297955</v>
       </c>
     </row>
   </sheetData>
@@ -2479,34 +2479,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.93415551717199</v>
+        <v>36.21132937425244</v>
       </c>
       <c r="C2" t="n">
-        <v>2166.551485832757</v>
+        <v>47.99226986282593</v>
       </c>
       <c r="D2" t="n">
-        <v>35.7957109896194</v>
+        <v>33.01205693266837</v>
       </c>
       <c r="E2" t="n">
-        <v>28.71884112797364</v>
+        <v>45.3404843853527</v>
       </c>
       <c r="F2" t="n">
-        <v>25.90979544333739</v>
+        <v>35.08349503020838</v>
       </c>
       <c r="G2" t="n">
-        <v>32.26497183457458</v>
+        <v>54.48146738257134</v>
       </c>
       <c r="H2" t="n">
-        <v>20.82802678245562</v>
+        <v>30.3555817356219</v>
       </c>
       <c r="I2" t="n">
-        <v>40.84742127147483</v>
+        <v>41.12761778552626</v>
       </c>
       <c r="J2" t="n">
-        <v>30.7588642453515</v>
+        <v>36.86158557560906</v>
       </c>
       <c r="K2" t="n">
-        <v>27.40867928083735</v>
+        <v>33.88431758883913</v>
       </c>
     </row>
   </sheetData>
@@ -2585,34 +2585,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.10123241730047</v>
+        <v>40.08015846912004</v>
       </c>
       <c r="C2" t="n">
-        <v>29.62149298413027</v>
+        <v>58.05203351083689</v>
       </c>
       <c r="D2" t="n">
-        <v>36.90627108580281</v>
+        <v>35.50692826223989</v>
       </c>
       <c r="E2" t="n">
-        <v>41.86425240222945</v>
+        <v>42.80831973653194</v>
       </c>
       <c r="F2" t="n">
-        <v>48.11975601844994</v>
+        <v>34.59586084938198</v>
       </c>
       <c r="G2" t="n">
-        <v>46.26170329117204</v>
+        <v>40.78176298017159</v>
       </c>
       <c r="H2" t="n">
-        <v>40.47453005009763</v>
+        <v>46.33931180591279</v>
       </c>
       <c r="I2" t="n">
-        <v>26.53548105391348</v>
+        <v>47.07818589770542</v>
       </c>
       <c r="J2" t="n">
-        <v>35.81062204286289</v>
+        <v>57.15469901964867</v>
       </c>
       <c r="K2" t="n">
-        <v>45.19665912549613</v>
+        <v>38.76843801330312</v>
       </c>
     </row>
   </sheetData>
@@ -2691,34 +2691,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.02491804147144</v>
+        <v>30.66405864970912</v>
       </c>
       <c r="C2" t="n">
-        <v>33.02929536410439</v>
+        <v>41.43858021232078</v>
       </c>
       <c r="D2" t="n">
-        <v>39.93474649721934</v>
+        <v>41.60684497390381</v>
       </c>
       <c r="E2" t="n">
-        <v>33.21369293101193</v>
+        <v>39.59159212456593</v>
       </c>
       <c r="F2" t="n">
-        <v>41.1316184098518</v>
+        <v>30.46367437287212</v>
       </c>
       <c r="G2" t="n">
-        <v>46.26377235386138</v>
+        <v>41.75401309184839</v>
       </c>
       <c r="H2" t="n">
-        <v>28.76217053644093</v>
+        <v>29.66358084027068</v>
       </c>
       <c r="I2" t="n">
-        <v>38.90014532426667</v>
+        <v>46.01295844462282</v>
       </c>
       <c r="J2" t="n">
-        <v>22.71561938419008</v>
+        <v>36.74209819772706</v>
       </c>
       <c r="K2" t="n">
-        <v>38.1631550234619</v>
+        <v>44.96682454593576</v>
       </c>
     </row>
   </sheetData>
@@ -2797,34 +2797,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.80970711994902</v>
+        <v>36.30582615148162</v>
       </c>
       <c r="C2" t="n">
-        <v>23.45727832029723</v>
+        <v>46.00983485124639</v>
       </c>
       <c r="D2" t="n">
-        <v>32.64936889813646</v>
+        <v>42.28392124837336</v>
       </c>
       <c r="E2" t="n">
-        <v>54.85793161390107</v>
+        <v>40.70301132687626</v>
       </c>
       <c r="F2" t="n">
-        <v>38.44073051806014</v>
+        <v>40.48419264118704</v>
       </c>
       <c r="G2" t="n">
-        <v>42.17585035811284</v>
+        <v>51.0307079878902</v>
       </c>
       <c r="H2" t="n">
-        <v>38.29529381745218</v>
+        <v>39.67115103098888</v>
       </c>
       <c r="I2" t="n">
-        <v>42.55963581083643</v>
+        <v>39.59392647475514</v>
       </c>
       <c r="J2" t="n">
-        <v>39.98121988861923</v>
+        <v>24.99019991932162</v>
       </c>
       <c r="K2" t="n">
-        <v>40.96965829394745</v>
+        <v>43.20572769000955</v>
       </c>
     </row>
   </sheetData>
@@ -2903,34 +2903,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.23050510546611</v>
+        <v>36.4432846920833</v>
       </c>
       <c r="C2" t="n">
-        <v>24.05011488752158</v>
+        <v>42.04406541305859</v>
       </c>
       <c r="D2" t="n">
-        <v>158.8099384893584</v>
+        <v>53.45294709504076</v>
       </c>
       <c r="E2" t="n">
-        <v>27.24704692307474</v>
+        <v>33.99892801767614</v>
       </c>
       <c r="F2" t="n">
-        <v>49.89339169285164</v>
+        <v>47.69244076205038</v>
       </c>
       <c r="G2" t="n">
-        <v>33.99527194096638</v>
+        <v>38.36002593984065</v>
       </c>
       <c r="H2" t="n">
-        <v>19.94451845290859</v>
+        <v>53.54860290272238</v>
       </c>
       <c r="I2" t="n">
-        <v>29.76924175865432</v>
+        <v>36.62038309269077</v>
       </c>
       <c r="J2" t="n">
-        <v>24.30650950283908</v>
+        <v>34.59640483162769</v>
       </c>
       <c r="K2" t="n">
-        <v>77.20799630420444</v>
+        <v>42.97255915375913</v>
       </c>
     </row>
   </sheetData>
@@ -3009,34 +3009,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.25982255944631</v>
+        <v>24.39134430797246</v>
       </c>
       <c r="C2" t="n">
-        <v>60.94851242422698</v>
+        <v>34.69500524183071</v>
       </c>
       <c r="D2" t="n">
-        <v>50.12892966197995</v>
+        <v>42.41759970617491</v>
       </c>
       <c r="E2" t="n">
-        <v>51.72693620420814</v>
+        <v>38.59540514968582</v>
       </c>
       <c r="F2" t="n">
-        <v>28.46400122845155</v>
+        <v>41.59248200167075</v>
       </c>
       <c r="G2" t="n">
-        <v>45.48329007149226</v>
+        <v>38.29956976362497</v>
       </c>
       <c r="H2" t="n">
-        <v>34.98595488306682</v>
+        <v>29.7685055439005</v>
       </c>
       <c r="I2" t="n">
-        <v>24.17751501939248</v>
+        <v>42.54211370832778</v>
       </c>
       <c r="J2" t="n">
-        <v>40.5123203723439</v>
+        <v>57.33840272733519</v>
       </c>
       <c r="K2" t="n">
-        <v>38.16222006323436</v>
+        <v>36.55630115796792</v>
       </c>
     </row>
   </sheetData>
@@ -3115,34 +3115,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.60511791106645</v>
+        <v>36.27459357244825</v>
       </c>
       <c r="C2" t="n">
-        <v>1134.955166603124</v>
+        <v>46.40773684365599</v>
       </c>
       <c r="D2" t="n">
-        <v>37.82185283896761</v>
+        <v>49.28664596553355</v>
       </c>
       <c r="E2" t="n">
-        <v>44.9278236896029</v>
+        <v>35.55498949504376</v>
       </c>
       <c r="F2" t="n">
-        <v>12.21411410418918</v>
+        <v>44.6712796756356</v>
       </c>
       <c r="G2" t="n">
-        <v>44.64996388407636</v>
+        <v>46.07306473861878</v>
       </c>
       <c r="H2" t="n">
-        <v>30.35541598001782</v>
+        <v>26.83188762708776</v>
       </c>
       <c r="I2" t="n">
-        <v>25.56413119813106</v>
+        <v>47.29427108001319</v>
       </c>
       <c r="J2" t="n">
-        <v>39.60143155116917</v>
+        <v>44.62835274630505</v>
       </c>
       <c r="K2" t="n">
-        <v>48.24563718038578</v>
+        <v>45.53503616197186</v>
       </c>
     </row>
   </sheetData>
@@ -3221,34 +3221,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.54745307176788</v>
+        <v>35.041831626368</v>
       </c>
       <c r="C2" t="n">
-        <v>36.96726152690833</v>
+        <v>37.72511189958442</v>
       </c>
       <c r="D2" t="n">
-        <v>34.97751889362946</v>
+        <v>59.43383703878504</v>
       </c>
       <c r="E2" t="n">
-        <v>48.60029293704836</v>
+        <v>42.82333011751896</v>
       </c>
       <c r="F2" t="n">
-        <v>36.72501662622498</v>
+        <v>41.7589773595468</v>
       </c>
       <c r="G2" t="n">
-        <v>46.55700447064255</v>
+        <v>42.29850411774094</v>
       </c>
       <c r="H2" t="n">
-        <v>48.93099433117327</v>
+        <v>41.84904598896173</v>
       </c>
       <c r="I2" t="n">
-        <v>39.0784964587305</v>
+        <v>47.75444785356656</v>
       </c>
       <c r="J2" t="n">
-        <v>30.73239882682691</v>
+        <v>51.53489845390569</v>
       </c>
       <c r="K2" t="n">
-        <v>52.55527299191999</v>
+        <v>39.07450397551237</v>
       </c>
     </row>
   </sheetData>
@@ -3327,34 +3327,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>48.95164119845822</v>
+        <v>42.59941392984104</v>
       </c>
       <c r="C2" t="n">
-        <v>26.02155567218464</v>
+        <v>36.16325513453874</v>
       </c>
       <c r="D2" t="n">
-        <v>32.72679887964768</v>
+        <v>53.40483432463724</v>
       </c>
       <c r="E2" t="n">
-        <v>31.94296504364816</v>
+        <v>41.81723565299838</v>
       </c>
       <c r="F2" t="n">
-        <v>36.42211774324285</v>
+        <v>25.67570015522721</v>
       </c>
       <c r="G2" t="n">
-        <v>57.44691044094647</v>
+        <v>42.01862880068384</v>
       </c>
       <c r="H2" t="n">
-        <v>34.50016424405943</v>
+        <v>44.13593472624927</v>
       </c>
       <c r="I2" t="n">
-        <v>36.6484531535751</v>
+        <v>39.19344096474602</v>
       </c>
       <c r="J2" t="n">
-        <v>42.39760605370824</v>
+        <v>39.68540811113443</v>
       </c>
       <c r="K2" t="n">
-        <v>34.35947361618653</v>
+        <v>37.39386698698717</v>
       </c>
     </row>
   </sheetData>
@@ -3433,34 +3433,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.81225342319538</v>
+        <v>41.60556935029523</v>
       </c>
       <c r="C2" t="n">
-        <v>51.79297801058051</v>
+        <v>45.75319627151122</v>
       </c>
       <c r="D2" t="n">
-        <v>28.25096725659662</v>
+        <v>58.67882209893488</v>
       </c>
       <c r="E2" t="n">
-        <v>41.28586300712808</v>
+        <v>37.54658271528959</v>
       </c>
       <c r="F2" t="n">
-        <v>46.44204291763356</v>
+        <v>39.12157778109263</v>
       </c>
       <c r="G2" t="n">
-        <v>34.03321324600808</v>
+        <v>39.7784092377222</v>
       </c>
       <c r="H2" t="n">
-        <v>50.43764571577291</v>
+        <v>38.18404778932091</v>
       </c>
       <c r="I2" t="n">
-        <v>43.64793387823865</v>
+        <v>44.86899844464816</v>
       </c>
       <c r="J2" t="n">
-        <v>37.93785801187904</v>
+        <v>30.07971887894899</v>
       </c>
       <c r="K2" t="n">
-        <v>41.33369782340181</v>
+        <v>37.48190780026776</v>
       </c>
     </row>
   </sheetData>
@@ -3539,34 +3539,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.7681951233571</v>
+        <v>38.37469407331012</v>
       </c>
       <c r="C2" t="n">
-        <v>35.42689878692492</v>
+        <v>34.89363134475398</v>
       </c>
       <c r="D2" t="n">
-        <v>34.53675311505188</v>
+        <v>44.81668003250033</v>
       </c>
       <c r="E2" t="n">
-        <v>38.8703516053947</v>
+        <v>30.9227644357994</v>
       </c>
       <c r="F2" t="n">
-        <v>26.75439210923295</v>
+        <v>54.37676181062734</v>
       </c>
       <c r="G2" t="n">
-        <v>42.34580762782331</v>
+        <v>32.12095321584997</v>
       </c>
       <c r="H2" t="n">
-        <v>28.35831179914846</v>
+        <v>38.63255632778954</v>
       </c>
       <c r="I2" t="n">
-        <v>28.09417293698876</v>
+        <v>43.0096313271743</v>
       </c>
       <c r="J2" t="n">
-        <v>50.41516556244049</v>
+        <v>37.23133200635491</v>
       </c>
       <c r="K2" t="n">
-        <v>43.55152013512784</v>
+        <v>35.85250486135634</v>
       </c>
     </row>
   </sheetData>
@@ -3645,34 +3645,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>46.342088888631</v>
+        <v>38.3970972518286</v>
       </c>
       <c r="C2" t="n">
-        <v>38.0198235666261</v>
+        <v>23.0648226136857</v>
       </c>
       <c r="D2" t="n">
-        <v>42.67505460192501</v>
+        <v>43.138386990726</v>
       </c>
       <c r="E2" t="n">
-        <v>55.72718859793067</v>
+        <v>40.26612867130176</v>
       </c>
       <c r="F2" t="n">
-        <v>31.95084941384608</v>
+        <v>50.06276971452505</v>
       </c>
       <c r="G2" t="n">
-        <v>26.50802858706254</v>
+        <v>42.05604864564657</v>
       </c>
       <c r="H2" t="n">
-        <v>34.90292048578549</v>
+        <v>43.11639270661723</v>
       </c>
       <c r="I2" t="n">
-        <v>35.93966169555264</v>
+        <v>36.452078226761</v>
       </c>
       <c r="J2" t="n">
-        <v>27.00250449045497</v>
+        <v>47.48529286339389</v>
       </c>
       <c r="K2" t="n">
-        <v>37.30179857040677</v>
+        <v>42.6578063427973</v>
       </c>
     </row>
   </sheetData>
@@ -3751,34 +3751,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.03408910689922</v>
+        <v>27.60216574803148</v>
       </c>
       <c r="C2" t="n">
-        <v>50.03584205616504</v>
+        <v>50.34819305531707</v>
       </c>
       <c r="D2" t="n">
-        <v>23.45848353491819</v>
+        <v>45.85886867349353</v>
       </c>
       <c r="E2" t="n">
-        <v>38.32726827229249</v>
+        <v>35.33076322438576</v>
       </c>
       <c r="F2" t="n">
-        <v>27.49784098682184</v>
+        <v>31.40146627477172</v>
       </c>
       <c r="G2" t="n">
-        <v>51.27083057291065</v>
+        <v>37.42840775007297</v>
       </c>
       <c r="H2" t="n">
-        <v>24.86147914719691</v>
+        <v>38.85917862378212</v>
       </c>
       <c r="I2" t="n">
-        <v>28.25967006601186</v>
+        <v>46.17978703807136</v>
       </c>
       <c r="J2" t="n">
-        <v>39.09871392569351</v>
+        <v>38.40129986160353</v>
       </c>
       <c r="K2" t="n">
-        <v>39.0630288871747</v>
+        <v>27.83281719402581</v>
       </c>
     </row>
   </sheetData>
@@ -3857,34 +3857,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.88809908609747</v>
+        <v>32.97780174274913</v>
       </c>
       <c r="C2" t="n">
-        <v>40.62685842735507</v>
+        <v>33.35184379154211</v>
       </c>
       <c r="D2" t="n">
-        <v>30.25061649218945</v>
+        <v>55.26121397422741</v>
       </c>
       <c r="E2" t="n">
-        <v>35.45836315302341</v>
+        <v>38.24656443387723</v>
       </c>
       <c r="F2" t="n">
-        <v>56.2521657436617</v>
+        <v>34.36953257889387</v>
       </c>
       <c r="G2" t="n">
-        <v>36.50282292822417</v>
+        <v>36.24219914397569</v>
       </c>
       <c r="H2" t="n">
-        <v>38.50746275006404</v>
+        <v>46.80336173801292</v>
       </c>
       <c r="I2" t="n">
-        <v>20.70130963741325</v>
+        <v>38.71876969273853</v>
       </c>
       <c r="J2" t="n">
-        <v>45.45486388074951</v>
+        <v>42.31165353805251</v>
       </c>
       <c r="K2" t="n">
-        <v>54.65069773019349</v>
+        <v>40.23249921360885</v>
       </c>
     </row>
   </sheetData>
@@ -3963,34 +3963,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.24057984216839</v>
+        <v>32.94366461909141</v>
       </c>
       <c r="C2" t="n">
-        <v>50.04906061465461</v>
+        <v>63.60861614082948</v>
       </c>
       <c r="D2" t="n">
-        <v>23.05139265687579</v>
+        <v>39.53974636825364</v>
       </c>
       <c r="E2" t="n">
-        <v>37.34114544960813</v>
+        <v>36.56480148797788</v>
       </c>
       <c r="F2" t="n">
-        <v>29.67736666634251</v>
+        <v>36.66585751654836</v>
       </c>
       <c r="G2" t="n">
-        <v>30.68197573260545</v>
+        <v>37.25795142227616</v>
       </c>
       <c r="H2" t="n">
-        <v>39.33627608125051</v>
+        <v>39.88337603842724</v>
       </c>
       <c r="I2" t="n">
-        <v>35.16477731713739</v>
+        <v>39.74577997692616</v>
       </c>
       <c r="J2" t="n">
-        <v>33.24515862127485</v>
+        <v>40.8257292223343</v>
       </c>
       <c r="K2" t="n">
-        <v>53.81887532803161</v>
+        <v>32.67204050442664</v>
       </c>
     </row>
   </sheetData>
@@ -4069,34 +4069,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.89997932691247</v>
+        <v>32.81559318392547</v>
       </c>
       <c r="C2" t="n">
-        <v>40.38452182746914</v>
+        <v>37.46793570880222</v>
       </c>
       <c r="D2" t="n">
-        <v>39.25418663277283</v>
+        <v>46.83247130571698</v>
       </c>
       <c r="E2" t="n">
-        <v>41.20561574790311</v>
+        <v>37.49492138283091</v>
       </c>
       <c r="F2" t="n">
-        <v>26.55433388641261</v>
+        <v>29.00674694604233</v>
       </c>
       <c r="G2" t="n">
-        <v>36.76096450416217</v>
+        <v>32.64882680917136</v>
       </c>
       <c r="H2" t="n">
-        <v>40.41989606525807</v>
+        <v>36.39990561471745</v>
       </c>
       <c r="I2" t="n">
-        <v>24.30150665313058</v>
+        <v>47.96643687109717</v>
       </c>
       <c r="J2" t="n">
-        <v>29.24704951342652</v>
+        <v>50.71483432303316</v>
       </c>
       <c r="K2" t="n">
-        <v>54.22001215131694</v>
+        <v>42.25034785442599</v>
       </c>
     </row>
   </sheetData>
@@ -4175,34 +4175,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.98869715570315</v>
+        <v>34.9444045353105</v>
       </c>
       <c r="C2" t="n">
-        <v>59.81117932792112</v>
+        <v>35.95849359829242</v>
       </c>
       <c r="D2" t="n">
-        <v>46.21527618127323</v>
+        <v>46.41609076640468</v>
       </c>
       <c r="E2" t="n">
-        <v>30.27739451280477</v>
+        <v>35.5187792898156</v>
       </c>
       <c r="F2" t="n">
-        <v>24.24258504692096</v>
+        <v>42.91693290345488</v>
       </c>
       <c r="G2" t="n">
-        <v>42.32634075303981</v>
+        <v>38.55918209321569</v>
       </c>
       <c r="H2" t="n">
-        <v>32.64701118267898</v>
+        <v>37.72851939785502</v>
       </c>
       <c r="I2" t="n">
-        <v>32.54446304432315</v>
+        <v>51.27757665155377</v>
       </c>
       <c r="J2" t="n">
-        <v>40.89915606946369</v>
+        <v>61.48887738940106</v>
       </c>
       <c r="K2" t="n">
-        <v>48.33649590662524</v>
+        <v>38.58105239372116</v>
       </c>
     </row>
   </sheetData>
@@ -4281,34 +4281,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.02513462588892</v>
+        <v>37.02408772454488</v>
       </c>
       <c r="C2" t="n">
-        <v>32.84967837480322</v>
+        <v>48.95058617305332</v>
       </c>
       <c r="D2" t="n">
-        <v>38.07747684742967</v>
+        <v>43.06066623509849</v>
       </c>
       <c r="E2" t="n">
-        <v>48.89932406441753</v>
+        <v>40.67942446938972</v>
       </c>
       <c r="F2" t="n">
-        <v>37.43880573006469</v>
+        <v>45.33705934574912</v>
       </c>
       <c r="G2" t="n">
-        <v>49.38577006310432</v>
+        <v>41.7420940966264</v>
       </c>
       <c r="H2" t="n">
-        <v>29.79696765048428</v>
+        <v>45.40094597507562</v>
       </c>
       <c r="I2" t="n">
-        <v>53.71249708995545</v>
+        <v>43.91515395596976</v>
       </c>
       <c r="J2" t="n">
-        <v>32.86394202764001</v>
+        <v>30.78779798635157</v>
       </c>
       <c r="K2" t="n">
-        <v>54.00839194757596</v>
+        <v>41.10436736984568</v>
       </c>
     </row>
   </sheetData>
@@ -4387,34 +4387,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.82321526877153</v>
+        <v>33.65959360318512</v>
       </c>
       <c r="C2" t="n">
-        <v>47.56741747514807</v>
+        <v>48.03866812798667</v>
       </c>
       <c r="D2" t="n">
-        <v>33.4460149701536</v>
+        <v>35.66251453806868</v>
       </c>
       <c r="E2" t="n">
-        <v>36.39025389761809</v>
+        <v>50.26273924495072</v>
       </c>
       <c r="F2" t="n">
-        <v>42.43001785327495</v>
+        <v>37.65669737257904</v>
       </c>
       <c r="G2" t="n">
-        <v>40.25244299506263</v>
+        <v>41.72825019629802</v>
       </c>
       <c r="H2" t="n">
-        <v>44.18918209774875</v>
+        <v>35.01191204842281</v>
       </c>
       <c r="I2" t="n">
-        <v>36.58466748542995</v>
+        <v>57.74659468621144</v>
       </c>
       <c r="J2" t="n">
-        <v>37.73120663774436</v>
+        <v>50.179914931822</v>
       </c>
       <c r="K2" t="n">
-        <v>36.7738482422531</v>
+        <v>29.2390503399232</v>
       </c>
     </row>
   </sheetData>
@@ -4493,34 +4493,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.13594719688565</v>
+        <v>45.20442905702851</v>
       </c>
       <c r="C2" t="n">
-        <v>32.38702528981074</v>
+        <v>46.01182426204456</v>
       </c>
       <c r="D2" t="n">
-        <v>26.13267407939979</v>
+        <v>51.23906421702625</v>
       </c>
       <c r="E2" t="n">
-        <v>31.49901380592344</v>
+        <v>35.14748119131809</v>
       </c>
       <c r="F2" t="n">
-        <v>41.72545703831009</v>
+        <v>56.13609127866126</v>
       </c>
       <c r="G2" t="n">
-        <v>48.55156529468078</v>
+        <v>35.96143334264577</v>
       </c>
       <c r="H2" t="n">
-        <v>35.16132227506672</v>
+        <v>41.3041490244349</v>
       </c>
       <c r="I2" t="n">
-        <v>23.59891583526336</v>
+        <v>52.22767086594577</v>
       </c>
       <c r="J2" t="n">
-        <v>37.12362894022358</v>
+        <v>47.29904210824542</v>
       </c>
       <c r="K2" t="n">
-        <v>3144.597192077009</v>
+        <v>31.48827060974472</v>
       </c>
     </row>
   </sheetData>
@@ -4599,34 +4599,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.42419693612249</v>
+        <v>27.28800214748943</v>
       </c>
       <c r="C2" t="n">
-        <v>42.45659696320987</v>
+        <v>51.48310952152464</v>
       </c>
       <c r="D2" t="n">
-        <v>37.54595925687634</v>
+        <v>53.22256947710962</v>
       </c>
       <c r="E2" t="n">
-        <v>29.64874303149206</v>
+        <v>42.27287665963769</v>
       </c>
       <c r="F2" t="n">
-        <v>40.59234361584051</v>
+        <v>26.88157918645167</v>
       </c>
       <c r="G2" t="n">
-        <v>44.92723023334266</v>
+        <v>47.40484942763079</v>
       </c>
       <c r="H2" t="n">
-        <v>25.76792054400232</v>
+        <v>49.56533828503495</v>
       </c>
       <c r="I2" t="n">
-        <v>27.39230027757187</v>
+        <v>34.58135549387214</v>
       </c>
       <c r="J2" t="n">
-        <v>39.97460540578478</v>
+        <v>63.89920049434404</v>
       </c>
       <c r="K2" t="n">
-        <v>55.35291760239632</v>
+        <v>40.05967975012712</v>
       </c>
     </row>
   </sheetData>
@@ -4705,34 +4705,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.16015232018669</v>
+        <v>31.68359043205722</v>
       </c>
       <c r="C2" t="n">
-        <v>50.95663837107001</v>
+        <v>44.91336028128244</v>
       </c>
       <c r="D2" t="n">
-        <v>32.8092633722386</v>
+        <v>50.88294294279081</v>
       </c>
       <c r="E2" t="n">
-        <v>42.40409330918699</v>
+        <v>42.9728423018073</v>
       </c>
       <c r="F2" t="n">
-        <v>35.17642753417488</v>
+        <v>39.68078780085369</v>
       </c>
       <c r="G2" t="n">
-        <v>34.59879125223635</v>
+        <v>40.63879742810289</v>
       </c>
       <c r="H2" t="n">
-        <v>32.67926378836548</v>
+        <v>40.38899331388776</v>
       </c>
       <c r="I2" t="n">
-        <v>40.64853111283269</v>
+        <v>42.420063288897</v>
       </c>
       <c r="J2" t="n">
-        <v>44.11114538475825</v>
+        <v>44.04790166988528</v>
       </c>
       <c r="K2" t="n">
-        <v>37.9212765611686</v>
+        <v>34.41619236269001</v>
       </c>
     </row>
   </sheetData>
@@ -4811,34 +4811,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>48.50447390907573</v>
+        <v>35.68387822320269</v>
       </c>
       <c r="C2" t="n">
-        <v>44.23874836715631</v>
+        <v>25.96625774765581</v>
       </c>
       <c r="D2" t="n">
-        <v>36.33086754471059</v>
+        <v>28.33928533579439</v>
       </c>
       <c r="E2" t="n">
-        <v>41.31976113344946</v>
+        <v>47.00859108181086</v>
       </c>
       <c r="F2" t="n">
-        <v>39.22114224131958</v>
+        <v>49.83410003807825</v>
       </c>
       <c r="G2" t="n">
-        <v>32.16434380660941</v>
+        <v>43.38206117380087</v>
       </c>
       <c r="H2" t="n">
-        <v>40.37848088687028</v>
+        <v>55.46111090857085</v>
       </c>
       <c r="I2" t="n">
-        <v>39.89549394550157</v>
+        <v>51.47631267550393</v>
       </c>
       <c r="J2" t="n">
-        <v>39.6133065570251</v>
+        <v>46.57549117146398</v>
       </c>
       <c r="K2" t="n">
-        <v>22.78098340404029</v>
+        <v>43.20701640652046</v>
       </c>
     </row>
   </sheetData>
@@ -4917,34 +4917,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.80420792273598</v>
+        <v>35.03321246495522</v>
       </c>
       <c r="C2" t="n">
-        <v>30.11833589195752</v>
+        <v>32.20165074674073</v>
       </c>
       <c r="D2" t="n">
-        <v>30.52563913396468</v>
+        <v>53.74631757177938</v>
       </c>
       <c r="E2" t="n">
-        <v>48.49561256897362</v>
+        <v>37.28641506692831</v>
       </c>
       <c r="F2" t="n">
-        <v>33.99731594126299</v>
+        <v>40.75473271671171</v>
       </c>
       <c r="G2" t="n">
-        <v>36.72600690596486</v>
+        <v>47.40522566325099</v>
       </c>
       <c r="H2" t="n">
-        <v>34.28004381138921</v>
+        <v>34.68131123265211</v>
       </c>
       <c r="I2" t="n">
-        <v>34.82766694298756</v>
+        <v>42.87702483190222</v>
       </c>
       <c r="J2" t="n">
-        <v>33.89759362613842</v>
+        <v>41.02405337696719</v>
       </c>
       <c r="K2" t="n">
-        <v>48.16756810234563</v>
+        <v>40.41351900467238</v>
       </c>
     </row>
   </sheetData>
@@ -5023,34 +5023,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.04967276738738</v>
+        <v>34.3126767978379</v>
       </c>
       <c r="C2" t="n">
-        <v>45.757297292765</v>
+        <v>45.65065743069254</v>
       </c>
       <c r="D2" t="n">
-        <v>43.20859843776387</v>
+        <v>45.70572757949197</v>
       </c>
       <c r="E2" t="n">
-        <v>35.14161774658391</v>
+        <v>38.42347091411131</v>
       </c>
       <c r="F2" t="n">
-        <v>46.60945243197832</v>
+        <v>39.94541996994084</v>
       </c>
       <c r="G2" t="n">
-        <v>31.82285116402382</v>
+        <v>34.25515271285986</v>
       </c>
       <c r="H2" t="n">
-        <v>25.032981349354</v>
+        <v>35.91518771620123</v>
       </c>
       <c r="I2" t="n">
-        <v>36.17304102651701</v>
+        <v>50.98595089032501</v>
       </c>
       <c r="J2" t="n">
-        <v>37.58837929259933</v>
+        <v>33.3108498041138</v>
       </c>
       <c r="K2" t="n">
-        <v>60.40612383113821</v>
+        <v>33.03169793660899</v>
       </c>
     </row>
   </sheetData>
@@ -5129,34 +5129,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.24834634597138</v>
+        <v>42.53410800097075</v>
       </c>
       <c r="C2" t="n">
-        <v>33.59817718151543</v>
+        <v>22.49795350537205</v>
       </c>
       <c r="D2" t="n">
-        <v>35.00150551607461</v>
+        <v>43.99018558737787</v>
       </c>
       <c r="E2" t="n">
-        <v>37.13430328506498</v>
+        <v>36.51866957154274</v>
       </c>
       <c r="F2" t="n">
-        <v>45.8399861400901</v>
+        <v>48.46139861640118</v>
       </c>
       <c r="G2" t="n">
-        <v>9.455462769718602</v>
+        <v>19.24425826431786</v>
       </c>
       <c r="H2" t="n">
-        <v>41.7503763853278</v>
+        <v>65.30604387711152</v>
       </c>
       <c r="I2" t="n">
-        <v>40.67212054821784</v>
+        <v>37.90496065040449</v>
       </c>
       <c r="J2" t="n">
-        <v>32.74335164772067</v>
+        <v>42.34555921657438</v>
       </c>
       <c r="K2" t="n">
-        <v>54.86170484812301</v>
+        <v>37.62308082451639</v>
       </c>
     </row>
   </sheetData>
@@ -5235,34 +5235,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.25026543331704</v>
+        <v>38.83914691991873</v>
       </c>
       <c r="C2" t="n">
-        <v>63.03566610114866</v>
+        <v>60.04418187718925</v>
       </c>
       <c r="D2" t="n">
-        <v>32.74020417430989</v>
+        <v>44.55139384187495</v>
       </c>
       <c r="E2" t="n">
-        <v>34.69661164817005</v>
+        <v>41.7249765699119</v>
       </c>
       <c r="F2" t="n">
-        <v>37.09881233959465</v>
+        <v>42.53514496745294</v>
       </c>
       <c r="G2" t="n">
-        <v>41.20086617656082</v>
+        <v>39.19873999723963</v>
       </c>
       <c r="H2" t="n">
-        <v>52.62061989749547</v>
+        <v>30.75664199729811</v>
       </c>
       <c r="I2" t="n">
-        <v>37.14120182818618</v>
+        <v>47.9976629889812</v>
       </c>
       <c r="J2" t="n">
-        <v>24.53346519327486</v>
+        <v>51.06181876356319</v>
       </c>
       <c r="K2" t="n">
-        <v>46.73201842570371</v>
+        <v>30.99242800385322</v>
       </c>
     </row>
   </sheetData>
@@ -5341,34 +5341,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.9078711849699</v>
+        <v>31.489121585399</v>
       </c>
       <c r="C2" t="n">
-        <v>41.71026822793605</v>
+        <v>31.227845622436</v>
       </c>
       <c r="D2" t="n">
-        <v>41.61086833452377</v>
+        <v>43.88156013332647</v>
       </c>
       <c r="E2" t="n">
-        <v>25.44432266599391</v>
+        <v>38.79687281393677</v>
       </c>
       <c r="F2" t="n">
-        <v>45.58553813976046</v>
+        <v>45.85250494132532</v>
       </c>
       <c r="G2" t="n">
-        <v>38.84027081014484</v>
+        <v>26.96612057401233</v>
       </c>
       <c r="H2" t="n">
-        <v>27.11233408048573</v>
+        <v>48.34567986496468</v>
       </c>
       <c r="I2" t="n">
-        <v>23.12204928100482</v>
+        <v>32.78801070700683</v>
       </c>
       <c r="J2" t="n">
-        <v>41.25001514204079</v>
+        <v>44.47349865374132</v>
       </c>
       <c r="K2" t="n">
-        <v>44.7307397904464</v>
+        <v>41.14036557581816</v>
       </c>
     </row>
   </sheetData>
@@ -5447,34 +5447,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.72246528700334</v>
+        <v>37.51468121483273</v>
       </c>
       <c r="C2" t="n">
-        <v>38.98849828628186</v>
+        <v>48.57889473322364</v>
       </c>
       <c r="D2" t="n">
-        <v>33.41063675226246</v>
+        <v>50.15336380945701</v>
       </c>
       <c r="E2" t="n">
-        <v>39.00880312167529</v>
+        <v>30.13621888177487</v>
       </c>
       <c r="F2" t="n">
-        <v>58.11023522112858</v>
+        <v>52.71636047122972</v>
       </c>
       <c r="G2" t="n">
-        <v>36.48968302602125</v>
+        <v>36.41835254339701</v>
       </c>
       <c r="H2" t="n">
-        <v>38.56030708483708</v>
+        <v>53.41471232694666</v>
       </c>
       <c r="I2" t="n">
-        <v>31.19169133161813</v>
+        <v>63.53819620644124</v>
       </c>
       <c r="J2" t="n">
-        <v>27.64795876094063</v>
+        <v>47.27966154407858</v>
       </c>
       <c r="K2" t="n">
-        <v>61.73845741158745</v>
+        <v>44.99469375958445</v>
       </c>
     </row>
   </sheetData>
@@ -5553,34 +5553,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.68144529513116</v>
+        <v>32.9359592593719</v>
       </c>
       <c r="C2" t="n">
-        <v>45.71933271001648</v>
+        <v>47.84077393325367</v>
       </c>
       <c r="D2" t="n">
-        <v>44.46702204354928</v>
+        <v>43.41924212534758</v>
       </c>
       <c r="E2" t="n">
-        <v>46.33434025883432</v>
+        <v>32.09408582635464</v>
       </c>
       <c r="F2" t="n">
-        <v>39.32018104416913</v>
+        <v>42.78325401212985</v>
       </c>
       <c r="G2" t="n">
-        <v>48.17311367459922</v>
+        <v>26.2199518080208</v>
       </c>
       <c r="H2" t="n">
-        <v>30.0183711194256</v>
+        <v>42.5638307099798</v>
       </c>
       <c r="I2" t="n">
-        <v>33.25658006577984</v>
+        <v>49.70107538136848</v>
       </c>
       <c r="J2" t="n">
-        <v>42.75366628001699</v>
+        <v>35.53235236555624</v>
       </c>
       <c r="K2" t="n">
-        <v>35.227658900892</v>
+        <v>54.20186946946583</v>
       </c>
     </row>
   </sheetData>
@@ -5659,34 +5659,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.78377766196814</v>
+        <v>28.65733015344617</v>
       </c>
       <c r="C2" t="n">
-        <v>40.17307026365601</v>
+        <v>34.03886966383601</v>
       </c>
       <c r="D2" t="n">
-        <v>27.02822311360219</v>
+        <v>30.44876243678883</v>
       </c>
       <c r="E2" t="n">
-        <v>29.22016367348017</v>
+        <v>38.06014870299938</v>
       </c>
       <c r="F2" t="n">
-        <v>52.18802574053457</v>
+        <v>48.14594402950292</v>
       </c>
       <c r="G2" t="n">
-        <v>33.62200333570966</v>
+        <v>44.70937294365372</v>
       </c>
       <c r="H2" t="n">
-        <v>37.37001855457002</v>
+        <v>31.37786538100256</v>
       </c>
       <c r="I2" t="n">
-        <v>23.4169440224249</v>
+        <v>28.39099029197426</v>
       </c>
       <c r="J2" t="n">
-        <v>29.71183458868289</v>
+        <v>25.12129830581712</v>
       </c>
       <c r="K2" t="n">
-        <v>29.73039292903701</v>
+        <v>38.62856750814427</v>
       </c>
     </row>
   </sheetData>
@@ -5765,34 +5765,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.87175508756395</v>
+        <v>43.2101812376976</v>
       </c>
       <c r="C2" t="n">
-        <v>56.07136037487278</v>
+        <v>50.77828383360706</v>
       </c>
       <c r="D2" t="n">
-        <v>56.81510189704743</v>
+        <v>35.42216405079245</v>
       </c>
       <c r="E2" t="n">
-        <v>40.59997272482837</v>
+        <v>37.69513308519301</v>
       </c>
       <c r="F2" t="n">
-        <v>32.1018266516448</v>
+        <v>47.80864405549774</v>
       </c>
       <c r="G2" t="n">
-        <v>20.01048002888002</v>
+        <v>42.88936451190832</v>
       </c>
       <c r="H2" t="n">
-        <v>41.55253913077343</v>
+        <v>47.10729978805899</v>
       </c>
       <c r="I2" t="n">
-        <v>34.21427768667146</v>
+        <v>51.29523048717454</v>
       </c>
       <c r="J2" t="n">
-        <v>33.03901698955432</v>
+        <v>34.58455183476206</v>
       </c>
       <c r="K2" t="n">
-        <v>48.48928867339532</v>
+        <v>33.23219069373488</v>
       </c>
     </row>
   </sheetData>
@@ -5871,34 +5871,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.30573000117766</v>
+        <v>32.51718786633761</v>
       </c>
       <c r="C2" t="n">
-        <v>34.92952790996168</v>
+        <v>39.76109844230138</v>
       </c>
       <c r="D2" t="n">
-        <v>39.00456998058124</v>
+        <v>24.074744362572</v>
       </c>
       <c r="E2" t="n">
-        <v>37.85277154692151</v>
+        <v>43.14284200533165</v>
       </c>
       <c r="F2" t="n">
-        <v>32.73838388945512</v>
+        <v>35.37428694994004</v>
       </c>
       <c r="G2" t="n">
-        <v>44.39355236240984</v>
+        <v>54.80513760838157</v>
       </c>
       <c r="H2" t="n">
-        <v>36.88233207302358</v>
+        <v>31.67893736999142</v>
       </c>
       <c r="I2" t="n">
-        <v>44.0640829521198</v>
+        <v>52.43024999315551</v>
       </c>
       <c r="J2" t="n">
-        <v>39.68036212381877</v>
+        <v>62.72454495868836</v>
       </c>
       <c r="K2" t="n">
-        <v>89.12104201950328</v>
+        <v>41.31268213135092</v>
       </c>
     </row>
   </sheetData>
@@ -5977,34 +5977,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.57175301798864</v>
+        <v>42.03942122735823</v>
       </c>
       <c r="C2" t="n">
-        <v>48.55273930039225</v>
+        <v>47.35576548908964</v>
       </c>
       <c r="D2" t="n">
-        <v>39.10242495003488</v>
+        <v>65.73735398722336</v>
       </c>
       <c r="E2" t="n">
-        <v>40.5127509568085</v>
+        <v>44.73420434659166</v>
       </c>
       <c r="F2" t="n">
-        <v>52.82959208425439</v>
+        <v>34.51320305539755</v>
       </c>
       <c r="G2" t="n">
-        <v>33.75309161401135</v>
+        <v>47.48332709462384</v>
       </c>
       <c r="H2" t="n">
-        <v>34.34707663038759</v>
+        <v>46.1985001786616</v>
       </c>
       <c r="I2" t="n">
-        <v>31.9545989560047</v>
+        <v>65.27079553578675</v>
       </c>
       <c r="J2" t="n">
-        <v>39.44821996608312</v>
+        <v>37.25621835453106</v>
       </c>
       <c r="K2" t="n">
-        <v>58.33806538779439</v>
+        <v>41.34559564941182</v>
       </c>
     </row>
   </sheetData>
@@ -6083,34 +6083,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.22165984468459</v>
+        <v>40.59528325039689</v>
       </c>
       <c r="C2" t="n">
-        <v>2429.916012059507</v>
+        <v>48.40930040681258</v>
       </c>
       <c r="D2" t="n">
-        <v>42.62779004412779</v>
+        <v>27.1979982198975</v>
       </c>
       <c r="E2" t="n">
-        <v>14.70757956003104</v>
+        <v>47.203640827596</v>
       </c>
       <c r="F2" t="n">
-        <v>38.15287121514071</v>
+        <v>37.66567375093705</v>
       </c>
       <c r="G2" t="n">
-        <v>66.10187656262887</v>
+        <v>38.38785235205749</v>
       </c>
       <c r="H2" t="n">
-        <v>46.05612380696235</v>
+        <v>38.13737838448135</v>
       </c>
       <c r="I2" t="n">
-        <v>18.86020137438308</v>
+        <v>53.53425998550551</v>
       </c>
       <c r="J2" t="n">
-        <v>26.4845115437911</v>
+        <v>50.52282412835543</v>
       </c>
       <c r="K2" t="n">
-        <v>19.34499560415906</v>
+        <v>42.51227909982296</v>
       </c>
     </row>
   </sheetData>
@@ -6189,34 +6189,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.09814248043576</v>
+        <v>44.81612815430926</v>
       </c>
       <c r="C2" t="n">
-        <v>26.78765786554446</v>
+        <v>45.53995795934265</v>
       </c>
       <c r="D2" t="n">
-        <v>29.70263473003671</v>
+        <v>50.98322923123533</v>
       </c>
       <c r="E2" t="n">
-        <v>28.23633386911946</v>
+        <v>47.79925561459756</v>
       </c>
       <c r="F2" t="n">
-        <v>44.18762602375079</v>
+        <v>32.71286840546576</v>
       </c>
       <c r="G2" t="n">
-        <v>38.90660694845437</v>
+        <v>46.59940836008778</v>
       </c>
       <c r="H2" t="n">
-        <v>30.56504081660719</v>
+        <v>40.03082734566733</v>
       </c>
       <c r="I2" t="n">
-        <v>44.46812898476112</v>
+        <v>36.51724282893634</v>
       </c>
       <c r="J2" t="n">
-        <v>43.46084586703587</v>
+        <v>33.10751395741786</v>
       </c>
       <c r="K2" t="n">
-        <v>45.45696365764167</v>
+        <v>31.0217782398925</v>
       </c>
     </row>
   </sheetData>
@@ -6295,34 +6295,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.61135353714696</v>
+        <v>27.28308114145814</v>
       </c>
       <c r="C2" t="n">
-        <v>3634.675190048376</v>
+        <v>40.93943263661059</v>
       </c>
       <c r="D2" t="n">
-        <v>25.72116520302363</v>
+        <v>43.77930978465964</v>
       </c>
       <c r="E2" t="n">
-        <v>27.65761647298463</v>
+        <v>40.54812160039298</v>
       </c>
       <c r="F2" t="n">
-        <v>29.58358471887837</v>
+        <v>39.81274304840852</v>
       </c>
       <c r="G2" t="n">
-        <v>39.63492891159284</v>
+        <v>26.55268217736936</v>
       </c>
       <c r="H2" t="n">
-        <v>36.72335618710176</v>
+        <v>34.68662680148107</v>
       </c>
       <c r="I2" t="n">
-        <v>22.23292834452345</v>
+        <v>63.48202120488993</v>
       </c>
       <c r="J2" t="n">
-        <v>30.16182852893842</v>
+        <v>35.29484848465297</v>
       </c>
       <c r="K2" t="n">
-        <v>37.84898172419268</v>
+        <v>31.41696003828418</v>
       </c>
     </row>
   </sheetData>
@@ -6401,34 +6401,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.05248016749752</v>
+        <v>39.61845709743475</v>
       </c>
       <c r="C2" t="n">
-        <v>48.94603264466204</v>
+        <v>48.49349648514534</v>
       </c>
       <c r="D2" t="n">
-        <v>37.01860875968055</v>
+        <v>41.21777245125734</v>
       </c>
       <c r="E2" t="n">
-        <v>34.65742962777973</v>
+        <v>37.29391898701576</v>
       </c>
       <c r="F2" t="n">
-        <v>41.4361838650705</v>
+        <v>33.37920252081475</v>
       </c>
       <c r="G2" t="n">
-        <v>40.97904162951409</v>
+        <v>32.09738018826823</v>
       </c>
       <c r="H2" t="n">
-        <v>38.53537221492472</v>
+        <v>30.57689988034739</v>
       </c>
       <c r="I2" t="n">
-        <v>21.88881763968845</v>
+        <v>50.66520838141836</v>
       </c>
       <c r="J2" t="n">
-        <v>27.26632852606123</v>
+        <v>41.37538647869282</v>
       </c>
       <c r="K2" t="n">
-        <v>44.17874954079876</v>
+        <v>39.2145966173043</v>
       </c>
     </row>
   </sheetData>
@@ -6507,34 +6507,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.95615084940241</v>
+        <v>50.14354915466971</v>
       </c>
       <c r="C2" t="n">
-        <v>46.3978968287979</v>
+        <v>38.93147215792845</v>
       </c>
       <c r="D2" t="n">
-        <v>51.50136094761785</v>
+        <v>33.45010240209781</v>
       </c>
       <c r="E2" t="n">
-        <v>35.40688528478103</v>
+        <v>39.24880846756693</v>
       </c>
       <c r="F2" t="n">
-        <v>37.00648275867115</v>
+        <v>50.53015102110722</v>
       </c>
       <c r="G2" t="n">
-        <v>42.96274283777161</v>
+        <v>35.89942702252949</v>
       </c>
       <c r="H2" t="n">
-        <v>26.70294057477687</v>
+        <v>47.97622252745931</v>
       </c>
       <c r="I2" t="n">
-        <v>36.77782089723362</v>
+        <v>45.21975271032595</v>
       </c>
       <c r="J2" t="n">
-        <v>40.0148741695997</v>
+        <v>40.79504974352132</v>
       </c>
       <c r="K2" t="n">
-        <v>45.7506118717016</v>
+        <v>33.29948760736584</v>
       </c>
     </row>
   </sheetData>
@@ -6613,34 +6613,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.18791466994691</v>
+        <v>33.49418310731877</v>
       </c>
       <c r="C2" t="n">
-        <v>37.60611326391416</v>
+        <v>32.55845710370332</v>
       </c>
       <c r="D2" t="n">
-        <v>26.05875364692691</v>
+        <v>48.14935757139429</v>
       </c>
       <c r="E2" t="n">
-        <v>41.62088228148081</v>
+        <v>39.32434204434737</v>
       </c>
       <c r="F2" t="n">
-        <v>44.60061987337725</v>
+        <v>45.45771017857535</v>
       </c>
       <c r="G2" t="n">
-        <v>33.12340174003651</v>
+        <v>33.4964592027965</v>
       </c>
       <c r="H2" t="n">
-        <v>31.06440594852761</v>
+        <v>42.22565893913583</v>
       </c>
       <c r="I2" t="n">
-        <v>29.1206766656092</v>
+        <v>40.42325613559604</v>
       </c>
       <c r="J2" t="n">
-        <v>43.89292254100869</v>
+        <v>56.54273250903886</v>
       </c>
       <c r="K2" t="n">
-        <v>53.80193448394409</v>
+        <v>35.73607925615934</v>
       </c>
     </row>
   </sheetData>
@@ -6719,34 +6719,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>73.63055013418629</v>
+        <v>48.00478296091822</v>
       </c>
       <c r="C2" t="n">
-        <v>62.3704215618521</v>
+        <v>65.34586470499404</v>
       </c>
       <c r="D2" t="n">
-        <v>38.79145340311308</v>
+        <v>47.82003471217764</v>
       </c>
       <c r="E2" t="n">
-        <v>30.15765653413235</v>
+        <v>46.2981036248386</v>
       </c>
       <c r="F2" t="n">
-        <v>27.44185915100622</v>
+        <v>34.7875144501886</v>
       </c>
       <c r="G2" t="n">
-        <v>33.74715373860494</v>
+        <v>37.57055789181707</v>
       </c>
       <c r="H2" t="n">
-        <v>34.18788559969007</v>
+        <v>34.81839839323781</v>
       </c>
       <c r="I2" t="n">
-        <v>31.59252312796839</v>
+        <v>39.59743886522589</v>
       </c>
       <c r="J2" t="n">
-        <v>39.52691879272005</v>
+        <v>30.0174064349475</v>
       </c>
       <c r="K2" t="n">
-        <v>47.00225025338403</v>
+        <v>60.02898067877656</v>
       </c>
     </row>
   </sheetData>
@@ -6825,34 +6825,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.03193010841468</v>
+        <v>34.84324675634711</v>
       </c>
       <c r="C2" t="n">
-        <v>39.13809032367077</v>
+        <v>59.4085172257811</v>
       </c>
       <c r="D2" t="n">
-        <v>49.75773701335952</v>
+        <v>57.43668234599112</v>
       </c>
       <c r="E2" t="n">
-        <v>52.80681447745168</v>
+        <v>38.42296250897238</v>
       </c>
       <c r="F2" t="n">
-        <v>23.83857530442491</v>
+        <v>50.37120428579951</v>
       </c>
       <c r="G2" t="n">
-        <v>44.84840062647617</v>
+        <v>31.31235942753319</v>
       </c>
       <c r="H2" t="n">
-        <v>43.73690663363389</v>
+        <v>44.63848103258707</v>
       </c>
       <c r="I2" t="n">
-        <v>34.60729911337824</v>
+        <v>34.56874291906593</v>
       </c>
       <c r="J2" t="n">
-        <v>56.80537725358707</v>
+        <v>49.00332331128518</v>
       </c>
       <c r="K2" t="n">
-        <v>31.01929251688111</v>
+        <v>33.92501420647769</v>
       </c>
     </row>
   </sheetData>
@@ -6931,34 +6931,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.61560276038439</v>
+        <v>47.17431787646705</v>
       </c>
       <c r="C2" t="n">
-        <v>72.16008241494639</v>
+        <v>41.48641571086637</v>
       </c>
       <c r="D2" t="n">
-        <v>28.33583309298219</v>
+        <v>47.89787860280087</v>
       </c>
       <c r="E2" t="n">
-        <v>62.14566091758934</v>
+        <v>41.10824012598169</v>
       </c>
       <c r="F2" t="n">
-        <v>38.89877988424288</v>
+        <v>44.33838287515213</v>
       </c>
       <c r="G2" t="n">
-        <v>27.489949587521</v>
+        <v>34.92429327034327</v>
       </c>
       <c r="H2" t="n">
-        <v>42.30366929354926</v>
+        <v>36.121792261024</v>
       </c>
       <c r="I2" t="n">
-        <v>36.06632453473647</v>
+        <v>35.99248900232535</v>
       </c>
       <c r="J2" t="n">
-        <v>33.16079457921396</v>
+        <v>49.82521285650814</v>
       </c>
       <c r="K2" t="n">
-        <v>37.10890089258897</v>
+        <v>38.54649070294478</v>
       </c>
     </row>
   </sheetData>
@@ -7037,34 +7037,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.90206582224451</v>
+        <v>21.12289406288351</v>
       </c>
       <c r="C2" t="n">
-        <v>43.65446391252382</v>
+        <v>33.84923029177595</v>
       </c>
       <c r="D2" t="n">
-        <v>30.30264342206442</v>
+        <v>37.64267008961057</v>
       </c>
       <c r="E2" t="n">
-        <v>50.14843019612344</v>
+        <v>45.82547890143487</v>
       </c>
       <c r="F2" t="n">
-        <v>41.39613934990783</v>
+        <v>46.65773788852032</v>
       </c>
       <c r="G2" t="n">
-        <v>59.7128874125255</v>
+        <v>53.24694514879903</v>
       </c>
       <c r="H2" t="n">
-        <v>19.31811436432935</v>
+        <v>42.88456111689218</v>
       </c>
       <c r="I2" t="n">
-        <v>47.20526340246118</v>
+        <v>53.28737799167514</v>
       </c>
       <c r="J2" t="n">
-        <v>40.51128309991793</v>
+        <v>59.49334787128181</v>
       </c>
       <c r="K2" t="n">
-        <v>18.5669064735638</v>
+        <v>44.554441528166</v>
       </c>
     </row>
   </sheetData>
@@ -7143,34 +7143,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.14950759106102</v>
+        <v>38.45942031113784</v>
       </c>
       <c r="C2" t="n">
-        <v>41.6826024999085</v>
+        <v>41.97231062189991</v>
       </c>
       <c r="D2" t="n">
-        <v>26.61817400992749</v>
+        <v>53.51741779480888</v>
       </c>
       <c r="E2" t="n">
-        <v>35.38539578082626</v>
+        <v>37.75473660495433</v>
       </c>
       <c r="F2" t="n">
-        <v>35.38289957423083</v>
+        <v>33.00413841650351</v>
       </c>
       <c r="G2" t="n">
-        <v>39.25523703132589</v>
+        <v>44.32039244729049</v>
       </c>
       <c r="H2" t="n">
-        <v>34.04628730589592</v>
+        <v>45.89695112352996</v>
       </c>
       <c r="I2" t="n">
-        <v>32.39679553971045</v>
+        <v>40.52851343555395</v>
       </c>
       <c r="J2" t="n">
-        <v>43.85196011855736</v>
+        <v>41.97239617031457</v>
       </c>
       <c r="K2" t="n">
-        <v>66.51277961275457</v>
+        <v>28.24160210191471</v>
       </c>
     </row>
   </sheetData>
@@ -7249,34 +7249,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.13250844532869</v>
+        <v>37.61627388602309</v>
       </c>
       <c r="C2" t="n">
-        <v>52.73051133774322</v>
+        <v>64.59816120570552</v>
       </c>
       <c r="D2" t="n">
-        <v>30.56829262503403</v>
+        <v>47.06719180405955</v>
       </c>
       <c r="E2" t="n">
-        <v>35.43644767308501</v>
+        <v>38.88297686675578</v>
       </c>
       <c r="F2" t="n">
-        <v>56.44843037121665</v>
+        <v>49.08527969146832</v>
       </c>
       <c r="G2" t="n">
-        <v>24.62372483993872</v>
+        <v>30.89171707880984</v>
       </c>
       <c r="H2" t="n">
-        <v>26.05064709421855</v>
+        <v>23.03966727438988</v>
       </c>
       <c r="I2" t="n">
-        <v>38.93538905215069</v>
+        <v>36.4636717876427</v>
       </c>
       <c r="J2" t="n">
-        <v>19.74808322354788</v>
+        <v>39.51697891477293</v>
       </c>
       <c r="K2" t="n">
-        <v>46.8223314784545</v>
+        <v>34.54854135162073</v>
       </c>
     </row>
   </sheetData>
@@ -7355,34 +7355,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.88092682332063</v>
+        <v>41.06191921936216</v>
       </c>
       <c r="C2" t="n">
-        <v>39.66338618044953</v>
+        <v>59.18300945555581</v>
       </c>
       <c r="D2" t="n">
-        <v>39.93927757376506</v>
+        <v>52.72427041253693</v>
       </c>
       <c r="E2" t="n">
-        <v>49.06632683659068</v>
+        <v>40.8193537332529</v>
       </c>
       <c r="F2" t="n">
-        <v>42.92998968282204</v>
+        <v>37.78085397540097</v>
       </c>
       <c r="G2" t="n">
-        <v>20.06401386266562</v>
+        <v>42.50649156325423</v>
       </c>
       <c r="H2" t="n">
-        <v>27.46693793341998</v>
+        <v>58.9202196802611</v>
       </c>
       <c r="I2" t="n">
-        <v>33.09284064254111</v>
+        <v>55.09729378586854</v>
       </c>
       <c r="J2" t="n">
-        <v>45.2647509272354</v>
+        <v>35.56726940117049</v>
       </c>
       <c r="K2" t="n">
-        <v>50.03760049531444</v>
+        <v>26.82688138941845</v>
       </c>
     </row>
   </sheetData>
@@ -7461,34 +7461,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.17468519280013</v>
+        <v>41.53647279504922</v>
       </c>
       <c r="C2" t="n">
-        <v>45.15187501039733</v>
+        <v>37.24665219539538</v>
       </c>
       <c r="D2" t="n">
-        <v>40.79148705563514</v>
+        <v>46.87385300457473</v>
       </c>
       <c r="E2" t="n">
-        <v>36.72188692266035</v>
+        <v>41.09944447393977</v>
       </c>
       <c r="F2" t="n">
-        <v>40.15705796820968</v>
+        <v>51.86925984955408</v>
       </c>
       <c r="G2" t="n">
-        <v>47.4818395899399</v>
+        <v>40.31703255153604</v>
       </c>
       <c r="H2" t="n">
-        <v>43.79991007041944</v>
+        <v>40.76504530777737</v>
       </c>
       <c r="I2" t="n">
-        <v>43.78527482405195</v>
+        <v>39.31277192292765</v>
       </c>
       <c r="J2" t="n">
-        <v>38.02434202157254</v>
+        <v>43.20800110935666</v>
       </c>
       <c r="K2" t="n">
-        <v>33.23214869427834</v>
+        <v>38.88896753624498</v>
       </c>
     </row>
   </sheetData>
@@ -7567,34 +7567,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.40771402000636</v>
+        <v>35.94013103877104</v>
       </c>
       <c r="C2" t="n">
-        <v>47.92718614343701</v>
+        <v>49.31722988917388</v>
       </c>
       <c r="D2" t="n">
-        <v>33.79601547368134</v>
+        <v>46.1555067663084</v>
       </c>
       <c r="E2" t="n">
-        <v>30.80623537969419</v>
+        <v>38.27950226855781</v>
       </c>
       <c r="F2" t="n">
-        <v>38.9932753243644</v>
+        <v>47.65517238289205</v>
       </c>
       <c r="G2" t="n">
-        <v>34.82387744394902</v>
+        <v>36.83149041021242</v>
       </c>
       <c r="H2" t="n">
-        <v>40.35051944439309</v>
+        <v>38.70003254060835</v>
       </c>
       <c r="I2" t="n">
-        <v>43.72061321373249</v>
+        <v>41.78374638653909</v>
       </c>
       <c r="J2" t="n">
-        <v>52.9075885328788</v>
+        <v>56.16325346503923</v>
       </c>
       <c r="K2" t="n">
-        <v>59.25119926526738</v>
+        <v>43.94164963314444</v>
       </c>
     </row>
   </sheetData>
@@ -7673,34 +7673,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.69382254266826</v>
+        <v>39.66534741937669</v>
       </c>
       <c r="C2" t="n">
-        <v>35.37417558405907</v>
+        <v>41.38816424545554</v>
       </c>
       <c r="D2" t="n">
-        <v>37.07276062280346</v>
+        <v>47.23085120379366</v>
       </c>
       <c r="E2" t="n">
-        <v>35.61567247016454</v>
+        <v>47.7877329644783</v>
       </c>
       <c r="F2" t="n">
-        <v>42.98822707909977</v>
+        <v>43.01728760033144</v>
       </c>
       <c r="G2" t="n">
-        <v>26.48784846640459</v>
+        <v>41.90514109112335</v>
       </c>
       <c r="H2" t="n">
-        <v>28.25246551462623</v>
+        <v>29.43718012248685</v>
       </c>
       <c r="I2" t="n">
-        <v>41.45490673069472</v>
+        <v>41.79686659672939</v>
       </c>
       <c r="J2" t="n">
-        <v>44.63586047134593</v>
+        <v>52.86494680360538</v>
       </c>
       <c r="K2" t="n">
-        <v>50.59479389468959</v>
+        <v>42.16217156843359</v>
       </c>
     </row>
   </sheetData>
@@ -7779,34 +7779,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.11868236430497</v>
+        <v>29.68847023268952</v>
       </c>
       <c r="C2" t="n">
-        <v>50.58655185573763</v>
+        <v>47.84176353411556</v>
       </c>
       <c r="D2" t="n">
-        <v>36.57569859411241</v>
+        <v>40.48122718108788</v>
       </c>
       <c r="E2" t="n">
-        <v>36.36091835060758</v>
+        <v>35.0556723233606</v>
       </c>
       <c r="F2" t="n">
-        <v>36.98835011458146</v>
+        <v>47.01139947852535</v>
       </c>
       <c r="G2" t="n">
-        <v>39.22468765379445</v>
+        <v>33.72838050503471</v>
       </c>
       <c r="H2" t="n">
-        <v>36.20308570739657</v>
+        <v>43.05845496067672</v>
       </c>
       <c r="I2" t="n">
-        <v>40.94401876410992</v>
+        <v>34.78156553225772</v>
       </c>
       <c r="J2" t="n">
-        <v>31.85647553654585</v>
+        <v>60.06130043475368</v>
       </c>
       <c r="K2" t="n">
-        <v>48.57932277977537</v>
+        <v>34.48906088001018</v>
       </c>
     </row>
   </sheetData>
@@ -7885,34 +7885,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.14935969100813</v>
+        <v>37.6167843617341</v>
       </c>
       <c r="C2" t="n">
-        <v>30.64983626749489</v>
+        <v>53.69131274387128</v>
       </c>
       <c r="D2" t="n">
-        <v>35.33755809704027</v>
+        <v>29.41224163101645</v>
       </c>
       <c r="E2" t="n">
-        <v>36.61517474934907</v>
+        <v>42.06411901030477</v>
       </c>
       <c r="F2" t="n">
-        <v>34.72367234131658</v>
+        <v>45.84729617327413</v>
       </c>
       <c r="G2" t="n">
-        <v>52.46681903908448</v>
+        <v>29.77342422567444</v>
       </c>
       <c r="H2" t="n">
-        <v>38.79503957647206</v>
+        <v>44.37750323504471</v>
       </c>
       <c r="I2" t="n">
-        <v>36.46622719007132</v>
+        <v>59.01601484940686</v>
       </c>
       <c r="J2" t="n">
-        <v>41.58746954289955</v>
+        <v>31.32635797439169</v>
       </c>
       <c r="K2" t="n">
-        <v>53.07484144179056</v>
+        <v>34.46588474155633</v>
       </c>
     </row>
   </sheetData>
@@ -7991,34 +7991,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.79739621794976</v>
+        <v>37.38734008585485</v>
       </c>
       <c r="C2" t="n">
-        <v>35.69074906650042</v>
+        <v>35.47054095554675</v>
       </c>
       <c r="D2" t="n">
-        <v>28.83117395979327</v>
+        <v>42.02273297063513</v>
       </c>
       <c r="E2" t="n">
-        <v>39.34294717083318</v>
+        <v>30.01244259520633</v>
       </c>
       <c r="F2" t="n">
-        <v>25.65949791782195</v>
+        <v>47.1351492102168</v>
       </c>
       <c r="G2" t="n">
-        <v>30.40314122624708</v>
+        <v>51.48987411017033</v>
       </c>
       <c r="H2" t="n">
-        <v>36.48900014261973</v>
+        <v>42.1666240745515</v>
       </c>
       <c r="I2" t="n">
-        <v>38.11141772662826</v>
+        <v>21.18904339642429</v>
       </c>
       <c r="J2" t="n">
-        <v>49.20553802941994</v>
+        <v>40.29591244306639</v>
       </c>
       <c r="K2" t="n">
-        <v>49.09639061347054</v>
+        <v>31.08761636103528</v>
       </c>
     </row>
   </sheetData>
@@ -8097,34 +8097,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.3775916785418</v>
+        <v>35.2686920464689</v>
       </c>
       <c r="C2" t="n">
-        <v>42.91984950334248</v>
+        <v>34.10769630547774</v>
       </c>
       <c r="D2" t="n">
-        <v>43.05075542971628</v>
+        <v>40.53967497598212</v>
       </c>
       <c r="E2" t="n">
-        <v>34.16517721040257</v>
+        <v>50.29009105457342</v>
       </c>
       <c r="F2" t="n">
-        <v>38.53481177498161</v>
+        <v>38.53650142495271</v>
       </c>
       <c r="G2" t="n">
-        <v>36.66647027124265</v>
+        <v>40.36702169504328</v>
       </c>
       <c r="H2" t="n">
-        <v>44.35986972564323</v>
+        <v>38.20548528105822</v>
       </c>
       <c r="I2" t="n">
-        <v>34.06198165616554</v>
+        <v>42.46073992123331</v>
       </c>
       <c r="J2" t="n">
-        <v>43.29344814446613</v>
+        <v>51.7196482380816</v>
       </c>
       <c r="K2" t="n">
-        <v>35.01739335682816</v>
+        <v>37.08311022482889</v>
       </c>
     </row>
   </sheetData>
@@ -8203,34 +8203,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.26973645512511</v>
+        <v>36.01430567622045</v>
       </c>
       <c r="C2" t="n">
-        <v>37.87209463487157</v>
+        <v>41.59791831093496</v>
       </c>
       <c r="D2" t="n">
-        <v>29.50718271683436</v>
+        <v>57.91312828093512</v>
       </c>
       <c r="E2" t="n">
-        <v>31.24480394004911</v>
+        <v>33.81630990482692</v>
       </c>
       <c r="F2" t="n">
-        <v>36.04162782568438</v>
+        <v>63.69325654255525</v>
       </c>
       <c r="G2" t="n">
-        <v>51.99482076952752</v>
+        <v>34.78225736660765</v>
       </c>
       <c r="H2" t="n">
-        <v>43.32811294392708</v>
+        <v>41.94930016402863</v>
       </c>
       <c r="I2" t="n">
-        <v>38.0853322011738</v>
+        <v>41.4754635006114</v>
       </c>
       <c r="J2" t="n">
-        <v>46.12354190809997</v>
+        <v>45.48168752187949</v>
       </c>
       <c r="K2" t="n">
-        <v>56.42875319244819</v>
+        <v>39.91891670422844</v>
       </c>
     </row>
   </sheetData>
@@ -8309,34 +8309,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.1722439781569</v>
+        <v>31.60616052834721</v>
       </c>
       <c r="C2" t="n">
-        <v>40.65351883460182</v>
+        <v>43.11194777238855</v>
       </c>
       <c r="D2" t="n">
-        <v>43.09379642040141</v>
+        <v>28.48116057039922</v>
       </c>
       <c r="E2" t="n">
-        <v>46.35974461299379</v>
+        <v>52.99834019235604</v>
       </c>
       <c r="F2" t="n">
-        <v>41.57683779182938</v>
+        <v>67.3791380992716</v>
       </c>
       <c r="G2" t="n">
-        <v>36.88651207464704</v>
+        <v>33.80576951528721</v>
       </c>
       <c r="H2" t="n">
-        <v>42.57238222077748</v>
+        <v>42.8333219693306</v>
       </c>
       <c r="I2" t="n">
-        <v>38.65524212586381</v>
+        <v>43.75882323126147</v>
       </c>
       <c r="J2" t="n">
-        <v>34.70967593793684</v>
+        <v>48.21566510897154</v>
       </c>
       <c r="K2" t="n">
-        <v>46.36013979758452</v>
+        <v>40.9661194414704</v>
       </c>
     </row>
   </sheetData>
@@ -8415,34 +8415,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.91877620687619</v>
+        <v>24.37047482966895</v>
       </c>
       <c r="C2" t="n">
-        <v>23.91640955098776</v>
+        <v>37.60361733671694</v>
       </c>
       <c r="D2" t="n">
-        <v>23.85387224570838</v>
+        <v>43.45258007748435</v>
       </c>
       <c r="E2" t="n">
-        <v>33.07322335386174</v>
+        <v>34.59385061297051</v>
       </c>
       <c r="F2" t="n">
-        <v>50.48411068468197</v>
+        <v>35.33746169257876</v>
       </c>
       <c r="G2" t="n">
-        <v>36.6654711853265</v>
+        <v>47.03247325123534</v>
       </c>
       <c r="H2" t="n">
-        <v>30.81748021775385</v>
+        <v>37.65565114910267</v>
       </c>
       <c r="I2" t="n">
-        <v>44.97686995289327</v>
+        <v>49.51865617134571</v>
       </c>
       <c r="J2" t="n">
-        <v>38.19099894607582</v>
+        <v>35.21338890088337</v>
       </c>
       <c r="K2" t="n">
-        <v>45.12438844374547</v>
+        <v>36.92504567253557</v>
       </c>
     </row>
   </sheetData>
@@ -8521,34 +8521,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.16495542243985</v>
+        <v>39.04470300311805</v>
       </c>
       <c r="C2" t="n">
-        <v>48.38604664050459</v>
+        <v>40.49241901690979</v>
       </c>
       <c r="D2" t="n">
-        <v>39.10494823357373</v>
+        <v>45.80458709564334</v>
       </c>
       <c r="E2" t="n">
-        <v>70.54836428484315</v>
+        <v>32.00886725175104</v>
       </c>
       <c r="F2" t="n">
-        <v>26.15523153052369</v>
+        <v>37.9495428314989</v>
       </c>
       <c r="G2" t="n">
-        <v>47.24466054262875</v>
+        <v>41.95143745453814</v>
       </c>
       <c r="H2" t="n">
-        <v>27.46951124045997</v>
+        <v>46.78915513316423</v>
       </c>
       <c r="I2" t="n">
-        <v>47.38502287204546</v>
+        <v>44.02252355623143</v>
       </c>
       <c r="J2" t="n">
-        <v>31.05445404357775</v>
+        <v>51.58143109264447</v>
       </c>
       <c r="K2" t="n">
-        <v>30.03733798124982</v>
+        <v>40.85623510420945</v>
       </c>
     </row>
   </sheetData>
@@ -8627,34 +8627,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.07754260045703</v>
+        <v>45.05570595333808</v>
       </c>
       <c r="C2" t="n">
-        <v>49.45268676177212</v>
+        <v>44.9895618464133</v>
       </c>
       <c r="D2" t="n">
-        <v>40.10939292016563</v>
+        <v>39.26847902130454</v>
       </c>
       <c r="E2" t="n">
-        <v>34.38784822103841</v>
+        <v>48.34643887170873</v>
       </c>
       <c r="F2" t="n">
-        <v>47.06214866076763</v>
+        <v>44.58988211373449</v>
       </c>
       <c r="G2" t="n">
-        <v>30.32066356394064</v>
+        <v>45.64100833224852</v>
       </c>
       <c r="H2" t="n">
-        <v>57.4093158223955</v>
+        <v>40.4277741467404</v>
       </c>
       <c r="I2" t="n">
-        <v>46.00376310618221</v>
+        <v>37.38423260522793</v>
       </c>
       <c r="J2" t="n">
-        <v>39.03995237762658</v>
+        <v>49.58277149582632</v>
       </c>
       <c r="K2" t="n">
-        <v>33.81045805486935</v>
+        <v>36.84082778414831</v>
       </c>
     </row>
   </sheetData>
@@ -8733,34 +8733,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.1550252394148</v>
+        <v>40.0888259313184</v>
       </c>
       <c r="C2" t="n">
-        <v>39.5933356284367</v>
+        <v>39.87499344151087</v>
       </c>
       <c r="D2" t="n">
-        <v>32.90488867470412</v>
+        <v>49.23786931779281</v>
       </c>
       <c r="E2" t="n">
-        <v>34.24327401150853</v>
+        <v>39.83936702605317</v>
       </c>
       <c r="F2" t="n">
-        <v>49.49666412152525</v>
+        <v>42.26191514760055</v>
       </c>
       <c r="G2" t="n">
-        <v>54.20417962814658</v>
+        <v>53.98774165634982</v>
       </c>
       <c r="H2" t="n">
-        <v>48.79133857037213</v>
+        <v>57.99820552551724</v>
       </c>
       <c r="I2" t="n">
-        <v>44.8067286933662</v>
+        <v>40.40319668568846</v>
       </c>
       <c r="J2" t="n">
-        <v>39.30430081920738</v>
+        <v>44.89254290424486</v>
       </c>
       <c r="K2" t="n">
-        <v>36.55590352417372</v>
+        <v>34.74726112096625</v>
       </c>
     </row>
   </sheetData>
@@ -8839,34 +8839,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.92220512850015</v>
+        <v>40.70050667593434</v>
       </c>
       <c r="C2" t="n">
-        <v>37.10799184850561</v>
+        <v>36.36387409750906</v>
       </c>
       <c r="D2" t="n">
-        <v>36.33538911325092</v>
+        <v>49.22953442295842</v>
       </c>
       <c r="E2" t="n">
-        <v>46.80918527339749</v>
+        <v>28.92394120925749</v>
       </c>
       <c r="F2" t="n">
-        <v>40.86816250126655</v>
+        <v>36.41385905527518</v>
       </c>
       <c r="G2" t="n">
-        <v>45.41995622197974</v>
+        <v>37.03979012494769</v>
       </c>
       <c r="H2" t="n">
-        <v>55.37589044321689</v>
+        <v>43.40695750116128</v>
       </c>
       <c r="I2" t="n">
-        <v>37.03792337327107</v>
+        <v>47.80933443332571</v>
       </c>
       <c r="J2" t="n">
-        <v>37.11568101009389</v>
+        <v>53.74458634154777</v>
       </c>
       <c r="K2" t="n">
-        <v>35.50528262376776</v>
+        <v>41.62403571050145</v>
       </c>
     </row>
   </sheetData>
@@ -8945,34 +8945,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.79704958030664</v>
+        <v>45.16747864522078</v>
       </c>
       <c r="C2" t="n">
-        <v>26.68117808156416</v>
+        <v>25.45534816307712</v>
       </c>
       <c r="D2" t="n">
-        <v>17.21715589723344</v>
+        <v>58.7756099597208</v>
       </c>
       <c r="E2" t="n">
-        <v>42.05692880756929</v>
+        <v>39.07025165626197</v>
       </c>
       <c r="F2" t="n">
-        <v>29.02929305594908</v>
+        <v>49.83958625893644</v>
       </c>
       <c r="G2" t="n">
-        <v>28.77079632630978</v>
+        <v>42.69193701880986</v>
       </c>
       <c r="H2" t="n">
-        <v>33.98484306439494</v>
+        <v>35.24949522190221</v>
       </c>
       <c r="I2" t="n">
-        <v>28.89554644009894</v>
+        <v>63.48023729392577</v>
       </c>
       <c r="J2" t="n">
-        <v>42.68869087491628</v>
+        <v>38.20359770001891</v>
       </c>
       <c r="K2" t="n">
-        <v>7027.038700760193</v>
+        <v>25.40302023225865</v>
       </c>
     </row>
   </sheetData>
@@ -9051,34 +9051,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.41694947402215</v>
+        <v>38.88136169062179</v>
       </c>
       <c r="C2" t="n">
-        <v>33.7745588752163</v>
+        <v>43.23152171826887</v>
       </c>
       <c r="D2" t="n">
-        <v>28.09919285998063</v>
+        <v>39.08805891010303</v>
       </c>
       <c r="E2" t="n">
-        <v>24.17769038282292</v>
+        <v>44.54265179960795</v>
       </c>
       <c r="F2" t="n">
-        <v>44.50067524631112</v>
+        <v>24.59047039928443</v>
       </c>
       <c r="G2" t="n">
-        <v>37.24239681246033</v>
+        <v>35.57552119283457</v>
       </c>
       <c r="H2" t="n">
-        <v>41.50382182475288</v>
+        <v>27.69090339701203</v>
       </c>
       <c r="I2" t="n">
-        <v>43.32108148028345</v>
+        <v>31.89908051998528</v>
       </c>
       <c r="J2" t="n">
-        <v>30.71245067026221</v>
+        <v>51.20212444088699</v>
       </c>
       <c r="K2" t="n">
-        <v>35.70548252106402</v>
+        <v>36.60317236421608</v>
       </c>
     </row>
   </sheetData>
@@ -9157,34 +9157,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.65223220901225</v>
+        <v>42.41716184652805</v>
       </c>
       <c r="C2" t="n">
-        <v>46.12817828632053</v>
+        <v>37.23496124984623</v>
       </c>
       <c r="D2" t="n">
-        <v>45.38393679515577</v>
+        <v>45.79886062926415</v>
       </c>
       <c r="E2" t="n">
-        <v>37.25133755751337</v>
+        <v>37.2628801274447</v>
       </c>
       <c r="F2" t="n">
-        <v>31.95452589393505</v>
+        <v>29.13883832133305</v>
       </c>
       <c r="G2" t="n">
-        <v>24.88715757646942</v>
+        <v>52.66874018171474</v>
       </c>
       <c r="H2" t="n">
-        <v>29.031740390667</v>
+        <v>41.9705340603848</v>
       </c>
       <c r="I2" t="n">
-        <v>54.97936436603499</v>
+        <v>37.62699626109913</v>
       </c>
       <c r="J2" t="n">
-        <v>25.92194798212203</v>
+        <v>37.88523884998172</v>
       </c>
       <c r="K2" t="n">
-        <v>48.88161984955173</v>
+        <v>45.67180738974077</v>
       </c>
     </row>
   </sheetData>
@@ -9263,34 +9263,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.93733236470903</v>
+        <v>43.62242774638835</v>
       </c>
       <c r="C2" t="n">
-        <v>38.57153382626701</v>
+        <v>38.9011373536425</v>
       </c>
       <c r="D2" t="n">
-        <v>37.59941438253748</v>
+        <v>53.43343594898536</v>
       </c>
       <c r="E2" t="n">
-        <v>52.18715387041377</v>
+        <v>35.20532420620081</v>
       </c>
       <c r="F2" t="n">
-        <v>38.48315093349163</v>
+        <v>42.53883176225502</v>
       </c>
       <c r="G2" t="n">
-        <v>50.82250855673446</v>
+        <v>46.01160082488963</v>
       </c>
       <c r="H2" t="n">
-        <v>29.16873880871886</v>
+        <v>52.90139969305586</v>
       </c>
       <c r="I2" t="n">
-        <v>31.7411921241286</v>
+        <v>40.93641256036086</v>
       </c>
       <c r="J2" t="n">
-        <v>38.16920785004159</v>
+        <v>45.03897818453573</v>
       </c>
       <c r="K2" t="n">
-        <v>39.46902558812258</v>
+        <v>32.22552686204577</v>
       </c>
     </row>
   </sheetData>
@@ -9369,34 +9369,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.75870749890672</v>
+        <v>41.06097175905074</v>
       </c>
       <c r="C2" t="n">
-        <v>20.89715276384561</v>
+        <v>50.93105383076087</v>
       </c>
       <c r="D2" t="n">
-        <v>39.38850122668602</v>
+        <v>41.19969622393207</v>
       </c>
       <c r="E2" t="n">
-        <v>32.48513773558472</v>
+        <v>43.28528439699733</v>
       </c>
       <c r="F2" t="n">
-        <v>34.13725899580015</v>
+        <v>28.17873085983864</v>
       </c>
       <c r="G2" t="n">
-        <v>24.03495795942998</v>
+        <v>57.61993765967375</v>
       </c>
       <c r="H2" t="n">
-        <v>10.56064618302453</v>
+        <v>32.6126331470742</v>
       </c>
       <c r="I2" t="n">
-        <v>31.61811630098307</v>
+        <v>43.13560758282995</v>
       </c>
       <c r="J2" t="n">
-        <v>25.44169996699964</v>
+        <v>26.10854806337244</v>
       </c>
       <c r="K2" t="n">
-        <v>795.0357060585118</v>
+        <v>30.1798964365335</v>
       </c>
     </row>
   </sheetData>
@@ -9475,34 +9475,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.87324416204458</v>
+        <v>35.2273598846795</v>
       </c>
       <c r="C2" t="n">
-        <v>30.07843882179245</v>
+        <v>27.41447654722809</v>
       </c>
       <c r="D2" t="n">
-        <v>54.56291126612668</v>
+        <v>29.5084631490961</v>
       </c>
       <c r="E2" t="n">
-        <v>32.51292482603945</v>
+        <v>32.9082349836203</v>
       </c>
       <c r="F2" t="n">
-        <v>45.78985082001184</v>
+        <v>35.93136117623217</v>
       </c>
       <c r="G2" t="n">
-        <v>20.61003200246273</v>
+        <v>55.28583736763448</v>
       </c>
       <c r="H2" t="n">
-        <v>30.64707198756279</v>
+        <v>17.08232622864702</v>
       </c>
       <c r="I2" t="n">
-        <v>11.15965322782774</v>
+        <v>40.20165935914785</v>
       </c>
       <c r="J2" t="n">
-        <v>32.45870323537216</v>
+        <v>44.70360534003198</v>
       </c>
       <c r="K2" t="n">
-        <v>2323.341395991707</v>
+        <v>29.49143008635597</v>
       </c>
     </row>
   </sheetData>
@@ -9581,34 +9581,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>13.41620534821527</v>
+        <v>29.29076462827413</v>
       </c>
       <c r="C2" t="n">
-        <v>26.02101777884998</v>
+        <v>36.70832217331714</v>
       </c>
       <c r="D2" t="n">
-        <v>35.37508585032879</v>
+        <v>27.13462590254429</v>
       </c>
       <c r="E2" t="n">
-        <v>58.6013073291252</v>
+        <v>31.85361947496384</v>
       </c>
       <c r="F2" t="n">
-        <v>33.30978732544459</v>
+        <v>45.56696693599488</v>
       </c>
       <c r="G2" t="n">
-        <v>33.48981346626405</v>
+        <v>38.40586318488801</v>
       </c>
       <c r="H2" t="n">
-        <v>35.78205759881191</v>
+        <v>33.27948781297005</v>
       </c>
       <c r="I2" t="n">
-        <v>22.99322073583805</v>
+        <v>38.15776509211134</v>
       </c>
       <c r="J2" t="n">
-        <v>40.89741501903128</v>
+        <v>34.64525326113815</v>
       </c>
       <c r="K2" t="n">
-        <v>3107.290946786455</v>
+        <v>43.72050326970325</v>
       </c>
     </row>
   </sheetData>
@@ -9687,34 +9687,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.1050251587061</v>
+        <v>44.56841976749011</v>
       </c>
       <c r="C2" t="n">
-        <v>55.97926478286045</v>
+        <v>46.61272845606999</v>
       </c>
       <c r="D2" t="n">
-        <v>25.66873987193425</v>
+        <v>32.16241623540172</v>
       </c>
       <c r="E2" t="n">
-        <v>37.90677736694909</v>
+        <v>44.38671992458235</v>
       </c>
       <c r="F2" t="n">
-        <v>33.96293679613849</v>
+        <v>38.65265568500391</v>
       </c>
       <c r="G2" t="n">
-        <v>45.52752158917572</v>
+        <v>53.44366653268107</v>
       </c>
       <c r="H2" t="n">
-        <v>29.83723745380843</v>
+        <v>51.56940983571171</v>
       </c>
       <c r="I2" t="n">
-        <v>41.93490802213319</v>
+        <v>42.8389565362343</v>
       </c>
       <c r="J2" t="n">
-        <v>39.24871368855518</v>
+        <v>51.55749007877089</v>
       </c>
       <c r="K2" t="n">
-        <v>25.91354040378261</v>
+        <v>34.17455992183801</v>
       </c>
     </row>
   </sheetData>
@@ -9793,34 +9793,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.87990628521971</v>
+        <v>52.77497396116254</v>
       </c>
       <c r="C2" t="n">
-        <v>47.75663412868641</v>
+        <v>55.4106313981524</v>
       </c>
       <c r="D2" t="n">
-        <v>15.31212426328063</v>
+        <v>54.89181999018835</v>
       </c>
       <c r="E2" t="n">
-        <v>27.25522990648532</v>
+        <v>33.28658483197054</v>
       </c>
       <c r="F2" t="n">
-        <v>46.6957274205981</v>
+        <v>50.99362619458433</v>
       </c>
       <c r="G2" t="n">
-        <v>30.58447478047168</v>
+        <v>29.59162274813816</v>
       </c>
       <c r="H2" t="n">
-        <v>49.98418540225185</v>
+        <v>31.41825017712339</v>
       </c>
       <c r="I2" t="n">
-        <v>34.3696392568957</v>
+        <v>34.78980856263772</v>
       </c>
       <c r="J2" t="n">
-        <v>51.41659943444459</v>
+        <v>30.28005590484926</v>
       </c>
       <c r="K2" t="n">
-        <v>51.90224291899786</v>
+        <v>30.44878511005873</v>
       </c>
     </row>
   </sheetData>
@@ -9899,34 +9899,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>48.08840662037652</v>
+        <v>40.49025944125442</v>
       </c>
       <c r="C2" t="n">
-        <v>36.02504215835697</v>
+        <v>48.63269852282272</v>
       </c>
       <c r="D2" t="n">
-        <v>31.37392163717007</v>
+        <v>35.13820403469703</v>
       </c>
       <c r="E2" t="n">
-        <v>41.57722452513284</v>
+        <v>43.47711514473392</v>
       </c>
       <c r="F2" t="n">
-        <v>50.83688111101789</v>
+        <v>32.24937766864259</v>
       </c>
       <c r="G2" t="n">
-        <v>37.08407508797051</v>
+        <v>43.32388349567518</v>
       </c>
       <c r="H2" t="n">
-        <v>33.78444610073305</v>
+        <v>41.09892172840784</v>
       </c>
       <c r="I2" t="n">
-        <v>28.94532746442559</v>
+        <v>43.25599122857866</v>
       </c>
       <c r="J2" t="n">
-        <v>41.47360431985327</v>
+        <v>47.46034436447289</v>
       </c>
       <c r="K2" t="n">
-        <v>33.09739344394623</v>
+        <v>34.15749730785251</v>
       </c>
     </row>
   </sheetData>
@@ -10005,34 +10005,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.81509380903128</v>
+        <v>33.31497566780985</v>
       </c>
       <c r="C2" t="n">
-        <v>40.90397755312924</v>
+        <v>42.76121873741406</v>
       </c>
       <c r="D2" t="n">
-        <v>47.77359540604868</v>
+        <v>46.45016377086966</v>
       </c>
       <c r="E2" t="n">
-        <v>31.67943785505656</v>
+        <v>41.30525718036018</v>
       </c>
       <c r="F2" t="n">
-        <v>49.26767777736103</v>
+        <v>45.47936079729467</v>
       </c>
       <c r="G2" t="n">
-        <v>49.39781330192038</v>
+        <v>43.26129804257506</v>
       </c>
       <c r="H2" t="n">
-        <v>34.04646962610827</v>
+        <v>53.83013252859185</v>
       </c>
       <c r="I2" t="n">
-        <v>42.04242810353338</v>
+        <v>39.2150475338891</v>
       </c>
       <c r="J2" t="n">
-        <v>38.62970787316576</v>
+        <v>44.12188407986589</v>
       </c>
       <c r="K2" t="n">
-        <v>34.64190558922986</v>
+        <v>42.69702075707838</v>
       </c>
     </row>
   </sheetData>
@@ -10111,34 +10111,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.82846892551272</v>
+        <v>45.55796764919718</v>
       </c>
       <c r="C2" t="n">
-        <v>41.16311178945146</v>
+        <v>51.48021662841895</v>
       </c>
       <c r="D2" t="n">
-        <v>24.4889182042428</v>
+        <v>63.28880062775931</v>
       </c>
       <c r="E2" t="n">
-        <v>86.70979252884867</v>
+        <v>31.93177807195525</v>
       </c>
       <c r="F2" t="n">
-        <v>20.68867688897333</v>
+        <v>36.41927945216747</v>
       </c>
       <c r="G2" t="n">
-        <v>24.79621107970446</v>
+        <v>25.33312855884254</v>
       </c>
       <c r="H2" t="n">
-        <v>32.78857659545864</v>
+        <v>41.71164899809809</v>
       </c>
       <c r="I2" t="n">
-        <v>34.7862989477906</v>
+        <v>38.93544386443807</v>
       </c>
       <c r="J2" t="n">
-        <v>47.59637110678212</v>
+        <v>41.49877954107916</v>
       </c>
       <c r="K2" t="n">
-        <v>42.09517541833832</v>
+        <v>32.32773310139562</v>
       </c>
     </row>
   </sheetData>
@@ -10217,34 +10217,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.09125151840328</v>
+        <v>37.99876654634175</v>
       </c>
       <c r="C2" t="n">
-        <v>39.39472434033435</v>
+        <v>36.06910532066728</v>
       </c>
       <c r="D2" t="n">
-        <v>35.90937761404115</v>
+        <v>39.19714758005703</v>
       </c>
       <c r="E2" t="n">
-        <v>30.77362188953439</v>
+        <v>35.78238283711585</v>
       </c>
       <c r="F2" t="n">
-        <v>45.11579026878941</v>
+        <v>41.34049051383</v>
       </c>
       <c r="G2" t="n">
-        <v>48.34283133207266</v>
+        <v>39.07267690126036</v>
       </c>
       <c r="H2" t="n">
-        <v>25.63024108161761</v>
+        <v>45.75046370811302</v>
       </c>
       <c r="I2" t="n">
-        <v>32.77709561850686</v>
+        <v>36.40205692295723</v>
       </c>
       <c r="J2" t="n">
-        <v>37.72154329208867</v>
+        <v>35.59171500293228</v>
       </c>
       <c r="K2" t="n">
-        <v>33.26606190540394</v>
+        <v>38.10663650548978</v>
       </c>
     </row>
   </sheetData>
@@ -10323,34 +10323,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>62.37495756336368</v>
+        <v>39.28572748696644</v>
       </c>
       <c r="C2" t="n">
-        <v>47.35911176727448</v>
+        <v>54.77554286673311</v>
       </c>
       <c r="D2" t="n">
-        <v>30.82262265448741</v>
+        <v>45.26205613027858</v>
       </c>
       <c r="E2" t="n">
-        <v>36.30114151452948</v>
+        <v>37.45597412049547</v>
       </c>
       <c r="F2" t="n">
-        <v>48.2161861035619</v>
+        <v>34.35925201188371</v>
       </c>
       <c r="G2" t="n">
-        <v>34.38841984545647</v>
+        <v>50.39707261359928</v>
       </c>
       <c r="H2" t="n">
-        <v>42.81482231945296</v>
+        <v>44.01111638044905</v>
       </c>
       <c r="I2" t="n">
-        <v>38.19906760122002</v>
+        <v>45.24705544699727</v>
       </c>
       <c r="J2" t="n">
-        <v>34.00050210463967</v>
+        <v>46.99120679983988</v>
       </c>
       <c r="K2" t="n">
-        <v>50.54102375586686</v>
+        <v>38.19446104395028</v>
       </c>
     </row>
   </sheetData>
@@ -10429,34 +10429,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.77966385989563</v>
+        <v>40.75686776972388</v>
       </c>
       <c r="C2" t="n">
-        <v>31.77500417833861</v>
+        <v>40.67947408671127</v>
       </c>
       <c r="D2" t="n">
-        <v>36.76028054539405</v>
+        <v>44.60439281925524</v>
       </c>
       <c r="E2" t="n">
-        <v>43.02886360873269</v>
+        <v>35.47929648913201</v>
       </c>
       <c r="F2" t="n">
-        <v>34.8480337672566</v>
+        <v>42.07787553338274</v>
       </c>
       <c r="G2" t="n">
-        <v>46.08949729385624</v>
+        <v>31.1637840474704</v>
       </c>
       <c r="H2" t="n">
-        <v>23.7795918594273</v>
+        <v>43.8485408618745</v>
       </c>
       <c r="I2" t="n">
-        <v>42.24574443550319</v>
+        <v>50.6195079509451</v>
       </c>
       <c r="J2" t="n">
-        <v>35.81867238988502</v>
+        <v>35.95189361571335</v>
       </c>
       <c r="K2" t="n">
-        <v>38.76418125251035</v>
+        <v>35.79871607915047</v>
       </c>
     </row>
   </sheetData>
@@ -10535,34 +10535,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.99165513927812</v>
+        <v>45.34952334814922</v>
       </c>
       <c r="C2" t="n">
-        <v>54.16676237374626</v>
+        <v>51.15094590344412</v>
       </c>
       <c r="D2" t="n">
-        <v>37.18811227441291</v>
+        <v>50.68108571507287</v>
       </c>
       <c r="E2" t="n">
-        <v>6072.045611610228</v>
+        <v>37.74802227042908</v>
       </c>
       <c r="F2" t="n">
-        <v>27.11538751929228</v>
+        <v>42.78904527202654</v>
       </c>
       <c r="G2" t="n">
-        <v>35.83883113800531</v>
+        <v>44.72190946250301</v>
       </c>
       <c r="H2" t="n">
-        <v>10.97440421227611</v>
+        <v>34.08397796783007</v>
       </c>
       <c r="I2" t="n">
-        <v>37.41343749992773</v>
+        <v>48.17706898054244</v>
       </c>
       <c r="J2" t="n">
-        <v>41.56617856565607</v>
+        <v>35.63907213365751</v>
       </c>
       <c r="K2" t="n">
-        <v>920.5429814765894</v>
+        <v>33.00628157995971</v>
       </c>
     </row>
   </sheetData>
@@ -10641,34 +10641,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.00460553501568</v>
+        <v>46.36843001870854</v>
       </c>
       <c r="C2" t="n">
-        <v>31.97716270740448</v>
+        <v>31.7100060750926</v>
       </c>
       <c r="D2" t="n">
-        <v>63.09267847627015</v>
+        <v>48.06443264834466</v>
       </c>
       <c r="E2" t="n">
-        <v>40.64487213390242</v>
+        <v>50.53138719425604</v>
       </c>
       <c r="F2" t="n">
-        <v>46.2215932761316</v>
+        <v>45.43009587285844</v>
       </c>
       <c r="G2" t="n">
-        <v>39.06822994873495</v>
+        <v>40.62447334096754</v>
       </c>
       <c r="H2" t="n">
-        <v>38.35441110090046</v>
+        <v>39.14368543983975</v>
       </c>
       <c r="I2" t="n">
-        <v>37.20815336375554</v>
+        <v>31.79694689169879</v>
       </c>
       <c r="J2" t="n">
-        <v>33.3140621334494</v>
+        <v>37.07449704974763</v>
       </c>
       <c r="K2" t="n">
-        <v>27.86031818314359</v>
+        <v>40.31159687311216</v>
       </c>
     </row>
   </sheetData>
@@ -10747,34 +10747,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.78853643990832</v>
+        <v>30.50518252999786</v>
       </c>
       <c r="C2" t="n">
-        <v>59.30398352401408</v>
+        <v>47.0541718939237</v>
       </c>
       <c r="D2" t="n">
-        <v>38.5497534711792</v>
+        <v>35.47289739963718</v>
       </c>
       <c r="E2" t="n">
-        <v>45.29528964961011</v>
+        <v>41.86383404754633</v>
       </c>
       <c r="F2" t="n">
-        <v>44.08510464285356</v>
+        <v>45.57296292459309</v>
       </c>
       <c r="G2" t="n">
-        <v>38.68352895817266</v>
+        <v>39.93465116001894</v>
       </c>
       <c r="H2" t="n">
-        <v>56.79224957798019</v>
+        <v>42.88199128159672</v>
       </c>
       <c r="I2" t="n">
-        <v>50.73702387535793</v>
+        <v>35.97074792133414</v>
       </c>
       <c r="J2" t="n">
-        <v>25.69375694007216</v>
+        <v>56.23338470700316</v>
       </c>
       <c r="K2" t="n">
-        <v>28.36923963183808</v>
+        <v>34.22374298680123</v>
       </c>
     </row>
   </sheetData>
@@ -10853,34 +10853,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.16319089384257</v>
+        <v>40.32578144414492</v>
       </c>
       <c r="C2" t="n">
-        <v>1600.94431561146</v>
+        <v>52.95442041137643</v>
       </c>
       <c r="D2" t="n">
-        <v>41.71003030341651</v>
+        <v>61.37347584015564</v>
       </c>
       <c r="E2" t="n">
-        <v>21.05101352498749</v>
+        <v>37.53062623943595</v>
       </c>
       <c r="F2" t="n">
-        <v>49.37246310090395</v>
+        <v>37.74547173512443</v>
       </c>
       <c r="G2" t="n">
-        <v>41.06013575914352</v>
+        <v>26.09484493634193</v>
       </c>
       <c r="H2" t="n">
-        <v>45.90854383291421</v>
+        <v>43.01944385871179</v>
       </c>
       <c r="I2" t="n">
-        <v>14.62039696786672</v>
+        <v>46.99554958029693</v>
       </c>
       <c r="J2" t="n">
-        <v>45.0985157027141</v>
+        <v>37.26029831905726</v>
       </c>
       <c r="K2" t="n">
-        <v>31.79523224595411</v>
+        <v>47.12200132489948</v>
       </c>
     </row>
   </sheetData>
@@ -10959,34 +10959,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.98297371383452</v>
+        <v>33.58788112441263</v>
       </c>
       <c r="C2" t="n">
-        <v>35.17462757936302</v>
+        <v>47.49391227167653</v>
       </c>
       <c r="D2" t="n">
-        <v>41.22029248191964</v>
+        <v>57.26755177043609</v>
       </c>
       <c r="E2" t="n">
-        <v>45.2553014528329</v>
+        <v>41.6860570797237</v>
       </c>
       <c r="F2" t="n">
-        <v>51.40721219184914</v>
+        <v>40.82367241480591</v>
       </c>
       <c r="G2" t="n">
-        <v>33.92737404061795</v>
+        <v>35.11265037173226</v>
       </c>
       <c r="H2" t="n">
-        <v>35.46263525452912</v>
+        <v>42.08852872901105</v>
       </c>
       <c r="I2" t="n">
-        <v>38.20762155312536</v>
+        <v>59.50958218262856</v>
       </c>
       <c r="J2" t="n">
-        <v>41.1145812526382</v>
+        <v>38.27010238602828</v>
       </c>
       <c r="K2" t="n">
-        <v>37.98447512369698</v>
+        <v>55.08170338467283</v>
       </c>
     </row>
   </sheetData>
@@ -11065,34 +11065,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.03551772893402</v>
+        <v>40.43990303711487</v>
       </c>
       <c r="C2" t="n">
-        <v>33.76167353106651</v>
+        <v>43.60736860913367</v>
       </c>
       <c r="D2" t="n">
-        <v>32.66101807926191</v>
+        <v>73.92777114615406</v>
       </c>
       <c r="E2" t="n">
-        <v>49.2471546715819</v>
+        <v>35.83281593211586</v>
       </c>
       <c r="F2" t="n">
-        <v>46.39888272323189</v>
+        <v>32.68501338638065</v>
       </c>
       <c r="G2" t="n">
-        <v>28.22474607902521</v>
+        <v>38.74124827522144</v>
       </c>
       <c r="H2" t="n">
-        <v>39.18910884139611</v>
+        <v>39.71324123621313</v>
       </c>
       <c r="I2" t="n">
-        <v>33.47569271877683</v>
+        <v>32.37128011657342</v>
       </c>
       <c r="J2" t="n">
-        <v>47.25740837961376</v>
+        <v>51.10060311360615</v>
       </c>
       <c r="K2" t="n">
-        <v>21.18895149948046</v>
+        <v>37.08852552629364</v>
       </c>
     </row>
   </sheetData>
@@ -11171,34 +11171,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.42101684058293</v>
+        <v>43.23273451929354</v>
       </c>
       <c r="C2" t="n">
-        <v>39.22761432915897</v>
+        <v>38.07506304618967</v>
       </c>
       <c r="D2" t="n">
-        <v>27.41031503673932</v>
+        <v>41.65612063895484</v>
       </c>
       <c r="E2" t="n">
-        <v>36.12571352367127</v>
+        <v>49.59051425792425</v>
       </c>
       <c r="F2" t="n">
-        <v>46.99722973697161</v>
+        <v>54.21185593484242</v>
       </c>
       <c r="G2" t="n">
-        <v>37.80167101128407</v>
+        <v>43.01477911282223</v>
       </c>
       <c r="H2" t="n">
-        <v>57.75292136562552</v>
+        <v>49.14246799416685</v>
       </c>
       <c r="I2" t="n">
-        <v>48.21556572067689</v>
+        <v>40.42011227811015</v>
       </c>
       <c r="J2" t="n">
-        <v>29.88604208716272</v>
+        <v>35.77602742948434</v>
       </c>
       <c r="K2" t="n">
-        <v>53.89086912418831</v>
+        <v>38.91406873932811</v>
       </c>
     </row>
   </sheetData>
@@ -11277,34 +11277,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.98054733384508</v>
+        <v>42.34520456036571</v>
       </c>
       <c r="C2" t="n">
-        <v>38.16748504990274</v>
+        <v>46.90114653728207</v>
       </c>
       <c r="D2" t="n">
-        <v>33.67344258079512</v>
+        <v>33.75898898407681</v>
       </c>
       <c r="E2" t="n">
-        <v>33.46872891524085</v>
+        <v>37.63173113040691</v>
       </c>
       <c r="F2" t="n">
-        <v>31.75831673872584</v>
+        <v>35.62510760103404</v>
       </c>
       <c r="G2" t="n">
-        <v>49.80778339402183</v>
+        <v>34.85031585467373</v>
       </c>
       <c r="H2" t="n">
-        <v>32.25244012959423</v>
+        <v>41.8355274022764</v>
       </c>
       <c r="I2" t="n">
-        <v>47.19278004476743</v>
+        <v>43.15688679979416</v>
       </c>
       <c r="J2" t="n">
-        <v>30.07746443618176</v>
+        <v>36.5474584196302</v>
       </c>
       <c r="K2" t="n">
-        <v>27.92247967631171</v>
+        <v>36.64606796320956</v>
       </c>
     </row>
   </sheetData>
@@ -11383,34 +11383,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.17310496563895</v>
+        <v>38.9206875594854</v>
       </c>
       <c r="C2" t="n">
-        <v>68.11151574990456</v>
+        <v>34.89894515464509</v>
       </c>
       <c r="D2" t="n">
-        <v>46.75195424183855</v>
+        <v>41.2359067568454</v>
       </c>
       <c r="E2" t="n">
-        <v>29.35788430754354</v>
+        <v>41.58472230397282</v>
       </c>
       <c r="F2" t="n">
-        <v>29.32064594601935</v>
+        <v>31.51316212038911</v>
       </c>
       <c r="G2" t="n">
-        <v>42.75491302066312</v>
+        <v>38.65408970060375</v>
       </c>
       <c r="H2" t="n">
-        <v>40.01687929043037</v>
+        <v>49.25838438866465</v>
       </c>
       <c r="I2" t="n">
-        <v>35.25482076767477</v>
+        <v>43.27342500884419</v>
       </c>
       <c r="J2" t="n">
-        <v>36.57627074826599</v>
+        <v>43.05072766077567</v>
       </c>
       <c r="K2" t="n">
-        <v>43.42588813191647</v>
+        <v>36.82586319090583</v>
       </c>
     </row>
   </sheetData>
@@ -11489,34 +11489,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.39663036022869</v>
+        <v>48.33514416482431</v>
       </c>
       <c r="C2" t="n">
-        <v>54.66827243142698</v>
+        <v>36.43504278000042</v>
       </c>
       <c r="D2" t="n">
-        <v>35.49192781190923</v>
+        <v>49.13934080313048</v>
       </c>
       <c r="E2" t="n">
-        <v>30.28371727308763</v>
+        <v>42.50821831807902</v>
       </c>
       <c r="F2" t="n">
-        <v>33.67938707675402</v>
+        <v>37.1927398605928</v>
       </c>
       <c r="G2" t="n">
-        <v>33.38084362109006</v>
+        <v>39.24098131937399</v>
       </c>
       <c r="H2" t="n">
-        <v>34.61736885416747</v>
+        <v>41.93846328413801</v>
       </c>
       <c r="I2" t="n">
-        <v>29.34242107703228</v>
+        <v>43.67044769870019</v>
       </c>
       <c r="J2" t="n">
-        <v>33.83305193331589</v>
+        <v>38.1526202394818</v>
       </c>
       <c r="K2" t="n">
-        <v>35.86435946208513</v>
+        <v>35.0234532261124</v>
       </c>
     </row>
   </sheetData>
@@ -11595,34 +11595,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.23374935612312</v>
+        <v>35.79681569777739</v>
       </c>
       <c r="C2" t="n">
-        <v>36.43935452668828</v>
+        <v>35.24820606154059</v>
       </c>
       <c r="D2" t="n">
-        <v>35.06240953149283</v>
+        <v>33.85845571140148</v>
       </c>
       <c r="E2" t="n">
-        <v>28.97066351503759</v>
+        <v>42.49512821814391</v>
       </c>
       <c r="F2" t="n">
-        <v>41.64876355679973</v>
+        <v>34.45655858024685</v>
       </c>
       <c r="G2" t="n">
-        <v>47.02835750763414</v>
+        <v>53.57819619024241</v>
       </c>
       <c r="H2" t="n">
-        <v>41.90062280652811</v>
+        <v>39.13859911348079</v>
       </c>
       <c r="I2" t="n">
-        <v>30.56639041479927</v>
+        <v>44.91406008083747</v>
       </c>
       <c r="J2" t="n">
-        <v>41.81156632257502</v>
+        <v>45.53366229086767</v>
       </c>
       <c r="K2" t="n">
-        <v>34.46907838423807</v>
+        <v>34.37516388679435</v>
       </c>
     </row>
   </sheetData>
@@ -11701,34 +11701,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.75857236885075</v>
+        <v>38.98166185664789</v>
       </c>
       <c r="C2" t="n">
-        <v>43.08129672677012</v>
+        <v>39.77186756658269</v>
       </c>
       <c r="D2" t="n">
-        <v>31.59067494762496</v>
+        <v>45.02754574097486</v>
       </c>
       <c r="E2" t="n">
-        <v>34.64835271930778</v>
+        <v>38.02003483808037</v>
       </c>
       <c r="F2" t="n">
-        <v>42.50552250337346</v>
+        <v>38.08150373853986</v>
       </c>
       <c r="G2" t="n">
-        <v>28.10105662990296</v>
+        <v>46.26389044042603</v>
       </c>
       <c r="H2" t="n">
-        <v>37.41247678045402</v>
+        <v>48.78444278691645</v>
       </c>
       <c r="I2" t="n">
-        <v>36.85072707685468</v>
+        <v>45.3973081116563</v>
       </c>
       <c r="J2" t="n">
-        <v>37.9367501993103</v>
+        <v>32.97532509570638</v>
       </c>
       <c r="K2" t="n">
-        <v>45.40913767023047</v>
+        <v>30.58759841797248</v>
       </c>
     </row>
   </sheetData>
@@ -11807,34 +11807,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.76784230143942</v>
+        <v>26.73023541171876</v>
       </c>
       <c r="C2" t="n">
-        <v>27.39371945595698</v>
+        <v>56.26500436798837</v>
       </c>
       <c r="D2" t="n">
-        <v>35.13887049752115</v>
+        <v>37.49407380843582</v>
       </c>
       <c r="E2" t="n">
-        <v>30.46905163825473</v>
+        <v>51.99284516212433</v>
       </c>
       <c r="F2" t="n">
-        <v>33.77861193095769</v>
+        <v>33.68305393166931</v>
       </c>
       <c r="G2" t="n">
-        <v>37.07985713014612</v>
+        <v>43.4627887083565</v>
       </c>
       <c r="H2" t="n">
-        <v>45.79890747690335</v>
+        <v>40.72938735757976</v>
       </c>
       <c r="I2" t="n">
-        <v>26.15755761370827</v>
+        <v>34.09344591482625</v>
       </c>
       <c r="J2" t="n">
-        <v>42.85096298158988</v>
+        <v>30.25317270210623</v>
       </c>
       <c r="K2" t="n">
-        <v>26.48169217014354</v>
+        <v>22.84497131880943</v>
       </c>
     </row>
   </sheetData>
@@ -11913,34 +11913,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.60580270531374</v>
+        <v>37.26741091104319</v>
       </c>
       <c r="C2" t="n">
-        <v>43.56167597528976</v>
+        <v>46.55382418198536</v>
       </c>
       <c r="D2" t="n">
-        <v>23.58930378850091</v>
+        <v>49.35561032102601</v>
       </c>
       <c r="E2" t="n">
-        <v>56.38061889492099</v>
+        <v>47.56469998016711</v>
       </c>
       <c r="F2" t="n">
-        <v>43.20587444862385</v>
+        <v>41.45531102397285</v>
       </c>
       <c r="G2" t="n">
-        <v>33.13478546861354</v>
+        <v>39.49727409319466</v>
       </c>
       <c r="H2" t="n">
-        <v>39.51355336068226</v>
+        <v>28.97221221619161</v>
       </c>
       <c r="I2" t="n">
-        <v>32.90358005177352</v>
+        <v>43.90130508523859</v>
       </c>
       <c r="J2" t="n">
-        <v>24.70811254201268</v>
+        <v>49.79226877816903</v>
       </c>
       <c r="K2" t="n">
-        <v>49.79226877816903</v>
+        <v>36.55151319760706</v>
       </c>
     </row>
   </sheetData>
@@ -12019,34 +12019,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.65181211981459</v>
+        <v>31.49338649277319</v>
       </c>
       <c r="C2" t="n">
-        <v>44.93243010655308</v>
+        <v>26.22170101719974</v>
       </c>
       <c r="D2" t="n">
-        <v>35.54522246446382</v>
+        <v>41.14935827148597</v>
       </c>
       <c r="E2" t="n">
-        <v>25.65079666995979</v>
+        <v>41.42975864166903</v>
       </c>
       <c r="F2" t="n">
-        <v>25.86321408768633</v>
+        <v>36.73727013543441</v>
       </c>
       <c r="G2" t="n">
-        <v>31.23832896735576</v>
+        <v>39.71977733789781</v>
       </c>
       <c r="H2" t="n">
-        <v>39.02844378120523</v>
+        <v>28.1988673608069</v>
       </c>
       <c r="I2" t="n">
-        <v>50.74119496547215</v>
+        <v>33.20903262971837</v>
       </c>
       <c r="J2" t="n">
-        <v>34.17041341458751</v>
+        <v>35.33728609103493</v>
       </c>
       <c r="K2" t="n">
-        <v>49.32512070740506</v>
+        <v>39.00281755794781</v>
       </c>
     </row>
   </sheetData>
@@ -12125,34 +12125,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.56994713111292</v>
+        <v>49.53197941326526</v>
       </c>
       <c r="C2" t="n">
-        <v>43.57797997040061</v>
+        <v>50.91227760755757</v>
       </c>
       <c r="D2" t="n">
-        <v>19.01695590159729</v>
+        <v>45.42660515395115</v>
       </c>
       <c r="E2" t="n">
-        <v>50.10283016985243</v>
+        <v>33.65344213798098</v>
       </c>
       <c r="F2" t="n">
-        <v>49.77437720254606</v>
+        <v>32.43339944645551</v>
       </c>
       <c r="G2" t="n">
-        <v>38.05400569271084</v>
+        <v>48.46528512271978</v>
       </c>
       <c r="H2" t="n">
-        <v>35.35433756475488</v>
+        <v>39.44064443819327</v>
       </c>
       <c r="I2" t="n">
-        <v>43.01970741988335</v>
+        <v>46.98312087661745</v>
       </c>
       <c r="J2" t="n">
-        <v>45.8812460476349</v>
+        <v>47.15788302647454</v>
       </c>
       <c r="K2" t="n">
-        <v>47.68808256005397</v>
+        <v>35.87927169903984</v>
       </c>
     </row>
   </sheetData>
@@ -12231,34 +12231,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.12778951780831</v>
+        <v>28.41472276640618</v>
       </c>
       <c r="C2" t="n">
-        <v>37.59736421192589</v>
+        <v>33.14445461426979</v>
       </c>
       <c r="D2" t="n">
-        <v>24.85157410495742</v>
+        <v>31.85600516312196</v>
       </c>
       <c r="E2" t="n">
-        <v>43.51373119167771</v>
+        <v>30.70536583036855</v>
       </c>
       <c r="F2" t="n">
-        <v>29.71911268349525</v>
+        <v>38.81940690508838</v>
       </c>
       <c r="G2" t="n">
-        <v>32.54416141981304</v>
+        <v>57.88166168728083</v>
       </c>
       <c r="H2" t="n">
-        <v>18.78232097306025</v>
+        <v>31.22879169997757</v>
       </c>
       <c r="I2" t="n">
-        <v>26.90170348523955</v>
+        <v>40.61907089457446</v>
       </c>
       <c r="J2" t="n">
-        <v>34.95326670255346</v>
+        <v>47.81844169407894</v>
       </c>
       <c r="K2" t="n">
-        <v>45.94563549591161</v>
+        <v>38.52285590518158</v>
       </c>
     </row>
   </sheetData>
@@ -12337,34 +12337,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49.07287053092926</v>
+        <v>32.24285555686281</v>
       </c>
       <c r="C2" t="n">
-        <v>60.4360195199715</v>
+        <v>41.16375818645014</v>
       </c>
       <c r="D2" t="n">
-        <v>39.29818721092551</v>
+        <v>42.57278908634242</v>
       </c>
       <c r="E2" t="n">
-        <v>34.06193146589218</v>
+        <v>33.53770347935532</v>
       </c>
       <c r="F2" t="n">
-        <v>35.15321973695235</v>
+        <v>46.81228386412106</v>
       </c>
       <c r="G2" t="n">
-        <v>20.29949158625636</v>
+        <v>28.82853466460266</v>
       </c>
       <c r="H2" t="n">
-        <v>33.64553439772851</v>
+        <v>60.96014659687519</v>
       </c>
       <c r="I2" t="n">
-        <v>57.11472955706353</v>
+        <v>34.11856904896133</v>
       </c>
       <c r="J2" t="n">
-        <v>14.81254581522548</v>
+        <v>51.27311462340652</v>
       </c>
       <c r="K2" t="n">
-        <v>54.65549818007349</v>
+        <v>36.3176475304308</v>
       </c>
     </row>
   </sheetData>
@@ -12443,34 +12443,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.97553784600953</v>
+        <v>46.92992732961097</v>
       </c>
       <c r="C2" t="n">
-        <v>45.32238367142207</v>
+        <v>47.78084926668202</v>
       </c>
       <c r="D2" t="n">
-        <v>41.05159274039436</v>
+        <v>43.68219572540068</v>
       </c>
       <c r="E2" t="n">
-        <v>36.52428462577515</v>
+        <v>30.18871063490786</v>
       </c>
       <c r="F2" t="n">
-        <v>33.03802053099722</v>
+        <v>46.79179751475947</v>
       </c>
       <c r="G2" t="n">
-        <v>43.49793996765993</v>
+        <v>40.89300221976712</v>
       </c>
       <c r="H2" t="n">
-        <v>34.97574093291852</v>
+        <v>47.90164723381164</v>
       </c>
       <c r="I2" t="n">
-        <v>43.78502021919029</v>
+        <v>39.32300364521821</v>
       </c>
       <c r="J2" t="n">
-        <v>44.47871784646748</v>
+        <v>39.61964841270434</v>
       </c>
       <c r="K2" t="n">
-        <v>40.85660148245812</v>
+        <v>49.53268656657238</v>
       </c>
     </row>
   </sheetData>
@@ -12549,34 +12549,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.01298291007764</v>
+        <v>45.48118476680339</v>
       </c>
       <c r="C2" t="n">
-        <v>42.8263014432343</v>
+        <v>50.18120127056714</v>
       </c>
       <c r="D2" t="n">
-        <v>35.75165989877553</v>
+        <v>51.71093183346932</v>
       </c>
       <c r="E2" t="n">
-        <v>37.29516729788795</v>
+        <v>30.16561107548863</v>
       </c>
       <c r="F2" t="n">
-        <v>51.10659073653871</v>
+        <v>44.70655286670737</v>
       </c>
       <c r="G2" t="n">
-        <v>28.99919029272044</v>
+        <v>38.67940045827744</v>
       </c>
       <c r="H2" t="n">
-        <v>49.45827830848849</v>
+        <v>53.73479884533781</v>
       </c>
       <c r="I2" t="n">
-        <v>44.80200683089905</v>
+        <v>41.17343548045471</v>
       </c>
       <c r="J2" t="n">
-        <v>27.40541351063984</v>
+        <v>46.67097209396645</v>
       </c>
       <c r="K2" t="n">
-        <v>47.72011497487215</v>
+        <v>30.31032545890334</v>
       </c>
     </row>
   </sheetData>
@@ -12655,34 +12655,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.26749982630677</v>
+        <v>29.40349548967203</v>
       </c>
       <c r="C2" t="n">
-        <v>28.91453579161078</v>
+        <v>30.09189429151405</v>
       </c>
       <c r="D2" t="n">
-        <v>24.41589862692093</v>
+        <v>27.52758064204163</v>
       </c>
       <c r="E2" t="n">
-        <v>45.72809410189731</v>
+        <v>31.71790344531834</v>
       </c>
       <c r="F2" t="n">
-        <v>44.40133503789374</v>
+        <v>32.73305662632769</v>
       </c>
       <c r="G2" t="n">
-        <v>64.56840751843663</v>
+        <v>45.46549095504577</v>
       </c>
       <c r="H2" t="n">
-        <v>39.26751139455714</v>
+        <v>47.98195798635916</v>
       </c>
       <c r="I2" t="n">
-        <v>20.22555568809124</v>
+        <v>50.33878830859081</v>
       </c>
       <c r="J2" t="n">
-        <v>41.90329891812141</v>
+        <v>37.96918477405661</v>
       </c>
       <c r="K2" t="n">
-        <v>27.77614339692519</v>
+        <v>39.02271199989223</v>
       </c>
     </row>
   </sheetData>
@@ -12761,34 +12761,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.29527928737068</v>
+        <v>31.48349118397029</v>
       </c>
       <c r="C2" t="n">
-        <v>37.77274048465032</v>
+        <v>52.17225522925884</v>
       </c>
       <c r="D2" t="n">
-        <v>49.6992634848107</v>
+        <v>58.64375716928195</v>
       </c>
       <c r="E2" t="n">
-        <v>37.86713886113712</v>
+        <v>41.63581880143353</v>
       </c>
       <c r="F2" t="n">
-        <v>35.68481066563115</v>
+        <v>44.94930650013053</v>
       </c>
       <c r="G2" t="n">
-        <v>27.98469932115376</v>
+        <v>35.26804816653868</v>
       </c>
       <c r="H2" t="n">
-        <v>28.90404128318439</v>
+        <v>37.45397872081247</v>
       </c>
       <c r="I2" t="n">
-        <v>44.94592460024811</v>
+        <v>43.5408914404837</v>
       </c>
       <c r="J2" t="n">
-        <v>29.19871035375127</v>
+        <v>39.32693587534822</v>
       </c>
       <c r="K2" t="n">
-        <v>67.03634972349096</v>
+        <v>45.50671289757982</v>
       </c>
     </row>
   </sheetData>
@@ -12867,34 +12867,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.97247749391376</v>
+        <v>43.29361439597461</v>
       </c>
       <c r="C2" t="n">
-        <v>49.19489012026639</v>
+        <v>46.35255359355762</v>
       </c>
       <c r="D2" t="n">
-        <v>43.2522148037835</v>
+        <v>63.9574133075246</v>
       </c>
       <c r="E2" t="n">
-        <v>26.3247244807167</v>
+        <v>30.54286446679004</v>
       </c>
       <c r="F2" t="n">
-        <v>41.81997051476647</v>
+        <v>34.07685909605665</v>
       </c>
       <c r="G2" t="n">
-        <v>42.18268179701649</v>
+        <v>52.23673475917576</v>
       </c>
       <c r="H2" t="n">
-        <v>33.9842138914614</v>
+        <v>31.72816794492099</v>
       </c>
       <c r="I2" t="n">
-        <v>26.93668204575471</v>
+        <v>51.80130319073392</v>
       </c>
       <c r="J2" t="n">
-        <v>36.47217440442315</v>
+        <v>43.68938063292195</v>
       </c>
       <c r="K2" t="n">
-        <v>58.11081778164343</v>
+        <v>40.04012770655685</v>
       </c>
     </row>
   </sheetData>
@@ -12973,34 +12973,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.76816896959949</v>
+        <v>32.98714043643638</v>
       </c>
       <c r="C2" t="n">
-        <v>2944.486461672109</v>
+        <v>33.97089985146339</v>
       </c>
       <c r="D2" t="n">
-        <v>24.95455228042307</v>
+        <v>33.57146983814588</v>
       </c>
       <c r="E2" t="n">
-        <v>37.62680634302395</v>
+        <v>38.94983603141532</v>
       </c>
       <c r="F2" t="n">
-        <v>44.24339545340766</v>
+        <v>47.54178724127812</v>
       </c>
       <c r="G2" t="n">
-        <v>35.25411016758198</v>
+        <v>56.5996838938995</v>
       </c>
       <c r="H2" t="n">
-        <v>42.88437339041628</v>
+        <v>42.65179610143961</v>
       </c>
       <c r="I2" t="n">
-        <v>34.84015764692729</v>
+        <v>46.55008145222901</v>
       </c>
       <c r="J2" t="n">
-        <v>31.95601720334597</v>
+        <v>32.36801251546353</v>
       </c>
       <c r="K2" t="n">
-        <v>25.03913365278713</v>
+        <v>41.6956183811833</v>
       </c>
     </row>
   </sheetData>
@@ -13079,34 +13079,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.55454470858</v>
+        <v>34.8211410553423</v>
       </c>
       <c r="C2" t="n">
-        <v>45.73285919817993</v>
+        <v>44.8851617475358</v>
       </c>
       <c r="D2" t="n">
-        <v>28.42429881400169</v>
+        <v>39.38381455772522</v>
       </c>
       <c r="E2" t="n">
-        <v>25.8289903651353</v>
+        <v>41.08373927795356</v>
       </c>
       <c r="F2" t="n">
-        <v>32.43087819376749</v>
+        <v>43.68089796545168</v>
       </c>
       <c r="G2" t="n">
-        <v>40.27029473928319</v>
+        <v>39.305955980524</v>
       </c>
       <c r="H2" t="n">
-        <v>43.37958013629763</v>
+        <v>36.76491706420492</v>
       </c>
       <c r="I2" t="n">
-        <v>33.18855675457069</v>
+        <v>36.51815122189218</v>
       </c>
       <c r="J2" t="n">
-        <v>35.08897875180003</v>
+        <v>35.99831269098203</v>
       </c>
       <c r="K2" t="n">
-        <v>40.01914596081535</v>
+        <v>34.9214078995466</v>
       </c>
     </row>
   </sheetData>
@@ -13185,34 +13185,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.73864466465453</v>
+        <v>39.24564405567916</v>
       </c>
       <c r="C2" t="n">
-        <v>30.33947752857344</v>
+        <v>38.01693848119044</v>
       </c>
       <c r="D2" t="n">
-        <v>20.39696894803205</v>
+        <v>49.72305495707809</v>
       </c>
       <c r="E2" t="n">
-        <v>26.19816787552889</v>
+        <v>24.38847549858798</v>
       </c>
       <c r="F2" t="n">
-        <v>50.76091639136847</v>
+        <v>45.99472555812012</v>
       </c>
       <c r="G2" t="n">
-        <v>50.51401960069427</v>
+        <v>40.6552188562416</v>
       </c>
       <c r="H2" t="n">
-        <v>63.48216579569137</v>
+        <v>39.98979891042892</v>
       </c>
       <c r="I2" t="n">
-        <v>34.83034030582887</v>
+        <v>46.04985456869147</v>
       </c>
       <c r="J2" t="n">
-        <v>28.22846102011999</v>
+        <v>48.60968371707612</v>
       </c>
       <c r="K2" t="n">
-        <v>38.71380960187162</v>
+        <v>38.80304921266953</v>
       </c>
     </row>
   </sheetData>
@@ -13291,34 +13291,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.37216718412581</v>
+        <v>47.66860855039023</v>
       </c>
       <c r="C2" t="n">
-        <v>35.57586991103108</v>
+        <v>39.68444389385164</v>
       </c>
       <c r="D2" t="n">
-        <v>34.86767820760288</v>
+        <v>40.7191650381291</v>
       </c>
       <c r="E2" t="n">
-        <v>43.19337067819205</v>
+        <v>32.95778690409166</v>
       </c>
       <c r="F2" t="n">
-        <v>28.86750113307953</v>
+        <v>36.88887812137568</v>
       </c>
       <c r="G2" t="n">
-        <v>48.13468734519257</v>
+        <v>53.1211940433835</v>
       </c>
       <c r="H2" t="n">
-        <v>30.60826637948647</v>
+        <v>43.81376754921552</v>
       </c>
       <c r="I2" t="n">
-        <v>59.01160849707145</v>
+        <v>29.02781743730448</v>
       </c>
       <c r="J2" t="n">
-        <v>34.24059641960555</v>
+        <v>37.14956477246666</v>
       </c>
       <c r="K2" t="n">
-        <v>36.82481941455636</v>
+        <v>47.73964641867369</v>
       </c>
     </row>
   </sheetData>
@@ -13397,34 +13397,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.74411944123959</v>
+        <v>41.30036363161017</v>
       </c>
       <c r="C2" t="n">
-        <v>31.39684212872686</v>
+        <v>35.68329881228888</v>
       </c>
       <c r="D2" t="n">
-        <v>38.95461100556602</v>
+        <v>50.82557104817025</v>
       </c>
       <c r="E2" t="n">
-        <v>40.59987066552233</v>
+        <v>38.806225004604</v>
       </c>
       <c r="F2" t="n">
-        <v>64.06378325804462</v>
+        <v>41.2655460665404</v>
       </c>
       <c r="G2" t="n">
-        <v>39.33823850906867</v>
+        <v>39.32324140164292</v>
       </c>
       <c r="H2" t="n">
-        <v>36.67738148822103</v>
+        <v>45.85445096431289</v>
       </c>
       <c r="I2" t="n">
-        <v>43.45086622984739</v>
+        <v>39.05531800061708</v>
       </c>
       <c r="J2" t="n">
-        <v>27.25628254912179</v>
+        <v>39.09320607085762</v>
       </c>
       <c r="K2" t="n">
-        <v>38.76960117774426</v>
+        <v>37.49401632106329</v>
       </c>
     </row>
   </sheetData>
@@ -13503,34 +13503,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.62279429108373</v>
+        <v>40.58414551533232</v>
       </c>
       <c r="C2" t="n">
-        <v>48.29275373558302</v>
+        <v>48.53405911565066</v>
       </c>
       <c r="D2" t="n">
-        <v>34.35173094775855</v>
+        <v>54.06549921710214</v>
       </c>
       <c r="E2" t="n">
-        <v>40.98558107233351</v>
+        <v>37.64542329874003</v>
       </c>
       <c r="F2" t="n">
-        <v>37.12000866386447</v>
+        <v>38.81799260924753</v>
       </c>
       <c r="G2" t="n">
-        <v>4361.610228058051</v>
+        <v>38.7882607605723</v>
       </c>
       <c r="H2" t="n">
-        <v>39.09480005270646</v>
+        <v>43.60543144751204</v>
       </c>
       <c r="I2" t="n">
-        <v>19.0964333910309</v>
+        <v>38.90337375133505</v>
       </c>
       <c r="J2" t="n">
-        <v>20.86937512242158</v>
+        <v>35.38718309637807</v>
       </c>
       <c r="K2" t="n">
-        <v>46.50192396908072</v>
+        <v>49.81452742681991</v>
       </c>
     </row>
   </sheetData>
@@ -13609,34 +13609,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.19255999685555</v>
+        <v>37.04343465698974</v>
       </c>
       <c r="C2" t="n">
-        <v>37.31986175773041</v>
+        <v>39.92329845658806</v>
       </c>
       <c r="D2" t="n">
-        <v>18.28313524297645</v>
+        <v>34.08028976250515</v>
       </c>
       <c r="E2" t="n">
-        <v>30.46424874516508</v>
+        <v>36.13870236337875</v>
       </c>
       <c r="F2" t="n">
-        <v>46.18305063546165</v>
+        <v>41.11797859174946</v>
       </c>
       <c r="G2" t="n">
-        <v>35.38761172209538</v>
+        <v>28.06048042263905</v>
       </c>
       <c r="H2" t="n">
-        <v>41.28009401498135</v>
+        <v>37.04971222982768</v>
       </c>
       <c r="I2" t="n">
-        <v>36.66681827048235</v>
+        <v>44.49648759088806</v>
       </c>
       <c r="J2" t="n">
-        <v>40.48089160623024</v>
+        <v>41.21695388478591</v>
       </c>
       <c r="K2" t="n">
-        <v>45.17587862149323</v>
+        <v>30.68296283232795</v>
       </c>
     </row>
   </sheetData>
@@ -13715,34 +13715,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.7534869446654</v>
+        <v>32.36258520656904</v>
       </c>
       <c r="C2" t="n">
-        <v>37.62233882955648</v>
+        <v>44.80115334988152</v>
       </c>
       <c r="D2" t="n">
-        <v>32.94103059502424</v>
+        <v>41.60463132876837</v>
       </c>
       <c r="E2" t="n">
-        <v>45.77427020379329</v>
+        <v>43.64578249306803</v>
       </c>
       <c r="F2" t="n">
-        <v>55.41405153431826</v>
+        <v>49.27471527534887</v>
       </c>
       <c r="G2" t="n">
-        <v>74.61525974108673</v>
+        <v>30.81561395302769</v>
       </c>
       <c r="H2" t="n">
-        <v>47.5510853894716</v>
+        <v>50.55901118558953</v>
       </c>
       <c r="I2" t="n">
-        <v>25.42630753516165</v>
+        <v>44.94364897577668</v>
       </c>
       <c r="J2" t="n">
-        <v>18.00558421834086</v>
+        <v>28.31285609726263</v>
       </c>
       <c r="K2" t="n">
-        <v>36.11441845523009</v>
+        <v>57.08369343466583</v>
       </c>
     </row>
   </sheetData>
@@ -13821,34 +13821,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.35424098547646</v>
+        <v>27.98697019666563</v>
       </c>
       <c r="C2" t="n">
-        <v>53.01211140877055</v>
+        <v>47.26714015688142</v>
       </c>
       <c r="D2" t="n">
-        <v>37.80425327728027</v>
+        <v>47.7188186755323</v>
       </c>
       <c r="E2" t="n">
-        <v>36.12269457663507</v>
+        <v>48.68209812844359</v>
       </c>
       <c r="F2" t="n">
-        <v>45.77048415083773</v>
+        <v>39.3795466659498</v>
       </c>
       <c r="G2" t="n">
-        <v>45.4939322990279</v>
+        <v>41.88264312567429</v>
       </c>
       <c r="H2" t="n">
-        <v>32.64359058779692</v>
+        <v>36.55820420239029</v>
       </c>
       <c r="I2" t="n">
-        <v>55.54339349128237</v>
+        <v>43.10061421899447</v>
       </c>
       <c r="J2" t="n">
-        <v>41.96460103346835</v>
+        <v>48.4871566410606</v>
       </c>
       <c r="K2" t="n">
-        <v>45.20705724680826</v>
+        <v>38.66135643862512</v>
       </c>
     </row>
   </sheetData>
@@ -13927,34 +13927,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.80098970812412</v>
+        <v>38.22084119088915</v>
       </c>
       <c r="C2" t="n">
-        <v>30.45184325592806</v>
+        <v>47.40961531665034</v>
       </c>
       <c r="D2" t="n">
-        <v>12.67643663171073</v>
+        <v>34.164442379144</v>
       </c>
       <c r="E2" t="n">
-        <v>51.89403320717193</v>
+        <v>32.05498193997661</v>
       </c>
       <c r="F2" t="n">
-        <v>38.74744287430377</v>
+        <v>40.1944683329817</v>
       </c>
       <c r="G2" t="n">
-        <v>44.67153170671868</v>
+        <v>38.33762692012998</v>
       </c>
       <c r="H2" t="n">
-        <v>49.50705488392122</v>
+        <v>54.77351837899653</v>
       </c>
       <c r="I2" t="n">
-        <v>48.23314511016551</v>
+        <v>42.59068896037636</v>
       </c>
       <c r="J2" t="n">
-        <v>70.84299965316846</v>
+        <v>53.30649782232456</v>
       </c>
       <c r="K2" t="n">
-        <v>36.23387041621863</v>
+        <v>45.69880198768023</v>
       </c>
     </row>
   </sheetData>
@@ -14033,34 +14033,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.81658953163778</v>
+        <v>24.25363616882249</v>
       </c>
       <c r="C2" t="n">
-        <v>51.5068691931128</v>
+        <v>42.99001398097923</v>
       </c>
       <c r="D2" t="n">
-        <v>23.11854800567001</v>
+        <v>51.39807589296292</v>
       </c>
       <c r="E2" t="n">
-        <v>41.40926387821322</v>
+        <v>36.10863927589377</v>
       </c>
       <c r="F2" t="n">
-        <v>38.30670220872197</v>
+        <v>49.9653183799055</v>
       </c>
       <c r="G2" t="n">
-        <v>35.13142179244518</v>
+        <v>35.7885884142886</v>
       </c>
       <c r="H2" t="n">
-        <v>36.90663871229621</v>
+        <v>47.0242354646634</v>
       </c>
       <c r="I2" t="n">
-        <v>39.98657462272593</v>
+        <v>45.9876998755657</v>
       </c>
       <c r="J2" t="n">
-        <v>37.76241425792074</v>
+        <v>25.69516789593589</v>
       </c>
       <c r="K2" t="n">
-        <v>25.58015543060429</v>
+        <v>34.49956519188535</v>
       </c>
     </row>
   </sheetData>
@@ -14139,34 +14139,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50.37279284776997</v>
+        <v>41.23602218911832</v>
       </c>
       <c r="C2" t="n">
-        <v>59.08560125865161</v>
+        <v>37.21365183027994</v>
       </c>
       <c r="D2" t="n">
-        <v>22.09944557204761</v>
+        <v>26.73786342505265</v>
       </c>
       <c r="E2" t="n">
-        <v>48.02858632109385</v>
+        <v>35.75354383280316</v>
       </c>
       <c r="F2" t="n">
-        <v>29.81677980429928</v>
+        <v>44.34861267351305</v>
       </c>
       <c r="G2" t="n">
-        <v>37.21365183027994</v>
+        <v>48.79246485966457</v>
       </c>
       <c r="H2" t="n">
-        <v>40.46310578936441</v>
+        <v>55.27444665020468</v>
       </c>
       <c r="I2" t="n">
-        <v>45.26390496917488</v>
+        <v>31.23072693399461</v>
       </c>
       <c r="J2" t="n">
-        <v>43.01706472611322</v>
+        <v>47.02321738784852</v>
       </c>
       <c r="K2" t="n">
-        <v>26.09074618017505</v>
+        <v>44.60931463106104</v>
       </c>
     </row>
   </sheetData>
@@ -14245,34 +14245,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.25780511576502</v>
+        <v>38.47247868869987</v>
       </c>
       <c r="C2" t="n">
-        <v>57.35104899728854</v>
+        <v>30.03599371679077</v>
       </c>
       <c r="D2" t="n">
-        <v>39.66414089436181</v>
+        <v>54.04798852986521</v>
       </c>
       <c r="E2" t="n">
-        <v>22.27427920685076</v>
+        <v>51.95168480408021</v>
       </c>
       <c r="F2" t="n">
-        <v>32.83590300843176</v>
+        <v>44.18239610560143</v>
       </c>
       <c r="G2" t="n">
-        <v>38.32607007810266</v>
+        <v>34.87311758532567</v>
       </c>
       <c r="H2" t="n">
-        <v>43.90277957125168</v>
+        <v>34.01866175873046</v>
       </c>
       <c r="I2" t="n">
-        <v>29.87665141753704</v>
+        <v>43.92038357363919</v>
       </c>
       <c r="J2" t="n">
-        <v>37.8478036988452</v>
+        <v>44.39777887339378</v>
       </c>
       <c r="K2" t="n">
-        <v>69.21025693359086</v>
+        <v>47.40229366058594</v>
       </c>
     </row>
   </sheetData>
@@ -14351,34 +14351,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.60944133572561</v>
+        <v>50.60266374032189</v>
       </c>
       <c r="C2" t="n">
-        <v>78.08522589551579</v>
+        <v>46.08722629107832</v>
       </c>
       <c r="D2" t="n">
-        <v>27.57669778134231</v>
+        <v>35.58150189492203</v>
       </c>
       <c r="E2" t="n">
-        <v>30.65437704124601</v>
+        <v>30.04363960601977</v>
       </c>
       <c r="F2" t="n">
-        <v>43.94230716421036</v>
+        <v>36.79928160322622</v>
       </c>
       <c r="G2" t="n">
-        <v>23.54604214275905</v>
+        <v>38.05033044439912</v>
       </c>
       <c r="H2" t="n">
-        <v>34.91687048900894</v>
+        <v>49.86949751472319</v>
       </c>
       <c r="I2" t="n">
-        <v>43.88126627025432</v>
+        <v>31.2824238904971</v>
       </c>
       <c r="J2" t="n">
-        <v>28.65002638387234</v>
+        <v>57.44806580670006</v>
       </c>
       <c r="K2" t="n">
-        <v>51.73094111974411</v>
+        <v>28.08022050155301</v>
       </c>
     </row>
   </sheetData>
@@ -14457,34 +14457,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.71447950951593</v>
+        <v>29.45984455549557</v>
       </c>
       <c r="C2" t="n">
-        <v>768.4968480982797</v>
+        <v>51.87768096728582</v>
       </c>
       <c r="D2" t="n">
-        <v>38.65521452802849</v>
+        <v>58.26995670168986</v>
       </c>
       <c r="E2" t="n">
-        <v>32.05902534045986</v>
+        <v>54.06613309698663</v>
       </c>
       <c r="F2" t="n">
-        <v>59.97296856351952</v>
+        <v>38.77475080826093</v>
       </c>
       <c r="G2" t="n">
-        <v>71.84700850628461</v>
+        <v>33.30596093911559</v>
       </c>
       <c r="H2" t="n">
-        <v>30.45410695034449</v>
+        <v>32.91836557202708</v>
       </c>
       <c r="I2" t="n">
-        <v>26.42146305375274</v>
+        <v>43.63786811321803</v>
       </c>
       <c r="J2" t="n">
-        <v>12.65392970734506</v>
+        <v>52.01532310760842</v>
       </c>
       <c r="K2" t="n">
-        <v>32.17321524241947</v>
+        <v>43.3767924919599</v>
       </c>
     </row>
   </sheetData>
@@ -14563,34 +14563,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.68294012759537</v>
+        <v>32.03576306922588</v>
       </c>
       <c r="C2" t="n">
-        <v>38.74876105513751</v>
+        <v>20.37671759624394</v>
       </c>
       <c r="D2" t="n">
-        <v>43.51236699092232</v>
+        <v>47.68019585933664</v>
       </c>
       <c r="E2" t="n">
-        <v>38.58432728964068</v>
+        <v>40.73963224385182</v>
       </c>
       <c r="F2" t="n">
-        <v>59.14470142385727</v>
+        <v>49.19309521561105</v>
       </c>
       <c r="G2" t="n">
-        <v>18.3909788783334</v>
+        <v>45.21471223121139</v>
       </c>
       <c r="H2" t="n">
-        <v>22.04302866096131</v>
+        <v>49.63241656502723</v>
       </c>
       <c r="I2" t="n">
-        <v>46.89686418108275</v>
+        <v>38.80333920302865</v>
       </c>
       <c r="J2" t="n">
-        <v>38.07224997373867</v>
+        <v>51.47225780441511</v>
       </c>
       <c r="K2" t="n">
-        <v>61.75521142967204</v>
+        <v>42.38206656814189</v>
       </c>
     </row>
   </sheetData>
@@ -14669,34 +14669,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.35451310426934</v>
+        <v>33.28266741691431</v>
       </c>
       <c r="C2" t="n">
-        <v>40.90255197785392</v>
+        <v>39.64853974207499</v>
       </c>
       <c r="D2" t="n">
-        <v>28.52141078421527</v>
+        <v>36.40787306985946</v>
       </c>
       <c r="E2" t="n">
-        <v>28.12053785764685</v>
+        <v>41.79848494958068</v>
       </c>
       <c r="F2" t="n">
-        <v>42.8953335708616</v>
+        <v>53.30723337428716</v>
       </c>
       <c r="G2" t="n">
-        <v>44.22489613154389</v>
+        <v>45.27701777933213</v>
       </c>
       <c r="H2" t="n">
-        <v>32.29209668550197</v>
+        <v>43.84014641226318</v>
       </c>
       <c r="I2" t="n">
-        <v>33.04522906470282</v>
+        <v>46.92464823537805</v>
       </c>
       <c r="J2" t="n">
-        <v>56.89257454353469</v>
+        <v>45.65182733832398</v>
       </c>
       <c r="K2" t="n">
-        <v>45.20919859272117</v>
+        <v>35.39785462083164</v>
       </c>
     </row>
   </sheetData>
@@ -14775,34 +14775,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.88404372010007</v>
+        <v>29.88189091454289</v>
       </c>
       <c r="C2" t="n">
-        <v>52.88686353209929</v>
+        <v>42.13668443330801</v>
       </c>
       <c r="D2" t="n">
-        <v>54.62716693461803</v>
+        <v>38.53746431356115</v>
       </c>
       <c r="E2" t="n">
-        <v>29.62742245169599</v>
+        <v>37.18675715183249</v>
       </c>
       <c r="F2" t="n">
-        <v>43.7381737091518</v>
+        <v>40.7131826352901</v>
       </c>
       <c r="G2" t="n">
-        <v>52.60952904191535</v>
+        <v>56.37349144572287</v>
       </c>
       <c r="H2" t="n">
-        <v>29.69162190573428</v>
+        <v>45.52286421536495</v>
       </c>
       <c r="I2" t="n">
-        <v>45.46271188139535</v>
+        <v>41.88428083191122</v>
       </c>
       <c r="J2" t="n">
-        <v>55.07879062795886</v>
+        <v>59.08650329077165</v>
       </c>
       <c r="K2" t="n">
-        <v>27.28924859224521</v>
+        <v>43.52125576236762</v>
       </c>
     </row>
   </sheetData>
@@ -14881,34 +14881,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.82182770045713</v>
+        <v>34.86836916150703</v>
       </c>
       <c r="C2" t="n">
-        <v>4489.892881824464</v>
+        <v>35.82076534986673</v>
       </c>
       <c r="D2" t="n">
-        <v>28.36234378684027</v>
+        <v>45.74918286867931</v>
       </c>
       <c r="E2" t="n">
-        <v>32.79671226661669</v>
+        <v>40.92411357704272</v>
       </c>
       <c r="F2" t="n">
-        <v>19.31793681263276</v>
+        <v>45.34919606689303</v>
       </c>
       <c r="G2" t="n">
-        <v>51.12280475978098</v>
+        <v>32.74906166934213</v>
       </c>
       <c r="H2" t="n">
-        <v>43.82261325664594</v>
+        <v>39.92576973593241</v>
       </c>
       <c r="I2" t="n">
-        <v>33.05685282124116</v>
+        <v>24.87024433803531</v>
       </c>
       <c r="J2" t="n">
-        <v>23.03086886264103</v>
+        <v>52.88239361126154</v>
       </c>
       <c r="K2" t="n">
-        <v>27.04829943560377</v>
+        <v>51.39640566887154</v>
       </c>
     </row>
   </sheetData>
@@ -14987,34 +14987,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.90162020998658</v>
+        <v>27.85613475779842</v>
       </c>
       <c r="C2" t="n">
-        <v>49.32324027022799</v>
+        <v>52.56586285179838</v>
       </c>
       <c r="D2" t="n">
-        <v>24.58749044811743</v>
+        <v>53.33648053829903</v>
       </c>
       <c r="E2" t="n">
-        <v>52.13059518233461</v>
+        <v>33.07064425164314</v>
       </c>
       <c r="F2" t="n">
-        <v>39.35125497397581</v>
+        <v>37.02873632407089</v>
       </c>
       <c r="G2" t="n">
-        <v>44.42778304112</v>
+        <v>32.81047106854499</v>
       </c>
       <c r="H2" t="n">
-        <v>28.48538795985611</v>
+        <v>53.88997161232973</v>
       </c>
       <c r="I2" t="n">
-        <v>34.28939631540214</v>
+        <v>44.89016351501549</v>
       </c>
       <c r="J2" t="n">
-        <v>37.10465323151504</v>
+        <v>39.8179158089156</v>
       </c>
       <c r="K2" t="n">
-        <v>48.67672197775057</v>
+        <v>36.73902684983879</v>
       </c>
     </row>
   </sheetData>
@@ -15093,34 +15093,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.53933462952099</v>
+        <v>41.65244130858949</v>
       </c>
       <c r="C2" t="n">
-        <v>51.74374107764525</v>
+        <v>51.27481170917659</v>
       </c>
       <c r="D2" t="n">
-        <v>35.03595469484683</v>
+        <v>35.51774807816872</v>
       </c>
       <c r="E2" t="n">
-        <v>39.45057874711399</v>
+        <v>43.4569081801689</v>
       </c>
       <c r="F2" t="n">
-        <v>45.86967772236796</v>
+        <v>46.75505554125932</v>
       </c>
       <c r="G2" t="n">
-        <v>29.22763816287027</v>
+        <v>39.87240193358325</v>
       </c>
       <c r="H2" t="n">
-        <v>41.36266329726325</v>
+        <v>32.61356749846939</v>
       </c>
       <c r="I2" t="n">
-        <v>27.52231107717024</v>
+        <v>29.26352135182952</v>
       </c>
       <c r="J2" t="n">
-        <v>36.1397945823479</v>
+        <v>33.36249359364778</v>
       </c>
       <c r="K2" t="n">
-        <v>39.09342699713927</v>
+        <v>39.23857980074997</v>
       </c>
     </row>
   </sheetData>
@@ -15199,34 +15199,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.11476908463457</v>
+        <v>34.94049907782077</v>
       </c>
       <c r="C2" t="n">
-        <v>36.54269561137964</v>
+        <v>47.84672314352892</v>
       </c>
       <c r="D2" t="n">
-        <v>45.92188419604719</v>
+        <v>45.43255638625369</v>
       </c>
       <c r="E2" t="n">
-        <v>32.70324618257287</v>
+        <v>39.86462510732416</v>
       </c>
       <c r="F2" t="n">
-        <v>21.07681707624797</v>
+        <v>34.71919700250012</v>
       </c>
       <c r="G2" t="n">
-        <v>29.62508480952265</v>
+        <v>43.44326798356561</v>
       </c>
       <c r="H2" t="n">
-        <v>49.48424915561132</v>
+        <v>30.32474958418554</v>
       </c>
       <c r="I2" t="n">
-        <v>34.69476766778739</v>
+        <v>31.48440002022688</v>
       </c>
       <c r="J2" t="n">
-        <v>46.53953653479146</v>
+        <v>33.56418248859322</v>
       </c>
       <c r="K2" t="n">
-        <v>49.31658766748116</v>
+        <v>42.64705783196214</v>
       </c>
     </row>
   </sheetData>
@@ -15305,34 +15305,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.04785094077233</v>
+        <v>32.10917653305446</v>
       </c>
       <c r="C2" t="n">
-        <v>39.50199333164409</v>
+        <v>29.49541621047559</v>
       </c>
       <c r="D2" t="n">
-        <v>31.75376627588473</v>
+        <v>38.99221051119205</v>
       </c>
       <c r="E2" t="n">
-        <v>43.17668694909809</v>
+        <v>31.65545372360845</v>
       </c>
       <c r="F2" t="n">
-        <v>42.03486899249751</v>
+        <v>33.0079295131861</v>
       </c>
       <c r="G2" t="n">
-        <v>51.77709699606362</v>
+        <v>41.01837583948218</v>
       </c>
       <c r="H2" t="n">
-        <v>32.25532069156258</v>
+        <v>42.68675637025651</v>
       </c>
       <c r="I2" t="n">
-        <v>40.67466272181457</v>
+        <v>41.30644425337707</v>
       </c>
       <c r="J2" t="n">
-        <v>20.10664582685313</v>
+        <v>46.34080174122921</v>
       </c>
       <c r="K2" t="n">
-        <v>37.63790940704167</v>
+        <v>34.48054889947133</v>
       </c>
     </row>
   </sheetData>
@@ -15411,34 +15411,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.23844059659282</v>
+        <v>37.52342723104999</v>
       </c>
       <c r="C2" t="n">
-        <v>41.83466345529068</v>
+        <v>53.23073536996189</v>
       </c>
       <c r="D2" t="n">
-        <v>46.80603163050193</v>
+        <v>43.8545793348656</v>
       </c>
       <c r="E2" t="n">
-        <v>48.40512724739973</v>
+        <v>31.61186180903486</v>
       </c>
       <c r="F2" t="n">
-        <v>26.4813168257315</v>
+        <v>33.80907384616652</v>
       </c>
       <c r="G2" t="n">
-        <v>45.72492855417489</v>
+        <v>51.18481062198932</v>
       </c>
       <c r="H2" t="n">
-        <v>42.45175088512539</v>
+        <v>29.99688739809884</v>
       </c>
       <c r="I2" t="n">
-        <v>27.04922534441371</v>
+        <v>45.42679169025472</v>
       </c>
       <c r="J2" t="n">
-        <v>20.92288772054687</v>
+        <v>43.3114543112861</v>
       </c>
       <c r="K2" t="n">
-        <v>43.71471130361272</v>
+        <v>28.60056950139438</v>
       </c>
     </row>
   </sheetData>
@@ -15517,34 +15517,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.85134028056816</v>
+        <v>37.24129533488475</v>
       </c>
       <c r="C2" t="n">
-        <v>52.32007863479598</v>
+        <v>26.13593157381842</v>
       </c>
       <c r="D2" t="n">
-        <v>28.25833438385565</v>
+        <v>43.26839141539102</v>
       </c>
       <c r="E2" t="n">
-        <v>42.52372383205103</v>
+        <v>42.10614939956783</v>
       </c>
       <c r="F2" t="n">
-        <v>41.23598193751462</v>
+        <v>39.17099562959695</v>
       </c>
       <c r="G2" t="n">
-        <v>30.77031866545309</v>
+        <v>33.86232184355572</v>
       </c>
       <c r="H2" t="n">
-        <v>33.63690921379538</v>
+        <v>37.64046052790538</v>
       </c>
       <c r="I2" t="n">
-        <v>29.73758330153771</v>
+        <v>36.31933459394298</v>
       </c>
       <c r="J2" t="n">
-        <v>36.93265064867109</v>
+        <v>44.85533976610565</v>
       </c>
       <c r="K2" t="n">
-        <v>21.29178721676648</v>
+        <v>35.4657620301986</v>
       </c>
     </row>
   </sheetData>
@@ -15623,34 +15623,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.07122752519261</v>
+        <v>44.37278205588456</v>
       </c>
       <c r="C2" t="n">
-        <v>41.98366750356507</v>
+        <v>40.75510507182497</v>
       </c>
       <c r="D2" t="n">
-        <v>48.21815654671229</v>
+        <v>47.59052213414481</v>
       </c>
       <c r="E2" t="n">
-        <v>59.09966513808171</v>
+        <v>45.03104887262199</v>
       </c>
       <c r="F2" t="n">
-        <v>35.82440012360781</v>
+        <v>36.60123908410184</v>
       </c>
       <c r="G2" t="n">
-        <v>29.40917193753502</v>
+        <v>34.91631267491449</v>
       </c>
       <c r="H2" t="n">
-        <v>37.45261204823056</v>
+        <v>52.6185168127083</v>
       </c>
       <c r="I2" t="n">
-        <v>38.95806859695874</v>
+        <v>47.79739530470106</v>
       </c>
       <c r="J2" t="n">
-        <v>41.83958530189118</v>
+        <v>55.68587341418144</v>
       </c>
       <c r="K2" t="n">
-        <v>33.41452915282508</v>
+        <v>42.94673261662515</v>
       </c>
     </row>
   </sheetData>
@@ -15729,34 +15729,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.73287100273521</v>
+        <v>33.73072053612895</v>
       </c>
       <c r="C2" t="n">
-        <v>32.96158610363511</v>
+        <v>47.3164969030931</v>
       </c>
       <c r="D2" t="n">
-        <v>33.16250293080412</v>
+        <v>32.48753183591831</v>
       </c>
       <c r="E2" t="n">
-        <v>52.03027636523719</v>
+        <v>38.15916307282467</v>
       </c>
       <c r="F2" t="n">
-        <v>29.14537023869989</v>
+        <v>36.23084842504827</v>
       </c>
       <c r="G2" t="n">
-        <v>43.05592036736424</v>
+        <v>49.94774791841849</v>
       </c>
       <c r="H2" t="n">
-        <v>34.7680060210326</v>
+        <v>29.5244350741556</v>
       </c>
       <c r="I2" t="n">
-        <v>39.52681660193354</v>
+        <v>38.80059898163822</v>
       </c>
       <c r="J2" t="n">
-        <v>32.13354616815419</v>
+        <v>34.17310632238068</v>
       </c>
       <c r="K2" t="n">
-        <v>30.85992055014781</v>
+        <v>49.91459568271885</v>
       </c>
     </row>
   </sheetData>
@@ -15835,34 +15835,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.1291850352511</v>
+        <v>45.35489514899353</v>
       </c>
       <c r="C2" t="n">
-        <v>39.56827852791442</v>
+        <v>36.43600015526428</v>
       </c>
       <c r="D2" t="n">
-        <v>16.71990951979833</v>
+        <v>50.01825914240231</v>
       </c>
       <c r="E2" t="n">
-        <v>21.47970775347143</v>
+        <v>35.46594659341881</v>
       </c>
       <c r="F2" t="n">
-        <v>47.84338669511416</v>
+        <v>39.30268357711986</v>
       </c>
       <c r="G2" t="n">
-        <v>7540.169315825846</v>
+        <v>33.15677352346505</v>
       </c>
       <c r="H2" t="n">
-        <v>37.02193150578449</v>
+        <v>46.67361979720602</v>
       </c>
       <c r="I2" t="n">
-        <v>33.8448398157123</v>
+        <v>39.45073243233261</v>
       </c>
       <c r="J2" t="n">
-        <v>22.94063726501687</v>
+        <v>48.80853829948821</v>
       </c>
       <c r="K2" t="n">
-        <v>31.66637015873878</v>
+        <v>38.33253135218353</v>
       </c>
     </row>
   </sheetData>
@@ -15941,34 +15941,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.98260720479912</v>
+        <v>50.01059311562925</v>
       </c>
       <c r="C2" t="n">
-        <v>21.72031456405425</v>
+        <v>50.46491172959729</v>
       </c>
       <c r="D2" t="n">
-        <v>30.91217818973963</v>
+        <v>37.03081839842664</v>
       </c>
       <c r="E2" t="n">
-        <v>38.69338437485983</v>
+        <v>35.42894450852878</v>
       </c>
       <c r="F2" t="n">
-        <v>32.2922132086488</v>
+        <v>31.08405940189869</v>
       </c>
       <c r="G2" t="n">
-        <v>41.40902774278031</v>
+        <v>56.8437671797183</v>
       </c>
       <c r="H2" t="n">
-        <v>48.21216191291224</v>
+        <v>40.45209999188957</v>
       </c>
       <c r="I2" t="n">
-        <v>40.56137600611856</v>
+        <v>46.29747518921772</v>
       </c>
       <c r="J2" t="n">
-        <v>34.04491004361045</v>
+        <v>27.77996550842258</v>
       </c>
       <c r="K2" t="n">
-        <v>57.02419115242155</v>
+        <v>31.83681242293265</v>
       </c>
     </row>
   </sheetData>
@@ -16047,34 +16047,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.09671402858616</v>
+        <v>40.74598992408374</v>
       </c>
       <c r="C2" t="n">
-        <v>33.79605016473048</v>
+        <v>42.06338187897364</v>
       </c>
       <c r="D2" t="n">
-        <v>39.06069169386249</v>
+        <v>46.81565178918708</v>
       </c>
       <c r="E2" t="n">
-        <v>34.42017321954414</v>
+        <v>40.81841971308854</v>
       </c>
       <c r="F2" t="n">
-        <v>35.35124652638832</v>
+        <v>34.84944108562144</v>
       </c>
       <c r="G2" t="n">
-        <v>46.90853257295791</v>
+        <v>36.89316921405893</v>
       </c>
       <c r="H2" t="n">
-        <v>23.96898875996307</v>
+        <v>28.60445196641038</v>
       </c>
       <c r="I2" t="n">
-        <v>28.71458620162512</v>
+        <v>46.37216731997416</v>
       </c>
       <c r="J2" t="n">
-        <v>27.31983781446178</v>
+        <v>44.54764046485501</v>
       </c>
       <c r="K2" t="n">
-        <v>1540.90890377603</v>
+        <v>30.14962722654598</v>
       </c>
     </row>
   </sheetData>
@@ -16153,34 +16153,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.27765062067744</v>
+        <v>34.89601269637802</v>
       </c>
       <c r="C2" t="n">
-        <v>30.43429991834614</v>
+        <v>51.43557234936505</v>
       </c>
       <c r="D2" t="n">
-        <v>36.2867263673415</v>
+        <v>34.38164811819279</v>
       </c>
       <c r="E2" t="n">
-        <v>41.30410127603471</v>
+        <v>44.6313260686461</v>
       </c>
       <c r="F2" t="n">
-        <v>20.23008776937205</v>
+        <v>37.58661019276641</v>
       </c>
       <c r="G2" t="n">
-        <v>24.8551762215204</v>
+        <v>35.86251833525642</v>
       </c>
       <c r="H2" t="n">
-        <v>38.33373514749456</v>
+        <v>30.27315375030353</v>
       </c>
       <c r="I2" t="n">
-        <v>35.69815159789088</v>
+        <v>37.02105934641823</v>
       </c>
       <c r="J2" t="n">
-        <v>31.48856102743422</v>
+        <v>49.45425438187623</v>
       </c>
       <c r="K2" t="n">
-        <v>4245.206209303963</v>
+        <v>32.92994925474056</v>
       </c>
     </row>
   </sheetData>
@@ -16259,34 +16259,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.72652490897872</v>
+        <v>34.3965065154778</v>
       </c>
       <c r="C2" t="n">
-        <v>65.6262866317248</v>
+        <v>60.99728337949934</v>
       </c>
       <c r="D2" t="n">
-        <v>28.85786714758897</v>
+        <v>56.63809025608203</v>
       </c>
       <c r="E2" t="n">
-        <v>44.72829976286035</v>
+        <v>35.48999335995606</v>
       </c>
       <c r="F2" t="n">
-        <v>34.17619845265588</v>
+        <v>31.90606980802426</v>
       </c>
       <c r="G2" t="n">
+        <v>32.57174462670439</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.94613601390988</v>
+      </c>
+      <c r="I2" t="n">
         <v>51.47642790280037</v>
       </c>
-      <c r="H2" t="n">
-        <v>36.57584403436007</v>
-      </c>
-      <c r="I2" t="n">
-        <v>27.35113879352406</v>
-      </c>
       <c r="J2" t="n">
-        <v>30.75212756107673</v>
+        <v>49.13988361330328</v>
       </c>
       <c r="K2" t="n">
-        <v>58.27579159889688</v>
+        <v>48.34018603441182</v>
       </c>
     </row>
   </sheetData>
@@ -16365,34 +16365,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.74282921420244</v>
+        <v>41.72337824455397</v>
       </c>
       <c r="C2" t="n">
-        <v>42.74550926610853</v>
+        <v>48.28729567550894</v>
       </c>
       <c r="D2" t="n">
-        <v>45.10012825137155</v>
+        <v>46.47588248754403</v>
       </c>
       <c r="E2" t="n">
-        <v>45.07640291302806</v>
+        <v>31.14681329932479</v>
       </c>
       <c r="F2" t="n">
-        <v>45.31710611882465</v>
+        <v>49.36472397530137</v>
       </c>
       <c r="G2" t="n">
-        <v>55.51546674251813</v>
+        <v>31.97529296875426</v>
       </c>
       <c r="H2" t="n">
-        <v>18.06772787228319</v>
+        <v>55.64141269833111</v>
       </c>
       <c r="I2" t="n">
-        <v>33.77470398089891</v>
+        <v>56.28129993745522</v>
       </c>
       <c r="J2" t="n">
-        <v>44.17383251971148</v>
+        <v>49.52643983758705</v>
       </c>
       <c r="K2" t="n">
-        <v>46.25078202059871</v>
+        <v>40.52421469316009</v>
       </c>
     </row>
   </sheetData>
@@ -16471,34 +16471,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.26105147326308</v>
+        <v>38.02961615344761</v>
       </c>
       <c r="C2" t="n">
-        <v>41.56224359194913</v>
+        <v>45.36262246268409</v>
       </c>
       <c r="D2" t="n">
-        <v>35.79998660888268</v>
+        <v>35.9556636640536</v>
       </c>
       <c r="E2" t="n">
-        <v>43.43529736252248</v>
+        <v>39.98471412369262</v>
       </c>
       <c r="F2" t="n">
-        <v>31.39065053651966</v>
+        <v>42.01382282131122</v>
       </c>
       <c r="G2" t="n">
-        <v>53.54788655553295</v>
+        <v>39.57035425421546</v>
       </c>
       <c r="H2" t="n">
-        <v>36.16611435214678</v>
+        <v>40.38565523554284</v>
       </c>
       <c r="I2" t="n">
-        <v>40.1517227297603</v>
+        <v>46.73777137865372</v>
       </c>
       <c r="J2" t="n">
-        <v>30.95368694328169</v>
+        <v>40.92352312180932</v>
       </c>
       <c r="K2" t="n">
-        <v>39.84064705529194</v>
+        <v>38.83292633912455</v>
       </c>
     </row>
   </sheetData>
@@ -16577,34 +16577,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.88435102665797</v>
+        <v>31.44450926761171</v>
       </c>
       <c r="C2" t="n">
-        <v>50.77619197338689</v>
+        <v>44.52993753110918</v>
       </c>
       <c r="D2" t="n">
-        <v>35.13258599199166</v>
+        <v>54.63594011150777</v>
       </c>
       <c r="E2" t="n">
-        <v>21.22429623981005</v>
+        <v>38.71684981455387</v>
       </c>
       <c r="F2" t="n">
-        <v>44.76556713795152</v>
+        <v>34.20139472868981</v>
       </c>
       <c r="G2" t="n">
-        <v>35.7340748275718</v>
+        <v>48.17616649079901</v>
       </c>
       <c r="H2" t="n">
-        <v>38.60982636738891</v>
+        <v>39.10954605170162</v>
       </c>
       <c r="I2" t="n">
-        <v>41.22890207566883</v>
+        <v>30.67731526467351</v>
       </c>
       <c r="J2" t="n">
-        <v>39.04215919007223</v>
+        <v>39.57925313078637</v>
       </c>
       <c r="K2" t="n">
-        <v>46.99441140444257</v>
+        <v>37.41348639316648</v>
       </c>
     </row>
   </sheetData>
@@ -16683,34 +16683,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.95096199695107</v>
+        <v>43.26664173600838</v>
       </c>
       <c r="C2" t="n">
-        <v>36.2018448479394</v>
+        <v>39.24606604306599</v>
       </c>
       <c r="D2" t="n">
-        <v>22.33858149129646</v>
+        <v>47.84456428411011</v>
       </c>
       <c r="E2" t="n">
-        <v>44.32443069498095</v>
+        <v>41.69677485000133</v>
       </c>
       <c r="F2" t="n">
-        <v>45.2837630413409</v>
+        <v>41.65906111603373</v>
       </c>
       <c r="G2" t="n">
-        <v>38.08182876838706</v>
+        <v>46.06443809027429</v>
       </c>
       <c r="H2" t="n">
-        <v>40.40818851682721</v>
+        <v>54.68856232845553</v>
       </c>
       <c r="I2" t="n">
-        <v>40.10557461140422</v>
+        <v>50.57057981193989</v>
       </c>
       <c r="J2" t="n">
-        <v>29.76759110121144</v>
+        <v>36.32730346143761</v>
       </c>
       <c r="K2" t="n">
-        <v>39.13595137653839</v>
+        <v>30.32880069267556</v>
       </c>
     </row>
   </sheetData>
@@ -16789,34 +16789,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.06660156852632</v>
+        <v>36.89439849031916</v>
       </c>
       <c r="C2" t="n">
-        <v>45.85177312038338</v>
+        <v>60.49524069376177</v>
       </c>
       <c r="D2" t="n">
-        <v>42.39497147331704</v>
+        <v>52.76628929164567</v>
       </c>
       <c r="E2" t="n">
-        <v>48.7784806894773</v>
+        <v>30.82365727757986</v>
       </c>
       <c r="F2" t="n">
-        <v>40.62989040282888</v>
+        <v>31.1865435117699</v>
       </c>
       <c r="G2" t="n">
-        <v>31.42527866525025</v>
+        <v>43.70831636376179</v>
       </c>
       <c r="H2" t="n">
-        <v>30.41067831836768</v>
+        <v>33.05154098723576</v>
       </c>
       <c r="I2" t="n">
-        <v>28.19057817282835</v>
+        <v>47.06256310316672</v>
       </c>
       <c r="J2" t="n">
-        <v>62.85300668722522</v>
+        <v>39.55738531400075</v>
       </c>
       <c r="K2" t="n">
-        <v>47.19689717668759</v>
+        <v>49.37045626469861</v>
       </c>
     </row>
   </sheetData>
@@ -16895,34 +16895,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.51658891653437</v>
+        <v>40.41952185742753</v>
       </c>
       <c r="C2" t="n">
-        <v>23.23189426455971</v>
+        <v>53.44730273288538</v>
       </c>
       <c r="D2" t="n">
-        <v>33.83835609492913</v>
+        <v>33.32533889594056</v>
       </c>
       <c r="E2" t="n">
-        <v>19.11253497631025</v>
+        <v>49.86999239731056</v>
       </c>
       <c r="F2" t="n">
-        <v>24.12411593773672</v>
+        <v>36.35740906832254</v>
       </c>
       <c r="G2" t="n">
-        <v>31.72189000563849</v>
+        <v>44.50435448330501</v>
       </c>
       <c r="H2" t="n">
-        <v>56.26190197049574</v>
+        <v>35.07469879442804</v>
       </c>
       <c r="I2" t="n">
-        <v>27.95064901313556</v>
+        <v>44.68389382822892</v>
       </c>
       <c r="J2" t="n">
-        <v>34.19959561447236</v>
+        <v>33.14197810541928</v>
       </c>
       <c r="K2" t="n">
-        <v>2082.584657912923</v>
+        <v>42.52413835783233</v>
       </c>
     </row>
   </sheetData>
@@ -17001,34 +17001,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.36083955130059</v>
+        <v>35.32603841221793</v>
       </c>
       <c r="C2" t="n">
-        <v>42.0592621151289</v>
+        <v>34.39879441722597</v>
       </c>
       <c r="D2" t="n">
-        <v>36.25015750395815</v>
+        <v>28.93262548537971</v>
       </c>
       <c r="E2" t="n">
-        <v>28.51345562030739</v>
+        <v>46.78397338336154</v>
       </c>
       <c r="F2" t="n">
-        <v>38.91032075267831</v>
+        <v>34.82288012422347</v>
       </c>
       <c r="G2" t="n">
-        <v>42.31479636084012</v>
+        <v>40.60593561402487</v>
       </c>
       <c r="H2" t="n">
-        <v>31.35371902904934</v>
+        <v>41.80672991599419</v>
       </c>
       <c r="I2" t="n">
-        <v>26.42007295720559</v>
+        <v>54.62017816805669</v>
       </c>
       <c r="J2" t="n">
-        <v>54.76433054856455</v>
+        <v>45.29474235280083</v>
       </c>
       <c r="K2" t="n">
-        <v>60.0098170041388</v>
+        <v>34.16846623154125</v>
       </c>
     </row>
   </sheetData>
@@ -17107,34 +17107,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.00090323591021</v>
+        <v>34.11737403718276</v>
       </c>
       <c r="C2" t="n">
-        <v>41.73020606804019</v>
+        <v>40.87635922074254</v>
       </c>
       <c r="D2" t="n">
-        <v>18.57471520954177</v>
+        <v>44.48028814752092</v>
       </c>
       <c r="E2" t="n">
-        <v>35.11474058593061</v>
+        <v>23.15967023442767</v>
       </c>
       <c r="F2" t="n">
-        <v>44.09759893539879</v>
+        <v>50.08157106654897</v>
       </c>
       <c r="G2" t="n">
-        <v>36.32480999862611</v>
+        <v>43.85997410972421</v>
       </c>
       <c r="H2" t="n">
-        <v>32.38281114349767</v>
+        <v>40.90257054767221</v>
       </c>
       <c r="I2" t="n">
-        <v>45.21516260144919</v>
+        <v>38.46773418810515</v>
       </c>
       <c r="J2" t="n">
-        <v>38.62956664508555</v>
+        <v>42.54443694522662</v>
       </c>
       <c r="K2" t="n">
-        <v>39.74948657854387</v>
+        <v>41.61564902771779</v>
       </c>
     </row>
   </sheetData>
@@ -17213,34 +17213,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50.86892614654413</v>
+        <v>40.80973566074284</v>
       </c>
       <c r="C2" t="n">
-        <v>42.48996358635145</v>
+        <v>51.98355728182431</v>
       </c>
       <c r="D2" t="n">
-        <v>22.35083662736928</v>
+        <v>49.0163891969377</v>
       </c>
       <c r="E2" t="n">
-        <v>41.85681370038697</v>
+        <v>37.34440225835211</v>
       </c>
       <c r="F2" t="n">
-        <v>33.48570442195347</v>
+        <v>64.73876391817504</v>
       </c>
       <c r="G2" t="n">
-        <v>37.30416932026751</v>
+        <v>41.74337721705641</v>
       </c>
       <c r="H2" t="n">
-        <v>27.17720268599589</v>
+        <v>46.81790616558691</v>
       </c>
       <c r="I2" t="n">
-        <v>38.34970548238525</v>
+        <v>44.36619870147163</v>
       </c>
       <c r="J2" t="n">
-        <v>47.48806895282412</v>
+        <v>41.89236119091989</v>
       </c>
       <c r="K2" t="n">
-        <v>58.83686186808474</v>
+        <v>29.45811016000884</v>
       </c>
     </row>
   </sheetData>
@@ -17319,34 +17319,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.50579253010393</v>
+        <v>38.51586435835427</v>
       </c>
       <c r="C2" t="n">
-        <v>69.23743955260409</v>
+        <v>46.64572556670498</v>
       </c>
       <c r="D2" t="n">
-        <v>38.40272979555621</v>
+        <v>55.78799034641629</v>
       </c>
       <c r="E2" t="n">
-        <v>33.46468350081093</v>
+        <v>26.7018086329525</v>
       </c>
       <c r="F2" t="n">
-        <v>31.23135366737511</v>
+        <v>28.87314773582638</v>
       </c>
       <c r="G2" t="n">
-        <v>41.17447574819319</v>
+        <v>32.94383818079847</v>
       </c>
       <c r="H2" t="n">
-        <v>15.34324397200632</v>
+        <v>46.94665579858101</v>
       </c>
       <c r="I2" t="n">
-        <v>35.88100718910456</v>
+        <v>44.26263356009768</v>
       </c>
       <c r="J2" t="n">
-        <v>46.93335545920062</v>
+        <v>59.24941333063904</v>
       </c>
       <c r="K2" t="n">
-        <v>48.4290468827948</v>
+        <v>37.98999161820911</v>
       </c>
     </row>
   </sheetData>
@@ -17425,34 +17425,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.24260369484</v>
+        <v>29.34638749258673</v>
       </c>
       <c r="C2" t="n">
-        <v>49.55890616348552</v>
+        <v>47.6598930847459</v>
       </c>
       <c r="D2" t="n">
-        <v>33.31042842311549</v>
+        <v>58.47004521970785</v>
       </c>
       <c r="E2" t="n">
-        <v>34.07922986059058</v>
+        <v>46.17979170190965</v>
       </c>
       <c r="F2" t="n">
-        <v>37.72775808364691</v>
+        <v>38.05611839786415</v>
       </c>
       <c r="G2" t="n">
-        <v>32.32016999103466</v>
+        <v>41.18572134145288</v>
       </c>
       <c r="H2" t="n">
-        <v>31.15749604332264</v>
+        <v>43.19055450981174</v>
       </c>
       <c r="I2" t="n">
-        <v>57.78364374726049</v>
+        <v>39.72440867135284</v>
       </c>
       <c r="J2" t="n">
-        <v>38.5582537392687</v>
+        <v>57.81424228677059</v>
       </c>
       <c r="K2" t="n">
-        <v>54.0253912589226</v>
+        <v>27.42023687822827</v>
       </c>
     </row>
   </sheetData>
@@ -17531,34 +17531,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.7508617273389</v>
+        <v>38.06055901625725</v>
       </c>
       <c r="C2" t="n">
-        <v>41.21820701355573</v>
+        <v>43.11990834305635</v>
       </c>
       <c r="D2" t="n">
-        <v>37.20369993451916</v>
+        <v>43.31636694816449</v>
       </c>
       <c r="E2" t="n">
-        <v>36.4717777876259</v>
+        <v>58.37179627411462</v>
       </c>
       <c r="F2" t="n">
-        <v>45.40854198455017</v>
+        <v>51.01055606827498</v>
       </c>
       <c r="G2" t="n">
-        <v>40.4785488430081</v>
+        <v>33.08171373886023</v>
       </c>
       <c r="H2" t="n">
-        <v>46.71275890311538</v>
+        <v>43.56049933011017</v>
       </c>
       <c r="I2" t="n">
-        <v>38.30683455257933</v>
+        <v>49.94586023757654</v>
       </c>
       <c r="J2" t="n">
-        <v>38.16566677511243</v>
+        <v>40.50013001355266</v>
       </c>
       <c r="K2" t="n">
-        <v>45.04334469779474</v>
+        <v>32.40865652624563</v>
       </c>
     </row>
   </sheetData>
@@ -17637,34 +17637,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.85609820944678</v>
+        <v>39.93280092723537</v>
       </c>
       <c r="C2" t="n">
-        <v>49.66296723117453</v>
+        <v>42.70446502322484</v>
       </c>
       <c r="D2" t="n">
-        <v>35.80291354250219</v>
+        <v>49.4409201499506</v>
       </c>
       <c r="E2" t="n">
-        <v>34.27057435089844</v>
+        <v>34.55638825134285</v>
       </c>
       <c r="F2" t="n">
-        <v>41.48760460776478</v>
+        <v>40.81645062352988</v>
       </c>
       <c r="G2" t="n">
-        <v>42.18584146102572</v>
+        <v>38.89296332447466</v>
       </c>
       <c r="H2" t="n">
-        <v>29.82989695546294</v>
+        <v>52.15224969711612</v>
       </c>
       <c r="I2" t="n">
-        <v>38.42295032961459</v>
+        <v>49.23988291205474</v>
       </c>
       <c r="J2" t="n">
-        <v>32.35612864638043</v>
+        <v>60.15933722764478</v>
       </c>
       <c r="K2" t="n">
-        <v>38.06976648866537</v>
+        <v>44.17062052513429</v>
       </c>
     </row>
   </sheetData>
@@ -17743,34 +17743,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.48366803113019</v>
+        <v>38.55934952295419</v>
       </c>
       <c r="C2" t="n">
+        <v>32.56465459510058</v>
+      </c>
+      <c r="D2" t="n">
         <v>54.86689002641894</v>
       </c>
-      <c r="D2" t="n">
-        <v>22.818466586293</v>
-      </c>
       <c r="E2" t="n">
-        <v>27.47292828679653</v>
+        <v>42.63710114688214</v>
       </c>
       <c r="F2" t="n">
-        <v>44.93545269596966</v>
+        <v>40.31172070456405</v>
       </c>
       <c r="G2" t="n">
-        <v>35.59769611941898</v>
+        <v>45.02895427888892</v>
       </c>
       <c r="H2" t="n">
-        <v>30.38231263526013</v>
+        <v>47.19950522699671</v>
       </c>
       <c r="I2" t="n">
-        <v>35.46532925331186</v>
+        <v>48.93902878521331</v>
       </c>
       <c r="J2" t="n">
-        <v>55.69427094575618</v>
+        <v>45.72424786548394</v>
       </c>
       <c r="K2" t="n">
-        <v>48.67085659393769</v>
+        <v>38.25119185243379</v>
       </c>
     </row>
   </sheetData>
@@ -17849,34 +17849,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.78474721419333</v>
+        <v>26.30690882921049</v>
       </c>
       <c r="C2" t="n">
-        <v>48.74908829685255</v>
+        <v>53.12414785982347</v>
       </c>
       <c r="D2" t="n">
-        <v>50.77372115487217</v>
+        <v>34.52531672793064</v>
       </c>
       <c r="E2" t="n">
-        <v>46.88786809669526</v>
+        <v>50.10336094493829</v>
       </c>
       <c r="F2" t="n">
-        <v>43.00818531994521</v>
+        <v>40.70852064558155</v>
       </c>
       <c r="G2" t="n">
-        <v>38.4682251039349</v>
+        <v>39.58219866868794</v>
       </c>
       <c r="H2" t="n">
-        <v>35.40874583696681</v>
+        <v>32.5185129093963</v>
       </c>
       <c r="I2" t="n">
-        <v>39.29572915233879</v>
+        <v>41.74192834052268</v>
       </c>
       <c r="J2" t="n">
-        <v>13.62221575572692</v>
+        <v>49.11261859213871</v>
       </c>
       <c r="K2" t="n">
-        <v>56.82940430631206</v>
+        <v>37.77821444499671</v>
       </c>
     </row>
   </sheetData>
@@ -17955,34 +17955,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.96026864715661</v>
+        <v>49.19531232062479</v>
       </c>
       <c r="C2" t="n">
-        <v>33.35287493913464</v>
+        <v>48.53688176589841</v>
       </c>
       <c r="D2" t="n">
-        <v>29.59776124350206</v>
+        <v>34.63553682368418</v>
       </c>
       <c r="E2" t="n">
-        <v>36.71304482827818</v>
+        <v>39.34593424057707</v>
       </c>
       <c r="F2" t="n">
-        <v>44.67544438031603</v>
+        <v>37.00577921813789</v>
       </c>
       <c r="G2" t="n">
-        <v>32.42414069089131</v>
+        <v>50.32945083422159</v>
       </c>
       <c r="H2" t="n">
-        <v>29.75814436924197</v>
+        <v>39.94917729695232</v>
       </c>
       <c r="I2" t="n">
-        <v>41.38911367884658</v>
+        <v>42.75190649452604</v>
       </c>
       <c r="J2" t="n">
-        <v>40.85010974666528</v>
+        <v>35.28524404866877</v>
       </c>
       <c r="K2" t="n">
-        <v>34.5395031532008</v>
+        <v>36.04974723803177</v>
       </c>
     </row>
   </sheetData>
@@ -18061,34 +18061,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.71115790403063</v>
+        <v>37.11055463372329</v>
       </c>
       <c r="C2" t="n">
-        <v>55.35557696258982</v>
+        <v>51.56135831234264</v>
       </c>
       <c r="D2" t="n">
-        <v>34.70466697382081</v>
+        <v>32.1128412747392</v>
       </c>
       <c r="E2" t="n">
-        <v>33.41513847294521</v>
+        <v>43.00890224781094</v>
       </c>
       <c r="F2" t="n">
-        <v>26.13907295192377</v>
+        <v>36.85278166522136</v>
       </c>
       <c r="G2" t="n">
-        <v>26.19638033406994</v>
+        <v>35.46564446273338</v>
       </c>
       <c r="H2" t="n">
-        <v>39.78978560593549</v>
+        <v>31.13482102696016</v>
       </c>
       <c r="I2" t="n">
-        <v>26.99582597576985</v>
+        <v>37.50401567061039</v>
       </c>
       <c r="J2" t="n">
-        <v>34.05758918563085</v>
+        <v>38.5837066291186</v>
       </c>
       <c r="K2" t="n">
-        <v>34.03921969284933</v>
+        <v>29.25754006242215</v>
       </c>
     </row>
   </sheetData>
@@ -18167,34 +18167,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.5500135130651</v>
+        <v>36.85386140379391</v>
       </c>
       <c r="C2" t="n">
-        <v>51.04740695436645</v>
+        <v>47.24020724474723</v>
       </c>
       <c r="D2" t="n">
-        <v>37.19489485397197</v>
+        <v>60.33310629658578</v>
       </c>
       <c r="E2" t="n">
-        <v>26.25721629787454</v>
+        <v>42.84584975665237</v>
       </c>
       <c r="F2" t="n">
-        <v>41.45007588352981</v>
+        <v>37.16874447059978</v>
       </c>
       <c r="G2" t="n">
-        <v>46.76253613200994</v>
+        <v>49.84610137965691</v>
       </c>
       <c r="H2" t="n">
-        <v>40.11446318667359</v>
+        <v>37.62067166309608</v>
       </c>
       <c r="I2" t="n">
-        <v>33.56336158672136</v>
+        <v>47.69317420463655</v>
       </c>
       <c r="J2" t="n">
-        <v>32.19567598508835</v>
+        <v>42.74349377882065</v>
       </c>
       <c r="K2" t="n">
-        <v>46.43124620458624</v>
+        <v>42.94297007014512</v>
       </c>
     </row>
   </sheetData>
@@ -18273,34 +18273,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.40294728771457</v>
+        <v>35.5679473062514</v>
       </c>
       <c r="C2" t="n">
-        <v>42.56938698230495</v>
+        <v>37.81548001628757</v>
       </c>
       <c r="D2" t="n">
-        <v>36.75076090161943</v>
+        <v>47.32256392527115</v>
       </c>
       <c r="E2" t="n">
-        <v>37.17504677164793</v>
+        <v>42.76570738444244</v>
       </c>
       <c r="F2" t="n">
-        <v>57.294181403202</v>
+        <v>40.37742241297495</v>
       </c>
       <c r="G2" t="n">
-        <v>42.62659712648605</v>
+        <v>47.18378778979914</v>
       </c>
       <c r="H2" t="n">
-        <v>19.95354484688919</v>
+        <v>41.75197059534641</v>
       </c>
       <c r="I2" t="n">
-        <v>31.96718443749327</v>
+        <v>58.37288429245512</v>
       </c>
       <c r="J2" t="n">
-        <v>39.87888367471434</v>
+        <v>56.50285431303852</v>
       </c>
       <c r="K2" t="n">
-        <v>3378.109882515549</v>
+        <v>30.1690343799815</v>
       </c>
     </row>
   </sheetData>
@@ -18379,34 +18379,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>48.92412739805106</v>
+        <v>48.54960314960691</v>
       </c>
       <c r="C2" t="n">
-        <v>34.57392077015543</v>
+        <v>57.30613919019507</v>
       </c>
       <c r="D2" t="n">
-        <v>33.893179749176</v>
+        <v>34.12663934344885</v>
       </c>
       <c r="E2" t="n">
-        <v>27.57506220857242</v>
+        <v>48.36609503101807</v>
       </c>
       <c r="F2" t="n">
-        <v>47.56478460993292</v>
+        <v>33.00886466633042</v>
       </c>
       <c r="G2" t="n">
-        <v>36.47755040026046</v>
+        <v>36.53867493814717</v>
       </c>
       <c r="H2" t="n">
-        <v>37.44509413999072</v>
+        <v>43.22819273311514</v>
       </c>
       <c r="I2" t="n">
-        <v>38.09816179828004</v>
+        <v>41.53324990345541</v>
       </c>
       <c r="J2" t="n">
-        <v>32.26120505585335</v>
+        <v>27.21273490942579</v>
       </c>
       <c r="K2" t="n">
-        <v>32.81027972471486</v>
+        <v>42.14936235293414</v>
       </c>
     </row>
   </sheetData>
@@ -18485,34 +18485,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.52752086860396</v>
+        <v>28.35933951635594</v>
       </c>
       <c r="C2" t="n">
-        <v>69.55526319690976</v>
+        <v>55.24545773022555</v>
       </c>
       <c r="D2" t="n">
-        <v>40.95197866688342</v>
+        <v>28.54406004391808</v>
       </c>
       <c r="E2" t="n">
-        <v>31.60653570667656</v>
+        <v>41.2195472695695</v>
       </c>
       <c r="F2" t="n">
-        <v>24.63853322749202</v>
+        <v>47.09013213515673</v>
       </c>
       <c r="G2" t="n">
-        <v>36.70740564366944</v>
+        <v>37.13077267960781</v>
       </c>
       <c r="H2" t="n">
-        <v>29.47217721862177</v>
+        <v>36.39376041318762</v>
       </c>
       <c r="I2" t="n">
-        <v>33.60805841755482</v>
+        <v>53.31402684175744</v>
       </c>
       <c r="J2" t="n">
-        <v>29.2473206458761</v>
+        <v>36.93856060414992</v>
       </c>
       <c r="K2" t="n">
-        <v>46.03207895255163</v>
+        <v>31.90743320767756</v>
       </c>
     </row>
   </sheetData>
@@ -18591,34 +18591,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.88004936203931</v>
+        <v>42.99213166285386</v>
       </c>
       <c r="C2" t="n">
-        <v>50.90066142209621</v>
+        <v>34.58011488063474</v>
       </c>
       <c r="D2" t="n">
-        <v>43.48972692815264</v>
+        <v>63.17671066884328</v>
       </c>
       <c r="E2" t="n">
-        <v>36.34388275302697</v>
+        <v>53.18115298997706</v>
       </c>
       <c r="F2" t="n">
-        <v>36.78454124454024</v>
+        <v>46.19605398201762</v>
       </c>
       <c r="G2" t="n">
-        <v>44.20269190259088</v>
+        <v>41.20730531314594</v>
       </c>
       <c r="H2" t="n">
-        <v>36.15432406779632</v>
+        <v>49.07711106114314</v>
       </c>
       <c r="I2" t="n">
-        <v>48.96613951585559</v>
+        <v>39.98329093394926</v>
       </c>
       <c r="J2" t="n">
-        <v>39.55722974444583</v>
+        <v>54.66835894369002</v>
       </c>
       <c r="K2" t="n">
-        <v>31.22502692635532</v>
+        <v>42.98510229548936</v>
       </c>
     </row>
   </sheetData>
@@ -18697,34 +18697,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.57263234545918</v>
+        <v>37.71367113815439</v>
       </c>
       <c r="C2" t="n">
-        <v>51.0771919270889</v>
+        <v>47.6934683610436</v>
       </c>
       <c r="D2" t="n">
-        <v>29.04915063955387</v>
+        <v>55.75666420146113</v>
       </c>
       <c r="E2" t="n">
-        <v>34.97579381540379</v>
+        <v>40.73666987655702</v>
       </c>
       <c r="F2" t="n">
-        <v>34.31346036940362</v>
+        <v>40.2569905371892</v>
       </c>
       <c r="G2" t="n">
-        <v>51.69286901202965</v>
+        <v>44.2523064007695</v>
       </c>
       <c r="H2" t="n">
-        <v>32.13843212074701</v>
+        <v>40.41104527222697</v>
       </c>
       <c r="I2" t="n">
-        <v>48.88401269516859</v>
+        <v>37.03474233035788</v>
       </c>
       <c r="J2" t="n">
-        <v>41.74991823459546</v>
+        <v>54.19188901177019</v>
       </c>
       <c r="K2" t="n">
-        <v>47.36901422558535</v>
+        <v>42.26154331786429</v>
       </c>
     </row>
   </sheetData>
@@ -18803,34 +18803,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.78339880190056</v>
+        <v>34.88211405868366</v>
       </c>
       <c r="C2" t="n">
-        <v>44.84196577670122</v>
+        <v>34.29106948421087</v>
       </c>
       <c r="D2" t="n">
-        <v>39.76420830746794</v>
+        <v>54.12236840000906</v>
       </c>
       <c r="E2" t="n">
-        <v>51.50059632914031</v>
+        <v>33.87360628502886</v>
       </c>
       <c r="F2" t="n">
-        <v>48.2743634798597</v>
+        <v>45.54808951247846</v>
       </c>
       <c r="G2" t="n">
-        <v>44.03095076376471</v>
+        <v>34.52029055790052</v>
       </c>
       <c r="H2" t="n">
-        <v>27.87758941809788</v>
+        <v>60.66624416751274</v>
       </c>
       <c r="I2" t="n">
-        <v>52.16531094133904</v>
+        <v>24.0896591754271</v>
       </c>
       <c r="J2" t="n">
-        <v>34.44156340775221</v>
+        <v>41.99049508759737</v>
       </c>
       <c r="K2" t="n">
-        <v>15.82291529350274</v>
+        <v>43.72722549408912</v>
       </c>
     </row>
   </sheetData>
@@ -18909,34 +18909,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.55048434159636</v>
+        <v>31.98499489545704</v>
       </c>
       <c r="C2" t="n">
-        <v>29.8622918234234</v>
+        <v>57.97811135598663</v>
       </c>
       <c r="D2" t="n">
-        <v>31.76611224044431</v>
+        <v>24.84110349245286</v>
       </c>
       <c r="E2" t="n">
-        <v>81.73209256343434</v>
+        <v>31.52820359507292</v>
       </c>
       <c r="F2" t="n">
-        <v>35.23119470949312</v>
+        <v>33.53864242634983</v>
       </c>
       <c r="G2" t="n">
-        <v>29.00401384907078</v>
+        <v>36.44124440419107</v>
       </c>
       <c r="H2" t="n">
-        <v>38.71850093621759</v>
+        <v>40.01424655661939</v>
       </c>
       <c r="I2" t="n">
-        <v>40.08606202304747</v>
+        <v>36.20998971627852</v>
       </c>
       <c r="J2" t="n">
-        <v>20.71550284494924</v>
+        <v>42.28940168997424</v>
       </c>
       <c r="K2" t="n">
-        <v>51.29433324467812</v>
+        <v>48.01024571077565</v>
       </c>
     </row>
   </sheetData>
@@ -19015,34 +19015,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.94165042216073</v>
+        <v>53.00541537305028</v>
       </c>
       <c r="C2" t="n">
-        <v>17.68069024119421</v>
+        <v>48.71473308703285</v>
       </c>
       <c r="D2" t="n">
-        <v>39.24770782573063</v>
+        <v>36.41968275566071</v>
       </c>
       <c r="E2" t="n">
-        <v>46.86575391912557</v>
+        <v>33.74033473798006</v>
       </c>
       <c r="F2" t="n">
-        <v>32.39307857306862</v>
+        <v>55.18470321083388</v>
       </c>
       <c r="G2" t="n">
-        <v>42.80345255480291</v>
+        <v>43.23001560387395</v>
       </c>
       <c r="H2" t="n">
-        <v>45.59944662380812</v>
+        <v>43.966791951837</v>
       </c>
       <c r="I2" t="n">
-        <v>41.27161332335105</v>
+        <v>35.93771813692288</v>
       </c>
       <c r="J2" t="n">
-        <v>32.91818262658609</v>
+        <v>39.48623038023167</v>
       </c>
       <c r="K2" t="n">
-        <v>6015.031098825155</v>
+        <v>68.0180844477986</v>
       </c>
     </row>
   </sheetData>
@@ -19121,34 +19121,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.50711056117496</v>
+        <v>33.45807073670338</v>
       </c>
       <c r="C2" t="n">
-        <v>41.63328790719207</v>
+        <v>41.71999834691766</v>
       </c>
       <c r="D2" t="n">
-        <v>43.75829673306357</v>
+        <v>41.61466323982181</v>
       </c>
       <c r="E2" t="n">
-        <v>45.54020866856419</v>
+        <v>32.88744683513383</v>
       </c>
       <c r="F2" t="n">
-        <v>46.43240287537824</v>
+        <v>46.85443971407794</v>
       </c>
       <c r="G2" t="n">
-        <v>30.07956525128515</v>
+        <v>53.56680671435166</v>
       </c>
       <c r="H2" t="n">
-        <v>54.21335854421471</v>
+        <v>38.26122511629559</v>
       </c>
       <c r="I2" t="n">
-        <v>25.14672002093055</v>
+        <v>49.19194207147046</v>
       </c>
       <c r="J2" t="n">
-        <v>37.4320472882735</v>
+        <v>57.65532714113612</v>
       </c>
       <c r="K2" t="n">
-        <v>46.05494907063058</v>
+        <v>40.52584820000857</v>
       </c>
     </row>
   </sheetData>
@@ -19227,34 +19227,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.69373256276177</v>
+        <v>44.95997397447193</v>
       </c>
       <c r="C2" t="n">
-        <v>53.10242132510422</v>
+        <v>44.29426533555465</v>
       </c>
       <c r="D2" t="n">
-        <v>41.4315745332183</v>
+        <v>35.72188345304465</v>
       </c>
       <c r="E2" t="n">
-        <v>34.69666726961245</v>
+        <v>44.44385463190761</v>
       </c>
       <c r="F2" t="n">
-        <v>28.60000211625431</v>
+        <v>37.96393237338935</v>
       </c>
       <c r="G2" t="n">
-        <v>19.26332445396159</v>
+        <v>38.85294495106405</v>
       </c>
       <c r="H2" t="n">
-        <v>38.76183078094488</v>
+        <v>35.67080509027276</v>
       </c>
       <c r="I2" t="n">
-        <v>37.17466672786283</v>
+        <v>46.6522915537989</v>
       </c>
       <c r="J2" t="n">
-        <v>41.36200911599422</v>
+        <v>52.5808250619382</v>
       </c>
       <c r="K2" t="n">
-        <v>36.82373926131181</v>
+        <v>36.39617075878764</v>
       </c>
     </row>
   </sheetData>
@@ -19333,34 +19333,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.67327946973592</v>
+        <v>28.30823562455951</v>
       </c>
       <c r="C2" t="n">
-        <v>40.20872589882818</v>
+        <v>42.02070249571815</v>
       </c>
       <c r="D2" t="n">
-        <v>30.28757086703239</v>
+        <v>50.92711439763028</v>
       </c>
       <c r="E2" t="n">
-        <v>37.96793556572769</v>
+        <v>38.81365176793035</v>
       </c>
       <c r="F2" t="n">
-        <v>37.00068396545458</v>
+        <v>38.5968403723416</v>
       </c>
       <c r="G2" t="n">
-        <v>34.80020928224129</v>
+        <v>35.38593833706256</v>
       </c>
       <c r="H2" t="n">
-        <v>39.13685928506114</v>
+        <v>41.13132465716512</v>
       </c>
       <c r="I2" t="n">
-        <v>33.64885531572617</v>
+        <v>42.09405512231657</v>
       </c>
       <c r="J2" t="n">
-        <v>27.09761657355039</v>
+        <v>49.7862691633231</v>
       </c>
       <c r="K2" t="n">
-        <v>48.55484362790813</v>
+        <v>37.95237077093542</v>
       </c>
     </row>
   </sheetData>
@@ -19439,34 +19439,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.95732112685755</v>
+        <v>29.92019296459</v>
       </c>
       <c r="C2" t="n">
-        <v>66.26938363930654</v>
+        <v>46.49919485902925</v>
       </c>
       <c r="D2" t="n">
-        <v>20.95787154192191</v>
+        <v>38.33640845747388</v>
       </c>
       <c r="E2" t="n">
-        <v>48.05503543986593</v>
+        <v>37.52041483981581</v>
       </c>
       <c r="F2" t="n">
-        <v>47.16806263342219</v>
+        <v>25.25692885638853</v>
       </c>
       <c r="G2" t="n">
-        <v>39.88560961219115</v>
+        <v>56.49156707189138</v>
       </c>
       <c r="H2" t="n">
-        <v>28.73339867541581</v>
+        <v>44.56078917578598</v>
       </c>
       <c r="I2" t="n">
-        <v>33.86408638519854</v>
+        <v>39.01905700419164</v>
       </c>
       <c r="J2" t="n">
-        <v>34.0891891454816</v>
+        <v>56.20235042031186</v>
       </c>
       <c r="K2" t="n">
-        <v>34.53521388818123</v>
+        <v>41.68733038748924</v>
       </c>
     </row>
   </sheetData>
@@ -19545,34 +19545,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.1634247750698</v>
+        <v>36.05177151774011</v>
       </c>
       <c r="C2" t="n">
-        <v>35.75996049275405</v>
+        <v>41.2293181167321</v>
       </c>
       <c r="D2" t="n">
-        <v>32.26886942194296</v>
+        <v>48.61931830093765</v>
       </c>
       <c r="E2" t="n">
-        <v>26.10224812457385</v>
+        <v>42.56375836249011</v>
       </c>
       <c r="F2" t="n">
-        <v>27.9234553698323</v>
+        <v>46.40995334946948</v>
       </c>
       <c r="G2" t="n">
-        <v>36.18303851973733</v>
+        <v>30.78520973757945</v>
       </c>
       <c r="H2" t="n">
-        <v>36.42477314669051</v>
+        <v>31.56708737503189</v>
       </c>
       <c r="I2" t="n">
-        <v>50.80911297466461</v>
+        <v>39.47347204023601</v>
       </c>
       <c r="J2" t="n">
-        <v>16.03105740662325</v>
+        <v>29.97366488050543</v>
       </c>
       <c r="K2" t="n">
-        <v>45.36405645314531</v>
+        <v>35.6637797140949</v>
       </c>
     </row>
   </sheetData>
@@ -19651,34 +19651,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.46052232728756</v>
+        <v>34.13694530437851</v>
       </c>
       <c r="C2" t="n">
-        <v>30.68989901967708</v>
+        <v>41.38905153060674</v>
       </c>
       <c r="D2" t="n">
-        <v>29.10131207756104</v>
+        <v>58.01481365630521</v>
       </c>
       <c r="E2" t="n">
-        <v>24.23274399857511</v>
+        <v>46.1114896642985</v>
       </c>
       <c r="F2" t="n">
-        <v>44.13996162957044</v>
+        <v>35.33493606563738</v>
       </c>
       <c r="G2" t="n">
-        <v>55.33132818595598</v>
+        <v>41.2772459938184</v>
       </c>
       <c r="H2" t="n">
-        <v>35.09725137992899</v>
+        <v>43.87192286720018</v>
       </c>
       <c r="I2" t="n">
-        <v>32.30455952219176</v>
+        <v>52.71183015311887</v>
       </c>
       <c r="J2" t="n">
-        <v>40.56603546695064</v>
+        <v>31.06314372033265</v>
       </c>
       <c r="K2" t="n">
-        <v>54.62847632132859</v>
+        <v>33.06290912225639</v>
       </c>
     </row>
   </sheetData>
@@ -19757,34 +19757,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.78342351431463</v>
+        <v>32.39949886454604</v>
       </c>
       <c r="C2" t="n">
-        <v>42.19554781820022</v>
+        <v>45.63937866064739</v>
       </c>
       <c r="D2" t="n">
-        <v>27.94865768531271</v>
+        <v>49.13930951999257</v>
       </c>
       <c r="E2" t="n">
-        <v>35.72856618873691</v>
+        <v>34.70602256043635</v>
       </c>
       <c r="F2" t="n">
-        <v>31.92727365124261</v>
+        <v>51.64818813547121</v>
       </c>
       <c r="G2" t="n">
-        <v>25.80760041434567</v>
+        <v>39.82937687760296</v>
       </c>
       <c r="H2" t="n">
-        <v>42.87667655589237</v>
+        <v>35.49455143009298</v>
       </c>
       <c r="I2" t="n">
-        <v>35.68112926187123</v>
+        <v>39.40441037884023</v>
       </c>
       <c r="J2" t="n">
-        <v>40.99674239016298</v>
+        <v>33.85387123646934</v>
       </c>
       <c r="K2" t="n">
-        <v>56.48720136966976</v>
+        <v>42.66904520654223</v>
       </c>
     </row>
   </sheetData>
@@ -19863,34 +19863,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.95409652138173</v>
+        <v>38.88040466436182</v>
       </c>
       <c r="C2" t="n">
-        <v>27.71588937673915</v>
+        <v>41.03366330338334</v>
       </c>
       <c r="D2" t="n">
-        <v>24.22779358912145</v>
+        <v>36.39958242270147</v>
       </c>
       <c r="E2" t="n">
-        <v>35.40206927974041</v>
+        <v>25.78993094137113</v>
       </c>
       <c r="F2" t="n">
-        <v>25.8799083906255</v>
+        <v>40.31116846835656</v>
       </c>
       <c r="G2" t="n">
-        <v>51.4326941250886</v>
+        <v>46.78555546962045</v>
       </c>
       <c r="H2" t="n">
-        <v>39.82553976844098</v>
+        <v>27.4758607408925</v>
       </c>
       <c r="I2" t="n">
-        <v>24.89587020108109</v>
+        <v>45.35985394425404</v>
       </c>
       <c r="J2" t="n">
-        <v>33.97638248706347</v>
+        <v>39.19223110256377</v>
       </c>
       <c r="K2" t="n">
-        <v>35.38115676175368</v>
+        <v>49.51531736185524</v>
       </c>
     </row>
   </sheetData>
@@ -19969,34 +19969,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.77852486675953</v>
+        <v>41.5544911622551</v>
       </c>
       <c r="C2" t="n">
-        <v>38.64033572753931</v>
+        <v>45.52558864443463</v>
       </c>
       <c r="D2" t="n">
-        <v>50.57032484973081</v>
+        <v>36.8887600355536</v>
       </c>
       <c r="E2" t="n">
-        <v>36.96803225898326</v>
+        <v>42.0039819913762</v>
       </c>
       <c r="F2" t="n">
-        <v>31.51124127633953</v>
+        <v>30.99947524565499</v>
       </c>
       <c r="G2" t="n">
-        <v>32.60318214530685</v>
+        <v>45.82019376275559</v>
       </c>
       <c r="H2" t="n">
-        <v>56.73150711647962</v>
+        <v>47.39998332497093</v>
       </c>
       <c r="I2" t="n">
-        <v>40.13875056733499</v>
+        <v>39.76438314408261</v>
       </c>
       <c r="J2" t="n">
-        <v>28.64419575009834</v>
+        <v>19.75010821830276</v>
       </c>
       <c r="K2" t="n">
-        <v>53.84984230400006</v>
+        <v>40.45869938938085</v>
       </c>
     </row>
   </sheetData>
@@ -20075,34 +20075,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.52338339824231</v>
+        <v>34.88478690609038</v>
       </c>
       <c r="C2" t="n">
-        <v>53.74708337109081</v>
+        <v>52.78284040722745</v>
       </c>
       <c r="D2" t="n">
-        <v>38.35461541195289</v>
+        <v>45.56021560146618</v>
       </c>
       <c r="E2" t="n">
-        <v>41.26289551834896</v>
+        <v>36.07932406636192</v>
       </c>
       <c r="F2" t="n">
-        <v>41.55171186480426</v>
+        <v>30.85985680466022</v>
       </c>
       <c r="G2" t="n">
-        <v>35.63149700497549</v>
+        <v>33.38447246487049</v>
       </c>
       <c r="H2" t="n">
-        <v>26.68355705582792</v>
+        <v>38.01495585067713</v>
       </c>
       <c r="I2" t="n">
-        <v>36.26263879181024</v>
+        <v>53.47528485430258</v>
       </c>
       <c r="J2" t="n">
-        <v>16.98470021262214</v>
+        <v>48.93957546515443</v>
       </c>
       <c r="K2" t="n">
-        <v>54.60377242112872</v>
+        <v>37.60068713936608</v>
       </c>
     </row>
   </sheetData>
@@ -20181,34 +20181,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.576538851235377</v>
+        <v>28.18259518036416</v>
       </c>
       <c r="C2" t="n">
-        <v>5801.226675881133</v>
+        <v>29.90458089020095</v>
       </c>
       <c r="D2" t="n">
-        <v>14.95264808456901</v>
+        <v>36.20866578710394</v>
       </c>
       <c r="E2" t="n">
-        <v>24.43938144532993</v>
+        <v>60.5009658642704</v>
       </c>
       <c r="F2" t="n">
-        <v>43.86334535552398</v>
+        <v>35.85543424876367</v>
       </c>
       <c r="G2" t="n">
-        <v>36.80144409114426</v>
+        <v>30.59029699633564</v>
       </c>
       <c r="H2" t="n">
-        <v>45.66802378517857</v>
+        <v>45.02525501004546</v>
       </c>
       <c r="I2" t="n">
-        <v>62.84364571480344</v>
+        <v>52.42890528849131</v>
       </c>
       <c r="J2" t="n">
-        <v>28.79007452790226</v>
+        <v>43.68960048258121</v>
       </c>
       <c r="K2" t="n">
-        <v>55.28329256777737</v>
+        <v>33.30534993433616</v>
       </c>
     </row>
   </sheetData>
@@ -20287,34 +20287,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.58385015679013</v>
+        <v>33.15291307559447</v>
       </c>
       <c r="C2" t="n">
-        <v>31.25458807462226</v>
+        <v>38.01940965637517</v>
       </c>
       <c r="D2" t="n">
-        <v>33.3045307632425</v>
+        <v>62.40269203508242</v>
       </c>
       <c r="E2" t="n">
-        <v>43.84686667415831</v>
+        <v>33.77100418472752</v>
       </c>
       <c r="F2" t="n">
-        <v>62.54969062293801</v>
+        <v>32.53616016425023</v>
       </c>
       <c r="G2" t="n">
-        <v>46.13283384483844</v>
+        <v>53.03462214727129</v>
       </c>
       <c r="H2" t="n">
-        <v>30.9470473896702</v>
+        <v>47.02605706780109</v>
       </c>
       <c r="I2" t="n">
-        <v>27.88136658012791</v>
+        <v>42.80861354039847</v>
       </c>
       <c r="J2" t="n">
-        <v>26.56599306019154</v>
+        <v>47.46542449204992</v>
       </c>
       <c r="K2" t="n">
-        <v>40.62030629052138</v>
+        <v>50.71653534177648</v>
       </c>
     </row>
   </sheetData>
@@ -20393,34 +20393,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.1814570962523</v>
+        <v>53.0808507928743</v>
       </c>
       <c r="C2" t="n">
-        <v>54.68282264299646</v>
+        <v>38.85576229285646</v>
       </c>
       <c r="D2" t="n">
-        <v>30.01161825934748</v>
+        <v>38.16334300775779</v>
       </c>
       <c r="E2" t="n">
-        <v>31.41353409423689</v>
+        <v>39.81719498348533</v>
       </c>
       <c r="F2" t="n">
-        <v>39.1692542016599</v>
+        <v>48.62484101130438</v>
       </c>
       <c r="G2" t="n">
-        <v>46.02711656251451</v>
+        <v>36.19992379201108</v>
       </c>
       <c r="H2" t="n">
-        <v>38.08560462167154</v>
+        <v>48.26250970564565</v>
       </c>
       <c r="I2" t="n">
-        <v>33.84146981093303</v>
+        <v>44.20853749655163</v>
       </c>
       <c r="J2" t="n">
-        <v>39.94567311068604</v>
+        <v>54.95589697124182</v>
       </c>
       <c r="K2" t="n">
-        <v>39.58931468017073</v>
+        <v>41.55911837212872</v>
       </c>
     </row>
   </sheetData>
@@ -20499,34 +20499,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.9747459329741</v>
+        <v>31.92185408006362</v>
       </c>
       <c r="C2" t="n">
-        <v>46.91645181302007</v>
+        <v>41.77436947503296</v>
       </c>
       <c r="D2" t="n">
-        <v>30.43482590176895</v>
+        <v>43.29821971049708</v>
       </c>
       <c r="E2" t="n">
-        <v>51.24097433312596</v>
+        <v>34.95823882721349</v>
       </c>
       <c r="F2" t="n">
-        <v>37.51841898427631</v>
+        <v>40.06649742370131</v>
       </c>
       <c r="G2" t="n">
-        <v>31.11521368226506</v>
+        <v>38.42534240116299</v>
       </c>
       <c r="H2" t="n">
-        <v>36.30249333077812</v>
+        <v>45.84262011769326</v>
       </c>
       <c r="I2" t="n">
-        <v>46.94844046571733</v>
+        <v>63.84676637668329</v>
       </c>
       <c r="J2" t="n">
-        <v>36.3511078326002</v>
+        <v>33.71313986914159</v>
       </c>
       <c r="K2" t="n">
-        <v>50.08222500851993</v>
+        <v>35.75935722005298</v>
       </c>
     </row>
   </sheetData>
@@ -20605,34 +20605,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.36873186471077</v>
+        <v>31.10660609070597</v>
       </c>
       <c r="C2" t="n">
-        <v>45.55134584401405</v>
+        <v>48.559879519983</v>
       </c>
       <c r="D2" t="n">
-        <v>12.92529070959435</v>
+        <v>51.77567930666636</v>
       </c>
       <c r="E2" t="n">
-        <v>49.21799500387687</v>
+        <v>38.70495643767205</v>
       </c>
       <c r="F2" t="n">
-        <v>37.04396616117456</v>
+        <v>48.39746399071417</v>
       </c>
       <c r="G2" t="n">
-        <v>44.79359185833064</v>
+        <v>45.49780589471222</v>
       </c>
       <c r="H2" t="n">
-        <v>20.14375506726259</v>
+        <v>35.41201719686379</v>
       </c>
       <c r="I2" t="n">
-        <v>52.39890731879264</v>
+        <v>43.956766168104</v>
       </c>
       <c r="J2" t="n">
-        <v>33.17263455321299</v>
+        <v>50.77036898851443</v>
       </c>
       <c r="K2" t="n">
-        <v>41.2735701034179</v>
+        <v>26.2382250736004</v>
       </c>
     </row>
   </sheetData>
@@ -20711,34 +20711,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.95372229885073</v>
+        <v>32.26746621009876</v>
       </c>
       <c r="C2" t="n">
-        <v>53.54782884667255</v>
+        <v>28.71953274073568</v>
       </c>
       <c r="D2" t="n">
-        <v>42.25147097334054</v>
+        <v>38.82202200311632</v>
       </c>
       <c r="E2" t="n">
-        <v>24.69171049037024</v>
+        <v>48.86518395254578</v>
       </c>
       <c r="F2" t="n">
-        <v>45.96166804607759</v>
+        <v>49.63801508308774</v>
       </c>
       <c r="G2" t="n">
-        <v>36.45765449204653</v>
+        <v>43.33751893433215</v>
       </c>
       <c r="H2" t="n">
-        <v>36.85885706601901</v>
+        <v>53.15907652899647</v>
       </c>
       <c r="I2" t="n">
-        <v>39.19407072576038</v>
+        <v>48.01962321596323</v>
       </c>
       <c r="J2" t="n">
-        <v>43.08925216096235</v>
+        <v>50.7928909890073</v>
       </c>
       <c r="K2" t="n">
-        <v>25.3388644016732</v>
+        <v>38.60882441403428</v>
       </c>
     </row>
   </sheetData>
@@ -20817,34 +20817,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>51.35427776659049</v>
+        <v>48.94642580191731</v>
       </c>
       <c r="C2" t="n">
-        <v>40.93356849761513</v>
+        <v>47.21314810931786</v>
       </c>
       <c r="D2" t="n">
-        <v>33.30073557787401</v>
+        <v>58.44966219393139</v>
       </c>
       <c r="E2" t="n">
-        <v>33.20086687967091</v>
+        <v>42.32088474512202</v>
       </c>
       <c r="F2" t="n">
-        <v>34.64762211884056</v>
+        <v>39.09068628426537</v>
       </c>
       <c r="G2" t="n">
-        <v>28.98422369120868</v>
+        <v>28.49364669762546</v>
       </c>
       <c r="H2" t="n">
-        <v>32.24888722438086</v>
+        <v>39.1888462018758</v>
       </c>
       <c r="I2" t="n">
-        <v>28.47853959619665</v>
+        <v>31.52699520549214</v>
       </c>
       <c r="J2" t="n">
-        <v>67.57980388807137</v>
+        <v>52.44032489029071</v>
       </c>
       <c r="K2" t="n">
-        <v>60.24183074506499</v>
+        <v>42.4062678908656</v>
       </c>
     </row>
   </sheetData>
@@ -20923,34 +20923,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.09683901912743</v>
+        <v>31.08598141296801</v>
       </c>
       <c r="C2" t="n">
-        <v>48.99030549097798</v>
+        <v>40.25545535878793</v>
       </c>
       <c r="D2" t="n">
-        <v>26.23813575672822</v>
+        <v>43.40297660090969</v>
       </c>
       <c r="E2" t="n">
-        <v>33.81820357702142</v>
+        <v>48.83160296743411</v>
       </c>
       <c r="F2" t="n">
-        <v>28.34645656696494</v>
+        <v>39.4796626600568</v>
       </c>
       <c r="G2" t="n">
-        <v>35.88503822698205</v>
+        <v>28.3566824207113</v>
       </c>
       <c r="H2" t="n">
-        <v>36.92385200589374</v>
+        <v>31.4874337227303</v>
       </c>
       <c r="I2" t="n">
-        <v>31.0039912836715</v>
+        <v>41.71784957928345</v>
       </c>
       <c r="J2" t="n">
-        <v>37.10661909431262</v>
+        <v>49.34037982083159</v>
       </c>
       <c r="K2" t="n">
-        <v>41.21428794214425</v>
+        <v>30.04759888934004</v>
       </c>
     </row>
   </sheetData>
@@ -21029,34 +21029,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.25075327057247</v>
+        <v>34.35034737681076</v>
       </c>
       <c r="C2" t="n">
-        <v>36.17186242296845</v>
+        <v>36.07466556137753</v>
       </c>
       <c r="D2" t="n">
-        <v>36.24307148710542</v>
+        <v>39.26301936002163</v>
       </c>
       <c r="E2" t="n">
-        <v>47.77295391127878</v>
+        <v>40.28066293326959</v>
       </c>
       <c r="F2" t="n">
-        <v>35.83402754123109</v>
+        <v>30.80039414921135</v>
       </c>
       <c r="G2" t="n">
-        <v>28.52535372524535</v>
+        <v>35.19934096425284</v>
       </c>
       <c r="H2" t="n">
-        <v>38.19261201282425</v>
+        <v>52.33726156939802</v>
       </c>
       <c r="I2" t="n">
-        <v>40.30980968760873</v>
+        <v>47.57428994576394</v>
       </c>
       <c r="J2" t="n">
-        <v>33.50955702581143</v>
+        <v>50.36057099886992</v>
       </c>
       <c r="K2" t="n">
-        <v>39.81765775695143</v>
+        <v>39.16873569852191</v>
       </c>
     </row>
   </sheetData>
@@ -21135,34 +21135,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.4441110658394</v>
+        <v>43.58898774480642</v>
       </c>
       <c r="C2" t="n">
-        <v>65.69837880955363</v>
+        <v>61.5474442719489</v>
       </c>
       <c r="D2" t="n">
-        <v>12.11432952594278</v>
+        <v>59.26536873247476</v>
       </c>
       <c r="E2" t="n">
-        <v>24.66052536872516</v>
+        <v>31.28791249811042</v>
       </c>
       <c r="F2" t="n">
-        <v>13.9658392489706</v>
+        <v>33.78329620509056</v>
       </c>
       <c r="G2" t="n">
-        <v>6114.806496199032</v>
+        <v>44.48766958161945</v>
       </c>
       <c r="H2" t="n">
-        <v>52.17356006296531</v>
+        <v>31.93492272128012</v>
       </c>
       <c r="I2" t="n">
-        <v>33.54101945646308</v>
+        <v>52.5340721701749</v>
       </c>
       <c r="J2" t="n">
-        <v>30.16496864008953</v>
+        <v>60.9421298855958</v>
       </c>
       <c r="K2" t="n">
-        <v>63.35855201039703</v>
+        <v>22.1985616542317</v>
       </c>
     </row>
   </sheetData>
@@ -21241,34 +21241,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.36320405431307</v>
+        <v>32.11069532292255</v>
       </c>
       <c r="C2" t="n">
-        <v>49.04902397631957</v>
+        <v>41.19513631308877</v>
       </c>
       <c r="D2" t="n">
-        <v>40.59692787272765</v>
+        <v>56.83284499737113</v>
       </c>
       <c r="E2" t="n">
-        <v>40.56813373420962</v>
+        <v>28.65925378901622</v>
       </c>
       <c r="F2" t="n">
-        <v>57.06921012770981</v>
+        <v>42.27879752697813</v>
       </c>
       <c r="G2" t="n">
-        <v>56.48983958306911</v>
+        <v>41.4698551946461</v>
       </c>
       <c r="H2" t="n">
-        <v>29.83562507837772</v>
+        <v>41.12500478484284</v>
       </c>
       <c r="I2" t="n">
-        <v>37.48302055692659</v>
+        <v>51.57057901836937</v>
       </c>
       <c r="J2" t="n">
-        <v>45.5459731096431</v>
+        <v>45.05046269626913</v>
       </c>
       <c r="K2" t="n">
-        <v>30.56216757204235</v>
+        <v>40.64977824034305</v>
       </c>
     </row>
   </sheetData>
@@ -21347,34 +21347,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.85091826190004</v>
+        <v>25.27862872981781</v>
       </c>
       <c r="C2" t="n">
-        <v>39.79712705405704</v>
+        <v>30.94591995234081</v>
       </c>
       <c r="D2" t="n">
-        <v>37.16555626558302</v>
+        <v>44.06855080653686</v>
       </c>
       <c r="E2" t="n">
-        <v>41.86074294970473</v>
+        <v>44.67871089744952</v>
       </c>
       <c r="F2" t="n">
-        <v>29.41460328608507</v>
+        <v>35.89524895033764</v>
       </c>
       <c r="G2" t="n">
-        <v>45.54644010583417</v>
+        <v>48.85369959450058</v>
       </c>
       <c r="H2" t="n">
-        <v>38.57859788137504</v>
+        <v>32.04119796354473</v>
       </c>
       <c r="I2" t="n">
-        <v>39.70543839084626</v>
+        <v>42.59354939289789</v>
       </c>
       <c r="J2" t="n">
-        <v>46.42071918580965</v>
+        <v>53.90038135207311</v>
       </c>
       <c r="K2" t="n">
-        <v>38.73952748738029</v>
+        <v>37.16735627298786</v>
       </c>
     </row>
   </sheetData>
@@ -21453,34 +21453,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.1266364502015</v>
+        <v>30.86847794932363</v>
       </c>
       <c r="C2" t="n">
-        <v>48.66245609743809</v>
+        <v>50.60464902200201</v>
       </c>
       <c r="D2" t="n">
-        <v>20.27038406868136</v>
+        <v>39.01128596473039</v>
       </c>
       <c r="E2" t="n">
-        <v>49.71055470779478</v>
+        <v>47.90545018764823</v>
       </c>
       <c r="F2" t="n">
-        <v>30.34851243291602</v>
+        <v>38.25946620059525</v>
       </c>
       <c r="G2" t="n">
-        <v>88.24658776383357</v>
+        <v>43.60636880040005</v>
       </c>
       <c r="H2" t="n">
-        <v>20.36356468810421</v>
+        <v>51.46304489929579</v>
       </c>
       <c r="I2" t="n">
-        <v>42.91911921134527</v>
+        <v>54.4684130055646</v>
       </c>
       <c r="J2" t="n">
-        <v>44.92816245142805</v>
+        <v>55.35811016079654</v>
       </c>
       <c r="K2" t="n">
-        <v>41.32519539263395</v>
+        <v>40.05469802043996</v>
       </c>
     </row>
   </sheetData>
@@ -21559,34 +21559,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.07430747694713</v>
+        <v>27.15594099041661</v>
       </c>
       <c r="C2" t="n">
-        <v>24.05798198837129</v>
+        <v>35.21114375235082</v>
       </c>
       <c r="D2" t="n">
-        <v>36.64724211620722</v>
+        <v>59.2519925361592</v>
       </c>
       <c r="E2" t="n">
-        <v>44.02137355599408</v>
+        <v>38.47637595388372</v>
       </c>
       <c r="F2" t="n">
-        <v>37.83670850168928</v>
+        <v>30.88591142918647</v>
       </c>
       <c r="G2" t="n">
-        <v>39.57780557135614</v>
+        <v>44.9000405228168</v>
       </c>
       <c r="H2" t="n">
-        <v>41.07514312202086</v>
+        <v>39.54962024819621</v>
       </c>
       <c r="I2" t="n">
-        <v>30.94508470899021</v>
+        <v>37.35744915633806</v>
       </c>
       <c r="J2" t="n">
-        <v>43.27202416080524</v>
+        <v>47.80363931354105</v>
       </c>
       <c r="K2" t="n">
-        <v>57.97532045076477</v>
+        <v>34.01403165450093</v>
       </c>
     </row>
   </sheetData>
@@ -21665,34 +21665,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.13514330720911</v>
+        <v>39.82845666769917</v>
       </c>
       <c r="C2" t="n">
-        <v>47.71936523298236</v>
+        <v>35.28718450816724</v>
       </c>
       <c r="D2" t="n">
-        <v>54.51070759405652</v>
+        <v>50.18050548338578</v>
       </c>
       <c r="E2" t="n">
-        <v>23.25932250689841</v>
+        <v>41.90782418109678</v>
       </c>
       <c r="F2" t="n">
-        <v>49.82201872284194</v>
+        <v>31.45532847447097</v>
       </c>
       <c r="G2" t="n">
-        <v>28.00938531307208</v>
+        <v>42.26849737794016</v>
       </c>
       <c r="H2" t="n">
-        <v>46.544362993458</v>
+        <v>35.12080649910915</v>
       </c>
       <c r="I2" t="n">
-        <v>33.16291372764416</v>
+        <v>34.88352150858467</v>
       </c>
       <c r="J2" t="n">
-        <v>32.85062005830819</v>
+        <v>49.81116146554098</v>
       </c>
       <c r="K2" t="n">
-        <v>32.96598334329104</v>
+        <v>41.4505620883567</v>
       </c>
     </row>
   </sheetData>
@@ -21771,34 +21771,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.98420164643721</v>
+        <v>31.35619047713361</v>
       </c>
       <c r="C2" t="n">
-        <v>53.12228396054301</v>
+        <v>49.39116439174689</v>
       </c>
       <c r="D2" t="n">
-        <v>38.93744806070474</v>
+        <v>36.88366968215102</v>
       </c>
       <c r="E2" t="n">
-        <v>37.65114317634589</v>
+        <v>26.2545370555253</v>
       </c>
       <c r="F2" t="n">
-        <v>43.17715796533628</v>
+        <v>41.46758070172487</v>
       </c>
       <c r="G2" t="n">
-        <v>44.23247064969731</v>
+        <v>42.68982376843365</v>
       </c>
       <c r="H2" t="n">
-        <v>33.13475533192878</v>
+        <v>49.35627016420461</v>
       </c>
       <c r="I2" t="n">
-        <v>38.10150716450692</v>
+        <v>34.58137208496299</v>
       </c>
       <c r="J2" t="n">
-        <v>29.17226889733614</v>
+        <v>51.99179918879942</v>
       </c>
       <c r="K2" t="n">
-        <v>29.65920615457888</v>
+        <v>53.78591857754674</v>
       </c>
     </row>
   </sheetData>

--- a/results/cluster_ga/UAVs10_GRID13/revenue/UAVs10_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs10_GRID13/revenue/UAVs10_GRID13_Greedy.xlsx
@@ -677,34 +677,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.22054674250523</v>
+        <v>30.64089997739027</v>
       </c>
       <c r="C2" t="n">
-        <v>47.13537731549437</v>
+        <v>54.95758115613536</v>
       </c>
       <c r="D2" t="n">
-        <v>49.78331449788804</v>
+        <v>33.31822946519443</v>
       </c>
       <c r="E2" t="n">
-        <v>34.33743365166012</v>
+        <v>37.33193623655075</v>
       </c>
       <c r="F2" t="n">
-        <v>45.19396748058821</v>
+        <v>50.39455743627249</v>
       </c>
       <c r="G2" t="n">
-        <v>47.41547461077329</v>
+        <v>51.04610831284837</v>
       </c>
       <c r="H2" t="n">
-        <v>42.95655358612392</v>
+        <v>44.74626962227806</v>
       </c>
       <c r="I2" t="n">
-        <v>42.56280719900322</v>
+        <v>37.6157323181909</v>
       </c>
       <c r="J2" t="n">
-        <v>47.58366512449121</v>
+        <v>31.18537199024974</v>
       </c>
       <c r="K2" t="n">
-        <v>35.95565757234522</v>
+        <v>44.87351461691586</v>
       </c>
     </row>
   </sheetData>
@@ -783,34 +783,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.47413593477366</v>
+        <v>57.87190614286904</v>
       </c>
       <c r="C2" t="n">
-        <v>44.99785474437438</v>
+        <v>50.1567681642511</v>
       </c>
       <c r="D2" t="n">
-        <v>37.04262602419476</v>
+        <v>37.95624928963225</v>
       </c>
       <c r="E2" t="n">
-        <v>34.74622546539155</v>
+        <v>39.3368374898076</v>
       </c>
       <c r="F2" t="n">
-        <v>43.41816092648317</v>
+        <v>51.35001834500388</v>
       </c>
       <c r="G2" t="n">
-        <v>48.76954253186084</v>
+        <v>48.01864917027741</v>
       </c>
       <c r="H2" t="n">
-        <v>32.59833204356726</v>
+        <v>28.98641850957833</v>
       </c>
       <c r="I2" t="n">
-        <v>46.16448615552773</v>
+        <v>45.80978215696096</v>
       </c>
       <c r="J2" t="n">
-        <v>43.06132202010377</v>
+        <v>34.09415816432296</v>
       </c>
       <c r="K2" t="n">
-        <v>47.24352628621109</v>
+        <v>39.69527329371493</v>
       </c>
     </row>
   </sheetData>
@@ -889,34 +889,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.66702684899588</v>
+        <v>36.08463815328094</v>
       </c>
       <c r="C2" t="n">
-        <v>64.27975386542074</v>
+        <v>56.11171233196637</v>
       </c>
       <c r="D2" t="n">
-        <v>60.72033156928761</v>
+        <v>33.47967049535403</v>
       </c>
       <c r="E2" t="n">
-        <v>41.89115696264947</v>
+        <v>50.9834111485218</v>
       </c>
       <c r="F2" t="n">
-        <v>35.47430181194961</v>
+        <v>34.01159807375255</v>
       </c>
       <c r="G2" t="n">
-        <v>42.28691129136051</v>
+        <v>43.41395956391906</v>
       </c>
       <c r="H2" t="n">
-        <v>33.40879419160696</v>
+        <v>39.13578350381007</v>
       </c>
       <c r="I2" t="n">
-        <v>36.92182801320267</v>
+        <v>37.47512181949529</v>
       </c>
       <c r="J2" t="n">
-        <v>54.99610356420734</v>
+        <v>45.61215807000271</v>
       </c>
       <c r="K2" t="n">
-        <v>30.55587791082006</v>
+        <v>49.65267055078131</v>
       </c>
     </row>
   </sheetData>
@@ -995,34 +995,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.28838048412923</v>
+        <v>28.50844163475163</v>
       </c>
       <c r="C2" t="n">
-        <v>44.51290460420543</v>
+        <v>43.8223662145997</v>
       </c>
       <c r="D2" t="n">
-        <v>37.58628440288663</v>
+        <v>46.72456027075841</v>
       </c>
       <c r="E2" t="n">
-        <v>38.65083345808363</v>
+        <v>49.28334677159812</v>
       </c>
       <c r="F2" t="n">
-        <v>54.95240662898911</v>
+        <v>44.1448320337952</v>
       </c>
       <c r="G2" t="n">
-        <v>31.16610861883115</v>
+        <v>49.7611240368251</v>
       </c>
       <c r="H2" t="n">
-        <v>50.91148802419979</v>
+        <v>51.50963882709388</v>
       </c>
       <c r="I2" t="n">
-        <v>46.826817941585</v>
+        <v>43.70288794299528</v>
       </c>
       <c r="J2" t="n">
-        <v>48.62605872767271</v>
+        <v>40.07105000490306</v>
       </c>
       <c r="K2" t="n">
-        <v>41.2924568799679</v>
+        <v>30.98799088745168</v>
       </c>
     </row>
   </sheetData>
@@ -1101,34 +1101,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.96126383869292</v>
+        <v>45.61653805204462</v>
       </c>
       <c r="C2" t="n">
-        <v>40.49998712398559</v>
+        <v>48.25028252580005</v>
       </c>
       <c r="D2" t="n">
-        <v>35.43089737023864</v>
+        <v>40.05124385219938</v>
       </c>
       <c r="E2" t="n">
-        <v>38.41181171515289</v>
+        <v>40.55258305490698</v>
       </c>
       <c r="F2" t="n">
-        <v>35.52073151719247</v>
+        <v>48.31524448406805</v>
       </c>
       <c r="G2" t="n">
-        <v>39.07236935757475</v>
+        <v>51.45249821999837</v>
       </c>
       <c r="H2" t="n">
-        <v>35.89617998715928</v>
+        <v>38.72235687206494</v>
       </c>
       <c r="I2" t="n">
-        <v>41.11904719874104</v>
+        <v>34.84648577740606</v>
       </c>
       <c r="J2" t="n">
-        <v>44.42927825367948</v>
+        <v>31.26249860478377</v>
       </c>
       <c r="K2" t="n">
-        <v>38.21833697702134</v>
+        <v>46.84485906682928</v>
       </c>
     </row>
   </sheetData>
@@ -1207,34 +1207,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.87661870122341</v>
+        <v>48.11131784894682</v>
       </c>
       <c r="C2" t="n">
-        <v>38.60900599166548</v>
+        <v>38.08944944803907</v>
       </c>
       <c r="D2" t="n">
-        <v>44.69156201624779</v>
+        <v>44.48486250819285</v>
       </c>
       <c r="E2" t="n">
-        <v>36.74773874837947</v>
+        <v>48.42757314807028</v>
       </c>
       <c r="F2" t="n">
-        <v>36.12566965103361</v>
+        <v>47.37164248431978</v>
       </c>
       <c r="G2" t="n">
-        <v>54.18227951753921</v>
+        <v>32.32249437264673</v>
       </c>
       <c r="H2" t="n">
-        <v>36.65471063727109</v>
+        <v>30.85166964924918</v>
       </c>
       <c r="I2" t="n">
-        <v>58.42294955663275</v>
+        <v>57.21197171643165</v>
       </c>
       <c r="J2" t="n">
-        <v>36.87151086453157</v>
+        <v>63.03256711243004</v>
       </c>
       <c r="K2" t="n">
-        <v>44.00874551730823</v>
+        <v>33.77991173083745</v>
       </c>
     </row>
   </sheetData>
@@ -1313,34 +1313,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.96190280387582</v>
+        <v>40.40226066975824</v>
       </c>
       <c r="C2" t="n">
-        <v>35.00518718708187</v>
+        <v>33.93863782835668</v>
       </c>
       <c r="D2" t="n">
-        <v>43.82085994750273</v>
+        <v>35.54499930329161</v>
       </c>
       <c r="E2" t="n">
-        <v>41.45988859005467</v>
+        <v>46.66405070437978</v>
       </c>
       <c r="F2" t="n">
-        <v>40.98889182368539</v>
+        <v>50.66365672066063</v>
       </c>
       <c r="G2" t="n">
-        <v>30.50049735499833</v>
+        <v>34.49233673338104</v>
       </c>
       <c r="H2" t="n">
-        <v>39.7707961566695</v>
+        <v>37.6970791111756</v>
       </c>
       <c r="I2" t="n">
-        <v>40.84410180567031</v>
+        <v>32.94781773082373</v>
       </c>
       <c r="J2" t="n">
-        <v>38.151529436796</v>
+        <v>37.68848387712523</v>
       </c>
       <c r="K2" t="n">
-        <v>45.3322220479571</v>
+        <v>43.86930942988788</v>
       </c>
     </row>
   </sheetData>
@@ -1419,34 +1419,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.69446731865425</v>
+        <v>49.64353694107789</v>
       </c>
       <c r="C2" t="n">
-        <v>43.40517342192121</v>
+        <v>44.21095318728227</v>
       </c>
       <c r="D2" t="n">
-        <v>40.3977985260758</v>
+        <v>34.04806810579638</v>
       </c>
       <c r="E2" t="n">
-        <v>38.08985833823472</v>
+        <v>36.86639637945191</v>
       </c>
       <c r="F2" t="n">
-        <v>30.84453396645617</v>
+        <v>47.3915934622591</v>
       </c>
       <c r="G2" t="n">
-        <v>39.55416162908715</v>
+        <v>52.52610552994792</v>
       </c>
       <c r="H2" t="n">
-        <v>25.048134627472</v>
+        <v>43.28043451550224</v>
       </c>
       <c r="I2" t="n">
-        <v>41.12394705977808</v>
+        <v>40.29488547364011</v>
       </c>
       <c r="J2" t="n">
-        <v>54.72450252025798</v>
+        <v>42.78498430859779</v>
       </c>
       <c r="K2" t="n">
-        <v>31.24589482821547</v>
+        <v>42.20000701770825</v>
       </c>
     </row>
   </sheetData>
@@ -1525,34 +1525,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.05302780717292</v>
+        <v>50.93347182393565</v>
       </c>
       <c r="C2" t="n">
-        <v>42.4147766481991</v>
+        <v>35.75598345766125</v>
       </c>
       <c r="D2" t="n">
-        <v>35.74139005600755</v>
+        <v>41.01165900873462</v>
       </c>
       <c r="E2" t="n">
-        <v>38.50197263710912</v>
+        <v>37.1589959187232</v>
       </c>
       <c r="F2" t="n">
-        <v>39.64013794736233</v>
+        <v>36.57968134923251</v>
       </c>
       <c r="G2" t="n">
-        <v>34.91618969114703</v>
+        <v>37.29207892399948</v>
       </c>
       <c r="H2" t="n">
-        <v>35.83564868741291</v>
+        <v>28.03161234253284</v>
       </c>
       <c r="I2" t="n">
-        <v>31.05150373919422</v>
+        <v>35.6157575747859</v>
       </c>
       <c r="J2" t="n">
-        <v>46.77464738798059</v>
+        <v>31.48378703649995</v>
       </c>
       <c r="K2" t="n">
-        <v>37.14068454956692</v>
+        <v>41.19740924695097</v>
       </c>
     </row>
   </sheetData>
@@ -1631,34 +1631,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.75239973143557</v>
+        <v>46.45023432680232</v>
       </c>
       <c r="C2" t="n">
-        <v>42.14718780005419</v>
+        <v>44.58228317455737</v>
       </c>
       <c r="D2" t="n">
-        <v>40.66917821824581</v>
+        <v>43.56509314728307</v>
       </c>
       <c r="E2" t="n">
-        <v>39.42052575083034</v>
+        <v>35.23161605874125</v>
       </c>
       <c r="F2" t="n">
-        <v>30.86615637823669</v>
+        <v>37.22899616728536</v>
       </c>
       <c r="G2" t="n">
-        <v>48.99387362716348</v>
+        <v>45.52627044027167</v>
       </c>
       <c r="H2" t="n">
-        <v>48.97376844795187</v>
+        <v>51.01058781560688</v>
       </c>
       <c r="I2" t="n">
-        <v>37.86190967773713</v>
+        <v>39.86319366258391</v>
       </c>
       <c r="J2" t="n">
-        <v>21.15390139315879</v>
+        <v>40.21036622836826</v>
       </c>
       <c r="K2" t="n">
-        <v>41.33318175806497</v>
+        <v>22.59306330220812</v>
       </c>
     </row>
   </sheetData>
@@ -1737,34 +1737,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.8656968851218</v>
+        <v>26.97620691784978</v>
       </c>
       <c r="C2" t="n">
-        <v>38.15991539214507</v>
+        <v>51.22414397015361</v>
       </c>
       <c r="D2" t="n">
-        <v>33.8192535335007</v>
+        <v>34.74270971112541</v>
       </c>
       <c r="E2" t="n">
-        <v>36.75190905661479</v>
+        <v>46.36567596370803</v>
       </c>
       <c r="F2" t="n">
-        <v>37.27137638900321</v>
+        <v>50.30884401442778</v>
       </c>
       <c r="G2" t="n">
-        <v>44.57990035064138</v>
+        <v>41.01511423935644</v>
       </c>
       <c r="H2" t="n">
-        <v>46.56825268170559</v>
+        <v>38.24692467879537</v>
       </c>
       <c r="I2" t="n">
-        <v>41.18496161803617</v>
+        <v>35.81139917537879</v>
       </c>
       <c r="J2" t="n">
-        <v>40.89327529033706</v>
+        <v>46.79599548303533</v>
       </c>
       <c r="K2" t="n">
-        <v>42.01395998779685</v>
+        <v>26.35542925653202</v>
       </c>
     </row>
   </sheetData>
@@ -1843,34 +1843,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.38094189065064</v>
+        <v>42.07460502733146</v>
       </c>
       <c r="C2" t="n">
-        <v>35.95887682871085</v>
+        <v>35.47706973101634</v>
       </c>
       <c r="D2" t="n">
-        <v>76.59213892637473</v>
+        <v>43.1170215334693</v>
       </c>
       <c r="E2" t="n">
-        <v>46.11466869853995</v>
+        <v>25.47663838072378</v>
       </c>
       <c r="F2" t="n">
-        <v>50.70736435153716</v>
+        <v>56.51114193087373</v>
       </c>
       <c r="G2" t="n">
-        <v>35.05456331358639</v>
+        <v>41.57518782247632</v>
       </c>
       <c r="H2" t="n">
-        <v>42.41896195021718</v>
+        <v>37.90127983310475</v>
       </c>
       <c r="I2" t="n">
-        <v>43.6314528429649</v>
+        <v>28.69762780951114</v>
       </c>
       <c r="J2" t="n">
-        <v>31.36972740476186</v>
+        <v>30.64162637625163</v>
       </c>
       <c r="K2" t="n">
-        <v>43.90532799993767</v>
+        <v>54.17465178429229</v>
       </c>
     </row>
   </sheetData>
@@ -1949,34 +1949,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.36138851684815</v>
+        <v>32.13045921266482</v>
       </c>
       <c r="C2" t="n">
-        <v>31.57289082854294</v>
+        <v>37.0455615997689</v>
       </c>
       <c r="D2" t="n">
-        <v>39.22008535843139</v>
+        <v>43.70445636387205</v>
       </c>
       <c r="E2" t="n">
-        <v>51.78977258675314</v>
+        <v>43.74280464795716</v>
       </c>
       <c r="F2" t="n">
-        <v>47.3763883659119</v>
+        <v>46.82165824909097</v>
       </c>
       <c r="G2" t="n">
-        <v>45.62412166172545</v>
+        <v>37.53198776943967</v>
       </c>
       <c r="H2" t="n">
-        <v>40.98851500928482</v>
+        <v>53.94583092444118</v>
       </c>
       <c r="I2" t="n">
-        <v>37.37908286071018</v>
+        <v>43.87067001562225</v>
       </c>
       <c r="J2" t="n">
-        <v>53.39476066988799</v>
+        <v>45.14753902842818</v>
       </c>
       <c r="K2" t="n">
-        <v>29.65524337227733</v>
+        <v>34.86817228467043</v>
       </c>
     </row>
   </sheetData>
@@ -2055,34 +2055,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.3364372375513</v>
+        <v>34.16955801486959</v>
       </c>
       <c r="C2" t="n">
-        <v>69.66414708321319</v>
+        <v>33.68681972143746</v>
       </c>
       <c r="D2" t="n">
-        <v>38.98422473848584</v>
+        <v>46.01388743053805</v>
       </c>
       <c r="E2" t="n">
-        <v>46.11601164469906</v>
+        <v>35.76231766995495</v>
       </c>
       <c r="F2" t="n">
-        <v>45.18815805297924</v>
+        <v>51.79447811595082</v>
       </c>
       <c r="G2" t="n">
-        <v>42.35412938566437</v>
+        <v>45.31822025989219</v>
       </c>
       <c r="H2" t="n">
-        <v>46.37733586615874</v>
+        <v>45.62026698483871</v>
       </c>
       <c r="I2" t="n">
-        <v>38.47392564690981</v>
+        <v>40.96213320481888</v>
       </c>
       <c r="J2" t="n">
-        <v>54.13194382302652</v>
+        <v>35.18874602604598</v>
       </c>
       <c r="K2" t="n">
-        <v>37.11099569803235</v>
+        <v>56.3473409282935</v>
       </c>
     </row>
   </sheetData>
@@ -2161,34 +2161,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.51643856977994</v>
+        <v>40.73970743537772</v>
       </c>
       <c r="C2" t="n">
-        <v>35.95988933554765</v>
+        <v>33.3701025908213</v>
       </c>
       <c r="D2" t="n">
-        <v>35.28063601910251</v>
+        <v>29.99710478977033</v>
       </c>
       <c r="E2" t="n">
-        <v>38.56698584874431</v>
+        <v>35.97643146415336</v>
       </c>
       <c r="F2" t="n">
-        <v>45.26372001385469</v>
+        <v>37.7733402848954</v>
       </c>
       <c r="G2" t="n">
-        <v>39.24371932088233</v>
+        <v>54.85899168719065</v>
       </c>
       <c r="H2" t="n">
-        <v>36.08024126297677</v>
+        <v>31.35778720812369</v>
       </c>
       <c r="I2" t="n">
-        <v>45.77976246871073</v>
+        <v>37.78639066962765</v>
       </c>
       <c r="J2" t="n">
-        <v>40.29177441427662</v>
+        <v>50.68699715345598</v>
       </c>
       <c r="K2" t="n">
-        <v>35.49033631701352</v>
+        <v>38.25673600963108</v>
       </c>
     </row>
   </sheetData>
@@ -2267,34 +2267,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.28152768111533</v>
+        <v>31.80280804247084</v>
       </c>
       <c r="C2" t="n">
-        <v>34.79479143339783</v>
+        <v>27.38204542965802</v>
       </c>
       <c r="D2" t="n">
-        <v>32.93019003136016</v>
+        <v>35.35474141255858</v>
       </c>
       <c r="E2" t="n">
-        <v>29.85582831035061</v>
+        <v>40.20050192786779</v>
       </c>
       <c r="F2" t="n">
-        <v>37.71742812902641</v>
+        <v>41.60183375212033</v>
       </c>
       <c r="G2" t="n">
-        <v>41.40108872704344</v>
+        <v>33.93218406349578</v>
       </c>
       <c r="H2" t="n">
-        <v>42.45889724318218</v>
+        <v>48.72667054142248</v>
       </c>
       <c r="I2" t="n">
-        <v>42.71434875290915</v>
+        <v>36.92873430571463</v>
       </c>
       <c r="J2" t="n">
-        <v>27.57077425792699</v>
+        <v>42.695912949313</v>
       </c>
       <c r="K2" t="n">
-        <v>33.69543820480887</v>
+        <v>49.13490413635948</v>
       </c>
     </row>
   </sheetData>
@@ -2373,34 +2373,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.14538727955615</v>
+        <v>33.05208841102104</v>
       </c>
       <c r="C2" t="n">
-        <v>43.87891956372281</v>
+        <v>35.78548927990241</v>
       </c>
       <c r="D2" t="n">
-        <v>40.6074463207006</v>
+        <v>31.70285796569258</v>
       </c>
       <c r="E2" t="n">
-        <v>30.83676910793844</v>
+        <v>43.29265842798586</v>
       </c>
       <c r="F2" t="n">
-        <v>44.00669156207945</v>
+        <v>44.67983585195687</v>
       </c>
       <c r="G2" t="n">
-        <v>34.00314795628655</v>
+        <v>35.47387560417287</v>
       </c>
       <c r="H2" t="n">
-        <v>36.8109779555072</v>
+        <v>47.05266256948081</v>
       </c>
       <c r="I2" t="n">
-        <v>30.63623006975062</v>
+        <v>30.17571083773352</v>
       </c>
       <c r="J2" t="n">
-        <v>41.65047837599344</v>
+        <v>38.34429849293087</v>
       </c>
       <c r="K2" t="n">
-        <v>33.80143045297955</v>
+        <v>26.34653305084527</v>
       </c>
     </row>
   </sheetData>
@@ -2479,34 +2479,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.21132937425244</v>
+        <v>42.58029191008541</v>
       </c>
       <c r="C2" t="n">
-        <v>47.99226986282593</v>
+        <v>36.76617382856871</v>
       </c>
       <c r="D2" t="n">
-        <v>33.01205693266837</v>
+        <v>42.31499190662817</v>
       </c>
       <c r="E2" t="n">
-        <v>45.3404843853527</v>
+        <v>33.4633669213746</v>
       </c>
       <c r="F2" t="n">
-        <v>35.08349503020838</v>
+        <v>45.2893275717307</v>
       </c>
       <c r="G2" t="n">
-        <v>54.48146738257134</v>
+        <v>42.4777428523372</v>
       </c>
       <c r="H2" t="n">
-        <v>30.3555817356219</v>
+        <v>33.19471205544873</v>
       </c>
       <c r="I2" t="n">
-        <v>41.12761778552626</v>
+        <v>39.39353575803526</v>
       </c>
       <c r="J2" t="n">
-        <v>36.86158557560906</v>
+        <v>35.40015889374805</v>
       </c>
       <c r="K2" t="n">
-        <v>33.88431758883913</v>
+        <v>42.38246418820881</v>
       </c>
     </row>
   </sheetData>
@@ -2585,34 +2585,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.08015846912004</v>
+        <v>50.70847406653667</v>
       </c>
       <c r="C2" t="n">
-        <v>58.05203351083689</v>
+        <v>43.81230386656838</v>
       </c>
       <c r="D2" t="n">
-        <v>35.50692826223989</v>
+        <v>45.11290672040904</v>
       </c>
       <c r="E2" t="n">
-        <v>42.80831973653194</v>
+        <v>51.75161494504387</v>
       </c>
       <c r="F2" t="n">
-        <v>34.59586084938198</v>
+        <v>49.31071035080238</v>
       </c>
       <c r="G2" t="n">
-        <v>40.78176298017159</v>
+        <v>31.8171861415668</v>
       </c>
       <c r="H2" t="n">
-        <v>46.33931180591279</v>
+        <v>32.19932393549931</v>
       </c>
       <c r="I2" t="n">
-        <v>47.07818589770542</v>
+        <v>40.29036020046139</v>
       </c>
       <c r="J2" t="n">
-        <v>57.15469901964867</v>
+        <v>50.2900215502075</v>
       </c>
       <c r="K2" t="n">
-        <v>38.76843801330312</v>
+        <v>43.76799110259428</v>
       </c>
     </row>
   </sheetData>
@@ -2691,34 +2691,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.66405864970912</v>
+        <v>33.77389446667507</v>
       </c>
       <c r="C2" t="n">
-        <v>41.43858021232078</v>
+        <v>41.25044427751882</v>
       </c>
       <c r="D2" t="n">
-        <v>41.60684497390381</v>
+        <v>38.20698784259065</v>
       </c>
       <c r="E2" t="n">
-        <v>39.59159212456593</v>
+        <v>48.04379175933571</v>
       </c>
       <c r="F2" t="n">
-        <v>30.46367437287212</v>
+        <v>36.42263311076469</v>
       </c>
       <c r="G2" t="n">
-        <v>41.75401309184839</v>
+        <v>37.24095929383308</v>
       </c>
       <c r="H2" t="n">
-        <v>29.66358084027068</v>
+        <v>37.07990854232575</v>
       </c>
       <c r="I2" t="n">
-        <v>46.01295844462282</v>
+        <v>48.20527080558043</v>
       </c>
       <c r="J2" t="n">
-        <v>36.74209819772706</v>
+        <v>33.91904253891816</v>
       </c>
       <c r="K2" t="n">
-        <v>44.96682454593576</v>
+        <v>29.12422445987088</v>
       </c>
     </row>
   </sheetData>
@@ -2797,34 +2797,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.30582615148162</v>
+        <v>47.36175920857941</v>
       </c>
       <c r="C2" t="n">
-        <v>46.00983485124639</v>
+        <v>36.11245820060865</v>
       </c>
       <c r="D2" t="n">
-        <v>42.28392124837336</v>
+        <v>41.80892424219833</v>
       </c>
       <c r="E2" t="n">
-        <v>40.70301132687626</v>
+        <v>38.10361768439782</v>
       </c>
       <c r="F2" t="n">
-        <v>40.48419264118704</v>
+        <v>55.00404022818945</v>
       </c>
       <c r="G2" t="n">
-        <v>51.0307079878902</v>
+        <v>33.57097927898278</v>
       </c>
       <c r="H2" t="n">
-        <v>39.67115103098888</v>
+        <v>44.38991704569496</v>
       </c>
       <c r="I2" t="n">
-        <v>39.59392647475514</v>
+        <v>49.22333878768842</v>
       </c>
       <c r="J2" t="n">
-        <v>24.99019991932162</v>
+        <v>57.22063073466213</v>
       </c>
       <c r="K2" t="n">
-        <v>43.20572769000955</v>
+        <v>35.3097737007979</v>
       </c>
     </row>
   </sheetData>
@@ -2903,34 +2903,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.4432846920833</v>
+        <v>32.61904513716598</v>
       </c>
       <c r="C2" t="n">
-        <v>42.04406541305859</v>
+        <v>33.6705130157228</v>
       </c>
       <c r="D2" t="n">
-        <v>53.45294709504076</v>
+        <v>48.15977106922453</v>
       </c>
       <c r="E2" t="n">
-        <v>33.99892801767614</v>
+        <v>42.13643743925883</v>
       </c>
       <c r="F2" t="n">
-        <v>47.69244076205038</v>
+        <v>39.37877566657392</v>
       </c>
       <c r="G2" t="n">
-        <v>38.36002593984065</v>
+        <v>33.24581620646983</v>
       </c>
       <c r="H2" t="n">
-        <v>53.54860290272238</v>
+        <v>52.55382505318993</v>
       </c>
       <c r="I2" t="n">
-        <v>36.62038309269077</v>
+        <v>33.90400343064431</v>
       </c>
       <c r="J2" t="n">
-        <v>34.59640483162769</v>
+        <v>40.98255010647119</v>
       </c>
       <c r="K2" t="n">
-        <v>42.97255915375913</v>
+        <v>35.49359055241307</v>
       </c>
     </row>
   </sheetData>
@@ -3009,34 +3009,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.39134430797246</v>
+        <v>35.71390907140409</v>
       </c>
       <c r="C2" t="n">
-        <v>34.69500524183071</v>
+        <v>53.53813580397915</v>
       </c>
       <c r="D2" t="n">
-        <v>42.41759970617491</v>
+        <v>39.39078534103634</v>
       </c>
       <c r="E2" t="n">
-        <v>38.59540514968582</v>
+        <v>30.1226580667862</v>
       </c>
       <c r="F2" t="n">
-        <v>41.59248200167075</v>
+        <v>39.59430504395938</v>
       </c>
       <c r="G2" t="n">
-        <v>38.29956976362497</v>
+        <v>26.10522898838907</v>
       </c>
       <c r="H2" t="n">
-        <v>29.7685055439005</v>
+        <v>44.02285198721886</v>
       </c>
       <c r="I2" t="n">
-        <v>42.54211370832778</v>
+        <v>49.07959699946989</v>
       </c>
       <c r="J2" t="n">
-        <v>57.33840272733519</v>
+        <v>42.25873493574563</v>
       </c>
       <c r="K2" t="n">
-        <v>36.55630115796792</v>
+        <v>39.22147670661276</v>
       </c>
     </row>
   </sheetData>
@@ -3115,34 +3115,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.27459357244825</v>
+        <v>44.47585251250133</v>
       </c>
       <c r="C2" t="n">
-        <v>46.40773684365599</v>
+        <v>23.80614835033256</v>
       </c>
       <c r="D2" t="n">
-        <v>49.28664596553355</v>
+        <v>42.41847193263498</v>
       </c>
       <c r="E2" t="n">
-        <v>35.55498949504376</v>
+        <v>26.04260906620736</v>
       </c>
       <c r="F2" t="n">
-        <v>44.6712796756356</v>
+        <v>42.01046708697654</v>
       </c>
       <c r="G2" t="n">
-        <v>46.07306473861878</v>
+        <v>42.571843191264</v>
       </c>
       <c r="H2" t="n">
-        <v>26.83188762708776</v>
+        <v>46.27663492117146</v>
       </c>
       <c r="I2" t="n">
-        <v>47.29427108001319</v>
+        <v>49.82552063914846</v>
       </c>
       <c r="J2" t="n">
-        <v>44.62835274630505</v>
+        <v>46.27755926558002</v>
       </c>
       <c r="K2" t="n">
-        <v>45.53503616197186</v>
+        <v>45.00168792151792</v>
       </c>
     </row>
   </sheetData>
@@ -3221,34 +3221,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.041831626368</v>
+        <v>47.30382576270173</v>
       </c>
       <c r="C2" t="n">
-        <v>37.72511189958442</v>
+        <v>36.07742922084312</v>
       </c>
       <c r="D2" t="n">
-        <v>59.43383703878504</v>
+        <v>38.7143658012318</v>
       </c>
       <c r="E2" t="n">
-        <v>42.82333011751896</v>
+        <v>42.03082178163994</v>
       </c>
       <c r="F2" t="n">
-        <v>41.7589773595468</v>
+        <v>50.57719278029118</v>
       </c>
       <c r="G2" t="n">
-        <v>42.29850411774094</v>
+        <v>43.53056769299518</v>
       </c>
       <c r="H2" t="n">
-        <v>41.84904598896173</v>
+        <v>41.32759458878441</v>
       </c>
       <c r="I2" t="n">
-        <v>47.75444785356656</v>
+        <v>40.87680572027634</v>
       </c>
       <c r="J2" t="n">
-        <v>51.53489845390569</v>
+        <v>44.01414968171147</v>
       </c>
       <c r="K2" t="n">
-        <v>39.07450397551237</v>
+        <v>54.66888191869032</v>
       </c>
     </row>
   </sheetData>
@@ -3327,34 +3327,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.59941392984104</v>
+        <v>36.75726402277333</v>
       </c>
       <c r="C2" t="n">
-        <v>36.16325513453874</v>
+        <v>54.14662258711635</v>
       </c>
       <c r="D2" t="n">
-        <v>53.40483432463724</v>
+        <v>39.7114609063508</v>
       </c>
       <c r="E2" t="n">
-        <v>41.81723565299838</v>
+        <v>45.62720785771901</v>
       </c>
       <c r="F2" t="n">
-        <v>25.67570015522721</v>
+        <v>34.72882596752087</v>
       </c>
       <c r="G2" t="n">
-        <v>42.01862880068384</v>
+        <v>43.51517976478326</v>
       </c>
       <c r="H2" t="n">
-        <v>44.13593472624927</v>
+        <v>53.38736509472228</v>
       </c>
       <c r="I2" t="n">
-        <v>39.19344096474602</v>
+        <v>25.0037506329218</v>
       </c>
       <c r="J2" t="n">
-        <v>39.68540811113443</v>
+        <v>41.5492454927582</v>
       </c>
       <c r="K2" t="n">
-        <v>37.39386698698717</v>
+        <v>44.99732640941694</v>
       </c>
     </row>
   </sheetData>
@@ -3433,34 +3433,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.60556935029523</v>
+        <v>29.80272797854187</v>
       </c>
       <c r="C2" t="n">
-        <v>45.75319627151122</v>
+        <v>50.94948936083339</v>
       </c>
       <c r="D2" t="n">
-        <v>58.67882209893488</v>
+        <v>50.03332735511025</v>
       </c>
       <c r="E2" t="n">
-        <v>37.54658271528959</v>
+        <v>41.73719779781288</v>
       </c>
       <c r="F2" t="n">
-        <v>39.12157778109263</v>
+        <v>42.53613024185367</v>
       </c>
       <c r="G2" t="n">
-        <v>39.7784092377222</v>
+        <v>40.13864501071649</v>
       </c>
       <c r="H2" t="n">
-        <v>38.18404778932091</v>
+        <v>46.04978683944653</v>
       </c>
       <c r="I2" t="n">
-        <v>44.86899844464816</v>
+        <v>36.08959627553029</v>
       </c>
       <c r="J2" t="n">
-        <v>30.07971887894899</v>
+        <v>41.5387508611796</v>
       </c>
       <c r="K2" t="n">
-        <v>37.48190780026776</v>
+        <v>57.40056450121188</v>
       </c>
     </row>
   </sheetData>
@@ -3539,34 +3539,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.37469407331012</v>
+        <v>41.98800067769824</v>
       </c>
       <c r="C2" t="n">
-        <v>34.89363134475398</v>
+        <v>41.37861208462154</v>
       </c>
       <c r="D2" t="n">
-        <v>44.81668003250033</v>
+        <v>35.22007122668241</v>
       </c>
       <c r="E2" t="n">
-        <v>30.9227644357994</v>
+        <v>29.23930046514567</v>
       </c>
       <c r="F2" t="n">
-        <v>54.37676181062734</v>
+        <v>37.09594656112732</v>
       </c>
       <c r="G2" t="n">
-        <v>32.12095321584997</v>
+        <v>38.90509187284484</v>
       </c>
       <c r="H2" t="n">
-        <v>38.63255632778954</v>
+        <v>35.52654903478152</v>
       </c>
       <c r="I2" t="n">
-        <v>43.0096313271743</v>
+        <v>37.81365998687782</v>
       </c>
       <c r="J2" t="n">
-        <v>37.23133200635491</v>
+        <v>50.41516556244049</v>
       </c>
       <c r="K2" t="n">
-        <v>35.85250486135634</v>
+        <v>30.81899485394101</v>
       </c>
     </row>
   </sheetData>
@@ -3645,34 +3645,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.3970972518286</v>
+        <v>35.20188010089843</v>
       </c>
       <c r="C2" t="n">
-        <v>23.0648226136857</v>
+        <v>36.42049643905392</v>
       </c>
       <c r="D2" t="n">
-        <v>43.138386990726</v>
+        <v>43.88253154075907</v>
       </c>
       <c r="E2" t="n">
-        <v>40.26612867130176</v>
+        <v>45.54115847452427</v>
       </c>
       <c r="F2" t="n">
-        <v>50.06276971452505</v>
+        <v>52.55504042541057</v>
       </c>
       <c r="G2" t="n">
-        <v>42.05604864564657</v>
+        <v>42.98081988989954</v>
       </c>
       <c r="H2" t="n">
-        <v>43.11639270661723</v>
+        <v>35.37496617107096</v>
       </c>
       <c r="I2" t="n">
-        <v>36.452078226761</v>
+        <v>36.95894589038976</v>
       </c>
       <c r="J2" t="n">
-        <v>47.48529286339389</v>
+        <v>51.92406310123715</v>
       </c>
       <c r="K2" t="n">
-        <v>42.6578063427973</v>
+        <v>34.18685607424593</v>
       </c>
     </row>
   </sheetData>
@@ -3751,34 +3751,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.60216574803148</v>
+        <v>46.80162037240715</v>
       </c>
       <c r="C2" t="n">
-        <v>50.34819305531707</v>
+        <v>45.80470843141832</v>
       </c>
       <c r="D2" t="n">
-        <v>45.85886867349353</v>
+        <v>34.82061497135966</v>
       </c>
       <c r="E2" t="n">
-        <v>35.33076322438576</v>
+        <v>41.2173562846838</v>
       </c>
       <c r="F2" t="n">
-        <v>31.40146627477172</v>
+        <v>33.39272821106442</v>
       </c>
       <c r="G2" t="n">
-        <v>37.42840775007297</v>
+        <v>43.96044239337867</v>
       </c>
       <c r="H2" t="n">
-        <v>38.85917862378212</v>
+        <v>35.71329353478352</v>
       </c>
       <c r="I2" t="n">
-        <v>46.17978703807136</v>
+        <v>30.36809199551633</v>
       </c>
       <c r="J2" t="n">
-        <v>38.40129986160353</v>
+        <v>30.97722119292651</v>
       </c>
       <c r="K2" t="n">
-        <v>27.83281719402581</v>
+        <v>51.82673514194846</v>
       </c>
     </row>
   </sheetData>
@@ -3857,34 +3857,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.97780174274913</v>
+        <v>34.66475550664873</v>
       </c>
       <c r="C2" t="n">
-        <v>33.35184379154211</v>
+        <v>37.61948881973557</v>
       </c>
       <c r="D2" t="n">
-        <v>55.26121397422741</v>
+        <v>36.1554552270179</v>
       </c>
       <c r="E2" t="n">
-        <v>38.24656443387723</v>
+        <v>38.53177954898662</v>
       </c>
       <c r="F2" t="n">
-        <v>34.36953257889387</v>
+        <v>45.39491244702416</v>
       </c>
       <c r="G2" t="n">
-        <v>36.24219914397569</v>
+        <v>43.49872285045834</v>
       </c>
       <c r="H2" t="n">
-        <v>46.80336173801292</v>
+        <v>58.60171623195939</v>
       </c>
       <c r="I2" t="n">
-        <v>38.71876969273853</v>
+        <v>28.71014608100121</v>
       </c>
       <c r="J2" t="n">
-        <v>42.31165353805251</v>
+        <v>45.98769968520831</v>
       </c>
       <c r="K2" t="n">
-        <v>40.23249921360885</v>
+        <v>46.89740925280762</v>
       </c>
     </row>
   </sheetData>
@@ -3963,34 +3963,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.94366461909141</v>
+        <v>39.27742883599997</v>
       </c>
       <c r="C2" t="n">
-        <v>63.60861614082948</v>
+        <v>41.43914826500342</v>
       </c>
       <c r="D2" t="n">
-        <v>39.53974636825364</v>
+        <v>38.60938388962517</v>
       </c>
       <c r="E2" t="n">
-        <v>36.56480148797788</v>
+        <v>36.08313146369031</v>
       </c>
       <c r="F2" t="n">
-        <v>36.66585751654836</v>
+        <v>38.67858941656505</v>
       </c>
       <c r="G2" t="n">
-        <v>37.25795142227616</v>
+        <v>22.56829502301234</v>
       </c>
       <c r="H2" t="n">
-        <v>39.88337603842724</v>
+        <v>52.07527302867529</v>
       </c>
       <c r="I2" t="n">
-        <v>39.74577997692616</v>
+        <v>35.8557651317091</v>
       </c>
       <c r="J2" t="n">
-        <v>40.8257292223343</v>
+        <v>45.02162017905925</v>
       </c>
       <c r="K2" t="n">
-        <v>32.67204050442664</v>
+        <v>44.8154381782542</v>
       </c>
     </row>
   </sheetData>
@@ -4069,34 +4069,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.81559318392547</v>
+        <v>34.5181221765256</v>
       </c>
       <c r="C2" t="n">
-        <v>37.46793570880222</v>
+        <v>33.43777351033079</v>
       </c>
       <c r="D2" t="n">
-        <v>46.83247130571698</v>
+        <v>36.02007088895827</v>
       </c>
       <c r="E2" t="n">
-        <v>37.49492138283091</v>
+        <v>38.90984781631667</v>
       </c>
       <c r="F2" t="n">
-        <v>29.00674694604233</v>
+        <v>27.40236312374617</v>
       </c>
       <c r="G2" t="n">
-        <v>32.64882680917136</v>
+        <v>34.59702859523264</v>
       </c>
       <c r="H2" t="n">
-        <v>36.39990561471745</v>
+        <v>47.55685604533166</v>
       </c>
       <c r="I2" t="n">
-        <v>47.96643687109717</v>
+        <v>39.90890844791048</v>
       </c>
       <c r="J2" t="n">
-        <v>50.71483432303316</v>
+        <v>43.31885341677646</v>
       </c>
       <c r="K2" t="n">
-        <v>42.25034785442599</v>
+        <v>44.0841136500645</v>
       </c>
     </row>
   </sheetData>
@@ -4175,34 +4175,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.9444045353105</v>
+        <v>29.52779237970335</v>
       </c>
       <c r="C2" t="n">
-        <v>35.95849359829242</v>
+        <v>42.15446845990002</v>
       </c>
       <c r="D2" t="n">
-        <v>46.41609076640468</v>
+        <v>37.12051360409135</v>
       </c>
       <c r="E2" t="n">
-        <v>35.5187792898156</v>
+        <v>60.33588821370268</v>
       </c>
       <c r="F2" t="n">
-        <v>42.91693290345488</v>
+        <v>35.35465933848212</v>
       </c>
       <c r="G2" t="n">
-        <v>38.55918209321569</v>
+        <v>35.56328236215366</v>
       </c>
       <c r="H2" t="n">
-        <v>37.72851939785502</v>
+        <v>33.30702404945357</v>
       </c>
       <c r="I2" t="n">
-        <v>51.27757665155377</v>
+        <v>55.54974884408233</v>
       </c>
       <c r="J2" t="n">
-        <v>61.48887738940106</v>
+        <v>43.68211197384853</v>
       </c>
       <c r="K2" t="n">
-        <v>38.58105239372116</v>
+        <v>30.40308337692808</v>
       </c>
     </row>
   </sheetData>
@@ -4281,34 +4281,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.02408772454488</v>
+        <v>39.65626125068405</v>
       </c>
       <c r="C2" t="n">
-        <v>48.95058617305332</v>
+        <v>45.63074196540773</v>
       </c>
       <c r="D2" t="n">
-        <v>43.06066623509849</v>
+        <v>43.77639450019177</v>
       </c>
       <c r="E2" t="n">
-        <v>40.67942446938972</v>
+        <v>41.10399825861794</v>
       </c>
       <c r="F2" t="n">
-        <v>45.33705934574912</v>
+        <v>31.62400369112984</v>
       </c>
       <c r="G2" t="n">
-        <v>41.7420940966264</v>
+        <v>55.35709667514531</v>
       </c>
       <c r="H2" t="n">
-        <v>45.40094597507562</v>
+        <v>45.86901161235007</v>
       </c>
       <c r="I2" t="n">
-        <v>43.91515395596976</v>
+        <v>44.84659554142877</v>
       </c>
       <c r="J2" t="n">
-        <v>30.78779798635157</v>
+        <v>51.1032547168081</v>
       </c>
       <c r="K2" t="n">
-        <v>41.10436736984568</v>
+        <v>37.25034136975769</v>
       </c>
     </row>
   </sheetData>
@@ -4387,34 +4387,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.65959360318512</v>
+        <v>39.17654793458436</v>
       </c>
       <c r="C2" t="n">
-        <v>48.03866812798667</v>
+        <v>37.37855553959743</v>
       </c>
       <c r="D2" t="n">
-        <v>35.66251453806868</v>
+        <v>53.48602070991529</v>
       </c>
       <c r="E2" t="n">
-        <v>50.26273924495072</v>
+        <v>36.9068557212344</v>
       </c>
       <c r="F2" t="n">
-        <v>37.65669737257904</v>
+        <v>31.90236898061685</v>
       </c>
       <c r="G2" t="n">
-        <v>41.72825019629802</v>
+        <v>59.23120147312274</v>
       </c>
       <c r="H2" t="n">
-        <v>35.01191204842281</v>
+        <v>45.77688289981458</v>
       </c>
       <c r="I2" t="n">
-        <v>57.74659468621144</v>
+        <v>56.68596633920264</v>
       </c>
       <c r="J2" t="n">
-        <v>50.179914931822</v>
+        <v>47.95572271809649</v>
       </c>
       <c r="K2" t="n">
-        <v>29.2390503399232</v>
+        <v>36.85294207840565</v>
       </c>
     </row>
   </sheetData>
@@ -4493,34 +4493,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.20442905702851</v>
+        <v>45.70292915591832</v>
       </c>
       <c r="C2" t="n">
-        <v>46.01182426204456</v>
+        <v>45.25343838903478</v>
       </c>
       <c r="D2" t="n">
-        <v>51.23906421702625</v>
+        <v>36.6910948044764</v>
       </c>
       <c r="E2" t="n">
-        <v>35.14748119131809</v>
+        <v>38.08574027545465</v>
       </c>
       <c r="F2" t="n">
-        <v>56.13609127866126</v>
+        <v>31.04987346947446</v>
       </c>
       <c r="G2" t="n">
-        <v>35.96143334264577</v>
+        <v>44.43668833976905</v>
       </c>
       <c r="H2" t="n">
-        <v>41.3041490244349</v>
+        <v>41.01864054799789</v>
       </c>
       <c r="I2" t="n">
-        <v>52.22767086594577</v>
+        <v>44.38456298101939</v>
       </c>
       <c r="J2" t="n">
-        <v>47.29904210824542</v>
+        <v>43.66332675216067</v>
       </c>
       <c r="K2" t="n">
-        <v>31.48827060974472</v>
+        <v>45.55917597825034</v>
       </c>
     </row>
   </sheetData>
@@ -4599,34 +4599,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.28800214748943</v>
+        <v>34.69469490115157</v>
       </c>
       <c r="C2" t="n">
-        <v>51.48310952152464</v>
+        <v>37.68681141396227</v>
       </c>
       <c r="D2" t="n">
-        <v>53.22256947710962</v>
+        <v>41.77790497442936</v>
       </c>
       <c r="E2" t="n">
-        <v>42.27287665963769</v>
+        <v>58.65115248975536</v>
       </c>
       <c r="F2" t="n">
-        <v>26.88157918645167</v>
+        <v>30.21274170971585</v>
       </c>
       <c r="G2" t="n">
-        <v>47.40484942763079</v>
+        <v>43.65964230977067</v>
       </c>
       <c r="H2" t="n">
-        <v>49.56533828503495</v>
+        <v>44.11012592852247</v>
       </c>
       <c r="I2" t="n">
-        <v>34.58135549387214</v>
+        <v>44.3434024809817</v>
       </c>
       <c r="J2" t="n">
-        <v>63.89920049434404</v>
+        <v>29.09938387725057</v>
       </c>
       <c r="K2" t="n">
-        <v>40.05967975012712</v>
+        <v>35.2386308087997</v>
       </c>
     </row>
   </sheetData>
@@ -4705,34 +4705,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.68359043205722</v>
+        <v>42.80505519722085</v>
       </c>
       <c r="C2" t="n">
-        <v>44.91336028128244</v>
+        <v>37.70358659965552</v>
       </c>
       <c r="D2" t="n">
-        <v>50.88294294279081</v>
+        <v>44.32108902063968</v>
       </c>
       <c r="E2" t="n">
-        <v>42.9728423018073</v>
+        <v>42.24436796027286</v>
       </c>
       <c r="F2" t="n">
-        <v>39.68078780085369</v>
+        <v>50.94712310691769</v>
       </c>
       <c r="G2" t="n">
-        <v>40.63879742810289</v>
+        <v>27.2135200253892</v>
       </c>
       <c r="H2" t="n">
-        <v>40.38899331388776</v>
+        <v>50.79890763578837</v>
       </c>
       <c r="I2" t="n">
-        <v>42.420063288897</v>
+        <v>40.35259298235615</v>
       </c>
       <c r="J2" t="n">
-        <v>44.04790166988528</v>
+        <v>44.6459238936923</v>
       </c>
       <c r="K2" t="n">
-        <v>34.41619236269001</v>
+        <v>34.8456478426173</v>
       </c>
     </row>
   </sheetData>
@@ -4811,34 +4811,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.68387822320269</v>
+        <v>37.05076872020719</v>
       </c>
       <c r="C2" t="n">
-        <v>25.96625774765581</v>
+        <v>43.26566257564593</v>
       </c>
       <c r="D2" t="n">
-        <v>28.33928533579439</v>
+        <v>54.15159983993639</v>
       </c>
       <c r="E2" t="n">
-        <v>47.00859108181086</v>
+        <v>48.12400276391451</v>
       </c>
       <c r="F2" t="n">
-        <v>49.83410003807825</v>
+        <v>37.24487479940383</v>
       </c>
       <c r="G2" t="n">
-        <v>43.38206117380087</v>
+        <v>27.19551524773145</v>
       </c>
       <c r="H2" t="n">
-        <v>55.46111090857085</v>
+        <v>53.41709302565957</v>
       </c>
       <c r="I2" t="n">
-        <v>51.47631267550393</v>
+        <v>38.74572672357913</v>
       </c>
       <c r="J2" t="n">
-        <v>46.57549117146398</v>
+        <v>37.58295544625231</v>
       </c>
       <c r="K2" t="n">
-        <v>43.20701640652046</v>
+        <v>37.00236402783524</v>
       </c>
     </row>
   </sheetData>
@@ -4917,34 +4917,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.03321246495522</v>
+        <v>50.53552788421815</v>
       </c>
       <c r="C2" t="n">
-        <v>32.20165074674073</v>
+        <v>38.63466573363817</v>
       </c>
       <c r="D2" t="n">
-        <v>53.74631757177938</v>
+        <v>39.44528269274897</v>
       </c>
       <c r="E2" t="n">
-        <v>37.28641506692831</v>
+        <v>57.53771749175974</v>
       </c>
       <c r="F2" t="n">
-        <v>40.75473271671171</v>
+        <v>30.63364326807127</v>
       </c>
       <c r="G2" t="n">
-        <v>47.40522566325099</v>
+        <v>41.32943126502003</v>
       </c>
       <c r="H2" t="n">
-        <v>34.68131123265211</v>
+        <v>35.05067448445332</v>
       </c>
       <c r="I2" t="n">
-        <v>42.87702483190222</v>
+        <v>39.02724466911013</v>
       </c>
       <c r="J2" t="n">
-        <v>41.02405337696719</v>
+        <v>40.07576871059024</v>
       </c>
       <c r="K2" t="n">
-        <v>40.41351900467238</v>
+        <v>34.24456570036298</v>
       </c>
     </row>
   </sheetData>
@@ -5023,34 +5023,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.3126767978379</v>
+        <v>55.80173405440532</v>
       </c>
       <c r="C2" t="n">
-        <v>45.65065743069254</v>
+        <v>43.45343933780971</v>
       </c>
       <c r="D2" t="n">
-        <v>45.70572757949197</v>
+        <v>30.45561589181359</v>
       </c>
       <c r="E2" t="n">
-        <v>38.42347091411131</v>
+        <v>32.6877137121872</v>
       </c>
       <c r="F2" t="n">
-        <v>39.94541996994084</v>
+        <v>35.80589150146699</v>
       </c>
       <c r="G2" t="n">
-        <v>34.25515271285986</v>
+        <v>42.02772801640191</v>
       </c>
       <c r="H2" t="n">
-        <v>35.91518771620123</v>
+        <v>46.63291668754922</v>
       </c>
       <c r="I2" t="n">
-        <v>50.98595089032501</v>
+        <v>46.60808486654869</v>
       </c>
       <c r="J2" t="n">
-        <v>33.3108498041138</v>
+        <v>33.51783752662431</v>
       </c>
       <c r="K2" t="n">
-        <v>33.03169793660899</v>
+        <v>35.43728095101845</v>
       </c>
     </row>
   </sheetData>
@@ -5129,34 +5129,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.53410800097075</v>
+        <v>31.86631436803382</v>
       </c>
       <c r="C2" t="n">
-        <v>22.49795350537205</v>
+        <v>39.90323861201563</v>
       </c>
       <c r="D2" t="n">
-        <v>43.99018558737787</v>
+        <v>48.2072708376086</v>
       </c>
       <c r="E2" t="n">
-        <v>36.51866957154274</v>
+        <v>52.47981217913998</v>
       </c>
       <c r="F2" t="n">
-        <v>48.46139861640118</v>
+        <v>30.26770883733339</v>
       </c>
       <c r="G2" t="n">
-        <v>19.24425826431786</v>
+        <v>40.01892370213663</v>
       </c>
       <c r="H2" t="n">
-        <v>65.30604387711152</v>
+        <v>40.97114270942208</v>
       </c>
       <c r="I2" t="n">
-        <v>37.90496065040449</v>
+        <v>87.2189685531457</v>
       </c>
       <c r="J2" t="n">
-        <v>42.34555921657438</v>
+        <v>37.51979542580398</v>
       </c>
       <c r="K2" t="n">
-        <v>37.62308082451639</v>
+        <v>32.76349995674585</v>
       </c>
     </row>
   </sheetData>
@@ -5235,34 +5235,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.83914691991873</v>
+        <v>45.38549609780686</v>
       </c>
       <c r="C2" t="n">
-        <v>60.04418187718925</v>
+        <v>41.30780947644168</v>
       </c>
       <c r="D2" t="n">
-        <v>44.55139384187495</v>
+        <v>33.92541916564952</v>
       </c>
       <c r="E2" t="n">
-        <v>41.7249765699119</v>
+        <v>49.55082444438448</v>
       </c>
       <c r="F2" t="n">
-        <v>42.53514496745294</v>
+        <v>37.64454026741568</v>
       </c>
       <c r="G2" t="n">
-        <v>39.19873999723963</v>
+        <v>36.69382087581005</v>
       </c>
       <c r="H2" t="n">
-        <v>30.75664199729811</v>
+        <v>44.63037195967772</v>
       </c>
       <c r="I2" t="n">
-        <v>47.9976629889812</v>
+        <v>42.72340054029409</v>
       </c>
       <c r="J2" t="n">
-        <v>51.06181876356319</v>
+        <v>40.89755562297375</v>
       </c>
       <c r="K2" t="n">
-        <v>30.99242800385322</v>
+        <v>36.68420117467335</v>
       </c>
     </row>
   </sheetData>
@@ -5341,34 +5341,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.489121585399</v>
+        <v>40.66853598493738</v>
       </c>
       <c r="C2" t="n">
-        <v>31.227845622436</v>
+        <v>30.47635100251204</v>
       </c>
       <c r="D2" t="n">
-        <v>43.88156013332647</v>
+        <v>58.4958059128784</v>
       </c>
       <c r="E2" t="n">
-        <v>38.79687281393677</v>
+        <v>48.86801300048007</v>
       </c>
       <c r="F2" t="n">
-        <v>45.85250494132532</v>
+        <v>24.5441328021548</v>
       </c>
       <c r="G2" t="n">
-        <v>26.96612057401233</v>
+        <v>35.76873588388083</v>
       </c>
       <c r="H2" t="n">
-        <v>48.34567986496468</v>
+        <v>33.10324427065272</v>
       </c>
       <c r="I2" t="n">
-        <v>32.78801070700683</v>
+        <v>38.71734534722066</v>
       </c>
       <c r="J2" t="n">
-        <v>44.47349865374132</v>
+        <v>27.70573710297736</v>
       </c>
       <c r="K2" t="n">
-        <v>41.14036557581816</v>
+        <v>43.30350680747012</v>
       </c>
     </row>
   </sheetData>
@@ -5447,34 +5447,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.51468121483273</v>
+        <v>47.44387711238274</v>
       </c>
       <c r="C2" t="n">
-        <v>48.57889473322364</v>
+        <v>37.42045151489278</v>
       </c>
       <c r="D2" t="n">
-        <v>50.15336380945701</v>
+        <v>48.81310585120038</v>
       </c>
       <c r="E2" t="n">
-        <v>30.13621888177487</v>
+        <v>48.88768401390119</v>
       </c>
       <c r="F2" t="n">
-        <v>52.71636047122972</v>
+        <v>33.05082770783759</v>
       </c>
       <c r="G2" t="n">
-        <v>36.41835254339701</v>
+        <v>33.79654494940704</v>
       </c>
       <c r="H2" t="n">
-        <v>53.41471232694666</v>
+        <v>59.89149086237198</v>
       </c>
       <c r="I2" t="n">
-        <v>63.53819620644124</v>
+        <v>45.75709499193413</v>
       </c>
       <c r="J2" t="n">
-        <v>47.27966154407858</v>
+        <v>31.01826134950525</v>
       </c>
       <c r="K2" t="n">
-        <v>44.99469375958445</v>
+        <v>40.04045266639684</v>
       </c>
     </row>
   </sheetData>
@@ -5553,34 +5553,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.9359592593719</v>
+        <v>38.75709762769878</v>
       </c>
       <c r="C2" t="n">
-        <v>47.84077393325367</v>
+        <v>38.44252510171944</v>
       </c>
       <c r="D2" t="n">
-        <v>43.41924212534758</v>
+        <v>43.75594582860889</v>
       </c>
       <c r="E2" t="n">
-        <v>32.09408582635464</v>
+        <v>32.3359812680104</v>
       </c>
       <c r="F2" t="n">
-        <v>42.78325401212985</v>
+        <v>40.16064725049503</v>
       </c>
       <c r="G2" t="n">
-        <v>26.2199518080208</v>
+        <v>35.20316546917324</v>
       </c>
       <c r="H2" t="n">
-        <v>42.5638307099798</v>
+        <v>52.08076628034522</v>
       </c>
       <c r="I2" t="n">
-        <v>49.70107538136848</v>
+        <v>41.52802018558839</v>
       </c>
       <c r="J2" t="n">
-        <v>35.53235236555624</v>
+        <v>40.66809709125958</v>
       </c>
       <c r="K2" t="n">
-        <v>54.20186946946583</v>
+        <v>48.81174251319207</v>
       </c>
     </row>
   </sheetData>
@@ -5659,34 +5659,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.65733015344617</v>
+        <v>24.00957448155331</v>
       </c>
       <c r="C2" t="n">
-        <v>34.03886966383601</v>
+        <v>35.44227879788966</v>
       </c>
       <c r="D2" t="n">
-        <v>30.44876243678883</v>
+        <v>52.08415960407256</v>
       </c>
       <c r="E2" t="n">
-        <v>38.06014870299938</v>
+        <v>46.14482112553917</v>
       </c>
       <c r="F2" t="n">
-        <v>48.14594402950292</v>
+        <v>32.07945476034348</v>
       </c>
       <c r="G2" t="n">
-        <v>44.70937294365372</v>
+        <v>47.18681548383486</v>
       </c>
       <c r="H2" t="n">
-        <v>31.37786538100256</v>
+        <v>29.95827886676141</v>
       </c>
       <c r="I2" t="n">
-        <v>28.39099029197426</v>
+        <v>35.07865103137571</v>
       </c>
       <c r="J2" t="n">
-        <v>25.12129830581712</v>
+        <v>32.40847311223252</v>
       </c>
       <c r="K2" t="n">
-        <v>38.62856750814427</v>
+        <v>33.05016312737878</v>
       </c>
     </row>
   </sheetData>
@@ -5765,34 +5765,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.2101812376976</v>
+        <v>49.61230217381587</v>
       </c>
       <c r="C2" t="n">
-        <v>50.77828383360706</v>
+        <v>41.67710005544317</v>
       </c>
       <c r="D2" t="n">
-        <v>35.42216405079245</v>
+        <v>44.31802913337167</v>
       </c>
       <c r="E2" t="n">
-        <v>37.69513308519301</v>
+        <v>48.32067925909328</v>
       </c>
       <c r="F2" t="n">
-        <v>47.80864405549774</v>
+        <v>38.99789298826037</v>
       </c>
       <c r="G2" t="n">
-        <v>42.88936451190832</v>
+        <v>56.2306123027384</v>
       </c>
       <c r="H2" t="n">
-        <v>47.10729978805899</v>
+        <v>43.5061722232697</v>
       </c>
       <c r="I2" t="n">
-        <v>51.29523048717454</v>
+        <v>36.94237135182716</v>
       </c>
       <c r="J2" t="n">
-        <v>34.58455183476206</v>
+        <v>39.30301728290623</v>
       </c>
       <c r="K2" t="n">
-        <v>33.23219069373488</v>
+        <v>41.32519411951345</v>
       </c>
     </row>
   </sheetData>
@@ -5871,34 +5871,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.51718786633761</v>
+        <v>31.03688931521669</v>
       </c>
       <c r="C2" t="n">
-        <v>39.76109844230138</v>
+        <v>45.89666364558908</v>
       </c>
       <c r="D2" t="n">
-        <v>24.074744362572</v>
+        <v>30.63424233207213</v>
       </c>
       <c r="E2" t="n">
-        <v>43.14284200533165</v>
+        <v>52.9883727250781</v>
       </c>
       <c r="F2" t="n">
-        <v>35.37428694994004</v>
+        <v>59.09738412411119</v>
       </c>
       <c r="G2" t="n">
-        <v>54.80513760838157</v>
+        <v>42.17683304042792</v>
       </c>
       <c r="H2" t="n">
-        <v>31.67893736999142</v>
+        <v>50.71173650647839</v>
       </c>
       <c r="I2" t="n">
-        <v>52.43024999315551</v>
+        <v>35.94203591022995</v>
       </c>
       <c r="J2" t="n">
-        <v>62.72454495868836</v>
+        <v>57.75940245774061</v>
       </c>
       <c r="K2" t="n">
-        <v>41.31268213135092</v>
+        <v>48.06289042724597</v>
       </c>
     </row>
   </sheetData>
@@ -5977,34 +5977,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.03942122735823</v>
+        <v>46.45309894894218</v>
       </c>
       <c r="C2" t="n">
-        <v>47.35576548908964</v>
+        <v>56.54095867724779</v>
       </c>
       <c r="D2" t="n">
-        <v>65.73735398722336</v>
+        <v>37.25621835453106</v>
       </c>
       <c r="E2" t="n">
-        <v>44.73420434659166</v>
+        <v>52.73268417621158</v>
       </c>
       <c r="F2" t="n">
-        <v>34.51320305539755</v>
+        <v>29.93371780298257</v>
       </c>
       <c r="G2" t="n">
-        <v>47.48332709462384</v>
+        <v>37.28343599079261</v>
       </c>
       <c r="H2" t="n">
-        <v>46.1985001786616</v>
+        <v>38.16961986580058</v>
       </c>
       <c r="I2" t="n">
-        <v>65.27079553578675</v>
+        <v>50.86230994249411</v>
       </c>
       <c r="J2" t="n">
-        <v>37.25621835453106</v>
+        <v>36.80766741578154</v>
       </c>
       <c r="K2" t="n">
-        <v>41.34559564941182</v>
+        <v>49.74272693355944</v>
       </c>
     </row>
   </sheetData>
@@ -6083,34 +6083,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.59528325039689</v>
+        <v>36.59239673275675</v>
       </c>
       <c r="C2" t="n">
-        <v>48.40930040681258</v>
+        <v>38.36168735943107</v>
       </c>
       <c r="D2" t="n">
-        <v>27.1979982198975</v>
+        <v>56.5664046719904</v>
       </c>
       <c r="E2" t="n">
-        <v>47.203640827596</v>
+        <v>39.06390407047851</v>
       </c>
       <c r="F2" t="n">
-        <v>37.66567375093705</v>
+        <v>25.8745328932995</v>
       </c>
       <c r="G2" t="n">
-        <v>38.38785235205749</v>
+        <v>46.36293198577678</v>
       </c>
       <c r="H2" t="n">
-        <v>38.13737838448135</v>
+        <v>62.31052034754568</v>
       </c>
       <c r="I2" t="n">
-        <v>53.53425998550551</v>
+        <v>42.22354489873427</v>
       </c>
       <c r="J2" t="n">
-        <v>50.52282412835543</v>
+        <v>33.39385728442217</v>
       </c>
       <c r="K2" t="n">
-        <v>42.51227909982296</v>
+        <v>40.51225738854989</v>
       </c>
     </row>
   </sheetData>
@@ -6189,34 +6189,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.81612815430926</v>
+        <v>32.07429386149815</v>
       </c>
       <c r="C2" t="n">
-        <v>45.53995795934265</v>
+        <v>45.3486820612667</v>
       </c>
       <c r="D2" t="n">
-        <v>50.98322923123533</v>
+        <v>47.81290819813742</v>
       </c>
       <c r="E2" t="n">
-        <v>47.79925561459756</v>
+        <v>44.31675619910523</v>
       </c>
       <c r="F2" t="n">
-        <v>32.71286840546576</v>
+        <v>49.67720763058525</v>
       </c>
       <c r="G2" t="n">
-        <v>46.59940836008778</v>
+        <v>35.52518299835496</v>
       </c>
       <c r="H2" t="n">
-        <v>40.03082734566733</v>
+        <v>37.1365179104513</v>
       </c>
       <c r="I2" t="n">
-        <v>36.51724282893634</v>
+        <v>36.33416148152313</v>
       </c>
       <c r="J2" t="n">
-        <v>33.10751395741786</v>
+        <v>32.57573437138259</v>
       </c>
       <c r="K2" t="n">
-        <v>31.0217782398925</v>
+        <v>34.592133397129</v>
       </c>
     </row>
   </sheetData>
@@ -6295,34 +6295,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.28308114145814</v>
+        <v>44.87775433375653</v>
       </c>
       <c r="C2" t="n">
-        <v>40.93943263661059</v>
+        <v>58.07345256436292</v>
       </c>
       <c r="D2" t="n">
-        <v>43.77930978465964</v>
+        <v>12.02275102472002</v>
       </c>
       <c r="E2" t="n">
-        <v>40.54812160039298</v>
+        <v>41.33134197761485</v>
       </c>
       <c r="F2" t="n">
-        <v>39.81274304840852</v>
+        <v>36.31365647792936</v>
       </c>
       <c r="G2" t="n">
-        <v>26.55268217736936</v>
+        <v>32.20789869618189</v>
       </c>
       <c r="H2" t="n">
-        <v>34.68662680148107</v>
+        <v>27.43798556962206</v>
       </c>
       <c r="I2" t="n">
-        <v>63.48202120488993</v>
+        <v>36.42800158178579</v>
       </c>
       <c r="J2" t="n">
-        <v>35.29484848465297</v>
+        <v>39.44769220935268</v>
       </c>
       <c r="K2" t="n">
-        <v>31.41696003828418</v>
+        <v>19.21407539213389</v>
       </c>
     </row>
   </sheetData>
@@ -6401,34 +6401,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.61845709743475</v>
+        <v>55.22918856957337</v>
       </c>
       <c r="C2" t="n">
-        <v>48.49349648514534</v>
+        <v>44.3418530751697</v>
       </c>
       <c r="D2" t="n">
-        <v>41.21777245125734</v>
+        <v>40.97946648382958</v>
       </c>
       <c r="E2" t="n">
-        <v>37.29391898701576</v>
+        <v>39.63188408742237</v>
       </c>
       <c r="F2" t="n">
-        <v>33.37920252081475</v>
+        <v>43.48154821871344</v>
       </c>
       <c r="G2" t="n">
-        <v>32.09738018826823</v>
+        <v>36.50545020601982</v>
       </c>
       <c r="H2" t="n">
-        <v>30.57689988034739</v>
+        <v>34.00695008954179</v>
       </c>
       <c r="I2" t="n">
-        <v>50.66520838141836</v>
+        <v>30.59208330237468</v>
       </c>
       <c r="J2" t="n">
-        <v>41.37538647869282</v>
+        <v>41.02508577566525</v>
       </c>
       <c r="K2" t="n">
-        <v>39.2145966173043</v>
+        <v>37.23910563938618</v>
       </c>
     </row>
   </sheetData>
@@ -6507,34 +6507,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50.14354915466971</v>
+        <v>40.86141990754147</v>
       </c>
       <c r="C2" t="n">
-        <v>38.93147215792845</v>
+        <v>48.66872369592966</v>
       </c>
       <c r="D2" t="n">
-        <v>33.45010240209781</v>
+        <v>66.67941651789707</v>
       </c>
       <c r="E2" t="n">
-        <v>39.24880846756693</v>
+        <v>47.104224615615</v>
       </c>
       <c r="F2" t="n">
-        <v>50.53015102110722</v>
+        <v>35.20585617573245</v>
       </c>
       <c r="G2" t="n">
-        <v>35.89942702252949</v>
+        <v>46.30797647976674</v>
       </c>
       <c r="H2" t="n">
-        <v>47.97622252745931</v>
+        <v>43.78265547274288</v>
       </c>
       <c r="I2" t="n">
-        <v>45.21975271032595</v>
+        <v>36.99554812639493</v>
       </c>
       <c r="J2" t="n">
-        <v>40.79504974352132</v>
+        <v>33.25872495698276</v>
       </c>
       <c r="K2" t="n">
-        <v>33.29948760736584</v>
+        <v>43.17135741694256</v>
       </c>
     </row>
   </sheetData>
@@ -6613,34 +6613,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.49418310731877</v>
+        <v>34.8363072611165</v>
       </c>
       <c r="C2" t="n">
-        <v>32.55845710370332</v>
+        <v>34.24873817084637</v>
       </c>
       <c r="D2" t="n">
-        <v>48.14935757139429</v>
+        <v>36.42951757366099</v>
       </c>
       <c r="E2" t="n">
-        <v>39.32434204434737</v>
+        <v>34.99435313740901</v>
       </c>
       <c r="F2" t="n">
-        <v>45.45771017857535</v>
+        <v>60.94285038105556</v>
       </c>
       <c r="G2" t="n">
-        <v>33.4964592027965</v>
+        <v>42.24047619155725</v>
       </c>
       <c r="H2" t="n">
-        <v>42.22565893913583</v>
+        <v>42.48202703541318</v>
       </c>
       <c r="I2" t="n">
-        <v>40.42325613559604</v>
+        <v>34.05280075874438</v>
       </c>
       <c r="J2" t="n">
-        <v>56.54273250903886</v>
+        <v>43.28071244242095</v>
       </c>
       <c r="K2" t="n">
-        <v>35.73607925615934</v>
+        <v>39.952329147895</v>
       </c>
     </row>
   </sheetData>
@@ -6719,34 +6719,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>48.00478296091822</v>
+        <v>53.02030728121687</v>
       </c>
       <c r="C2" t="n">
-        <v>65.34586470499404</v>
+        <v>42.6430123945463</v>
       </c>
       <c r="D2" t="n">
-        <v>47.82003471217764</v>
+        <v>42.3026131248362</v>
       </c>
       <c r="E2" t="n">
-        <v>46.2981036248386</v>
+        <v>48.56756703166565</v>
       </c>
       <c r="F2" t="n">
-        <v>34.7875144501886</v>
+        <v>40.34291067340183</v>
       </c>
       <c r="G2" t="n">
-        <v>37.57055789181707</v>
+        <v>46.71051856060137</v>
       </c>
       <c r="H2" t="n">
-        <v>34.81839839323781</v>
+        <v>43.37500457638687</v>
       </c>
       <c r="I2" t="n">
-        <v>39.59743886522589</v>
+        <v>22.43331205639407</v>
       </c>
       <c r="J2" t="n">
-        <v>30.0174064349475</v>
+        <v>39.09534762006491</v>
       </c>
       <c r="K2" t="n">
-        <v>60.02898067877656</v>
+        <v>47.22985523744155</v>
       </c>
     </row>
   </sheetData>
@@ -6825,34 +6825,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.84324675634711</v>
+        <v>32.35103182050958</v>
       </c>
       <c r="C2" t="n">
-        <v>59.4085172257811</v>
+        <v>51.73768741026257</v>
       </c>
       <c r="D2" t="n">
-        <v>57.43668234599112</v>
+        <v>38.88782917742618</v>
       </c>
       <c r="E2" t="n">
-        <v>38.42296250897238</v>
+        <v>56.05835314414472</v>
       </c>
       <c r="F2" t="n">
-        <v>50.37120428579951</v>
+        <v>36.09813905343869</v>
       </c>
       <c r="G2" t="n">
-        <v>31.31235942753319</v>
+        <v>58.87067512682032</v>
       </c>
       <c r="H2" t="n">
-        <v>44.63848103258707</v>
+        <v>24.43886662839803</v>
       </c>
       <c r="I2" t="n">
-        <v>34.56874291906593</v>
+        <v>38.42004366458765</v>
       </c>
       <c r="J2" t="n">
-        <v>49.00332331128518</v>
+        <v>31.6411899872142</v>
       </c>
       <c r="K2" t="n">
-        <v>33.92501420647769</v>
+        <v>35.96350385408191</v>
       </c>
     </row>
   </sheetData>
@@ -6931,34 +6931,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.17431787646705</v>
+        <v>36.04905583898364</v>
       </c>
       <c r="C2" t="n">
-        <v>41.48641571086637</v>
+        <v>36.86270511379573</v>
       </c>
       <c r="D2" t="n">
-        <v>47.89787860280087</v>
+        <v>36.42045117694128</v>
       </c>
       <c r="E2" t="n">
-        <v>41.10824012598169</v>
+        <v>38.77945900312916</v>
       </c>
       <c r="F2" t="n">
-        <v>44.33838287515213</v>
+        <v>37.51667520268533</v>
       </c>
       <c r="G2" t="n">
-        <v>34.92429327034327</v>
+        <v>40.30515323461675</v>
       </c>
       <c r="H2" t="n">
-        <v>36.121792261024</v>
+        <v>42.47870843674377</v>
       </c>
       <c r="I2" t="n">
-        <v>35.99248900232535</v>
+        <v>62.01723242145147</v>
       </c>
       <c r="J2" t="n">
-        <v>49.82521285650814</v>
+        <v>43.60442227036982</v>
       </c>
       <c r="K2" t="n">
-        <v>38.54649070294478</v>
+        <v>43.70684386272876</v>
       </c>
     </row>
   </sheetData>
@@ -7037,34 +7037,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.12289406288351</v>
+        <v>39.41459071764916</v>
       </c>
       <c r="C2" t="n">
-        <v>33.84923029177595</v>
+        <v>53.21933236403707</v>
       </c>
       <c r="D2" t="n">
-        <v>37.64267008961057</v>
+        <v>47.97435100814655</v>
       </c>
       <c r="E2" t="n">
-        <v>45.82547890143487</v>
+        <v>41.40185147883972</v>
       </c>
       <c r="F2" t="n">
-        <v>46.65773788852032</v>
+        <v>39.87440566319285</v>
       </c>
       <c r="G2" t="n">
-        <v>53.24694514879903</v>
+        <v>30.93090470457406</v>
       </c>
       <c r="H2" t="n">
-        <v>42.88456111689218</v>
+        <v>44.59416803494421</v>
       </c>
       <c r="I2" t="n">
-        <v>53.28737799167514</v>
+        <v>38.17527915794919</v>
       </c>
       <c r="J2" t="n">
-        <v>59.49334787128181</v>
+        <v>47.25077411268636</v>
       </c>
       <c r="K2" t="n">
-        <v>44.554441528166</v>
+        <v>21.62615302653732</v>
       </c>
     </row>
   </sheetData>
@@ -7143,34 +7143,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.45942031113784</v>
+        <v>43.09145053712555</v>
       </c>
       <c r="C2" t="n">
-        <v>41.97231062189991</v>
+        <v>44.59056207089601</v>
       </c>
       <c r="D2" t="n">
-        <v>53.51741779480888</v>
+        <v>49.95918081232801</v>
       </c>
       <c r="E2" t="n">
-        <v>37.75473660495433</v>
+        <v>42.29074012562396</v>
       </c>
       <c r="F2" t="n">
-        <v>33.00413841650351</v>
+        <v>47.08592490209627</v>
       </c>
       <c r="G2" t="n">
-        <v>44.32039244729049</v>
+        <v>34.30969358632315</v>
       </c>
       <c r="H2" t="n">
-        <v>45.89695112352996</v>
+        <v>36.97414205166603</v>
       </c>
       <c r="I2" t="n">
-        <v>40.52851343555395</v>
+        <v>32.22758394601008</v>
       </c>
       <c r="J2" t="n">
-        <v>41.97239617031457</v>
+        <v>31.50705973542255</v>
       </c>
       <c r="K2" t="n">
-        <v>28.24160210191471</v>
+        <v>50.93130299487752</v>
       </c>
     </row>
   </sheetData>
@@ -7249,34 +7249,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.61627388602309</v>
+        <v>32.92533675371501</v>
       </c>
       <c r="C2" t="n">
-        <v>64.59816120570552</v>
+        <v>47.07501465239793</v>
       </c>
       <c r="D2" t="n">
-        <v>47.06719180405955</v>
+        <v>60.59046158293221</v>
       </c>
       <c r="E2" t="n">
-        <v>38.88297686675578</v>
+        <v>54.66124933423868</v>
       </c>
       <c r="F2" t="n">
-        <v>49.08527969146832</v>
+        <v>44.32250364348472</v>
       </c>
       <c r="G2" t="n">
-        <v>30.89171707880984</v>
+        <v>33.28414706162769</v>
       </c>
       <c r="H2" t="n">
-        <v>23.03966727438988</v>
+        <v>44.05737951392093</v>
       </c>
       <c r="I2" t="n">
-        <v>36.4636717876427</v>
+        <v>27.10655751156512</v>
       </c>
       <c r="J2" t="n">
-        <v>39.51697891477293</v>
+        <v>27.22363031669123</v>
       </c>
       <c r="K2" t="n">
-        <v>34.54854135162073</v>
+        <v>46.06433489467351</v>
       </c>
     </row>
   </sheetData>
@@ -7355,34 +7355,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.06191921936216</v>
+        <v>23.19515511504483</v>
       </c>
       <c r="C2" t="n">
-        <v>59.18300945555581</v>
+        <v>32.71001916544157</v>
       </c>
       <c r="D2" t="n">
-        <v>52.72427041253693</v>
+        <v>39.29420143461078</v>
       </c>
       <c r="E2" t="n">
-        <v>40.8193537332529</v>
+        <v>45.94395663120162</v>
       </c>
       <c r="F2" t="n">
-        <v>37.78085397540097</v>
+        <v>42.2067449282571</v>
       </c>
       <c r="G2" t="n">
-        <v>42.50649156325423</v>
+        <v>39.84017710846223</v>
       </c>
       <c r="H2" t="n">
-        <v>58.9202196802611</v>
+        <v>42.74107055691761</v>
       </c>
       <c r="I2" t="n">
-        <v>55.09729378586854</v>
+        <v>38.26280724129343</v>
       </c>
       <c r="J2" t="n">
-        <v>35.56726940117049</v>
+        <v>39.5662194143338</v>
       </c>
       <c r="K2" t="n">
-        <v>26.82688138941845</v>
+        <v>52.17986145887908</v>
       </c>
     </row>
   </sheetData>
@@ -7461,34 +7461,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.53647279504922</v>
+        <v>46.35357394665724</v>
       </c>
       <c r="C2" t="n">
-        <v>37.24665219539538</v>
+        <v>48.78998660338274</v>
       </c>
       <c r="D2" t="n">
-        <v>46.87385300457473</v>
+        <v>51.57379674140793</v>
       </c>
       <c r="E2" t="n">
-        <v>41.09944447393977</v>
+        <v>41.61071344438628</v>
       </c>
       <c r="F2" t="n">
-        <v>51.86925984955408</v>
+        <v>38.60828218806606</v>
       </c>
       <c r="G2" t="n">
-        <v>40.31703255153604</v>
+        <v>39.74881579349653</v>
       </c>
       <c r="H2" t="n">
-        <v>40.76504530777737</v>
+        <v>31.87753762663511</v>
       </c>
       <c r="I2" t="n">
-        <v>39.31277192292765</v>
+        <v>44.26177805394803</v>
       </c>
       <c r="J2" t="n">
-        <v>43.20800110935666</v>
+        <v>41.73264811805324</v>
       </c>
       <c r="K2" t="n">
-        <v>38.88896753624498</v>
+        <v>48.77949653469064</v>
       </c>
     </row>
   </sheetData>
@@ -7567,34 +7567,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.94013103877104</v>
+        <v>48.32321499817544</v>
       </c>
       <c r="C2" t="n">
-        <v>49.31722988917388</v>
+        <v>40.75325540988866</v>
       </c>
       <c r="D2" t="n">
-        <v>46.1555067663084</v>
+        <v>49.705125914375</v>
       </c>
       <c r="E2" t="n">
-        <v>38.27950226855781</v>
+        <v>36.02378348312958</v>
       </c>
       <c r="F2" t="n">
-        <v>47.65517238289205</v>
+        <v>46.25267356115364</v>
       </c>
       <c r="G2" t="n">
-        <v>36.83149041021242</v>
+        <v>37.87970175565353</v>
       </c>
       <c r="H2" t="n">
-        <v>38.70003254060835</v>
+        <v>37.88439847284344</v>
       </c>
       <c r="I2" t="n">
-        <v>41.78374638653909</v>
+        <v>54.92728065397148</v>
       </c>
       <c r="J2" t="n">
-        <v>56.16325346503923</v>
+        <v>43.28880252991639</v>
       </c>
       <c r="K2" t="n">
-        <v>43.94164963314444</v>
+        <v>40.28622842789023</v>
       </c>
     </row>
   </sheetData>
@@ -7673,34 +7673,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.66534741937669</v>
+        <v>42.37968560647555</v>
       </c>
       <c r="C2" t="n">
-        <v>41.38816424545554</v>
+        <v>49.92628570228721</v>
       </c>
       <c r="D2" t="n">
-        <v>47.23085120379366</v>
+        <v>33.77473953352683</v>
       </c>
       <c r="E2" t="n">
-        <v>47.7877329644783</v>
+        <v>30.01797934274861</v>
       </c>
       <c r="F2" t="n">
-        <v>43.01728760033144</v>
+        <v>42.88972700986216</v>
       </c>
       <c r="G2" t="n">
-        <v>41.90514109112335</v>
+        <v>31.88940887552844</v>
       </c>
       <c r="H2" t="n">
-        <v>29.43718012248685</v>
+        <v>46.04742201527993</v>
       </c>
       <c r="I2" t="n">
-        <v>41.79686659672939</v>
+        <v>44.58541543177835</v>
       </c>
       <c r="J2" t="n">
-        <v>52.86494680360538</v>
+        <v>47.37895553657327</v>
       </c>
       <c r="K2" t="n">
-        <v>42.16217156843359</v>
+        <v>44.98329682275478</v>
       </c>
     </row>
   </sheetData>
@@ -7779,34 +7779,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.68847023268952</v>
+        <v>38.73913112929698</v>
       </c>
       <c r="C2" t="n">
-        <v>47.84176353411556</v>
+        <v>49.71094319306505</v>
       </c>
       <c r="D2" t="n">
-        <v>40.48122718108788</v>
+        <v>26.19629428815284</v>
       </c>
       <c r="E2" t="n">
-        <v>35.0556723233606</v>
+        <v>29.15870468671938</v>
       </c>
       <c r="F2" t="n">
-        <v>47.01139947852535</v>
+        <v>45.64948359006539</v>
       </c>
       <c r="G2" t="n">
-        <v>33.72838050503471</v>
+        <v>39.21935982132701</v>
       </c>
       <c r="H2" t="n">
-        <v>43.05845496067672</v>
+        <v>40.04035580857041</v>
       </c>
       <c r="I2" t="n">
-        <v>34.78156553225772</v>
+        <v>35.09419345362161</v>
       </c>
       <c r="J2" t="n">
-        <v>60.06130043475368</v>
+        <v>38.55930480367332</v>
       </c>
       <c r="K2" t="n">
-        <v>34.48906088001018</v>
+        <v>50.6070712401276</v>
       </c>
     </row>
   </sheetData>
@@ -7885,34 +7885,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.6167843617341</v>
+        <v>42.86160753954142</v>
       </c>
       <c r="C2" t="n">
-        <v>53.69131274387128</v>
+        <v>26.60336742569431</v>
       </c>
       <c r="D2" t="n">
+        <v>43.77186892022279</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.20159171266015</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.38825468007136</v>
+      </c>
+      <c r="G2" t="n">
+        <v>49.22249479390771</v>
+      </c>
+      <c r="H2" t="n">
+        <v>49.69683415408358</v>
+      </c>
+      <c r="I2" t="n">
+        <v>35.93329470081655</v>
+      </c>
+      <c r="J2" t="n">
+        <v>46.04266066816</v>
+      </c>
+      <c r="K2" t="n">
         <v>29.41224163101645</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.06411901030477</v>
-      </c>
-      <c r="F2" t="n">
-        <v>45.84729617327413</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.77342422567444</v>
-      </c>
-      <c r="H2" t="n">
-        <v>44.37750323504471</v>
-      </c>
-      <c r="I2" t="n">
-        <v>59.01601484940686</v>
-      </c>
-      <c r="J2" t="n">
-        <v>31.32635797439169</v>
-      </c>
-      <c r="K2" t="n">
-        <v>34.46588474155633</v>
       </c>
     </row>
   </sheetData>
@@ -7991,34 +7991,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.38734008585485</v>
+        <v>55.45848206706495</v>
       </c>
       <c r="C2" t="n">
-        <v>35.47054095554675</v>
+        <v>33.59068062970609</v>
       </c>
       <c r="D2" t="n">
-        <v>42.02273297063513</v>
+        <v>35.76829628848439</v>
       </c>
       <c r="E2" t="n">
-        <v>30.01244259520633</v>
+        <v>37.85945837044683</v>
       </c>
       <c r="F2" t="n">
-        <v>47.1351492102168</v>
+        <v>37.0425847215075</v>
       </c>
       <c r="G2" t="n">
-        <v>51.48987411017033</v>
+        <v>38.04293863426781</v>
       </c>
       <c r="H2" t="n">
-        <v>42.1666240745515</v>
+        <v>40.04612209783779</v>
       </c>
       <c r="I2" t="n">
-        <v>21.18904339642429</v>
+        <v>53.12547847651718</v>
       </c>
       <c r="J2" t="n">
-        <v>40.29591244306639</v>
+        <v>34.53908330650228</v>
       </c>
       <c r="K2" t="n">
-        <v>31.08761636103528</v>
+        <v>32.15965157310105</v>
       </c>
     </row>
   </sheetData>
@@ -8097,34 +8097,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.2686920464689</v>
+        <v>35.34642023496993</v>
       </c>
       <c r="C2" t="n">
-        <v>34.10769630547774</v>
+        <v>44.99740150235453</v>
       </c>
       <c r="D2" t="n">
-        <v>40.53967497598212</v>
+        <v>41.94564360538817</v>
       </c>
       <c r="E2" t="n">
-        <v>50.29009105457342</v>
+        <v>42.36018341669419</v>
       </c>
       <c r="F2" t="n">
-        <v>38.53650142495271</v>
+        <v>42.48359891846528</v>
       </c>
       <c r="G2" t="n">
-        <v>40.36702169504328</v>
+        <v>43.06073318993955</v>
       </c>
       <c r="H2" t="n">
-        <v>38.20548528105822</v>
+        <v>31.11019455247558</v>
       </c>
       <c r="I2" t="n">
-        <v>42.46073992123331</v>
+        <v>54.99867577337749</v>
       </c>
       <c r="J2" t="n">
-        <v>51.7196482380816</v>
+        <v>48.37445925598053</v>
       </c>
       <c r="K2" t="n">
-        <v>37.08311022482889</v>
+        <v>51.5771887869906</v>
       </c>
     </row>
   </sheetData>
@@ -8203,34 +8203,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.01430567622045</v>
+        <v>52.8748821079281</v>
       </c>
       <c r="C2" t="n">
-        <v>41.59791831093496</v>
+        <v>35.84924136013471</v>
       </c>
       <c r="D2" t="n">
-        <v>57.91312828093512</v>
+        <v>44.97779068697646</v>
       </c>
       <c r="E2" t="n">
-        <v>33.81630990482692</v>
+        <v>42.34785736954248</v>
       </c>
       <c r="F2" t="n">
-        <v>63.69325654255525</v>
+        <v>30.16804919801722</v>
       </c>
       <c r="G2" t="n">
-        <v>34.78225736660765</v>
+        <v>51.98771751374185</v>
       </c>
       <c r="H2" t="n">
-        <v>41.94930016402863</v>
+        <v>51.25618922895423</v>
       </c>
       <c r="I2" t="n">
-        <v>41.4754635006114</v>
+        <v>40.37794206236384</v>
       </c>
       <c r="J2" t="n">
-        <v>45.48168752187949</v>
+        <v>39.64373011602611</v>
       </c>
       <c r="K2" t="n">
-        <v>39.91891670422844</v>
+        <v>28.45792670413898</v>
       </c>
     </row>
   </sheetData>
@@ -8309,34 +8309,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.60616052834721</v>
+        <v>46.36013979758452</v>
       </c>
       <c r="C2" t="n">
-        <v>43.11194777238855</v>
+        <v>42.38590176794026</v>
       </c>
       <c r="D2" t="n">
-        <v>28.48116057039922</v>
+        <v>33.90230636225978</v>
       </c>
       <c r="E2" t="n">
-        <v>52.99834019235604</v>
+        <v>43.78885976052663</v>
       </c>
       <c r="F2" t="n">
-        <v>67.3791380992716</v>
+        <v>41.6618782885226</v>
       </c>
       <c r="G2" t="n">
-        <v>33.80576951528721</v>
+        <v>42.46009863934005</v>
       </c>
       <c r="H2" t="n">
-        <v>42.8333219693306</v>
+        <v>44.99398152506799</v>
       </c>
       <c r="I2" t="n">
-        <v>43.75882323126147</v>
+        <v>49.93956619152031</v>
       </c>
       <c r="J2" t="n">
-        <v>48.21566510897154</v>
+        <v>41.42985425698779</v>
       </c>
       <c r="K2" t="n">
-        <v>40.9661194414704</v>
+        <v>49.60856868668361</v>
       </c>
     </row>
   </sheetData>
@@ -8415,34 +8415,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.37047482966895</v>
+        <v>35.79657274896906</v>
       </c>
       <c r="C2" t="n">
-        <v>37.60361733671694</v>
+        <v>33.57493516267528</v>
       </c>
       <c r="D2" t="n">
-        <v>43.45258007748435</v>
+        <v>47.60438006711291</v>
       </c>
       <c r="E2" t="n">
-        <v>34.59385061297051</v>
+        <v>40.86009576001536</v>
       </c>
       <c r="F2" t="n">
-        <v>35.33746169257876</v>
+        <v>26.54441890860878</v>
       </c>
       <c r="G2" t="n">
-        <v>47.03247325123534</v>
+        <v>43.47482026460143</v>
       </c>
       <c r="H2" t="n">
-        <v>37.65565114910267</v>
+        <v>37.04460687475841</v>
       </c>
       <c r="I2" t="n">
-        <v>49.51865617134571</v>
+        <v>38.81282905032445</v>
       </c>
       <c r="J2" t="n">
-        <v>35.21338890088337</v>
+        <v>40.49789177259076</v>
       </c>
       <c r="K2" t="n">
-        <v>36.92504567253557</v>
+        <v>37.40024551789979</v>
       </c>
     </row>
   </sheetData>
@@ -8521,34 +8521,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.04470300311805</v>
+        <v>41.99572968587805</v>
       </c>
       <c r="C2" t="n">
-        <v>40.49241901690979</v>
+        <v>55.0340411216272</v>
       </c>
       <c r="D2" t="n">
-        <v>45.80458709564334</v>
+        <v>50.12902035172632</v>
       </c>
       <c r="E2" t="n">
-        <v>32.00886725175104</v>
+        <v>43.88286984906065</v>
       </c>
       <c r="F2" t="n">
-        <v>37.9495428314989</v>
+        <v>48.26068251883262</v>
       </c>
       <c r="G2" t="n">
-        <v>41.95143745453814</v>
+        <v>34.82758490941499</v>
       </c>
       <c r="H2" t="n">
-        <v>46.78915513316423</v>
+        <v>30.59314983081621</v>
       </c>
       <c r="I2" t="n">
-        <v>44.02252355623143</v>
+        <v>45.17099336313316</v>
       </c>
       <c r="J2" t="n">
-        <v>51.58143109264447</v>
+        <v>38.02098335811567</v>
       </c>
       <c r="K2" t="n">
-        <v>40.85623510420945</v>
+        <v>30.24665779385695</v>
       </c>
     </row>
   </sheetData>
@@ -8627,34 +8627,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.05570595333808</v>
+        <v>32.67121740005531</v>
       </c>
       <c r="C2" t="n">
-        <v>44.9895618464133</v>
+        <v>52.4177513252499</v>
       </c>
       <c r="D2" t="n">
-        <v>39.26847902130454</v>
+        <v>38.82805772954442</v>
       </c>
       <c r="E2" t="n">
-        <v>48.34643887170873</v>
+        <v>45.26055664460348</v>
       </c>
       <c r="F2" t="n">
-        <v>44.58988211373449</v>
+        <v>51.66413763963325</v>
       </c>
       <c r="G2" t="n">
-        <v>45.64100833224852</v>
+        <v>45.94958432945006</v>
       </c>
       <c r="H2" t="n">
-        <v>40.4277741467404</v>
+        <v>46.39058582069432</v>
       </c>
       <c r="I2" t="n">
-        <v>37.38423260522793</v>
+        <v>43.80655977755541</v>
       </c>
       <c r="J2" t="n">
-        <v>49.58277149582632</v>
+        <v>50.08806302784473</v>
       </c>
       <c r="K2" t="n">
-        <v>36.84082778414831</v>
+        <v>44.2259394694486</v>
       </c>
     </row>
   </sheetData>
@@ -8733,34 +8733,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.0888259313184</v>
+        <v>43.9067910308357</v>
       </c>
       <c r="C2" t="n">
-        <v>39.87499344151087</v>
+        <v>44.17734508020798</v>
       </c>
       <c r="D2" t="n">
-        <v>49.23786931779281</v>
+        <v>35.01124551274401</v>
       </c>
       <c r="E2" t="n">
-        <v>39.83936702605317</v>
+        <v>38.72302235459818</v>
       </c>
       <c r="F2" t="n">
-        <v>42.26191514760055</v>
+        <v>39.80857888392033</v>
       </c>
       <c r="G2" t="n">
-        <v>53.98774165634982</v>
+        <v>39.33497686237114</v>
       </c>
       <c r="H2" t="n">
-        <v>57.99820552551724</v>
+        <v>36.35545912661914</v>
       </c>
       <c r="I2" t="n">
-        <v>40.40319668568846</v>
+        <v>50.54316541564542</v>
       </c>
       <c r="J2" t="n">
-        <v>44.89254290424486</v>
+        <v>51.31514577652344</v>
       </c>
       <c r="K2" t="n">
-        <v>34.74726112096625</v>
+        <v>45.04493076835917</v>
       </c>
     </row>
   </sheetData>
@@ -8839,34 +8839,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.70050667593434</v>
+        <v>41.12225185007123</v>
       </c>
       <c r="C2" t="n">
-        <v>36.36387409750906</v>
+        <v>40.15373303909996</v>
       </c>
       <c r="D2" t="n">
-        <v>49.22953442295842</v>
+        <v>33.25677734544122</v>
       </c>
       <c r="E2" t="n">
-        <v>28.92394120925749</v>
+        <v>46.35555546724409</v>
       </c>
       <c r="F2" t="n">
-        <v>36.41385905527518</v>
+        <v>43.98879568287744</v>
       </c>
       <c r="G2" t="n">
-        <v>37.03979012494769</v>
+        <v>33.37327451503599</v>
       </c>
       <c r="H2" t="n">
-        <v>43.40695750116128</v>
+        <v>45.78170111743219</v>
       </c>
       <c r="I2" t="n">
-        <v>47.80933443332571</v>
+        <v>57.51380700872294</v>
       </c>
       <c r="J2" t="n">
-        <v>53.74458634154777</v>
+        <v>50.81856890190167</v>
       </c>
       <c r="K2" t="n">
-        <v>41.62403571050145</v>
+        <v>37.32116671198887</v>
       </c>
     </row>
   </sheetData>
@@ -8945,34 +8945,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.16747864522078</v>
+        <v>50.90099963471025</v>
       </c>
       <c r="C2" t="n">
-        <v>25.45534816307712</v>
+        <v>49.23685387701571</v>
       </c>
       <c r="D2" t="n">
-        <v>58.7756099597208</v>
+        <v>31.63861033326786</v>
       </c>
       <c r="E2" t="n">
-        <v>39.07025165626197</v>
+        <v>30.09996616774669</v>
       </c>
       <c r="F2" t="n">
-        <v>49.83958625893644</v>
+        <v>32.81686397124536</v>
       </c>
       <c r="G2" t="n">
-        <v>42.69193701880986</v>
+        <v>49.19874994158165</v>
       </c>
       <c r="H2" t="n">
-        <v>35.24949522190221</v>
+        <v>39.90305385863496</v>
       </c>
       <c r="I2" t="n">
-        <v>63.48023729392577</v>
+        <v>38.88872601302403</v>
       </c>
       <c r="J2" t="n">
-        <v>38.20359770001891</v>
+        <v>35.35101256418555</v>
       </c>
       <c r="K2" t="n">
-        <v>25.40302023225865</v>
+        <v>34.57086230284349</v>
       </c>
     </row>
   </sheetData>
@@ -9051,34 +9051,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.88136169062179</v>
+        <v>48.19370639897797</v>
       </c>
       <c r="C2" t="n">
-        <v>43.23152171826887</v>
+        <v>43.04427178759137</v>
       </c>
       <c r="D2" t="n">
-        <v>39.08805891010303</v>
+        <v>34.69926627193546</v>
       </c>
       <c r="E2" t="n">
-        <v>44.54265179960795</v>
+        <v>36.14707552339951</v>
       </c>
       <c r="F2" t="n">
-        <v>24.59047039928443</v>
+        <v>32.4611315407644</v>
       </c>
       <c r="G2" t="n">
-        <v>35.57552119283457</v>
+        <v>38.59499372605755</v>
       </c>
       <c r="H2" t="n">
-        <v>27.69090339701203</v>
+        <v>46.09992934333774</v>
       </c>
       <c r="I2" t="n">
-        <v>31.89908051998528</v>
+        <v>51.3326301420806</v>
       </c>
       <c r="J2" t="n">
-        <v>51.20212444088699</v>
+        <v>26.1995857270143</v>
       </c>
       <c r="K2" t="n">
-        <v>36.60317236421608</v>
+        <v>36.96498616657937</v>
       </c>
     </row>
   </sheetData>
@@ -9157,34 +9157,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.41716184652805</v>
+        <v>35.81249450013768</v>
       </c>
       <c r="C2" t="n">
-        <v>37.23496124984623</v>
+        <v>33.53552772823103</v>
       </c>
       <c r="D2" t="n">
-        <v>45.79886062926415</v>
+        <v>50.57390234028563</v>
       </c>
       <c r="E2" t="n">
-        <v>37.2628801274447</v>
+        <v>36.97606707702401</v>
       </c>
       <c r="F2" t="n">
-        <v>29.13883832133305</v>
+        <v>45.4145206523303</v>
       </c>
       <c r="G2" t="n">
-        <v>52.66874018171474</v>
+        <v>24.08523805621218</v>
       </c>
       <c r="H2" t="n">
-        <v>41.9705340603848</v>
+        <v>37.26131710139358</v>
       </c>
       <c r="I2" t="n">
-        <v>37.62699626109913</v>
+        <v>33.76726190459281</v>
       </c>
       <c r="J2" t="n">
-        <v>37.88523884998172</v>
+        <v>53.66686346878338</v>
       </c>
       <c r="K2" t="n">
-        <v>45.67180738974077</v>
+        <v>54.30691199182742</v>
       </c>
     </row>
   </sheetData>
@@ -9263,34 +9263,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.62242774638835</v>
+        <v>39.65021905963616</v>
       </c>
       <c r="C2" t="n">
-        <v>38.9011373536425</v>
+        <v>35.05526357994045</v>
       </c>
       <c r="D2" t="n">
-        <v>53.43343594898536</v>
+        <v>41.20188931454533</v>
       </c>
       <c r="E2" t="n">
-        <v>35.20532420620081</v>
+        <v>38.56874693083513</v>
       </c>
       <c r="F2" t="n">
-        <v>42.53883176225502</v>
+        <v>37.16306301279993</v>
       </c>
       <c r="G2" t="n">
-        <v>46.01160082488963</v>
+        <v>49.10208628592994</v>
       </c>
       <c r="H2" t="n">
-        <v>52.90139969305586</v>
+        <v>43.56550695171989</v>
       </c>
       <c r="I2" t="n">
-        <v>40.93641256036086</v>
+        <v>28.87239582711438</v>
       </c>
       <c r="J2" t="n">
-        <v>45.03897818453573</v>
+        <v>48.1909269186074</v>
       </c>
       <c r="K2" t="n">
-        <v>32.22552686204577</v>
+        <v>48.77177168782859</v>
       </c>
     </row>
   </sheetData>
@@ -9369,34 +9369,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.06097175905074</v>
+        <v>55.68960493941384</v>
       </c>
       <c r="C2" t="n">
-        <v>50.93105383076087</v>
+        <v>29.67429421434626</v>
       </c>
       <c r="D2" t="n">
-        <v>41.19969622393207</v>
+        <v>45.81307578753714</v>
       </c>
       <c r="E2" t="n">
-        <v>43.28528439699733</v>
+        <v>24.19046652358556</v>
       </c>
       <c r="F2" t="n">
-        <v>28.17873085983864</v>
+        <v>31.03198697936333</v>
       </c>
       <c r="G2" t="n">
-        <v>57.61993765967375</v>
+        <v>42.76301725197794</v>
       </c>
       <c r="H2" t="n">
-        <v>32.6126331470742</v>
+        <v>53.34631040300322</v>
       </c>
       <c r="I2" t="n">
-        <v>43.13560758282995</v>
+        <v>43.79037122762582</v>
       </c>
       <c r="J2" t="n">
-        <v>26.10854806337244</v>
+        <v>43.34449559151159</v>
       </c>
       <c r="K2" t="n">
-        <v>30.1798964365335</v>
+        <v>27.83213414247333</v>
       </c>
     </row>
   </sheetData>
@@ -9475,34 +9475,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.2273598846795</v>
+        <v>23.11456260762775</v>
       </c>
       <c r="C2" t="n">
-        <v>27.41447654722809</v>
+        <v>22.89437084054471</v>
       </c>
       <c r="D2" t="n">
-        <v>29.5084631490961</v>
+        <v>47.59688761549933</v>
       </c>
       <c r="E2" t="n">
-        <v>32.9082349836203</v>
+        <v>55.9170633315559</v>
       </c>
       <c r="F2" t="n">
-        <v>35.93136117623217</v>
+        <v>31.98266353979074</v>
       </c>
       <c r="G2" t="n">
-        <v>55.28583736763448</v>
+        <v>65.34294367506661</v>
       </c>
       <c r="H2" t="n">
-        <v>17.08232622864702</v>
+        <v>23.00571377673002</v>
       </c>
       <c r="I2" t="n">
-        <v>40.20165935914785</v>
+        <v>38.44622374193374</v>
       </c>
       <c r="J2" t="n">
-        <v>44.70360534003198</v>
+        <v>37.54374917557553</v>
       </c>
       <c r="K2" t="n">
-        <v>29.49143008635597</v>
+        <v>40.62699230743668</v>
       </c>
     </row>
   </sheetData>
@@ -9581,34 +9581,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.29076462827413</v>
+        <v>37.44431036003952</v>
       </c>
       <c r="C2" t="n">
-        <v>36.70832217331714</v>
+        <v>44.77613618155906</v>
       </c>
       <c r="D2" t="n">
-        <v>27.13462590254429</v>
+        <v>37.62065220281365</v>
       </c>
       <c r="E2" t="n">
-        <v>31.85361947496384</v>
+        <v>30.18209195197692</v>
       </c>
       <c r="F2" t="n">
-        <v>45.56696693599488</v>
+        <v>27.14309382753574</v>
       </c>
       <c r="G2" t="n">
-        <v>38.40586318488801</v>
+        <v>35.04633218616072</v>
       </c>
       <c r="H2" t="n">
-        <v>33.27948781297005</v>
+        <v>34.91544409917501</v>
       </c>
       <c r="I2" t="n">
-        <v>38.15776509211134</v>
+        <v>35.78124970917418</v>
       </c>
       <c r="J2" t="n">
-        <v>34.64525326113815</v>
+        <v>48.29242274982903</v>
       </c>
       <c r="K2" t="n">
-        <v>43.72050326970325</v>
+        <v>32.02726398132221</v>
       </c>
     </row>
   </sheetData>
@@ -9687,34 +9687,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.56841976749011</v>
+        <v>46.53787790389367</v>
       </c>
       <c r="C2" t="n">
-        <v>46.61272845606999</v>
+        <v>55.67142285417744</v>
       </c>
       <c r="D2" t="n">
-        <v>32.16241623540172</v>
+        <v>37.24428531147635</v>
       </c>
       <c r="E2" t="n">
-        <v>44.38671992458235</v>
+        <v>42.20466253242765</v>
       </c>
       <c r="F2" t="n">
-        <v>38.65265568500391</v>
+        <v>24.40311779167209</v>
       </c>
       <c r="G2" t="n">
-        <v>53.44366653268107</v>
+        <v>33.13823245606515</v>
       </c>
       <c r="H2" t="n">
-        <v>51.56940983571171</v>
+        <v>40.49896657735089</v>
       </c>
       <c r="I2" t="n">
-        <v>42.8389565362343</v>
+        <v>38.02360947938487</v>
       </c>
       <c r="J2" t="n">
-        <v>51.55749007877089</v>
+        <v>41.21374707907196</v>
       </c>
       <c r="K2" t="n">
-        <v>34.17455992183801</v>
+        <v>47.16992543359434</v>
       </c>
     </row>
   </sheetData>
@@ -9793,34 +9793,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>52.77497396116254</v>
+        <v>55.30449533149814</v>
       </c>
       <c r="C2" t="n">
-        <v>55.4106313981524</v>
+        <v>45.18424863917352</v>
       </c>
       <c r="D2" t="n">
-        <v>54.89181999018835</v>
+        <v>48.30516549200205</v>
       </c>
       <c r="E2" t="n">
-        <v>33.28658483197054</v>
+        <v>30.29685493569435</v>
       </c>
       <c r="F2" t="n">
-        <v>50.99362619458433</v>
+        <v>49.18968040088314</v>
       </c>
       <c r="G2" t="n">
-        <v>29.59162274813816</v>
+        <v>40.84343827115761</v>
       </c>
       <c r="H2" t="n">
-        <v>31.41825017712339</v>
+        <v>38.69469920445262</v>
       </c>
       <c r="I2" t="n">
-        <v>34.78980856263772</v>
+        <v>24.99218645844466</v>
       </c>
       <c r="J2" t="n">
-        <v>30.28005590484926</v>
+        <v>42.71585604098538</v>
       </c>
       <c r="K2" t="n">
-        <v>30.44878511005873</v>
+        <v>31.31476727210658</v>
       </c>
     </row>
   </sheetData>
@@ -9899,34 +9899,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.49025944125442</v>
+        <v>40.4531473809712</v>
       </c>
       <c r="C2" t="n">
-        <v>48.63269852282272</v>
+        <v>45.51909852758126</v>
       </c>
       <c r="D2" t="n">
-        <v>35.13820403469703</v>
+        <v>31.91622662479672</v>
       </c>
       <c r="E2" t="n">
-        <v>43.47711514473392</v>
+        <v>44.80209328975477</v>
       </c>
       <c r="F2" t="n">
-        <v>32.24937766864259</v>
+        <v>34.20176159844058</v>
       </c>
       <c r="G2" t="n">
-        <v>43.32388349567518</v>
+        <v>38.80181508260521</v>
       </c>
       <c r="H2" t="n">
-        <v>41.09892172840784</v>
+        <v>35.56416796720985</v>
       </c>
       <c r="I2" t="n">
-        <v>43.25599122857866</v>
+        <v>33.91748784632215</v>
       </c>
       <c r="J2" t="n">
-        <v>47.46034436447289</v>
+        <v>37.21023316984518</v>
       </c>
       <c r="K2" t="n">
-        <v>34.15749730785251</v>
+        <v>39.26914704383033</v>
       </c>
     </row>
   </sheetData>
@@ -10005,34 +10005,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.31497566780985</v>
+        <v>33.96439262567071</v>
       </c>
       <c r="C2" t="n">
-        <v>42.76121873741406</v>
+        <v>46.5192484755994</v>
       </c>
       <c r="D2" t="n">
-        <v>46.45016377086966</v>
+        <v>39.2504658414407</v>
       </c>
       <c r="E2" t="n">
-        <v>41.30525718036018</v>
+        <v>42.56854343962473</v>
       </c>
       <c r="F2" t="n">
-        <v>45.47936079729467</v>
+        <v>45.77696943689097</v>
       </c>
       <c r="G2" t="n">
-        <v>43.26129804257506</v>
+        <v>47.23624827066728</v>
       </c>
       <c r="H2" t="n">
-        <v>53.83013252859185</v>
+        <v>44.58433856275684</v>
       </c>
       <c r="I2" t="n">
-        <v>39.2150475338891</v>
+        <v>41.67604549567279</v>
       </c>
       <c r="J2" t="n">
-        <v>44.12188407986589</v>
+        <v>41.70682971468067</v>
       </c>
       <c r="K2" t="n">
-        <v>42.69702075707838</v>
+        <v>31.68500360978286</v>
       </c>
     </row>
   </sheetData>
@@ -10111,34 +10111,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.55796764919718</v>
+        <v>49.54504955455143</v>
       </c>
       <c r="C2" t="n">
-        <v>51.48021662841895</v>
+        <v>24.57915195103729</v>
       </c>
       <c r="D2" t="n">
-        <v>63.28880062775931</v>
+        <v>41.34962180414737</v>
       </c>
       <c r="E2" t="n">
-        <v>31.93177807195525</v>
+        <v>44.52713028637036</v>
       </c>
       <c r="F2" t="n">
-        <v>36.41927945216747</v>
+        <v>21.11278503982513</v>
       </c>
       <c r="G2" t="n">
-        <v>25.33312855884254</v>
+        <v>59.63987095091296</v>
       </c>
       <c r="H2" t="n">
-        <v>41.71164899809809</v>
+        <v>54.751932755734</v>
       </c>
       <c r="I2" t="n">
-        <v>38.93544386443807</v>
+        <v>33.58237371284634</v>
       </c>
       <c r="J2" t="n">
-        <v>41.49877954107916</v>
+        <v>45.90080416861716</v>
       </c>
       <c r="K2" t="n">
-        <v>32.32773310139562</v>
+        <v>35.65562138654372</v>
       </c>
     </row>
   </sheetData>
@@ -10217,34 +10217,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.99876654634175</v>
+        <v>30.77129566924009</v>
       </c>
       <c r="C2" t="n">
-        <v>36.06910532066728</v>
+        <v>46.95780058055898</v>
       </c>
       <c r="D2" t="n">
-        <v>39.19714758005703</v>
+        <v>30.2016312201563</v>
       </c>
       <c r="E2" t="n">
-        <v>35.78238283711585</v>
+        <v>46.02688131318104</v>
       </c>
       <c r="F2" t="n">
-        <v>41.34049051383</v>
+        <v>39.93688821025606</v>
       </c>
       <c r="G2" t="n">
-        <v>39.07267690126036</v>
+        <v>32.71590800737241</v>
       </c>
       <c r="H2" t="n">
-        <v>45.75046370811302</v>
+        <v>28.05769752985083</v>
       </c>
       <c r="I2" t="n">
-        <v>36.40205692295723</v>
+        <v>34.83496234236425</v>
       </c>
       <c r="J2" t="n">
-        <v>35.59171500293228</v>
+        <v>53.50606016729472</v>
       </c>
       <c r="K2" t="n">
-        <v>38.10663650548978</v>
+        <v>32.66971473584982</v>
       </c>
     </row>
   </sheetData>
@@ -10323,34 +10323,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.28572748696644</v>
+        <v>44.923453661985</v>
       </c>
       <c r="C2" t="n">
-        <v>54.77554286673311</v>
+        <v>40.72340392126416</v>
       </c>
       <c r="D2" t="n">
-        <v>45.26205613027858</v>
+        <v>65.10722379971948</v>
       </c>
       <c r="E2" t="n">
-        <v>37.45597412049547</v>
+        <v>43.88522849697367</v>
       </c>
       <c r="F2" t="n">
-        <v>34.35925201188371</v>
+        <v>31.26805649513982</v>
       </c>
       <c r="G2" t="n">
-        <v>50.39707261359928</v>
+        <v>33.7069090361309</v>
       </c>
       <c r="H2" t="n">
-        <v>44.01111638044905</v>
+        <v>43.91376603371261</v>
       </c>
       <c r="I2" t="n">
-        <v>45.24705544699727</v>
+        <v>43.27305967454323</v>
       </c>
       <c r="J2" t="n">
-        <v>46.99120679983988</v>
+        <v>48.58214094641937</v>
       </c>
       <c r="K2" t="n">
-        <v>38.19446104395028</v>
+        <v>34.60235141287219</v>
       </c>
     </row>
   </sheetData>
@@ -10429,34 +10429,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.75686776972388</v>
+        <v>37.83471372710866</v>
       </c>
       <c r="C2" t="n">
-        <v>40.67947408671127</v>
+        <v>40.56254516772498</v>
       </c>
       <c r="D2" t="n">
-        <v>44.60439281925524</v>
+        <v>47.97288309379041</v>
       </c>
       <c r="E2" t="n">
-        <v>35.47929648913201</v>
+        <v>45.12701059272079</v>
       </c>
       <c r="F2" t="n">
-        <v>42.07787553338274</v>
+        <v>36.3217452566432</v>
       </c>
       <c r="G2" t="n">
-        <v>31.1637840474704</v>
+        <v>28.91541772269668</v>
       </c>
       <c r="H2" t="n">
-        <v>43.8485408618745</v>
+        <v>34.1118196918237</v>
       </c>
       <c r="I2" t="n">
-        <v>50.6195079509451</v>
+        <v>38.40188618356895</v>
       </c>
       <c r="J2" t="n">
-        <v>35.95189361571335</v>
+        <v>35.86775632809686</v>
       </c>
       <c r="K2" t="n">
-        <v>35.79871607915047</v>
+        <v>44.44562990728462</v>
       </c>
     </row>
   </sheetData>
@@ -10535,34 +10535,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.34952334814922</v>
+        <v>41.64485372202264</v>
       </c>
       <c r="C2" t="n">
-        <v>51.15094590344412</v>
+        <v>33.14522795878748</v>
       </c>
       <c r="D2" t="n">
-        <v>50.68108571507287</v>
+        <v>46.78908408105101</v>
       </c>
       <c r="E2" t="n">
-        <v>37.74802227042908</v>
+        <v>47.84772778222398</v>
       </c>
       <c r="F2" t="n">
-        <v>42.78904527202654</v>
+        <v>47.44266738673102</v>
       </c>
       <c r="G2" t="n">
-        <v>44.72190946250301</v>
+        <v>17.22110003691799</v>
       </c>
       <c r="H2" t="n">
-        <v>34.08397796783007</v>
+        <v>47.16863835861452</v>
       </c>
       <c r="I2" t="n">
-        <v>48.17706898054244</v>
+        <v>49.23558666039872</v>
       </c>
       <c r="J2" t="n">
-        <v>35.63907213365751</v>
+        <v>57.58465268135958</v>
       </c>
       <c r="K2" t="n">
-        <v>33.00628157995971</v>
+        <v>46.27510959418689</v>
       </c>
     </row>
   </sheetData>
@@ -10641,34 +10641,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>46.36843001870854</v>
+        <v>36.95166268933832</v>
       </c>
       <c r="C2" t="n">
-        <v>31.7100060750926</v>
+        <v>52.54205281760735</v>
       </c>
       <c r="D2" t="n">
-        <v>48.06443264834466</v>
+        <v>42.66035393919784</v>
       </c>
       <c r="E2" t="n">
-        <v>50.53138719425604</v>
+        <v>40.64017493281342</v>
       </c>
       <c r="F2" t="n">
-        <v>45.43009587285844</v>
+        <v>62.89098626734673</v>
       </c>
       <c r="G2" t="n">
-        <v>40.62447334096754</v>
+        <v>43.85459620488752</v>
       </c>
       <c r="H2" t="n">
-        <v>39.14368543983975</v>
+        <v>43.6983150600644</v>
       </c>
       <c r="I2" t="n">
-        <v>31.79694689169879</v>
+        <v>32.82304060568499</v>
       </c>
       <c r="J2" t="n">
-        <v>37.07449704974763</v>
+        <v>41.67074063416934</v>
       </c>
       <c r="K2" t="n">
-        <v>40.31159687311216</v>
+        <v>48.87465316487078</v>
       </c>
     </row>
   </sheetData>
@@ -10747,34 +10747,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.50518252999786</v>
+        <v>36.84005449277496</v>
       </c>
       <c r="C2" t="n">
-        <v>47.0541718939237</v>
+        <v>48.80043302317608</v>
       </c>
       <c r="D2" t="n">
-        <v>35.47289739963718</v>
+        <v>49.28847526900272</v>
       </c>
       <c r="E2" t="n">
-        <v>41.86383404754633</v>
+        <v>51.93329089055716</v>
       </c>
       <c r="F2" t="n">
-        <v>45.57296292459309</v>
+        <v>37.59990320472507</v>
       </c>
       <c r="G2" t="n">
-        <v>39.93465116001894</v>
+        <v>42.33625191100701</v>
       </c>
       <c r="H2" t="n">
-        <v>42.88199128159672</v>
+        <v>40.81618256083269</v>
       </c>
       <c r="I2" t="n">
-        <v>35.97074792133414</v>
+        <v>34.39186109135466</v>
       </c>
       <c r="J2" t="n">
-        <v>56.23338470700316</v>
+        <v>35.85154103449263</v>
       </c>
       <c r="K2" t="n">
-        <v>34.22374298680123</v>
+        <v>45.32681710391294</v>
       </c>
     </row>
   </sheetData>
@@ -10853,34 +10853,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.32578144414492</v>
+        <v>55.36787800456628</v>
       </c>
       <c r="C2" t="n">
-        <v>52.95442041137643</v>
+        <v>50.99099826772135</v>
       </c>
       <c r="D2" t="n">
-        <v>61.37347584015564</v>
+        <v>44.65947923753068</v>
       </c>
       <c r="E2" t="n">
-        <v>37.53062623943595</v>
+        <v>47.9459773021678</v>
       </c>
       <c r="F2" t="n">
-        <v>37.74547173512443</v>
+        <v>37.33196476189026</v>
       </c>
       <c r="G2" t="n">
-        <v>26.09484493634193</v>
+        <v>29.25515964701802</v>
       </c>
       <c r="H2" t="n">
-        <v>43.01944385871179</v>
+        <v>48.3204199807627</v>
       </c>
       <c r="I2" t="n">
-        <v>46.99554958029693</v>
+        <v>26.69041400914473</v>
       </c>
       <c r="J2" t="n">
-        <v>37.26029831905726</v>
+        <v>35.96855301225538</v>
       </c>
       <c r="K2" t="n">
-        <v>47.12200132489948</v>
+        <v>40.67955760953828</v>
       </c>
     </row>
   </sheetData>
@@ -10959,34 +10959,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.58788112441263</v>
+        <v>41.22713078262596</v>
       </c>
       <c r="C2" t="n">
-        <v>47.49391227167653</v>
+        <v>44.11178592904248</v>
       </c>
       <c r="D2" t="n">
-        <v>57.26755177043609</v>
+        <v>43.21424481289937</v>
       </c>
       <c r="E2" t="n">
-        <v>41.6860570797237</v>
+        <v>40.41126904441469</v>
       </c>
       <c r="F2" t="n">
-        <v>40.82367241480591</v>
+        <v>35.45327971794921</v>
       </c>
       <c r="G2" t="n">
-        <v>35.11265037173226</v>
+        <v>43.5558721558278</v>
       </c>
       <c r="H2" t="n">
-        <v>42.08852872901105</v>
+        <v>31.01729070156061</v>
       </c>
       <c r="I2" t="n">
-        <v>59.50958218262856</v>
+        <v>38.78237608443197</v>
       </c>
       <c r="J2" t="n">
-        <v>38.27010238602828</v>
+        <v>51.59957919495875</v>
       </c>
       <c r="K2" t="n">
-        <v>55.08170338467283</v>
+        <v>46.37246177323959</v>
       </c>
     </row>
   </sheetData>
@@ -11065,34 +11065,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.43990303711487</v>
+        <v>47.44713355741115</v>
       </c>
       <c r="C2" t="n">
-        <v>43.60736860913367</v>
+        <v>41.7402915624543</v>
       </c>
       <c r="D2" t="n">
-        <v>73.92777114615406</v>
+        <v>39.05680981635653</v>
       </c>
       <c r="E2" t="n">
-        <v>35.83281593211586</v>
+        <v>33.36553431009987</v>
       </c>
       <c r="F2" t="n">
-        <v>32.68501338638065</v>
+        <v>23.46114241216032</v>
       </c>
       <c r="G2" t="n">
-        <v>38.74124827522144</v>
+        <v>51.79704399635434</v>
       </c>
       <c r="H2" t="n">
-        <v>39.71324123621313</v>
+        <v>50.8560710534735</v>
       </c>
       <c r="I2" t="n">
-        <v>32.37128011657342</v>
+        <v>36.54311332652774</v>
       </c>
       <c r="J2" t="n">
-        <v>51.10060311360615</v>
+        <v>39.49236479410475</v>
       </c>
       <c r="K2" t="n">
-        <v>37.08852552629364</v>
+        <v>36.83078948116398</v>
       </c>
     </row>
   </sheetData>
@@ -11171,34 +11171,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.23273451929354</v>
+        <v>51.66063516343397</v>
       </c>
       <c r="C2" t="n">
-        <v>38.07506304618967</v>
+        <v>31.27686099634127</v>
       </c>
       <c r="D2" t="n">
-        <v>41.65612063895484</v>
+        <v>57.79014425542273</v>
       </c>
       <c r="E2" t="n">
-        <v>49.59051425792425</v>
+        <v>48.15424409620532</v>
       </c>
       <c r="F2" t="n">
-        <v>54.21185593484242</v>
+        <v>31.89008919023319</v>
       </c>
       <c r="G2" t="n">
-        <v>43.01477911282223</v>
+        <v>47.44290428900752</v>
       </c>
       <c r="H2" t="n">
-        <v>49.14246799416685</v>
+        <v>32.93899673664229</v>
       </c>
       <c r="I2" t="n">
-        <v>40.42011227811015</v>
+        <v>40.76968492859262</v>
       </c>
       <c r="J2" t="n">
-        <v>35.77602742948434</v>
+        <v>42.74788559513632</v>
       </c>
       <c r="K2" t="n">
-        <v>38.91406873932811</v>
+        <v>37.39333818429704</v>
       </c>
     </row>
   </sheetData>
@@ -11277,34 +11277,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.34520456036571</v>
+        <v>44.62087358635117</v>
       </c>
       <c r="C2" t="n">
-        <v>46.90114653728207</v>
+        <v>39.93752244469111</v>
       </c>
       <c r="D2" t="n">
-        <v>33.75898898407681</v>
+        <v>36.188599513144</v>
       </c>
       <c r="E2" t="n">
-        <v>37.63173113040691</v>
+        <v>40.16787518717445</v>
       </c>
       <c r="F2" t="n">
-        <v>35.62510760103404</v>
+        <v>49.01708606989771</v>
       </c>
       <c r="G2" t="n">
-        <v>34.85031585467373</v>
+        <v>43.49996334708031</v>
       </c>
       <c r="H2" t="n">
-        <v>41.8355274022764</v>
+        <v>45.9942508325083</v>
       </c>
       <c r="I2" t="n">
-        <v>43.15688679979416</v>
+        <v>35.23845138425136</v>
       </c>
       <c r="J2" t="n">
-        <v>36.5474584196302</v>
+        <v>35.60459462989069</v>
       </c>
       <c r="K2" t="n">
-        <v>36.64606796320956</v>
+        <v>27.99633849627728</v>
       </c>
     </row>
   </sheetData>
@@ -11383,34 +11383,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.9206875594854</v>
+        <v>28.50408281958977</v>
       </c>
       <c r="C2" t="n">
-        <v>34.89894515464509</v>
+        <v>58.74547908514554</v>
       </c>
       <c r="D2" t="n">
-        <v>41.2359067568454</v>
+        <v>42.64139452489396</v>
       </c>
       <c r="E2" t="n">
-        <v>41.58472230397282</v>
+        <v>36.67364307268954</v>
       </c>
       <c r="F2" t="n">
-        <v>31.51316212038911</v>
+        <v>40.22639269298259</v>
       </c>
       <c r="G2" t="n">
-        <v>38.65408970060375</v>
+        <v>35.48622075130581</v>
       </c>
       <c r="H2" t="n">
-        <v>49.25838438866465</v>
+        <v>43.13578891572152</v>
       </c>
       <c r="I2" t="n">
-        <v>43.27342500884419</v>
+        <v>35.47542351721007</v>
       </c>
       <c r="J2" t="n">
-        <v>43.05072766077567</v>
+        <v>30.8248869532104</v>
       </c>
       <c r="K2" t="n">
-        <v>36.82586319090583</v>
+        <v>48.79486850033385</v>
       </c>
     </row>
   </sheetData>
@@ -11489,34 +11489,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>48.33514416482431</v>
+        <v>49.5745629482236</v>
       </c>
       <c r="C2" t="n">
-        <v>36.43504278000042</v>
+        <v>41.05008362028345</v>
       </c>
       <c r="D2" t="n">
-        <v>49.13934080313048</v>
+        <v>35.8710373008353</v>
       </c>
       <c r="E2" t="n">
-        <v>42.50821831807902</v>
+        <v>36.21459791858825</v>
       </c>
       <c r="F2" t="n">
-        <v>37.1927398605928</v>
+        <v>42.05091557749412</v>
       </c>
       <c r="G2" t="n">
-        <v>39.24098131937399</v>
+        <v>37.76651495081104</v>
       </c>
       <c r="H2" t="n">
-        <v>41.93846328413801</v>
+        <v>40.16333597126185</v>
       </c>
       <c r="I2" t="n">
-        <v>43.67044769870019</v>
+        <v>38.79864613321668</v>
       </c>
       <c r="J2" t="n">
-        <v>38.1526202394818</v>
+        <v>32.92520126413275</v>
       </c>
       <c r="K2" t="n">
-        <v>35.0234532261124</v>
+        <v>45.37890296621949</v>
       </c>
     </row>
   </sheetData>
@@ -11595,34 +11595,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.79681569777739</v>
+        <v>32.06920237197876</v>
       </c>
       <c r="C2" t="n">
-        <v>35.24820606154059</v>
+        <v>53.57548267279843</v>
       </c>
       <c r="D2" t="n">
-        <v>33.85845571140148</v>
+        <v>45.52073741835905</v>
       </c>
       <c r="E2" t="n">
-        <v>42.49512821814391</v>
+        <v>29.08599299839735</v>
       </c>
       <c r="F2" t="n">
-        <v>34.45655858024685</v>
+        <v>49.42681121701717</v>
       </c>
       <c r="G2" t="n">
-        <v>53.57819619024241</v>
+        <v>31.42114406440015</v>
       </c>
       <c r="H2" t="n">
-        <v>39.13859911348079</v>
+        <v>46.73492101793156</v>
       </c>
       <c r="I2" t="n">
-        <v>44.91406008083747</v>
+        <v>43.98711725267503</v>
       </c>
       <c r="J2" t="n">
-        <v>45.53366229086767</v>
+        <v>33.61865996150154</v>
       </c>
       <c r="K2" t="n">
-        <v>34.37516388679435</v>
+        <v>29.29732777862106</v>
       </c>
     </row>
   </sheetData>
@@ -11701,34 +11701,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.98166185664789</v>
+        <v>37.20272873756086</v>
       </c>
       <c r="C2" t="n">
-        <v>39.77186756658269</v>
+        <v>38.92413710973042</v>
       </c>
       <c r="D2" t="n">
-        <v>45.02754574097486</v>
+        <v>49.30583622250169</v>
       </c>
       <c r="E2" t="n">
-        <v>38.02003483808037</v>
+        <v>42.21607953378461</v>
       </c>
       <c r="F2" t="n">
-        <v>38.08150373853986</v>
+        <v>38.83656668385397</v>
       </c>
       <c r="G2" t="n">
-        <v>46.26389044042603</v>
+        <v>35.23217028826532</v>
       </c>
       <c r="H2" t="n">
-        <v>48.78444278691645</v>
+        <v>56.23023437689165</v>
       </c>
       <c r="I2" t="n">
-        <v>45.3973081116563</v>
+        <v>41.4621190647093</v>
       </c>
       <c r="J2" t="n">
-        <v>32.97532509570638</v>
+        <v>35.25997716432838</v>
       </c>
       <c r="K2" t="n">
-        <v>30.58759841797248</v>
+        <v>32.21149963879652</v>
       </c>
     </row>
   </sheetData>
@@ -11807,34 +11807,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.73023541171876</v>
+        <v>26.73675219035381</v>
       </c>
       <c r="C2" t="n">
-        <v>56.26500436798837</v>
+        <v>33.23284401270821</v>
       </c>
       <c r="D2" t="n">
-        <v>37.49407380843582</v>
+        <v>33.4615510102417</v>
       </c>
       <c r="E2" t="n">
-        <v>51.99284516212433</v>
+        <v>41.27484250560163</v>
       </c>
       <c r="F2" t="n">
-        <v>33.68305393166931</v>
+        <v>41.22245009838855</v>
       </c>
       <c r="G2" t="n">
-        <v>43.4627887083565</v>
+        <v>27.79398406254631</v>
       </c>
       <c r="H2" t="n">
-        <v>40.72938735757976</v>
+        <v>35.55557375321784</v>
       </c>
       <c r="I2" t="n">
-        <v>34.09344591482625</v>
+        <v>36.03188459431244</v>
       </c>
       <c r="J2" t="n">
-        <v>30.25317270210623</v>
+        <v>36.70514793655881</v>
       </c>
       <c r="K2" t="n">
-        <v>22.84497131880943</v>
+        <v>44.10761077581735</v>
       </c>
     </row>
   </sheetData>
@@ -11913,34 +11913,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.26741091104319</v>
+        <v>49.83232441921402</v>
       </c>
       <c r="C2" t="n">
-        <v>46.55382418198536</v>
+        <v>35.44802608633351</v>
       </c>
       <c r="D2" t="n">
-        <v>49.35561032102601</v>
+        <v>45.93893917535017</v>
       </c>
       <c r="E2" t="n">
-        <v>47.56469998016711</v>
+        <v>32.54937532565297</v>
       </c>
       <c r="F2" t="n">
-        <v>41.45531102397285</v>
+        <v>37.76161615349253</v>
       </c>
       <c r="G2" t="n">
-        <v>39.49727409319466</v>
+        <v>39.34758474242305</v>
       </c>
       <c r="H2" t="n">
-        <v>28.97221221619161</v>
+        <v>40.07970902663053</v>
       </c>
       <c r="I2" t="n">
-        <v>43.90130508523859</v>
+        <v>42.32417239165593</v>
       </c>
       <c r="J2" t="n">
-        <v>49.79226877816903</v>
+        <v>37.83126279029435</v>
       </c>
       <c r="K2" t="n">
-        <v>36.55151319760706</v>
+        <v>37.80834192035439</v>
       </c>
     </row>
   </sheetData>
@@ -12019,34 +12019,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.49338649277319</v>
+        <v>45.17365758024923</v>
       </c>
       <c r="C2" t="n">
-        <v>26.22170101719974</v>
+        <v>43.77369606729187</v>
       </c>
       <c r="D2" t="n">
-        <v>41.14935827148597</v>
+        <v>39.23556533834559</v>
       </c>
       <c r="E2" t="n">
-        <v>41.42975864166903</v>
+        <v>48.84548537330872</v>
       </c>
       <c r="F2" t="n">
-        <v>36.73727013543441</v>
+        <v>35.53785016027707</v>
       </c>
       <c r="G2" t="n">
-        <v>39.71977733789781</v>
+        <v>37.26791034279361</v>
       </c>
       <c r="H2" t="n">
-        <v>28.1988673608069</v>
+        <v>30.54939233563797</v>
       </c>
       <c r="I2" t="n">
-        <v>33.20903262971837</v>
+        <v>38.06057224994628</v>
       </c>
       <c r="J2" t="n">
-        <v>35.33728609103493</v>
+        <v>39.76843249939034</v>
       </c>
       <c r="K2" t="n">
-        <v>39.00281755794781</v>
+        <v>34.98694577699148</v>
       </c>
     </row>
   </sheetData>
@@ -12125,34 +12125,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49.53197941326526</v>
+        <v>51.64000117841974</v>
       </c>
       <c r="C2" t="n">
-        <v>50.91227760755757</v>
+        <v>39.29061004753273</v>
       </c>
       <c r="D2" t="n">
-        <v>45.42660515395115</v>
+        <v>35.14969856840009</v>
       </c>
       <c r="E2" t="n">
-        <v>33.65344213798098</v>
+        <v>27.96754326475375</v>
       </c>
       <c r="F2" t="n">
-        <v>32.43339944645551</v>
+        <v>42.82147800043825</v>
       </c>
       <c r="G2" t="n">
-        <v>48.46528512271978</v>
+        <v>40.84430535250344</v>
       </c>
       <c r="H2" t="n">
-        <v>39.44064443819327</v>
+        <v>45.45907227263688</v>
       </c>
       <c r="I2" t="n">
-        <v>46.98312087661745</v>
+        <v>55.85195744577411</v>
       </c>
       <c r="J2" t="n">
-        <v>47.15788302647454</v>
+        <v>49.28541528410318</v>
       </c>
       <c r="K2" t="n">
-        <v>35.87927169903984</v>
+        <v>48.29402314243264</v>
       </c>
     </row>
   </sheetData>
@@ -12231,34 +12231,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.41472276640618</v>
+        <v>36.05923916125249</v>
       </c>
       <c r="C2" t="n">
-        <v>33.14445461426979</v>
+        <v>29.71281150420371</v>
       </c>
       <c r="D2" t="n">
-        <v>31.85600516312196</v>
+        <v>40.77606915542216</v>
       </c>
       <c r="E2" t="n">
-        <v>30.70536583036855</v>
+        <v>30.3928265643429</v>
       </c>
       <c r="F2" t="n">
-        <v>38.81940690508838</v>
+        <v>27.8517848650612</v>
       </c>
       <c r="G2" t="n">
-        <v>57.88166168728083</v>
+        <v>54.87981015800065</v>
       </c>
       <c r="H2" t="n">
-        <v>31.22879169997757</v>
+        <v>30.10938893615035</v>
       </c>
       <c r="I2" t="n">
-        <v>40.61907089457446</v>
+        <v>46.14496250655372</v>
       </c>
       <c r="J2" t="n">
-        <v>47.81844169407894</v>
+        <v>27.91513008764369</v>
       </c>
       <c r="K2" t="n">
-        <v>38.52285590518158</v>
+        <v>27.79630680989473</v>
       </c>
     </row>
   </sheetData>
@@ -12337,34 +12337,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.24285555686281</v>
+        <v>39.54004075060851</v>
       </c>
       <c r="C2" t="n">
-        <v>41.16375818645014</v>
+        <v>51.12628988126303</v>
       </c>
       <c r="D2" t="n">
-        <v>42.57278908634242</v>
+        <v>36.32753368325594</v>
       </c>
       <c r="E2" t="n">
-        <v>33.53770347935532</v>
+        <v>33.13625131796102</v>
       </c>
       <c r="F2" t="n">
-        <v>46.81228386412106</v>
+        <v>54.9208104487375</v>
       </c>
       <c r="G2" t="n">
-        <v>28.82853466460266</v>
+        <v>46.90419015635688</v>
       </c>
       <c r="H2" t="n">
-        <v>60.96014659687519</v>
+        <v>35.37983064778555</v>
       </c>
       <c r="I2" t="n">
-        <v>34.11856904896133</v>
+        <v>43.75273492308591</v>
       </c>
       <c r="J2" t="n">
-        <v>51.27311462340652</v>
+        <v>40.84285571563202</v>
       </c>
       <c r="K2" t="n">
-        <v>36.3176475304308</v>
+        <v>41.78246305808856</v>
       </c>
     </row>
   </sheetData>
@@ -12443,34 +12443,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>46.92992732961097</v>
+        <v>41.18320409305016</v>
       </c>
       <c r="C2" t="n">
-        <v>47.78084926668202</v>
+        <v>34.49135943431597</v>
       </c>
       <c r="D2" t="n">
-        <v>43.68219572540068</v>
+        <v>50.69228584559489</v>
       </c>
       <c r="E2" t="n">
-        <v>30.18871063490786</v>
+        <v>37.77987671327077</v>
       </c>
       <c r="F2" t="n">
-        <v>46.79179751475947</v>
+        <v>39.11818594136139</v>
       </c>
       <c r="G2" t="n">
-        <v>40.89300221976712</v>
+        <v>42.94168810477329</v>
       </c>
       <c r="H2" t="n">
-        <v>47.90164723381164</v>
+        <v>50.53246703809751</v>
       </c>
       <c r="I2" t="n">
-        <v>39.32300364521821</v>
+        <v>38.59255878103754</v>
       </c>
       <c r="J2" t="n">
-        <v>39.61964841270434</v>
+        <v>52.71542474895082</v>
       </c>
       <c r="K2" t="n">
-        <v>49.53268656657238</v>
+        <v>41.94258067408273</v>
       </c>
     </row>
   </sheetData>
@@ -12549,34 +12549,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.48118476680339</v>
+        <v>43.32887710203971</v>
       </c>
       <c r="C2" t="n">
-        <v>50.18120127056714</v>
+        <v>38.63686341516248</v>
       </c>
       <c r="D2" t="n">
-        <v>51.71093183346932</v>
+        <v>47.20770749623724</v>
       </c>
       <c r="E2" t="n">
-        <v>30.16561107548863</v>
+        <v>33.54010786108915</v>
       </c>
       <c r="F2" t="n">
-        <v>44.70655286670737</v>
+        <v>42.74296212325605</v>
       </c>
       <c r="G2" t="n">
-        <v>38.67940045827744</v>
+        <v>44.54826177595782</v>
       </c>
       <c r="H2" t="n">
-        <v>53.73479884533781</v>
+        <v>43.42012296161482</v>
       </c>
       <c r="I2" t="n">
-        <v>41.17343548045471</v>
+        <v>39.60293149772233</v>
       </c>
       <c r="J2" t="n">
-        <v>46.67097209396645</v>
+        <v>36.54991203686053</v>
       </c>
       <c r="K2" t="n">
-        <v>30.31032545890334</v>
+        <v>51.95711855319546</v>
       </c>
     </row>
   </sheetData>
@@ -12655,34 +12655,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.40349548967203</v>
+        <v>30.79123515395085</v>
       </c>
       <c r="C2" t="n">
-        <v>30.09189429151405</v>
+        <v>35.63345531860929</v>
       </c>
       <c r="D2" t="n">
-        <v>27.52758064204163</v>
+        <v>44.61341519264275</v>
       </c>
       <c r="E2" t="n">
-        <v>31.71790344531834</v>
+        <v>37.1442138403137</v>
       </c>
       <c r="F2" t="n">
-        <v>32.73305662632769</v>
+        <v>46.21739578433284</v>
       </c>
       <c r="G2" t="n">
-        <v>45.46549095504577</v>
+        <v>40.05156926507372</v>
       </c>
       <c r="H2" t="n">
-        <v>47.98195798635916</v>
+        <v>33.06556794366274</v>
       </c>
       <c r="I2" t="n">
-        <v>50.33878830859081</v>
+        <v>43.34527399916284</v>
       </c>
       <c r="J2" t="n">
-        <v>37.96918477405661</v>
+        <v>42.6343562772612</v>
       </c>
       <c r="K2" t="n">
-        <v>39.02271199989223</v>
+        <v>39.86658398147232</v>
       </c>
     </row>
   </sheetData>
@@ -12761,34 +12761,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.48349118397029</v>
+        <v>47.55265116166088</v>
       </c>
       <c r="C2" t="n">
-        <v>52.17225522925884</v>
+        <v>44.34945197671834</v>
       </c>
       <c r="D2" t="n">
-        <v>58.64375716928195</v>
+        <v>43.70081365728223</v>
       </c>
       <c r="E2" t="n">
-        <v>41.63581880143353</v>
+        <v>39.26377775540449</v>
       </c>
       <c r="F2" t="n">
-        <v>44.94930650013053</v>
+        <v>36.06422760883811</v>
       </c>
       <c r="G2" t="n">
-        <v>35.26804816653868</v>
+        <v>41.71409737352798</v>
       </c>
       <c r="H2" t="n">
-        <v>37.45397872081247</v>
+        <v>30.73143544266909</v>
       </c>
       <c r="I2" t="n">
-        <v>43.5408914404837</v>
+        <v>39.08765418596403</v>
       </c>
       <c r="J2" t="n">
-        <v>39.32693587534822</v>
+        <v>63.46710030169166</v>
       </c>
       <c r="K2" t="n">
-        <v>45.50671289757982</v>
+        <v>41.79392144507622</v>
       </c>
     </row>
   </sheetData>
@@ -12867,34 +12867,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.29361439597461</v>
+        <v>44.87970561862215</v>
       </c>
       <c r="C2" t="n">
-        <v>46.35255359355762</v>
+        <v>61.41345408726418</v>
       </c>
       <c r="D2" t="n">
-        <v>63.9574133075246</v>
+        <v>30.96859011896896</v>
       </c>
       <c r="E2" t="n">
-        <v>30.54286446679004</v>
+        <v>35.97613361027557</v>
       </c>
       <c r="F2" t="n">
-        <v>34.07685909605665</v>
+        <v>33.96720590125854</v>
       </c>
       <c r="G2" t="n">
-        <v>52.23673475917576</v>
+        <v>44.70060943545036</v>
       </c>
       <c r="H2" t="n">
-        <v>31.72816794492099</v>
+        <v>38.89580248737084</v>
       </c>
       <c r="I2" t="n">
-        <v>51.80130319073392</v>
+        <v>49.85863443347831</v>
       </c>
       <c r="J2" t="n">
-        <v>43.68938063292195</v>
+        <v>41.5457699529143</v>
       </c>
       <c r="K2" t="n">
-        <v>40.04012770655685</v>
+        <v>32.61939587263073</v>
       </c>
     </row>
   </sheetData>
@@ -12973,34 +12973,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.98714043643638</v>
+        <v>57.07604250970104</v>
       </c>
       <c r="C2" t="n">
-        <v>33.97089985146339</v>
+        <v>34.5851294651717</v>
       </c>
       <c r="D2" t="n">
-        <v>33.57146983814588</v>
+        <v>51.3496291333423</v>
       </c>
       <c r="E2" t="n">
-        <v>38.94983603141532</v>
+        <v>39.3162900344244</v>
       </c>
       <c r="F2" t="n">
-        <v>47.54178724127812</v>
+        <v>32.24173925768895</v>
       </c>
       <c r="G2" t="n">
-        <v>56.5996838938995</v>
+        <v>43.20058940814253</v>
       </c>
       <c r="H2" t="n">
-        <v>42.65179610143961</v>
+        <v>51.05090080019556</v>
       </c>
       <c r="I2" t="n">
-        <v>46.55008145222901</v>
+        <v>53.27082668443169</v>
       </c>
       <c r="J2" t="n">
-        <v>32.36801251546353</v>
+        <v>36.48168932890555</v>
       </c>
       <c r="K2" t="n">
-        <v>41.6956183811833</v>
+        <v>42.41005439158444</v>
       </c>
     </row>
   </sheetData>
@@ -13079,34 +13079,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.8211410553423</v>
+        <v>41.50554175397161</v>
       </c>
       <c r="C2" t="n">
-        <v>44.8851617475358</v>
+        <v>47.73866527886594</v>
       </c>
       <c r="D2" t="n">
-        <v>39.38381455772522</v>
+        <v>37.40709306412095</v>
       </c>
       <c r="E2" t="n">
-        <v>41.08373927795356</v>
+        <v>41.78619934203246</v>
       </c>
       <c r="F2" t="n">
-        <v>43.68089796545168</v>
+        <v>32.4238715065986</v>
       </c>
       <c r="G2" t="n">
-        <v>39.305955980524</v>
+        <v>60.72251266542179</v>
       </c>
       <c r="H2" t="n">
-        <v>36.76491706420492</v>
+        <v>34.22347316725659</v>
       </c>
       <c r="I2" t="n">
-        <v>36.51815122189218</v>
+        <v>42.51698384279597</v>
       </c>
       <c r="J2" t="n">
-        <v>35.99831269098203</v>
+        <v>45.61061444860373</v>
       </c>
       <c r="K2" t="n">
-        <v>34.9214078995466</v>
+        <v>44.45951644811851</v>
       </c>
     </row>
   </sheetData>
@@ -13185,34 +13185,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.24564405567916</v>
+        <v>38.1881225621783</v>
       </c>
       <c r="C2" t="n">
-        <v>38.01693848119044</v>
+        <v>37.54435367253856</v>
       </c>
       <c r="D2" t="n">
-        <v>49.72305495707809</v>
+        <v>41.48019946353926</v>
       </c>
       <c r="E2" t="n">
-        <v>24.38847549858798</v>
+        <v>37.4799338092614</v>
       </c>
       <c r="F2" t="n">
-        <v>45.99472555812012</v>
+        <v>43.47136975753605</v>
       </c>
       <c r="G2" t="n">
-        <v>40.6552188562416</v>
+        <v>53.45878816513264</v>
       </c>
       <c r="H2" t="n">
-        <v>39.98979891042892</v>
+        <v>36.09821228425663</v>
       </c>
       <c r="I2" t="n">
-        <v>46.04985456869147</v>
+        <v>39.20042227524115</v>
       </c>
       <c r="J2" t="n">
-        <v>48.60968371707612</v>
+        <v>46.19420679096792</v>
       </c>
       <c r="K2" t="n">
-        <v>38.80304921266953</v>
+        <v>30.50232014221784</v>
       </c>
     </row>
   </sheetData>
@@ -13291,34 +13291,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.66860855039023</v>
+        <v>50.9305851964066</v>
       </c>
       <c r="C2" t="n">
-        <v>39.68444389385164</v>
+        <v>37.95935514269348</v>
       </c>
       <c r="D2" t="n">
-        <v>40.7191650381291</v>
+        <v>58.46255519306365</v>
       </c>
       <c r="E2" t="n">
-        <v>32.95778690409166</v>
+        <v>24.49680049380828</v>
       </c>
       <c r="F2" t="n">
-        <v>36.88887812137568</v>
+        <v>55.45464774395306</v>
       </c>
       <c r="G2" t="n">
-        <v>53.1211940433835</v>
+        <v>39.3619124626521</v>
       </c>
       <c r="H2" t="n">
-        <v>43.81376754921552</v>
+        <v>38.20312918061266</v>
       </c>
       <c r="I2" t="n">
-        <v>29.02781743730448</v>
+        <v>35.22148531576916</v>
       </c>
       <c r="J2" t="n">
-        <v>37.14956477246666</v>
+        <v>36.46275477131196</v>
       </c>
       <c r="K2" t="n">
-        <v>47.73964641867369</v>
+        <v>35.12172501303346</v>
       </c>
     </row>
   </sheetData>
@@ -13397,34 +13397,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.30036363161017</v>
+        <v>37.76446520344778</v>
       </c>
       <c r="C2" t="n">
-        <v>35.68329881228888</v>
+        <v>49.83776858115197</v>
       </c>
       <c r="D2" t="n">
-        <v>50.82557104817025</v>
+        <v>38.21975911116076</v>
       </c>
       <c r="E2" t="n">
-        <v>38.806225004604</v>
+        <v>35.73950622104421</v>
       </c>
       <c r="F2" t="n">
-        <v>41.2655460665404</v>
+        <v>40.49591054109781</v>
       </c>
       <c r="G2" t="n">
-        <v>39.32324140164292</v>
+        <v>37.97953851066968</v>
       </c>
       <c r="H2" t="n">
-        <v>45.85445096431289</v>
+        <v>39.37674772905704</v>
       </c>
       <c r="I2" t="n">
-        <v>39.05531800061708</v>
+        <v>47.97427363926052</v>
       </c>
       <c r="J2" t="n">
-        <v>39.09320607085762</v>
+        <v>33.4154735167834</v>
       </c>
       <c r="K2" t="n">
-        <v>37.49401632106329</v>
+        <v>30.03343075985319</v>
       </c>
     </row>
   </sheetData>
@@ -13503,34 +13503,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.58414551533232</v>
+        <v>66.6448852652286</v>
       </c>
       <c r="C2" t="n">
-        <v>48.53405911565066</v>
+        <v>41.66722581597411</v>
       </c>
       <c r="D2" t="n">
-        <v>54.06549921710214</v>
+        <v>46.45470669497135</v>
       </c>
       <c r="E2" t="n">
-        <v>37.64542329874003</v>
+        <v>41.92713919642183</v>
       </c>
       <c r="F2" t="n">
-        <v>38.81799260924753</v>
+        <v>31.86723793554827</v>
       </c>
       <c r="G2" t="n">
-        <v>38.7882607605723</v>
+        <v>37.79108922656612</v>
       </c>
       <c r="H2" t="n">
-        <v>43.60543144751204</v>
+        <v>38.91057758539123</v>
       </c>
       <c r="I2" t="n">
-        <v>38.90337375133505</v>
+        <v>40.4493487662286</v>
       </c>
       <c r="J2" t="n">
-        <v>35.38718309637807</v>
+        <v>48.58683605428232</v>
       </c>
       <c r="K2" t="n">
-        <v>49.81452742681991</v>
+        <v>35.45136333713052</v>
       </c>
     </row>
   </sheetData>
@@ -13609,34 +13609,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.04343465698974</v>
+        <v>34.44645559132724</v>
       </c>
       <c r="C2" t="n">
-        <v>39.92329845658806</v>
+        <v>30.71378620624894</v>
       </c>
       <c r="D2" t="n">
-        <v>34.08028976250515</v>
+        <v>41.96945867359436</v>
       </c>
       <c r="E2" t="n">
-        <v>36.13870236337875</v>
+        <v>31.35316246321928</v>
       </c>
       <c r="F2" t="n">
-        <v>41.11797859174946</v>
+        <v>49.10429900430706</v>
       </c>
       <c r="G2" t="n">
-        <v>28.06048042263905</v>
+        <v>41.65670511294064</v>
       </c>
       <c r="H2" t="n">
-        <v>37.04971222982768</v>
+        <v>38.86605824455729</v>
       </c>
       <c r="I2" t="n">
-        <v>44.49648759088806</v>
+        <v>42.19253479439337</v>
       </c>
       <c r="J2" t="n">
-        <v>41.21695388478591</v>
+        <v>54.10130310391623</v>
       </c>
       <c r="K2" t="n">
-        <v>30.68296283232795</v>
+        <v>31.30635588416547</v>
       </c>
     </row>
   </sheetData>
@@ -13715,34 +13715,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.36258520656904</v>
+        <v>41.52670062247953</v>
       </c>
       <c r="C2" t="n">
-        <v>44.80115334988152</v>
+        <v>40.46584573505485</v>
       </c>
       <c r="D2" t="n">
-        <v>41.60463132876837</v>
+        <v>45.64085607223861</v>
       </c>
       <c r="E2" t="n">
-        <v>43.64578249306803</v>
+        <v>36.69206005840376</v>
       </c>
       <c r="F2" t="n">
-        <v>49.27471527534887</v>
+        <v>22.59455323383089</v>
       </c>
       <c r="G2" t="n">
-        <v>30.81561395302769</v>
+        <v>49.52596870900369</v>
       </c>
       <c r="H2" t="n">
-        <v>50.55901118558953</v>
+        <v>49.60105318157153</v>
       </c>
       <c r="I2" t="n">
-        <v>44.94364897577668</v>
+        <v>46.99272608838751</v>
       </c>
       <c r="J2" t="n">
-        <v>28.31285609726263</v>
+        <v>50.38257382979712</v>
       </c>
       <c r="K2" t="n">
-        <v>57.08369343466583</v>
+        <v>35.19375452570804</v>
       </c>
     </row>
   </sheetData>
@@ -13821,34 +13821,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.98697019666563</v>
+        <v>38.30988704564602</v>
       </c>
       <c r="C2" t="n">
-        <v>47.26714015688142</v>
+        <v>32.96836377913294</v>
       </c>
       <c r="D2" t="n">
-        <v>47.7188186755323</v>
+        <v>50.99079254758629</v>
       </c>
       <c r="E2" t="n">
-        <v>48.68209812844359</v>
+        <v>50.93195422579562</v>
       </c>
       <c r="F2" t="n">
-        <v>39.3795466659498</v>
+        <v>45.98618843837149</v>
       </c>
       <c r="G2" t="n">
-        <v>41.88264312567429</v>
+        <v>46.30035788636026</v>
       </c>
       <c r="H2" t="n">
-        <v>36.55820420239029</v>
+        <v>42.38756965293836</v>
       </c>
       <c r="I2" t="n">
-        <v>43.10061421899447</v>
+        <v>31.85657539359903</v>
       </c>
       <c r="J2" t="n">
-        <v>48.4871566410606</v>
+        <v>41.23520167750516</v>
       </c>
       <c r="K2" t="n">
-        <v>38.66135643862512</v>
+        <v>42.32770600562003</v>
       </c>
     </row>
   </sheetData>
@@ -13927,34 +13927,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.22084119088915</v>
+        <v>42.67375249952514</v>
       </c>
       <c r="C2" t="n">
-        <v>47.40961531665034</v>
+        <v>52.08920801517548</v>
       </c>
       <c r="D2" t="n">
-        <v>34.164442379144</v>
+        <v>31.89084583006079</v>
       </c>
       <c r="E2" t="n">
-        <v>32.05498193997661</v>
+        <v>47.21877190326821</v>
       </c>
       <c r="F2" t="n">
-        <v>40.1944683329817</v>
+        <v>46.66365921269258</v>
       </c>
       <c r="G2" t="n">
-        <v>38.33762692012998</v>
+        <v>38.89936226188642</v>
       </c>
       <c r="H2" t="n">
-        <v>54.77351837899653</v>
+        <v>41.10934002328008</v>
       </c>
       <c r="I2" t="n">
-        <v>42.59068896037636</v>
+        <v>55.22812514697094</v>
       </c>
       <c r="J2" t="n">
-        <v>53.30649782232456</v>
+        <v>34.29787028552391</v>
       </c>
       <c r="K2" t="n">
-        <v>45.69880198768023</v>
+        <v>31.76027863695827</v>
       </c>
     </row>
   </sheetData>
@@ -14033,34 +14033,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.25363616882249</v>
+        <v>30.8345876888616</v>
       </c>
       <c r="C2" t="n">
-        <v>42.99001398097923</v>
+        <v>29.68267134085984</v>
       </c>
       <c r="D2" t="n">
-        <v>51.39807589296292</v>
+        <v>40.83689291099758</v>
       </c>
       <c r="E2" t="n">
-        <v>36.10863927589377</v>
+        <v>44.12247261922227</v>
       </c>
       <c r="F2" t="n">
-        <v>49.9653183799055</v>
+        <v>44.89616232252946</v>
       </c>
       <c r="G2" t="n">
-        <v>35.7885884142886</v>
+        <v>33.18929366277444</v>
       </c>
       <c r="H2" t="n">
-        <v>47.0242354646634</v>
+        <v>27.23226658161643</v>
       </c>
       <c r="I2" t="n">
-        <v>45.9876998755657</v>
+        <v>32.27850944728133</v>
       </c>
       <c r="J2" t="n">
-        <v>25.69516789593589</v>
+        <v>57.14774517894593</v>
       </c>
       <c r="K2" t="n">
-        <v>34.49956519188535</v>
+        <v>35.23982491128792</v>
       </c>
     </row>
   </sheetData>
@@ -14139,34 +14139,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.23602218911832</v>
+        <v>42.31109958967303</v>
       </c>
       <c r="C2" t="n">
-        <v>37.21365183027994</v>
+        <v>58.08792247251557</v>
       </c>
       <c r="D2" t="n">
-        <v>26.73786342505265</v>
+        <v>47.74588904207773</v>
       </c>
       <c r="E2" t="n">
-        <v>35.75354383280316</v>
+        <v>35.40103872674094</v>
       </c>
       <c r="F2" t="n">
-        <v>44.34861267351305</v>
+        <v>34.91781858717217</v>
       </c>
       <c r="G2" t="n">
-        <v>48.79246485966457</v>
+        <v>54.75595362724132</v>
       </c>
       <c r="H2" t="n">
-        <v>55.27444665020468</v>
+        <v>44.31893374627396</v>
       </c>
       <c r="I2" t="n">
-        <v>31.23072693399461</v>
+        <v>34.88385795462582</v>
       </c>
       <c r="J2" t="n">
-        <v>47.02321738784852</v>
+        <v>39.80967553040641</v>
       </c>
       <c r="K2" t="n">
-        <v>44.60931463106104</v>
+        <v>27.67628761457252</v>
       </c>
     </row>
   </sheetData>
@@ -14245,34 +14245,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.47247868869987</v>
+        <v>41.90960064908728</v>
       </c>
       <c r="C2" t="n">
-        <v>30.03599371679077</v>
+        <v>42.35278374369572</v>
       </c>
       <c r="D2" t="n">
-        <v>54.04798852986521</v>
+        <v>43.56616899705371</v>
       </c>
       <c r="E2" t="n">
-        <v>51.95168480408021</v>
+        <v>30.32962239032873</v>
       </c>
       <c r="F2" t="n">
-        <v>44.18239610560143</v>
+        <v>39.32027972199376</v>
       </c>
       <c r="G2" t="n">
-        <v>34.87311758532567</v>
+        <v>47.47220581852513</v>
       </c>
       <c r="H2" t="n">
-        <v>34.01866175873046</v>
+        <v>44.50361940912278</v>
       </c>
       <c r="I2" t="n">
-        <v>43.92038357363919</v>
+        <v>39.24141323803062</v>
       </c>
       <c r="J2" t="n">
-        <v>44.39777887339378</v>
+        <v>58.74268420634078</v>
       </c>
       <c r="K2" t="n">
-        <v>47.40229366058594</v>
+        <v>35.31853068197643</v>
       </c>
     </row>
   </sheetData>
@@ -14351,34 +14351,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50.60266374032189</v>
+        <v>33.02562595343392</v>
       </c>
       <c r="C2" t="n">
-        <v>46.08722629107832</v>
+        <v>42.83705296543891</v>
       </c>
       <c r="D2" t="n">
-        <v>35.58150189492203</v>
+        <v>42.44702031143783</v>
       </c>
       <c r="E2" t="n">
-        <v>30.04363960601977</v>
+        <v>32.28454274145985</v>
       </c>
       <c r="F2" t="n">
-        <v>36.79928160322622</v>
+        <v>45.67640698611427</v>
       </c>
       <c r="G2" t="n">
-        <v>38.05033044439912</v>
+        <v>50.5240910304714</v>
       </c>
       <c r="H2" t="n">
-        <v>49.86949751472319</v>
+        <v>38.79020775609448</v>
       </c>
       <c r="I2" t="n">
-        <v>31.2824238904971</v>
+        <v>57.54480431045145</v>
       </c>
       <c r="J2" t="n">
-        <v>57.44806580670006</v>
+        <v>31.44541599867215</v>
       </c>
       <c r="K2" t="n">
-        <v>28.08022050155301</v>
+        <v>28.87882974946213</v>
       </c>
     </row>
   </sheetData>
@@ -14457,34 +14457,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.45984455549557</v>
+        <v>35.42252017201852</v>
       </c>
       <c r="C2" t="n">
-        <v>51.87768096728582</v>
+        <v>56.65984274800587</v>
       </c>
       <c r="D2" t="n">
-        <v>58.26995670168986</v>
+        <v>50.04258378350266</v>
       </c>
       <c r="E2" t="n">
-        <v>54.06613309698663</v>
+        <v>38.79328804617992</v>
       </c>
       <c r="F2" t="n">
-        <v>38.77475080826093</v>
+        <v>26.6591953934009</v>
       </c>
       <c r="G2" t="n">
-        <v>33.30596093911559</v>
+        <v>37.50707048128518</v>
       </c>
       <c r="H2" t="n">
-        <v>32.91836557202708</v>
+        <v>47.35684973754703</v>
       </c>
       <c r="I2" t="n">
-        <v>43.63786811321803</v>
+        <v>61.29663661645674</v>
       </c>
       <c r="J2" t="n">
-        <v>52.01532310760842</v>
+        <v>41.68093463441936</v>
       </c>
       <c r="K2" t="n">
-        <v>43.3767924919599</v>
+        <v>49.64465434826117</v>
       </c>
     </row>
   </sheetData>
@@ -14563,34 +14563,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.03576306922588</v>
+        <v>48.72905909381089</v>
       </c>
       <c r="C2" t="n">
-        <v>20.37671759624394</v>
+        <v>45.8107744798598</v>
       </c>
       <c r="D2" t="n">
-        <v>47.68019585933664</v>
+        <v>47.4397468167701</v>
       </c>
       <c r="E2" t="n">
-        <v>40.73963224385182</v>
+        <v>30.49579555862159</v>
       </c>
       <c r="F2" t="n">
-        <v>49.19309521561105</v>
+        <v>58.20853329982376</v>
       </c>
       <c r="G2" t="n">
-        <v>45.21471223121139</v>
+        <v>47.33120913550767</v>
       </c>
       <c r="H2" t="n">
-        <v>49.63241656502723</v>
+        <v>34.56051148369522</v>
       </c>
       <c r="I2" t="n">
-        <v>38.80333920302865</v>
+        <v>36.36976305838174</v>
       </c>
       <c r="J2" t="n">
-        <v>51.47225780441511</v>
+        <v>50.58263197984496</v>
       </c>
       <c r="K2" t="n">
-        <v>42.38206656814189</v>
+        <v>51.45532701952381</v>
       </c>
     </row>
   </sheetData>
@@ -14669,34 +14669,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.28266741691431</v>
+        <v>44.29317278101465</v>
       </c>
       <c r="C2" t="n">
-        <v>39.64853974207499</v>
+        <v>44.39161850993096</v>
       </c>
       <c r="D2" t="n">
-        <v>36.40787306985946</v>
+        <v>26.87422709099512</v>
       </c>
       <c r="E2" t="n">
-        <v>41.79848494958068</v>
+        <v>31.52138387667755</v>
       </c>
       <c r="F2" t="n">
-        <v>53.30723337428716</v>
+        <v>50.80140879484367</v>
       </c>
       <c r="G2" t="n">
-        <v>45.27701777933213</v>
+        <v>55.62257349269791</v>
       </c>
       <c r="H2" t="n">
-        <v>43.84014641226318</v>
+        <v>52.90482563720764</v>
       </c>
       <c r="I2" t="n">
-        <v>46.92464823537805</v>
+        <v>46.15598292303221</v>
       </c>
       <c r="J2" t="n">
-        <v>45.65182733832398</v>
+        <v>41.19650028536795</v>
       </c>
       <c r="K2" t="n">
-        <v>35.39785462083164</v>
+        <v>41.74909572038849</v>
       </c>
     </row>
   </sheetData>
@@ -14775,34 +14775,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.88189091454289</v>
+        <v>38.05648999281414</v>
       </c>
       <c r="C2" t="n">
-        <v>42.13668443330801</v>
+        <v>29.93098156218627</v>
       </c>
       <c r="D2" t="n">
-        <v>38.53746431356115</v>
+        <v>38.80701902565836</v>
       </c>
       <c r="E2" t="n">
-        <v>37.18675715183249</v>
+        <v>49.68289931653209</v>
       </c>
       <c r="F2" t="n">
-        <v>40.7131826352901</v>
+        <v>37.81177460626618</v>
       </c>
       <c r="G2" t="n">
-        <v>56.37349144572287</v>
+        <v>47.39628421309137</v>
       </c>
       <c r="H2" t="n">
-        <v>45.52286421536495</v>
+        <v>50.11511037953991</v>
       </c>
       <c r="I2" t="n">
-        <v>41.88428083191122</v>
+        <v>36.9166301347731</v>
       </c>
       <c r="J2" t="n">
-        <v>59.08650329077165</v>
+        <v>35.72710126773632</v>
       </c>
       <c r="K2" t="n">
-        <v>43.52125576236762</v>
+        <v>37.94715871931582</v>
       </c>
     </row>
   </sheetData>
@@ -14881,34 +14881,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.86836916150703</v>
+        <v>46.43117470620491</v>
       </c>
       <c r="C2" t="n">
-        <v>35.82076534986673</v>
+        <v>44.29640558289621</v>
       </c>
       <c r="D2" t="n">
-        <v>45.74918286867931</v>
+        <v>34.84654785899992</v>
       </c>
       <c r="E2" t="n">
-        <v>40.92411357704272</v>
+        <v>40.79865296642177</v>
       </c>
       <c r="F2" t="n">
-        <v>45.34919606689303</v>
+        <v>31.3029982618174</v>
       </c>
       <c r="G2" t="n">
-        <v>32.74906166934213</v>
+        <v>37.08686055081219</v>
       </c>
       <c r="H2" t="n">
-        <v>39.92576973593241</v>
+        <v>33.22284605361004</v>
       </c>
       <c r="I2" t="n">
-        <v>24.87024433803531</v>
+        <v>37.33744353087073</v>
       </c>
       <c r="J2" t="n">
-        <v>52.88239361126154</v>
+        <v>36.58243823999828</v>
       </c>
       <c r="K2" t="n">
-        <v>51.39640566887154</v>
+        <v>37.86844096939616</v>
       </c>
     </row>
   </sheetData>
@@ -14987,34 +14987,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.85613475779842</v>
+        <v>35.58264557310182</v>
       </c>
       <c r="C2" t="n">
-        <v>52.56586285179838</v>
+        <v>37.13331240092531</v>
       </c>
       <c r="D2" t="n">
-        <v>53.33648053829903</v>
+        <v>42.42207336458763</v>
       </c>
       <c r="E2" t="n">
-        <v>33.07064425164314</v>
+        <v>52.54619409542003</v>
       </c>
       <c r="F2" t="n">
-        <v>37.02873632407089</v>
+        <v>38.35861822600649</v>
       </c>
       <c r="G2" t="n">
-        <v>32.81047106854499</v>
+        <v>30.47364295819383</v>
       </c>
       <c r="H2" t="n">
-        <v>53.88997161232973</v>
+        <v>33.27041192467566</v>
       </c>
       <c r="I2" t="n">
-        <v>44.89016351501549</v>
+        <v>40.58645357813954</v>
       </c>
       <c r="J2" t="n">
-        <v>39.8179158089156</v>
+        <v>31.51761271717516</v>
       </c>
       <c r="K2" t="n">
-        <v>36.73902684983879</v>
+        <v>49.32532034558569</v>
       </c>
     </row>
   </sheetData>
@@ -15093,34 +15093,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.65244130858949</v>
+        <v>39.01811320789328</v>
       </c>
       <c r="C2" t="n">
-        <v>51.27481170917659</v>
+        <v>32.9833384692912</v>
       </c>
       <c r="D2" t="n">
-        <v>35.51774807816872</v>
+        <v>36.67785535550687</v>
       </c>
       <c r="E2" t="n">
-        <v>43.4569081801689</v>
+        <v>23.04917695484936</v>
       </c>
       <c r="F2" t="n">
-        <v>46.75505554125932</v>
+        <v>44.30287224573168</v>
       </c>
       <c r="G2" t="n">
-        <v>39.87240193358325</v>
+        <v>51.09828356902336</v>
       </c>
       <c r="H2" t="n">
-        <v>32.61356749846939</v>
+        <v>50.8003216126309</v>
       </c>
       <c r="I2" t="n">
-        <v>29.26352135182952</v>
+        <v>45.6611783983313</v>
       </c>
       <c r="J2" t="n">
-        <v>33.36249359364778</v>
+        <v>44.83887971190423</v>
       </c>
       <c r="K2" t="n">
-        <v>39.23857980074997</v>
+        <v>47.24053637438332</v>
       </c>
     </row>
   </sheetData>
@@ -15199,34 +15199,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.94049907782077</v>
+        <v>32.8323886868599</v>
       </c>
       <c r="C2" t="n">
-        <v>47.84672314352892</v>
+        <v>47.13427937010077</v>
       </c>
       <c r="D2" t="n">
-        <v>45.43255638625369</v>
+        <v>52.14017285713685</v>
       </c>
       <c r="E2" t="n">
-        <v>39.86462510732416</v>
+        <v>36.43314958740626</v>
       </c>
       <c r="F2" t="n">
-        <v>34.71919700250012</v>
+        <v>29.60151381778573</v>
       </c>
       <c r="G2" t="n">
-        <v>43.44326798356561</v>
+        <v>43.02890919133417</v>
       </c>
       <c r="H2" t="n">
-        <v>30.32474958418554</v>
+        <v>49.88778793618841</v>
       </c>
       <c r="I2" t="n">
-        <v>31.48440002022688</v>
+        <v>48.66514956762794</v>
       </c>
       <c r="J2" t="n">
-        <v>33.56418248859322</v>
+        <v>39.5355981628276</v>
       </c>
       <c r="K2" t="n">
-        <v>42.64705783196214</v>
+        <v>44.67241143098216</v>
       </c>
     </row>
   </sheetData>
@@ -15305,34 +15305,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.10917653305446</v>
+        <v>43.25364590357398</v>
       </c>
       <c r="C2" t="n">
-        <v>29.49541621047559</v>
+        <v>31.81089825306026</v>
       </c>
       <c r="D2" t="n">
-        <v>38.99221051119205</v>
+        <v>46.03463827760253</v>
       </c>
       <c r="E2" t="n">
-        <v>31.65545372360845</v>
+        <v>37.45418764899127</v>
       </c>
       <c r="F2" t="n">
-        <v>33.0079295131861</v>
+        <v>46.22349189209655</v>
       </c>
       <c r="G2" t="n">
-        <v>41.01837583948218</v>
+        <v>40.02754149607546</v>
       </c>
       <c r="H2" t="n">
-        <v>42.68675637025651</v>
+        <v>39.17143820520212</v>
       </c>
       <c r="I2" t="n">
-        <v>41.30644425337707</v>
+        <v>28.03993261468443</v>
       </c>
       <c r="J2" t="n">
-        <v>46.34080174122921</v>
+        <v>30.54621786815423</v>
       </c>
       <c r="K2" t="n">
-        <v>34.48054889947133</v>
+        <v>35.26545122760446</v>
       </c>
     </row>
   </sheetData>
@@ -15411,34 +15411,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.52342723104999</v>
+        <v>32.71345461012002</v>
       </c>
       <c r="C2" t="n">
-        <v>53.23073536996189</v>
+        <v>30.44781911091724</v>
       </c>
       <c r="D2" t="n">
-        <v>43.8545793348656</v>
+        <v>44.20065061490735</v>
       </c>
       <c r="E2" t="n">
-        <v>31.61186180903486</v>
+        <v>44.11622071070953</v>
       </c>
       <c r="F2" t="n">
-        <v>33.80907384616652</v>
+        <v>34.3944506128221</v>
       </c>
       <c r="G2" t="n">
-        <v>51.18481062198932</v>
+        <v>39.17564922686081</v>
       </c>
       <c r="H2" t="n">
-        <v>29.99688739809884</v>
+        <v>39.27477978248981</v>
       </c>
       <c r="I2" t="n">
-        <v>45.42679169025472</v>
+        <v>41.34715688028319</v>
       </c>
       <c r="J2" t="n">
-        <v>43.3114543112861</v>
+        <v>36.61553117271718</v>
       </c>
       <c r="K2" t="n">
-        <v>28.60056950139438</v>
+        <v>41.3876267310095</v>
       </c>
     </row>
   </sheetData>
@@ -15517,34 +15517,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.24129533488475</v>
+        <v>35.70535836605781</v>
       </c>
       <c r="C2" t="n">
-        <v>26.13593157381842</v>
+        <v>39.29862409172831</v>
       </c>
       <c r="D2" t="n">
-        <v>43.26839141539102</v>
+        <v>38.5983597210999</v>
       </c>
       <c r="E2" t="n">
-        <v>42.10614939956783</v>
+        <v>45.46257787344462</v>
       </c>
       <c r="F2" t="n">
-        <v>39.17099562959695</v>
+        <v>40.54807275106901</v>
       </c>
       <c r="G2" t="n">
-        <v>33.86232184355572</v>
+        <v>25.1486907078257</v>
       </c>
       <c r="H2" t="n">
-        <v>37.64046052790538</v>
+        <v>42.29347147943715</v>
       </c>
       <c r="I2" t="n">
-        <v>36.31933459394298</v>
+        <v>37.00607421486438</v>
       </c>
       <c r="J2" t="n">
-        <v>44.85533976610565</v>
+        <v>40.89870742576558</v>
       </c>
       <c r="K2" t="n">
-        <v>35.4657620301986</v>
+        <v>43.32972238242201</v>
       </c>
     </row>
   </sheetData>
@@ -15623,34 +15623,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.37278205588456</v>
+        <v>41.23676990702923</v>
       </c>
       <c r="C2" t="n">
-        <v>40.75510507182497</v>
+        <v>48.26213381041058</v>
       </c>
       <c r="D2" t="n">
-        <v>47.59052213414481</v>
+        <v>57.92749919348</v>
       </c>
       <c r="E2" t="n">
-        <v>45.03104887262199</v>
+        <v>43.88150397796606</v>
       </c>
       <c r="F2" t="n">
-        <v>36.60123908410184</v>
+        <v>38.69195493646703</v>
       </c>
       <c r="G2" t="n">
-        <v>34.91631267491449</v>
+        <v>44.0835180549069</v>
       </c>
       <c r="H2" t="n">
-        <v>52.6185168127083</v>
+        <v>43.22001955303537</v>
       </c>
       <c r="I2" t="n">
-        <v>47.79739530470106</v>
+        <v>47.09902884248939</v>
       </c>
       <c r="J2" t="n">
-        <v>55.68587341418144</v>
+        <v>43.12782760227861</v>
       </c>
       <c r="K2" t="n">
-        <v>42.94673261662515</v>
+        <v>41.55655755869804</v>
       </c>
     </row>
   </sheetData>
@@ -15729,34 +15729,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.73072053612895</v>
+        <v>34.25693502927506</v>
       </c>
       <c r="C2" t="n">
-        <v>47.3164969030931</v>
+        <v>38.66608846761122</v>
       </c>
       <c r="D2" t="n">
-        <v>32.48753183591831</v>
+        <v>49.92547652358292</v>
       </c>
       <c r="E2" t="n">
-        <v>38.15916307282467</v>
+        <v>37.02218084010397</v>
       </c>
       <c r="F2" t="n">
-        <v>36.23084842504827</v>
+        <v>42.88501196526105</v>
       </c>
       <c r="G2" t="n">
-        <v>49.94774791841849</v>
+        <v>41.12941418556612</v>
       </c>
       <c r="H2" t="n">
-        <v>29.5244350741556</v>
+        <v>32.26667413542926</v>
       </c>
       <c r="I2" t="n">
-        <v>38.80059898163822</v>
+        <v>43.62965279748504</v>
       </c>
       <c r="J2" t="n">
-        <v>34.17310632238068</v>
+        <v>33.0573220498616</v>
       </c>
       <c r="K2" t="n">
-        <v>49.91459568271885</v>
+        <v>73.58473410426009</v>
       </c>
     </row>
   </sheetData>
@@ -15835,34 +15835,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.35489514899353</v>
+        <v>31.78334688730222</v>
       </c>
       <c r="C2" t="n">
-        <v>36.43600015526428</v>
+        <v>51.57993410570225</v>
       </c>
       <c r="D2" t="n">
-        <v>50.01825914240231</v>
+        <v>49.53050953686134</v>
       </c>
       <c r="E2" t="n">
-        <v>35.46594659341881</v>
+        <v>43.59591706341793</v>
       </c>
       <c r="F2" t="n">
-        <v>39.30268357711986</v>
+        <v>34.42540064535319</v>
       </c>
       <c r="G2" t="n">
-        <v>33.15677352346505</v>
+        <v>39.26338260469782</v>
       </c>
       <c r="H2" t="n">
-        <v>46.67361979720602</v>
+        <v>42.61016469782415</v>
       </c>
       <c r="I2" t="n">
-        <v>39.45073243233261</v>
+        <v>37.69273146833046</v>
       </c>
       <c r="J2" t="n">
-        <v>48.80853829948821</v>
+        <v>47.82728793031112</v>
       </c>
       <c r="K2" t="n">
-        <v>38.33253135218353</v>
+        <v>32.09987324510161</v>
       </c>
     </row>
   </sheetData>
@@ -15941,34 +15941,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50.01059311562925</v>
+        <v>40.91712120160056</v>
       </c>
       <c r="C2" t="n">
-        <v>50.46491172959729</v>
+        <v>54.43075213195551</v>
       </c>
       <c r="D2" t="n">
-        <v>37.03081839842664</v>
+        <v>34.0558051531211</v>
       </c>
       <c r="E2" t="n">
-        <v>35.42894450852878</v>
+        <v>36.79721477690825</v>
       </c>
       <c r="F2" t="n">
-        <v>31.08405940189869</v>
+        <v>41.21588702173108</v>
       </c>
       <c r="G2" t="n">
-        <v>56.8437671797183</v>
+        <v>34.56513103598792</v>
       </c>
       <c r="H2" t="n">
-        <v>40.45209999188957</v>
+        <v>48.82861135562333</v>
       </c>
       <c r="I2" t="n">
-        <v>46.29747518921772</v>
+        <v>41.92209624000142</v>
       </c>
       <c r="J2" t="n">
-        <v>27.77996550842258</v>
+        <v>43.83095491313285</v>
       </c>
       <c r="K2" t="n">
-        <v>31.83681242293265</v>
+        <v>24.92311359295483</v>
       </c>
     </row>
   </sheetData>
@@ -16047,34 +16047,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.74598992408374</v>
+        <v>42.40318845814829</v>
       </c>
       <c r="C2" t="n">
-        <v>42.06338187897364</v>
+        <v>38.42897173903754</v>
       </c>
       <c r="D2" t="n">
-        <v>46.81565178918708</v>
+        <v>41.581973407321</v>
       </c>
       <c r="E2" t="n">
-        <v>40.81841971308854</v>
+        <v>43.00892364678066</v>
       </c>
       <c r="F2" t="n">
-        <v>34.84944108562144</v>
+        <v>39.287269435033</v>
       </c>
       <c r="G2" t="n">
-        <v>36.89316921405893</v>
+        <v>48.3836768750091</v>
       </c>
       <c r="H2" t="n">
-        <v>28.60445196641038</v>
+        <v>32.51563453019705</v>
       </c>
       <c r="I2" t="n">
-        <v>46.37216731997416</v>
+        <v>48.80120895116702</v>
       </c>
       <c r="J2" t="n">
-        <v>44.54764046485501</v>
+        <v>45.5582388445243</v>
       </c>
       <c r="K2" t="n">
-        <v>30.14962722654598</v>
+        <v>45.05113597392727</v>
       </c>
     </row>
   </sheetData>
@@ -16153,34 +16153,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.89601269637802</v>
+        <v>38.82277320357824</v>
       </c>
       <c r="C2" t="n">
-        <v>51.43557234936505</v>
+        <v>35.3227133675224</v>
       </c>
       <c r="D2" t="n">
-        <v>34.38164811819279</v>
+        <v>34.99595905544398</v>
       </c>
       <c r="E2" t="n">
-        <v>44.6313260686461</v>
+        <v>42.62289935769812</v>
       </c>
       <c r="F2" t="n">
-        <v>37.58661019276641</v>
+        <v>37.45042346567558</v>
       </c>
       <c r="G2" t="n">
-        <v>35.86251833525642</v>
+        <v>42.0766055504904</v>
       </c>
       <c r="H2" t="n">
-        <v>30.27315375030353</v>
+        <v>36.0294397683412</v>
       </c>
       <c r="I2" t="n">
-        <v>37.02105934641823</v>
+        <v>31.96698698471366</v>
       </c>
       <c r="J2" t="n">
-        <v>49.45425438187623</v>
+        <v>38.60546854285558</v>
       </c>
       <c r="K2" t="n">
-        <v>32.92994925474056</v>
+        <v>40.09070097999503</v>
       </c>
     </row>
   </sheetData>
@@ -16259,34 +16259,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.3965065154778</v>
+        <v>36.1139413692931</v>
       </c>
       <c r="C2" t="n">
-        <v>60.99728337949934</v>
+        <v>36.24312420957683</v>
       </c>
       <c r="D2" t="n">
-        <v>56.63809025608203</v>
+        <v>30.15281271055272</v>
       </c>
       <c r="E2" t="n">
-        <v>35.48999335995606</v>
+        <v>35.84055592231252</v>
       </c>
       <c r="F2" t="n">
-        <v>31.90606980802426</v>
+        <v>36.61249484718294</v>
       </c>
       <c r="G2" t="n">
-        <v>32.57174462670439</v>
+        <v>53.67379734571858</v>
       </c>
       <c r="H2" t="n">
-        <v>39.94613601390988</v>
+        <v>41.88474015755338</v>
       </c>
       <c r="I2" t="n">
-        <v>51.47642790280037</v>
+        <v>47.82981115030486</v>
       </c>
       <c r="J2" t="n">
-        <v>49.13988361330328</v>
+        <v>40.73930999213975</v>
       </c>
       <c r="K2" t="n">
-        <v>48.34018603441182</v>
+        <v>38.9947803668584</v>
       </c>
     </row>
   </sheetData>
@@ -16365,34 +16365,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.72337824455397</v>
+        <v>48.27076373990897</v>
       </c>
       <c r="C2" t="n">
-        <v>48.28729567550894</v>
+        <v>53.2703368852049</v>
       </c>
       <c r="D2" t="n">
-        <v>46.47588248754403</v>
+        <v>47.16529252466633</v>
       </c>
       <c r="E2" t="n">
-        <v>31.14681329932479</v>
+        <v>39.82597990358001</v>
       </c>
       <c r="F2" t="n">
-        <v>49.36472397530137</v>
+        <v>46.21090554649456</v>
       </c>
       <c r="G2" t="n">
-        <v>31.97529296875426</v>
+        <v>43.15640159594155</v>
       </c>
       <c r="H2" t="n">
-        <v>55.64141269833111</v>
+        <v>54.99869054409848</v>
       </c>
       <c r="I2" t="n">
-        <v>56.28129993745522</v>
+        <v>37.65557022523262</v>
       </c>
       <c r="J2" t="n">
-        <v>49.52643983758705</v>
+        <v>40.22057805620729</v>
       </c>
       <c r="K2" t="n">
-        <v>40.52421469316009</v>
+        <v>37.13723882869608</v>
       </c>
     </row>
   </sheetData>
@@ -16471,34 +16471,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.02961615344761</v>
+        <v>49.74205365006367</v>
       </c>
       <c r="C2" t="n">
-        <v>45.36262246268409</v>
+        <v>41.97557650606104</v>
       </c>
       <c r="D2" t="n">
-        <v>35.9556636640536</v>
+        <v>43.99619392966392</v>
       </c>
       <c r="E2" t="n">
-        <v>39.98471412369262</v>
+        <v>38.55568052630458</v>
       </c>
       <c r="F2" t="n">
-        <v>42.01382282131122</v>
+        <v>41.2430942048604</v>
       </c>
       <c r="G2" t="n">
-        <v>39.57035425421546</v>
+        <v>39.98033854994674</v>
       </c>
       <c r="H2" t="n">
-        <v>40.38565523554284</v>
+        <v>33.47365382752751</v>
       </c>
       <c r="I2" t="n">
-        <v>46.73777137865372</v>
+        <v>42.31301728508722</v>
       </c>
       <c r="J2" t="n">
-        <v>40.92352312180932</v>
+        <v>37.6213678786184</v>
       </c>
       <c r="K2" t="n">
-        <v>38.83292633912455</v>
+        <v>39.97013824210564</v>
       </c>
     </row>
   </sheetData>
@@ -16577,34 +16577,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.44450926761171</v>
+        <v>32.98254565168146</v>
       </c>
       <c r="C2" t="n">
-        <v>44.52993753110918</v>
+        <v>40.28182773147263</v>
       </c>
       <c r="D2" t="n">
-        <v>54.63594011150777</v>
+        <v>31.39516101024411</v>
       </c>
       <c r="E2" t="n">
-        <v>38.71684981455387</v>
+        <v>40.02239118182934</v>
       </c>
       <c r="F2" t="n">
-        <v>34.20139472868981</v>
+        <v>30.9603996255237</v>
       </c>
       <c r="G2" t="n">
-        <v>48.17616649079901</v>
+        <v>45.95699605568232</v>
       </c>
       <c r="H2" t="n">
-        <v>39.10954605170162</v>
+        <v>38.14721061343781</v>
       </c>
       <c r="I2" t="n">
-        <v>30.67731526467351</v>
+        <v>42.78759924095779</v>
       </c>
       <c r="J2" t="n">
-        <v>39.57925313078637</v>
+        <v>42.84337681266752</v>
       </c>
       <c r="K2" t="n">
-        <v>37.41348639316648</v>
+        <v>47.32262989106156</v>
       </c>
     </row>
   </sheetData>
@@ -16683,34 +16683,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.26664173600838</v>
+        <v>39.75644702287984</v>
       </c>
       <c r="C2" t="n">
-        <v>39.24606604306599</v>
+        <v>41.63382245947945</v>
       </c>
       <c r="D2" t="n">
-        <v>47.84456428411011</v>
+        <v>35.83500486896882</v>
       </c>
       <c r="E2" t="n">
-        <v>41.69677485000133</v>
+        <v>40.44921997886823</v>
       </c>
       <c r="F2" t="n">
-        <v>41.65906111603373</v>
+        <v>30.46166889955701</v>
       </c>
       <c r="G2" t="n">
-        <v>46.06443809027429</v>
+        <v>47.97273301828424</v>
       </c>
       <c r="H2" t="n">
-        <v>54.68856232845553</v>
+        <v>35.72889586351747</v>
       </c>
       <c r="I2" t="n">
-        <v>50.57057981193989</v>
+        <v>36.74974976711251</v>
       </c>
       <c r="J2" t="n">
-        <v>36.32730346143761</v>
+        <v>38.63975526002081</v>
       </c>
       <c r="K2" t="n">
-        <v>30.32880069267556</v>
+        <v>54.31159830547914</v>
       </c>
     </row>
   </sheetData>
@@ -16789,34 +16789,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.89439849031916</v>
+        <v>45.01622392338524</v>
       </c>
       <c r="C2" t="n">
-        <v>60.49524069376177</v>
+        <v>56.90203642319787</v>
       </c>
       <c r="D2" t="n">
-        <v>52.76628929164567</v>
+        <v>46.66416978942468</v>
       </c>
       <c r="E2" t="n">
-        <v>30.82365727757986</v>
+        <v>47.1633396043946</v>
       </c>
       <c r="F2" t="n">
-        <v>31.1865435117699</v>
+        <v>35.82684015253724</v>
       </c>
       <c r="G2" t="n">
-        <v>43.70831636376179</v>
+        <v>42.73575407531578</v>
       </c>
       <c r="H2" t="n">
-        <v>33.05154098723576</v>
+        <v>31.44210682695136</v>
       </c>
       <c r="I2" t="n">
-        <v>47.06256310316672</v>
+        <v>30.68141635046573</v>
       </c>
       <c r="J2" t="n">
-        <v>39.55738531400075</v>
+        <v>39.60264889848443</v>
       </c>
       <c r="K2" t="n">
-        <v>49.37045626469861</v>
+        <v>51.44044625076319</v>
       </c>
     </row>
   </sheetData>
@@ -16895,34 +16895,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.41952185742753</v>
+        <v>41.85982409237955</v>
       </c>
       <c r="C2" t="n">
-        <v>53.44730273288538</v>
+        <v>44.04921811622263</v>
       </c>
       <c r="D2" t="n">
-        <v>33.32533889594056</v>
+        <v>42.69057881674752</v>
       </c>
       <c r="E2" t="n">
-        <v>49.86999239731056</v>
+        <v>35.3744906371056</v>
       </c>
       <c r="F2" t="n">
-        <v>36.35740906832254</v>
+        <v>31.59322591162984</v>
       </c>
       <c r="G2" t="n">
-        <v>44.50435448330501</v>
+        <v>38.86173601497406</v>
       </c>
       <c r="H2" t="n">
-        <v>35.07469879442804</v>
+        <v>18.30894358057951</v>
       </c>
       <c r="I2" t="n">
-        <v>44.68389382822892</v>
+        <v>39.74318700091469</v>
       </c>
       <c r="J2" t="n">
-        <v>33.14197810541928</v>
+        <v>42.38144430186753</v>
       </c>
       <c r="K2" t="n">
-        <v>42.52413835783233</v>
+        <v>44.54305486203778</v>
       </c>
     </row>
   </sheetData>
@@ -17001,34 +17001,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.32603841221793</v>
+        <v>46.45794513388842</v>
       </c>
       <c r="C2" t="n">
-        <v>34.39879441722597</v>
+        <v>48.65787366839543</v>
       </c>
       <c r="D2" t="n">
-        <v>28.93262548537971</v>
+        <v>40.57351424917817</v>
       </c>
       <c r="E2" t="n">
-        <v>46.78397338336154</v>
+        <v>41.03204221804343</v>
       </c>
       <c r="F2" t="n">
-        <v>34.82288012422347</v>
+        <v>27.26776905100474</v>
       </c>
       <c r="G2" t="n">
-        <v>40.60593561402487</v>
+        <v>27.68527388893607</v>
       </c>
       <c r="H2" t="n">
-        <v>41.80672991599419</v>
+        <v>50.83750450666026</v>
       </c>
       <c r="I2" t="n">
-        <v>54.62017816805669</v>
+        <v>42.33138741183349</v>
       </c>
       <c r="J2" t="n">
-        <v>45.29474235280083</v>
+        <v>39.46833091346325</v>
       </c>
       <c r="K2" t="n">
-        <v>34.16846623154125</v>
+        <v>36.36194829399727</v>
       </c>
     </row>
   </sheetData>
@@ -17107,34 +17107,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.11737403718276</v>
+        <v>37.91460893482194</v>
       </c>
       <c r="C2" t="n">
-        <v>40.87635922074254</v>
+        <v>21.56402828069924</v>
       </c>
       <c r="D2" t="n">
-        <v>44.48028814752092</v>
+        <v>41.07874228617203</v>
       </c>
       <c r="E2" t="n">
-        <v>23.15967023442767</v>
+        <v>35.79928459801474</v>
       </c>
       <c r="F2" t="n">
-        <v>50.08157106654897</v>
+        <v>39.17327473042024</v>
       </c>
       <c r="G2" t="n">
-        <v>43.85997410972421</v>
+        <v>42.03138380561165</v>
       </c>
       <c r="H2" t="n">
-        <v>40.90257054767221</v>
+        <v>39.26672862674182</v>
       </c>
       <c r="I2" t="n">
-        <v>38.46773418810515</v>
+        <v>48.98932311257037</v>
       </c>
       <c r="J2" t="n">
-        <v>42.54443694522662</v>
+        <v>36.57734833308684</v>
       </c>
       <c r="K2" t="n">
-        <v>41.61564902771779</v>
+        <v>42.88146227655648</v>
       </c>
     </row>
   </sheetData>
@@ -17213,34 +17213,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.80973566074284</v>
+        <v>41.50118040776037</v>
       </c>
       <c r="C2" t="n">
-        <v>51.98355728182431</v>
+        <v>37.44548500262787</v>
       </c>
       <c r="D2" t="n">
-        <v>49.0163891969377</v>
+        <v>51.21560479929127</v>
       </c>
       <c r="E2" t="n">
-        <v>37.34440225835211</v>
+        <v>38.78971201959709</v>
       </c>
       <c r="F2" t="n">
-        <v>64.73876391817504</v>
+        <v>28.44160661171616</v>
       </c>
       <c r="G2" t="n">
-        <v>41.74337721705641</v>
+        <v>47.47397089694802</v>
       </c>
       <c r="H2" t="n">
-        <v>46.81790616558691</v>
+        <v>36.53692970573826</v>
       </c>
       <c r="I2" t="n">
-        <v>44.36619870147163</v>
+        <v>45.84876464739383</v>
       </c>
       <c r="J2" t="n">
-        <v>41.89236119091989</v>
+        <v>59.75151813038547</v>
       </c>
       <c r="K2" t="n">
-        <v>29.45811016000884</v>
+        <v>37.8385988960471</v>
       </c>
     </row>
   </sheetData>
@@ -17319,34 +17319,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.51586435835427</v>
+        <v>32.68980690791428</v>
       </c>
       <c r="C2" t="n">
-        <v>46.64572556670498</v>
+        <v>34.61152892698351</v>
       </c>
       <c r="D2" t="n">
-        <v>55.78799034641629</v>
+        <v>39.40898943856037</v>
       </c>
       <c r="E2" t="n">
-        <v>26.7018086329525</v>
+        <v>34.66486877159923</v>
       </c>
       <c r="F2" t="n">
-        <v>28.87314773582638</v>
+        <v>60.21052840687187</v>
       </c>
       <c r="G2" t="n">
-        <v>32.94383818079847</v>
+        <v>49.01489165025908</v>
       </c>
       <c r="H2" t="n">
-        <v>46.94665579858101</v>
+        <v>37.72124263545518</v>
       </c>
       <c r="I2" t="n">
-        <v>44.26263356009768</v>
+        <v>39.06704308892579</v>
       </c>
       <c r="J2" t="n">
-        <v>59.24941333063904</v>
+        <v>14.87353886780343</v>
       </c>
       <c r="K2" t="n">
-        <v>37.98999161820911</v>
+        <v>47.20851375784665</v>
       </c>
     </row>
   </sheetData>
@@ -17425,34 +17425,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.34638749258673</v>
+        <v>39.45089430979953</v>
       </c>
       <c r="C2" t="n">
-        <v>47.6598930847459</v>
+        <v>39.83096222760857</v>
       </c>
       <c r="D2" t="n">
-        <v>58.47004521970785</v>
+        <v>35.97353269617837</v>
       </c>
       <c r="E2" t="n">
-        <v>46.17979170190965</v>
+        <v>30.38746090983773</v>
       </c>
       <c r="F2" t="n">
-        <v>38.05611839786415</v>
+        <v>53.46087208404543</v>
       </c>
       <c r="G2" t="n">
-        <v>41.18572134145288</v>
+        <v>32.86919861320487</v>
       </c>
       <c r="H2" t="n">
-        <v>43.19055450981174</v>
+        <v>31.67288261489044</v>
       </c>
       <c r="I2" t="n">
-        <v>39.72440867135284</v>
+        <v>46.97115794373494</v>
       </c>
       <c r="J2" t="n">
-        <v>57.81424228677059</v>
+        <v>32.94000533790692</v>
       </c>
       <c r="K2" t="n">
-        <v>27.42023687822827</v>
+        <v>34.99565149380805</v>
       </c>
     </row>
   </sheetData>
@@ -17531,34 +17531,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.06055901625725</v>
+        <v>31.45041165443901</v>
       </c>
       <c r="C2" t="n">
-        <v>43.11990834305635</v>
+        <v>69.09593516366149</v>
       </c>
       <c r="D2" t="n">
-        <v>43.31636694816449</v>
+        <v>47.52155082971682</v>
       </c>
       <c r="E2" t="n">
-        <v>58.37179627411462</v>
+        <v>38.95706902401236</v>
       </c>
       <c r="F2" t="n">
-        <v>51.01055606827498</v>
+        <v>43.51298624989574</v>
       </c>
       <c r="G2" t="n">
-        <v>33.08171373886023</v>
+        <v>40.67435849323812</v>
       </c>
       <c r="H2" t="n">
-        <v>43.56049933011017</v>
+        <v>29.77688009609374</v>
       </c>
       <c r="I2" t="n">
-        <v>49.94586023757654</v>
+        <v>48.64649271205139</v>
       </c>
       <c r="J2" t="n">
-        <v>40.50013001355266</v>
+        <v>46.30062335528211</v>
       </c>
       <c r="K2" t="n">
-        <v>32.40865652624563</v>
+        <v>46.42275628792649</v>
       </c>
     </row>
   </sheetData>
@@ -17637,34 +17637,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.93280092723537</v>
+        <v>39.42073101759016</v>
       </c>
       <c r="C2" t="n">
-        <v>42.70446502322484</v>
+        <v>48.10273545726845</v>
       </c>
       <c r="D2" t="n">
-        <v>49.4409201499506</v>
+        <v>28.32632164943787</v>
       </c>
       <c r="E2" t="n">
-        <v>34.55638825134285</v>
+        <v>46.88340152424848</v>
       </c>
       <c r="F2" t="n">
-        <v>40.81645062352988</v>
+        <v>48.39155525077568</v>
       </c>
       <c r="G2" t="n">
-        <v>38.89296332447466</v>
+        <v>40.50706699981107</v>
       </c>
       <c r="H2" t="n">
-        <v>52.15224969711612</v>
+        <v>40.31539369160505</v>
       </c>
       <c r="I2" t="n">
-        <v>49.23988291205474</v>
+        <v>38.87949885581156</v>
       </c>
       <c r="J2" t="n">
-        <v>60.15933722764478</v>
+        <v>54.78024346438085</v>
       </c>
       <c r="K2" t="n">
-        <v>44.17062052513429</v>
+        <v>47.95039088642623</v>
       </c>
     </row>
   </sheetData>
@@ -17743,34 +17743,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.55934952295419</v>
+        <v>43.3027913328885</v>
       </c>
       <c r="C2" t="n">
-        <v>32.56465459510058</v>
+        <v>53.66043831286741</v>
       </c>
       <c r="D2" t="n">
-        <v>54.86689002641894</v>
+        <v>49.05085073739018</v>
       </c>
       <c r="E2" t="n">
-        <v>42.63710114688214</v>
+        <v>42.78186006184799</v>
       </c>
       <c r="F2" t="n">
-        <v>40.31172070456405</v>
+        <v>38.46942641966157</v>
       </c>
       <c r="G2" t="n">
-        <v>45.02895427888892</v>
+        <v>40.25087892269009</v>
       </c>
       <c r="H2" t="n">
-        <v>47.19950522699671</v>
+        <v>45.43527726545909</v>
       </c>
       <c r="I2" t="n">
-        <v>48.93902878521331</v>
+        <v>34.5422181984199</v>
       </c>
       <c r="J2" t="n">
-        <v>45.72424786548394</v>
+        <v>47.87886006680775</v>
       </c>
       <c r="K2" t="n">
-        <v>38.25119185243379</v>
+        <v>37.64499902169509</v>
       </c>
     </row>
   </sheetData>
@@ -17849,34 +17849,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.30690882921049</v>
+        <v>39.53653340483583</v>
       </c>
       <c r="C2" t="n">
-        <v>53.12414785982347</v>
+        <v>37.66666149691</v>
       </c>
       <c r="D2" t="n">
-        <v>34.52531672793064</v>
+        <v>42.4841726754624</v>
       </c>
       <c r="E2" t="n">
-        <v>50.10336094493829</v>
+        <v>37.67807936049265</v>
       </c>
       <c r="F2" t="n">
-        <v>40.70852064558155</v>
+        <v>38.53282702019192</v>
       </c>
       <c r="G2" t="n">
-        <v>39.58219866868794</v>
+        <v>51.89938385280453</v>
       </c>
       <c r="H2" t="n">
-        <v>32.5185129093963</v>
+        <v>24.7156039998189</v>
       </c>
       <c r="I2" t="n">
-        <v>41.74192834052268</v>
+        <v>46.86531926446545</v>
       </c>
       <c r="J2" t="n">
-        <v>49.11261859213871</v>
+        <v>54.01984335887837</v>
       </c>
       <c r="K2" t="n">
-        <v>37.77821444499671</v>
+        <v>43.73684076978272</v>
       </c>
     </row>
   </sheetData>
@@ -17955,34 +17955,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49.19531232062479</v>
+        <v>38.17566638188902</v>
       </c>
       <c r="C2" t="n">
-        <v>48.53688176589841</v>
+        <v>38.54243394496699</v>
       </c>
       <c r="D2" t="n">
-        <v>34.63553682368418</v>
+        <v>46.16928021587607</v>
       </c>
       <c r="E2" t="n">
-        <v>39.34593424057707</v>
+        <v>33.87957770366973</v>
       </c>
       <c r="F2" t="n">
-        <v>37.00577921813789</v>
+        <v>43.20812252882082</v>
       </c>
       <c r="G2" t="n">
-        <v>50.32945083422159</v>
+        <v>34.506379293542</v>
       </c>
       <c r="H2" t="n">
-        <v>39.94917729695232</v>
+        <v>38.04018045831292</v>
       </c>
       <c r="I2" t="n">
-        <v>42.75190649452604</v>
+        <v>31.69569949885099</v>
       </c>
       <c r="J2" t="n">
-        <v>35.28524404866877</v>
+        <v>36.64446501876885</v>
       </c>
       <c r="K2" t="n">
-        <v>36.04974723803177</v>
+        <v>41.90689904286119</v>
       </c>
     </row>
   </sheetData>
@@ -18061,34 +18061,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.11055463372329</v>
+        <v>35.4178271640214</v>
       </c>
       <c r="C2" t="n">
-        <v>51.56135831234264</v>
+        <v>27.22718733310859</v>
       </c>
       <c r="D2" t="n">
-        <v>32.1128412747392</v>
+        <v>46.44304432712423</v>
       </c>
       <c r="E2" t="n">
-        <v>43.00890224781094</v>
+        <v>16.66663155055877</v>
       </c>
       <c r="F2" t="n">
-        <v>36.85278166522136</v>
+        <v>34.57459912361831</v>
       </c>
       <c r="G2" t="n">
-        <v>35.46564446273338</v>
+        <v>40.03219966830866</v>
       </c>
       <c r="H2" t="n">
-        <v>31.13482102696016</v>
+        <v>35.79373745862533</v>
       </c>
       <c r="I2" t="n">
-        <v>37.50401567061039</v>
+        <v>36.42821653443553</v>
       </c>
       <c r="J2" t="n">
-        <v>38.5837066291186</v>
+        <v>51.86606868177092</v>
       </c>
       <c r="K2" t="n">
-        <v>29.25754006242215</v>
+        <v>41.95667095164234</v>
       </c>
     </row>
   </sheetData>
@@ -18167,34 +18167,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.85386140379391</v>
+        <v>48.12951319190354</v>
       </c>
       <c r="C2" t="n">
-        <v>47.24020724474723</v>
+        <v>53.88552489077368</v>
       </c>
       <c r="D2" t="n">
-        <v>60.33310629658578</v>
+        <v>41.45697474607929</v>
       </c>
       <c r="E2" t="n">
-        <v>42.84584975665237</v>
+        <v>40.56050679451636</v>
       </c>
       <c r="F2" t="n">
-        <v>37.16874447059978</v>
+        <v>29.29811768250764</v>
       </c>
       <c r="G2" t="n">
-        <v>49.84610137965691</v>
+        <v>42.58011735563414</v>
       </c>
       <c r="H2" t="n">
-        <v>37.62067166309608</v>
+        <v>31.90708255373931</v>
       </c>
       <c r="I2" t="n">
-        <v>47.69317420463655</v>
+        <v>35.79032634241664</v>
       </c>
       <c r="J2" t="n">
-        <v>42.74349377882065</v>
+        <v>34.46685187059048</v>
       </c>
       <c r="K2" t="n">
-        <v>42.94297007014512</v>
+        <v>46.60374238362404</v>
       </c>
     </row>
   </sheetData>
@@ -18273,34 +18273,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.5679473062514</v>
+        <v>46.66313464920998</v>
       </c>
       <c r="C2" t="n">
-        <v>37.81548001628757</v>
+        <v>48.27528437868538</v>
       </c>
       <c r="D2" t="n">
-        <v>47.32256392527115</v>
+        <v>33.77856384909045</v>
       </c>
       <c r="E2" t="n">
-        <v>42.76570738444244</v>
+        <v>37.85003658103615</v>
       </c>
       <c r="F2" t="n">
-        <v>40.37742241297495</v>
+        <v>47.1754222405841</v>
       </c>
       <c r="G2" t="n">
-        <v>47.18378778979914</v>
+        <v>45.33680623506415</v>
       </c>
       <c r="H2" t="n">
-        <v>41.75197059534641</v>
+        <v>43.61536560551261</v>
       </c>
       <c r="I2" t="n">
-        <v>58.37288429245512</v>
+        <v>43.27093604018997</v>
       </c>
       <c r="J2" t="n">
-        <v>56.50285431303852</v>
+        <v>35.83564489023661</v>
       </c>
       <c r="K2" t="n">
-        <v>30.1690343799815</v>
+        <v>34.12675008524005</v>
       </c>
     </row>
   </sheetData>
@@ -18379,34 +18379,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>48.54960314960691</v>
+        <v>31.43330775982816</v>
       </c>
       <c r="C2" t="n">
-        <v>57.30613919019507</v>
+        <v>35.76652380499289</v>
       </c>
       <c r="D2" t="n">
-        <v>34.12663934344885</v>
+        <v>46.20298148609901</v>
       </c>
       <c r="E2" t="n">
-        <v>48.36609503101807</v>
+        <v>49.14000954993851</v>
       </c>
       <c r="F2" t="n">
-        <v>33.00886466633042</v>
+        <v>39.21563758514624</v>
       </c>
       <c r="G2" t="n">
-        <v>36.53867493814717</v>
+        <v>39.46846523202936</v>
       </c>
       <c r="H2" t="n">
-        <v>43.22819273311514</v>
+        <v>45.59244435797503</v>
       </c>
       <c r="I2" t="n">
-        <v>41.53324990345541</v>
+        <v>34.48951884367386</v>
       </c>
       <c r="J2" t="n">
-        <v>27.21273490942579</v>
+        <v>34.87935038762144</v>
       </c>
       <c r="K2" t="n">
-        <v>42.14936235293414</v>
+        <v>44.29819131112264</v>
       </c>
     </row>
   </sheetData>
@@ -18485,34 +18485,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.35933951635594</v>
+        <v>44.37372936795713</v>
       </c>
       <c r="C2" t="n">
-        <v>55.24545773022555</v>
+        <v>42.12354790685691</v>
       </c>
       <c r="D2" t="n">
-        <v>28.54406004391808</v>
+        <v>38.40470243139736</v>
       </c>
       <c r="E2" t="n">
-        <v>41.2195472695695</v>
+        <v>36.15384618002118</v>
       </c>
       <c r="F2" t="n">
-        <v>47.09013213515673</v>
+        <v>35.00784291288304</v>
       </c>
       <c r="G2" t="n">
-        <v>37.13077267960781</v>
+        <v>30.12948855751518</v>
       </c>
       <c r="H2" t="n">
-        <v>36.39376041318762</v>
+        <v>32.16066742071132</v>
       </c>
       <c r="I2" t="n">
-        <v>53.31402684175744</v>
+        <v>34.59243794105069</v>
       </c>
       <c r="J2" t="n">
-        <v>36.93856060414992</v>
+        <v>39.86396234641442</v>
       </c>
       <c r="K2" t="n">
-        <v>31.90743320767756</v>
+        <v>32.86824354882828</v>
       </c>
     </row>
   </sheetData>
@@ -18591,34 +18591,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.99213166285386</v>
+        <v>62.51131528063725</v>
       </c>
       <c r="C2" t="n">
-        <v>34.58011488063474</v>
+        <v>41.82274108627852</v>
       </c>
       <c r="D2" t="n">
-        <v>63.17671066884328</v>
+        <v>39.37958155061315</v>
       </c>
       <c r="E2" t="n">
-        <v>53.18115298997706</v>
+        <v>64.61784891557551</v>
       </c>
       <c r="F2" t="n">
-        <v>46.19605398201762</v>
+        <v>31.86486219380767</v>
       </c>
       <c r="G2" t="n">
-        <v>41.20730531314594</v>
+        <v>45.42711405225523</v>
       </c>
       <c r="H2" t="n">
-        <v>49.07711106114314</v>
+        <v>40.97486358897509</v>
       </c>
       <c r="I2" t="n">
-        <v>39.98329093394926</v>
+        <v>36.58997347475766</v>
       </c>
       <c r="J2" t="n">
-        <v>54.66835894369002</v>
+        <v>34.41846948155369</v>
       </c>
       <c r="K2" t="n">
-        <v>42.98510229548936</v>
+        <v>42.14735519777027</v>
       </c>
     </row>
   </sheetData>
@@ -18697,34 +18697,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.71367113815439</v>
+        <v>63.60369962250034</v>
       </c>
       <c r="C2" t="n">
-        <v>47.6934683610436</v>
+        <v>48.22825851464558</v>
       </c>
       <c r="D2" t="n">
-        <v>55.75666420146113</v>
+        <v>47.88186119136418</v>
       </c>
       <c r="E2" t="n">
-        <v>40.73666987655702</v>
+        <v>48.24681688896861</v>
       </c>
       <c r="F2" t="n">
-        <v>40.2569905371892</v>
+        <v>41.61200298826575</v>
       </c>
       <c r="G2" t="n">
-        <v>44.2523064007695</v>
+        <v>41.12739164283407</v>
       </c>
       <c r="H2" t="n">
-        <v>40.41104527222697</v>
+        <v>40.84881945187296</v>
       </c>
       <c r="I2" t="n">
-        <v>37.03474233035788</v>
+        <v>34.86078776871282</v>
       </c>
       <c r="J2" t="n">
-        <v>54.19188901177019</v>
+        <v>44.49157906768249</v>
       </c>
       <c r="K2" t="n">
-        <v>42.26154331786429</v>
+        <v>50.70981705701411</v>
       </c>
     </row>
   </sheetData>
@@ -18803,34 +18803,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.88211405868366</v>
+        <v>58.92988502408817</v>
       </c>
       <c r="C2" t="n">
-        <v>34.29106948421087</v>
+        <v>48.44277942773002</v>
       </c>
       <c r="D2" t="n">
-        <v>54.12236840000906</v>
+        <v>35.58126838834441</v>
       </c>
       <c r="E2" t="n">
-        <v>33.87360628502886</v>
+        <v>31.44887168695905</v>
       </c>
       <c r="F2" t="n">
-        <v>45.54808951247846</v>
+        <v>44.13622465353065</v>
       </c>
       <c r="G2" t="n">
-        <v>34.52029055790052</v>
+        <v>31.89742457031442</v>
       </c>
       <c r="H2" t="n">
-        <v>60.66624416751274</v>
+        <v>41.50456705886042</v>
       </c>
       <c r="I2" t="n">
-        <v>24.0896591754271</v>
+        <v>55.76557356891057</v>
       </c>
       <c r="J2" t="n">
-        <v>41.99049508759737</v>
+        <v>55.77372382808036</v>
       </c>
       <c r="K2" t="n">
-        <v>43.72722549408912</v>
+        <v>48.13629336007916</v>
       </c>
     </row>
   </sheetData>
@@ -18909,34 +18909,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.98499489545704</v>
+        <v>44.07679277578714</v>
       </c>
       <c r="C2" t="n">
-        <v>57.97811135598663</v>
+        <v>33.03081649488477</v>
       </c>
       <c r="D2" t="n">
-        <v>24.84110349245286</v>
+        <v>33.39220733904304</v>
       </c>
       <c r="E2" t="n">
-        <v>31.52820359507292</v>
+        <v>33.31447063683147</v>
       </c>
       <c r="F2" t="n">
-        <v>33.53864242634983</v>
+        <v>43.76540424300766</v>
       </c>
       <c r="G2" t="n">
-        <v>36.44124440419107</v>
+        <v>45.28648065825737</v>
       </c>
       <c r="H2" t="n">
-        <v>40.01424655661939</v>
+        <v>31.93092476605001</v>
       </c>
       <c r="I2" t="n">
-        <v>36.20998971627852</v>
+        <v>38.09146950328119</v>
       </c>
       <c r="J2" t="n">
-        <v>42.28940168997424</v>
+        <v>31.23666833252891</v>
       </c>
       <c r="K2" t="n">
-        <v>48.01024571077565</v>
+        <v>27.76847537725181</v>
       </c>
     </row>
   </sheetData>
@@ -19015,34 +19015,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>53.00541537305028</v>
+        <v>41.60528197204412</v>
       </c>
       <c r="C2" t="n">
-        <v>48.71473308703285</v>
+        <v>45.14254365801965</v>
       </c>
       <c r="D2" t="n">
-        <v>36.41968275566071</v>
+        <v>56.34198539452052</v>
       </c>
       <c r="E2" t="n">
-        <v>33.74033473798006</v>
+        <v>43.62074831522313</v>
       </c>
       <c r="F2" t="n">
-        <v>55.18470321083388</v>
+        <v>41.30966525983627</v>
       </c>
       <c r="G2" t="n">
-        <v>43.23001560387395</v>
+        <v>42.12233485436818</v>
       </c>
       <c r="H2" t="n">
-        <v>43.966791951837</v>
+        <v>41.950048854355</v>
       </c>
       <c r="I2" t="n">
-        <v>35.93771813692288</v>
+        <v>45.49534051520445</v>
       </c>
       <c r="J2" t="n">
-        <v>39.48623038023167</v>
+        <v>39.61858046476655</v>
       </c>
       <c r="K2" t="n">
-        <v>68.0180844477986</v>
+        <v>33.45550847109947</v>
       </c>
     </row>
   </sheetData>
@@ -19121,34 +19121,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.45807073670338</v>
+        <v>36.06917366640091</v>
       </c>
       <c r="C2" t="n">
-        <v>41.71999834691766</v>
+        <v>29.30508445968513</v>
       </c>
       <c r="D2" t="n">
-        <v>41.61466323982181</v>
+        <v>40.21349405732132</v>
       </c>
       <c r="E2" t="n">
-        <v>32.88744683513383</v>
+        <v>45.86851916494088</v>
       </c>
       <c r="F2" t="n">
-        <v>46.85443971407794</v>
+        <v>47.69621592742374</v>
       </c>
       <c r="G2" t="n">
-        <v>53.56680671435166</v>
+        <v>32.73499481062986</v>
       </c>
       <c r="H2" t="n">
-        <v>38.26122511629559</v>
+        <v>47.32812464103996</v>
       </c>
       <c r="I2" t="n">
-        <v>49.19194207147046</v>
+        <v>58.16868895165841</v>
       </c>
       <c r="J2" t="n">
-        <v>57.65532714113612</v>
+        <v>31.61768595648689</v>
       </c>
       <c r="K2" t="n">
-        <v>40.52584820000857</v>
+        <v>49.54201150613791</v>
       </c>
     </row>
   </sheetData>
@@ -19227,34 +19227,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.95997397447193</v>
+        <v>39.87933538593099</v>
       </c>
       <c r="C2" t="n">
-        <v>44.29426533555465</v>
+        <v>40.1088527854829</v>
       </c>
       <c r="D2" t="n">
-        <v>35.72188345304465</v>
+        <v>43.26842681782892</v>
       </c>
       <c r="E2" t="n">
-        <v>44.44385463190761</v>
+        <v>37.91877962041531</v>
       </c>
       <c r="F2" t="n">
-        <v>37.96393237338935</v>
+        <v>40.56684265745658</v>
       </c>
       <c r="G2" t="n">
-        <v>38.85294495106405</v>
+        <v>49.01378734610211</v>
       </c>
       <c r="H2" t="n">
-        <v>35.67080509027276</v>
+        <v>30.07006735002648</v>
       </c>
       <c r="I2" t="n">
-        <v>46.6522915537989</v>
+        <v>40.16805150571169</v>
       </c>
       <c r="J2" t="n">
-        <v>52.5808250619382</v>
+        <v>37.50587568595673</v>
       </c>
       <c r="K2" t="n">
-        <v>36.39617075878764</v>
+        <v>36.73313466056961</v>
       </c>
     </row>
   </sheetData>
@@ -19333,34 +19333,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.30823562455951</v>
+        <v>35.71123496923395</v>
       </c>
       <c r="C2" t="n">
-        <v>42.02070249571815</v>
+        <v>40.27199491059212</v>
       </c>
       <c r="D2" t="n">
-        <v>50.92711439763028</v>
+        <v>35.42955544049335</v>
       </c>
       <c r="E2" t="n">
-        <v>38.81365176793035</v>
+        <v>34.4775842760882</v>
       </c>
       <c r="F2" t="n">
-        <v>38.5968403723416</v>
+        <v>40.60584746099536</v>
       </c>
       <c r="G2" t="n">
-        <v>35.38593833706256</v>
+        <v>33.97237644764073</v>
       </c>
       <c r="H2" t="n">
-        <v>41.13132465716512</v>
+        <v>37.03658037315371</v>
       </c>
       <c r="I2" t="n">
-        <v>42.09405512231657</v>
+        <v>49.44988956403913</v>
       </c>
       <c r="J2" t="n">
-        <v>49.7862691633231</v>
+        <v>45.12434850383497</v>
       </c>
       <c r="K2" t="n">
-        <v>37.95237077093542</v>
+        <v>39.23770347411967</v>
       </c>
     </row>
   </sheetData>
@@ -19439,34 +19439,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.92019296459</v>
+        <v>38.63189411173707</v>
       </c>
       <c r="C2" t="n">
-        <v>46.49919485902925</v>
+        <v>47.66612111057959</v>
       </c>
       <c r="D2" t="n">
-        <v>38.33640845747388</v>
+        <v>40.62392840806446</v>
       </c>
       <c r="E2" t="n">
-        <v>37.52041483981581</v>
+        <v>49.86973220491738</v>
       </c>
       <c r="F2" t="n">
-        <v>25.25692885638853</v>
+        <v>36.71760798779393</v>
       </c>
       <c r="G2" t="n">
-        <v>56.49156707189138</v>
+        <v>38.65475763451362</v>
       </c>
       <c r="H2" t="n">
-        <v>44.56078917578598</v>
+        <v>28.89942558884365</v>
       </c>
       <c r="I2" t="n">
-        <v>39.01905700419164</v>
+        <v>30.23244745530285</v>
       </c>
       <c r="J2" t="n">
-        <v>56.20235042031186</v>
+        <v>29.60345445769175</v>
       </c>
       <c r="K2" t="n">
-        <v>41.68733038748924</v>
+        <v>55.81464166077782</v>
       </c>
     </row>
   </sheetData>
@@ -19545,34 +19545,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.05177151774011</v>
+        <v>27.3321986112423</v>
       </c>
       <c r="C2" t="n">
-        <v>41.2293181167321</v>
+        <v>37.8521147893743</v>
       </c>
       <c r="D2" t="n">
-        <v>48.61931830093765</v>
+        <v>38.82222932409386</v>
       </c>
       <c r="E2" t="n">
-        <v>42.56375836249011</v>
+        <v>43.71334786116451</v>
       </c>
       <c r="F2" t="n">
-        <v>46.40995334946948</v>
+        <v>45.98354861646445</v>
       </c>
       <c r="G2" t="n">
-        <v>30.78520973757945</v>
+        <v>32.27513626400563</v>
       </c>
       <c r="H2" t="n">
-        <v>31.56708737503189</v>
+        <v>58.31134844686794</v>
       </c>
       <c r="I2" t="n">
-        <v>39.47347204023601</v>
+        <v>39.3643046004799</v>
       </c>
       <c r="J2" t="n">
-        <v>29.97366488050543</v>
+        <v>50.79754344006191</v>
       </c>
       <c r="K2" t="n">
-        <v>35.6637797140949</v>
+        <v>31.01139488352451</v>
       </c>
     </row>
   </sheetData>
@@ -19651,34 +19651,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.13694530437851</v>
+        <v>49.76749659557807</v>
       </c>
       <c r="C2" t="n">
-        <v>41.38905153060674</v>
+        <v>30.96270764997778</v>
       </c>
       <c r="D2" t="n">
-        <v>58.01481365630521</v>
+        <v>32.30426434951115</v>
       </c>
       <c r="E2" t="n">
-        <v>46.1114896642985</v>
+        <v>41.86247331729646</v>
       </c>
       <c r="F2" t="n">
-        <v>35.33493606563738</v>
+        <v>32.09005432558342</v>
       </c>
       <c r="G2" t="n">
-        <v>41.2772459938184</v>
+        <v>43.45972812017855</v>
       </c>
       <c r="H2" t="n">
-        <v>43.87192286720018</v>
+        <v>51.64571125001032</v>
       </c>
       <c r="I2" t="n">
-        <v>52.71183015311887</v>
+        <v>52.00980846128624</v>
       </c>
       <c r="J2" t="n">
-        <v>31.06314372033265</v>
+        <v>36.26906272760073</v>
       </c>
       <c r="K2" t="n">
-        <v>33.06290912225639</v>
+        <v>45.57144222205289</v>
       </c>
     </row>
   </sheetData>
@@ -19757,34 +19757,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.39949886454604</v>
+        <v>43.58691111198387</v>
       </c>
       <c r="C2" t="n">
-        <v>45.63937866064739</v>
+        <v>42.03919775223464</v>
       </c>
       <c r="D2" t="n">
-        <v>49.13930951999257</v>
+        <v>40.87997962610272</v>
       </c>
       <c r="E2" t="n">
-        <v>34.70602256043635</v>
+        <v>37.41864427451048</v>
       </c>
       <c r="F2" t="n">
-        <v>51.64818813547121</v>
+        <v>31.13889412231826</v>
       </c>
       <c r="G2" t="n">
-        <v>39.82937687760296</v>
+        <v>56.61518126595341</v>
       </c>
       <c r="H2" t="n">
-        <v>35.49455143009298</v>
+        <v>33.6035158727725</v>
       </c>
       <c r="I2" t="n">
-        <v>39.40441037884023</v>
+        <v>35.30602562742346</v>
       </c>
       <c r="J2" t="n">
-        <v>33.85387123646934</v>
+        <v>35.89756645683376</v>
       </c>
       <c r="K2" t="n">
-        <v>42.66904520654223</v>
+        <v>42.7932954329446</v>
       </c>
     </row>
   </sheetData>
@@ -19863,34 +19863,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.88040466436182</v>
+        <v>37.75590321645205</v>
       </c>
       <c r="C2" t="n">
-        <v>41.03366330338334</v>
+        <v>31.15500342902367</v>
       </c>
       <c r="D2" t="n">
-        <v>36.39958242270147</v>
+        <v>31.92429355681729</v>
       </c>
       <c r="E2" t="n">
-        <v>25.78993094137113</v>
+        <v>36.68167770298787</v>
       </c>
       <c r="F2" t="n">
-        <v>40.31116846835656</v>
+        <v>33.6573327531632</v>
       </c>
       <c r="G2" t="n">
-        <v>46.78555546962045</v>
+        <v>56.42106263184249</v>
       </c>
       <c r="H2" t="n">
-        <v>27.4758607408925</v>
+        <v>36.16208212848072</v>
       </c>
       <c r="I2" t="n">
-        <v>45.35985394425404</v>
+        <v>43.26089262572744</v>
       </c>
       <c r="J2" t="n">
-        <v>39.19223110256377</v>
+        <v>41.49690943112408</v>
       </c>
       <c r="K2" t="n">
-        <v>49.51531736185524</v>
+        <v>39.05993430161705</v>
       </c>
     </row>
   </sheetData>
@@ -19969,34 +19969,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.5544911622551</v>
+        <v>40.26956634003487</v>
       </c>
       <c r="C2" t="n">
-        <v>45.52558864443463</v>
+        <v>36.76648555161502</v>
       </c>
       <c r="D2" t="n">
-        <v>36.8887600355536</v>
+        <v>44.34456953167558</v>
       </c>
       <c r="E2" t="n">
-        <v>42.0039819913762</v>
+        <v>43.04892834605902</v>
       </c>
       <c r="F2" t="n">
-        <v>30.99947524565499</v>
+        <v>42.946798027783</v>
       </c>
       <c r="G2" t="n">
-        <v>45.82019376275559</v>
+        <v>16.43979955007029</v>
       </c>
       <c r="H2" t="n">
-        <v>47.39998332497093</v>
+        <v>50.33363378693406</v>
       </c>
       <c r="I2" t="n">
-        <v>39.76438314408261</v>
+        <v>35.30933603746862</v>
       </c>
       <c r="J2" t="n">
-        <v>19.75010821830276</v>
+        <v>40.27060043320928</v>
       </c>
       <c r="K2" t="n">
-        <v>40.45869938938085</v>
+        <v>34.51735724357094</v>
       </c>
     </row>
   </sheetData>
@@ -20075,34 +20075,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.88478690609038</v>
+        <v>29.07938250863889</v>
       </c>
       <c r="C2" t="n">
-        <v>52.78284040722745</v>
+        <v>42.64007445749001</v>
       </c>
       <c r="D2" t="n">
-        <v>45.56021560146618</v>
+        <v>35.39880320852564</v>
       </c>
       <c r="E2" t="n">
-        <v>36.07932406636192</v>
+        <v>41.18109475946765</v>
       </c>
       <c r="F2" t="n">
-        <v>30.85985680466022</v>
+        <v>36.98735380110224</v>
       </c>
       <c r="G2" t="n">
-        <v>33.38447246487049</v>
+        <v>35.75869721224734</v>
       </c>
       <c r="H2" t="n">
-        <v>38.01495585067713</v>
+        <v>42.22987611853613</v>
       </c>
       <c r="I2" t="n">
-        <v>53.47528485430258</v>
+        <v>37.95407719611719</v>
       </c>
       <c r="J2" t="n">
-        <v>48.93957546515443</v>
+        <v>33.07725599810005</v>
       </c>
       <c r="K2" t="n">
-        <v>37.60068713936608</v>
+        <v>33.12759143515493</v>
       </c>
     </row>
   </sheetData>
@@ -20181,34 +20181,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.18259518036416</v>
+        <v>34.26230813763262</v>
       </c>
       <c r="C2" t="n">
-        <v>29.90458089020095</v>
+        <v>29.18715451318385</v>
       </c>
       <c r="D2" t="n">
-        <v>36.20866578710394</v>
+        <v>48.66653776837403</v>
       </c>
       <c r="E2" t="n">
-        <v>60.5009658642704</v>
+        <v>38.30290350845283</v>
       </c>
       <c r="F2" t="n">
-        <v>35.85543424876367</v>
+        <v>39.08297672455338</v>
       </c>
       <c r="G2" t="n">
-        <v>30.59029699633564</v>
+        <v>37.66602414097702</v>
       </c>
       <c r="H2" t="n">
-        <v>45.02525501004546</v>
+        <v>46.05965173758234</v>
       </c>
       <c r="I2" t="n">
-        <v>52.42890528849131</v>
+        <v>60.64174128512128</v>
       </c>
       <c r="J2" t="n">
-        <v>43.68960048258121</v>
+        <v>37.67277354985603</v>
       </c>
       <c r="K2" t="n">
-        <v>33.30534993433616</v>
+        <v>38.24501127098114</v>
       </c>
     </row>
   </sheetData>
@@ -20287,34 +20287,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.15291307559447</v>
+        <v>57.28160581838127</v>
       </c>
       <c r="C2" t="n">
-        <v>38.01940965637517</v>
+        <v>35.82143359510547</v>
       </c>
       <c r="D2" t="n">
-        <v>62.40269203508242</v>
+        <v>32.61134873203449</v>
       </c>
       <c r="E2" t="n">
-        <v>33.77100418472752</v>
+        <v>43.16603068624315</v>
       </c>
       <c r="F2" t="n">
-        <v>32.53616016425023</v>
+        <v>46.91266418795599</v>
       </c>
       <c r="G2" t="n">
-        <v>53.03462214727129</v>
+        <v>38.0370807148505</v>
       </c>
       <c r="H2" t="n">
-        <v>47.02605706780109</v>
+        <v>47.46542449204992</v>
       </c>
       <c r="I2" t="n">
-        <v>42.80861354039847</v>
+        <v>60.44623668975104</v>
       </c>
       <c r="J2" t="n">
-        <v>47.46542449204992</v>
+        <v>36.53393254226607</v>
       </c>
       <c r="K2" t="n">
-        <v>50.71653534177648</v>
+        <v>35.44992814734424</v>
       </c>
     </row>
   </sheetData>
@@ -20393,34 +20393,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>53.0808507928743</v>
+        <v>50.54320888225768</v>
       </c>
       <c r="C2" t="n">
-        <v>38.85576229285646</v>
+        <v>37.36809249502561</v>
       </c>
       <c r="D2" t="n">
-        <v>38.16334300775779</v>
+        <v>36.33451516263286</v>
       </c>
       <c r="E2" t="n">
-        <v>39.81719498348533</v>
+        <v>34.22205625236179</v>
       </c>
       <c r="F2" t="n">
-        <v>48.62484101130438</v>
+        <v>48.3359961230548</v>
       </c>
       <c r="G2" t="n">
-        <v>36.19992379201108</v>
+        <v>56.11565526565423</v>
       </c>
       <c r="H2" t="n">
-        <v>48.26250970564565</v>
+        <v>51.94084449034825</v>
       </c>
       <c r="I2" t="n">
-        <v>44.20853749655163</v>
+        <v>47.79621823801343</v>
       </c>
       <c r="J2" t="n">
-        <v>54.95589697124182</v>
+        <v>37.34110816286586</v>
       </c>
       <c r="K2" t="n">
-        <v>41.55911837212872</v>
+        <v>37.77237479319804</v>
       </c>
     </row>
   </sheetData>
@@ -20499,34 +20499,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.92185408006362</v>
+        <v>39.36133380454995</v>
       </c>
       <c r="C2" t="n">
-        <v>41.77436947503296</v>
+        <v>35.22566459615228</v>
       </c>
       <c r="D2" t="n">
-        <v>43.29821971049708</v>
+        <v>38.72632547387291</v>
       </c>
       <c r="E2" t="n">
-        <v>34.95823882721349</v>
+        <v>39.95725943187433</v>
       </c>
       <c r="F2" t="n">
-        <v>40.06649742370131</v>
+        <v>43.0546218765449</v>
       </c>
       <c r="G2" t="n">
-        <v>38.42534240116299</v>
+        <v>51.067497260627</v>
       </c>
       <c r="H2" t="n">
-        <v>45.84262011769326</v>
+        <v>39.04415112890467</v>
       </c>
       <c r="I2" t="n">
-        <v>63.84676637668329</v>
+        <v>38.60357530966766</v>
       </c>
       <c r="J2" t="n">
-        <v>33.71313986914159</v>
+        <v>35.55112476580614</v>
       </c>
       <c r="K2" t="n">
-        <v>35.75935722005298</v>
+        <v>43.95425184850541</v>
       </c>
     </row>
   </sheetData>
@@ -20605,34 +20605,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.10660609070597</v>
+        <v>38.45855087170636</v>
       </c>
       <c r="C2" t="n">
-        <v>48.559879519983</v>
+        <v>43.93885498353</v>
       </c>
       <c r="D2" t="n">
-        <v>51.77567930666636</v>
+        <v>40.3685124671552</v>
       </c>
       <c r="E2" t="n">
-        <v>38.70495643767205</v>
+        <v>29.75924340264368</v>
       </c>
       <c r="F2" t="n">
-        <v>48.39746399071417</v>
+        <v>46.30340034990783</v>
       </c>
       <c r="G2" t="n">
-        <v>45.49780589471222</v>
+        <v>41.93435412390945</v>
       </c>
       <c r="H2" t="n">
-        <v>35.41201719686379</v>
+        <v>47.29203499512778</v>
       </c>
       <c r="I2" t="n">
-        <v>43.956766168104</v>
+        <v>43.82911627821695</v>
       </c>
       <c r="J2" t="n">
-        <v>50.77036898851443</v>
+        <v>48.71843296945619</v>
       </c>
       <c r="K2" t="n">
-        <v>26.2382250736004</v>
+        <v>36.89930203684494</v>
       </c>
     </row>
   </sheetData>
@@ -20711,34 +20711,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.26746621009876</v>
+        <v>32.0534457563831</v>
       </c>
       <c r="C2" t="n">
-        <v>28.71953274073568</v>
+        <v>29.754905615652</v>
       </c>
       <c r="D2" t="n">
-        <v>38.82202200311632</v>
+        <v>46.16446828135841</v>
       </c>
       <c r="E2" t="n">
-        <v>48.86518395254578</v>
+        <v>46.67093224543128</v>
       </c>
       <c r="F2" t="n">
-        <v>49.63801508308774</v>
+        <v>44.20363693347656</v>
       </c>
       <c r="G2" t="n">
-        <v>43.33751893433215</v>
+        <v>44.61639883885658</v>
       </c>
       <c r="H2" t="n">
-        <v>53.15907652899647</v>
+        <v>44.82393019508518</v>
       </c>
       <c r="I2" t="n">
-        <v>48.01962321596323</v>
+        <v>45.82778968779756</v>
       </c>
       <c r="J2" t="n">
-        <v>50.7928909890073</v>
+        <v>26.7636883214236</v>
       </c>
       <c r="K2" t="n">
-        <v>38.60882441403428</v>
+        <v>42.57808865993258</v>
       </c>
     </row>
   </sheetData>
@@ -20817,34 +20817,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>48.94642580191731</v>
+        <v>48.05583947827066</v>
       </c>
       <c r="C2" t="n">
-        <v>47.21314810931786</v>
+        <v>32.32958681964016</v>
       </c>
       <c r="D2" t="n">
-        <v>58.44966219393139</v>
+        <v>38.27273420712822</v>
       </c>
       <c r="E2" t="n">
-        <v>42.32088474512202</v>
+        <v>49.57929048193881</v>
       </c>
       <c r="F2" t="n">
-        <v>39.09068628426537</v>
+        <v>44.86840642984019</v>
       </c>
       <c r="G2" t="n">
-        <v>28.49364669762546</v>
+        <v>40.96686541899659</v>
       </c>
       <c r="H2" t="n">
-        <v>39.1888462018758</v>
+        <v>59.1393989011391</v>
       </c>
       <c r="I2" t="n">
-        <v>31.52699520549214</v>
+        <v>43.82636323212309</v>
       </c>
       <c r="J2" t="n">
-        <v>52.44032489029071</v>
+        <v>49.94674490807952</v>
       </c>
       <c r="K2" t="n">
-        <v>42.4062678908656</v>
+        <v>29.85213821447872</v>
       </c>
     </row>
   </sheetData>
@@ -20923,34 +20923,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.08598141296801</v>
+        <v>22.80914392813674</v>
       </c>
       <c r="C2" t="n">
-        <v>40.25545535878793</v>
+        <v>33.82642708945543</v>
       </c>
       <c r="D2" t="n">
-        <v>43.40297660090969</v>
+        <v>38.37360010421734</v>
       </c>
       <c r="E2" t="n">
-        <v>48.83160296743411</v>
+        <v>66.37376128761922</v>
       </c>
       <c r="F2" t="n">
-        <v>39.4796626600568</v>
+        <v>29.8435754272591</v>
       </c>
       <c r="G2" t="n">
-        <v>28.3566824207113</v>
+        <v>39.90584642561835</v>
       </c>
       <c r="H2" t="n">
-        <v>31.4874337227303</v>
+        <v>49.69277376776752</v>
       </c>
       <c r="I2" t="n">
-        <v>41.71784957928345</v>
+        <v>37.50824873860172</v>
       </c>
       <c r="J2" t="n">
-        <v>49.34037982083159</v>
+        <v>45.75675546864126</v>
       </c>
       <c r="K2" t="n">
-        <v>30.04759888934004</v>
+        <v>41.58050868769374</v>
       </c>
     </row>
   </sheetData>
@@ -21029,34 +21029,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.35034737681076</v>
+        <v>47.05910053133646</v>
       </c>
       <c r="C2" t="n">
-        <v>36.07466556137753</v>
+        <v>38.39313699082916</v>
       </c>
       <c r="D2" t="n">
-        <v>39.26301936002163</v>
+        <v>33.05297460786935</v>
       </c>
       <c r="E2" t="n">
-        <v>40.28066293326959</v>
+        <v>29.62053461280191</v>
       </c>
       <c r="F2" t="n">
-        <v>30.80039414921135</v>
+        <v>48.14830986551969</v>
       </c>
       <c r="G2" t="n">
-        <v>35.19934096425284</v>
+        <v>48.89785870973792</v>
       </c>
       <c r="H2" t="n">
-        <v>52.33726156939802</v>
+        <v>43.92829540041848</v>
       </c>
       <c r="I2" t="n">
-        <v>47.57428994576394</v>
+        <v>38.48843039970777</v>
       </c>
       <c r="J2" t="n">
-        <v>50.36057099886992</v>
+        <v>42.48909530728874</v>
       </c>
       <c r="K2" t="n">
-        <v>39.16873569852191</v>
+        <v>32.47068501727916</v>
       </c>
     </row>
   </sheetData>
@@ -21135,34 +21135,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.58898774480642</v>
+        <v>20.99180833568746</v>
       </c>
       <c r="C2" t="n">
-        <v>61.5474442719489</v>
+        <v>27.13787292435108</v>
       </c>
       <c r="D2" t="n">
-        <v>59.26536873247476</v>
+        <v>52.22760208512888</v>
       </c>
       <c r="E2" t="n">
-        <v>31.28791249811042</v>
+        <v>47.25548617871966</v>
       </c>
       <c r="F2" t="n">
-        <v>33.78329620509056</v>
+        <v>45.14143252935824</v>
       </c>
       <c r="G2" t="n">
-        <v>44.48766958161945</v>
+        <v>37.40375899403196</v>
       </c>
       <c r="H2" t="n">
-        <v>31.93492272128012</v>
+        <v>40.28691059103154</v>
       </c>
       <c r="I2" t="n">
-        <v>52.5340721701749</v>
+        <v>32.55653890084961</v>
       </c>
       <c r="J2" t="n">
-        <v>60.9421298855958</v>
+        <v>35.10834403952596</v>
       </c>
       <c r="K2" t="n">
-        <v>22.1985616542317</v>
+        <v>59.97034011272522</v>
       </c>
     </row>
   </sheetData>
@@ -21241,34 +21241,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.11069532292255</v>
+        <v>32.15773590774006</v>
       </c>
       <c r="C2" t="n">
-        <v>41.19513631308877</v>
+        <v>42.88264664806587</v>
       </c>
       <c r="D2" t="n">
-        <v>56.83284499737113</v>
+        <v>41.49316480743701</v>
       </c>
       <c r="E2" t="n">
-        <v>28.65925378901622</v>
+        <v>43.39062005388531</v>
       </c>
       <c r="F2" t="n">
-        <v>42.27879752697813</v>
+        <v>36.94470546067058</v>
       </c>
       <c r="G2" t="n">
-        <v>41.4698551946461</v>
+        <v>42.31556574018398</v>
       </c>
       <c r="H2" t="n">
-        <v>41.12500478484284</v>
+        <v>41.21576466940095</v>
       </c>
       <c r="I2" t="n">
-        <v>51.57057901836937</v>
+        <v>43.35425694470592</v>
       </c>
       <c r="J2" t="n">
-        <v>45.05046269626913</v>
+        <v>32.90252229837401</v>
       </c>
       <c r="K2" t="n">
-        <v>40.64977824034305</v>
+        <v>35.07398839502144</v>
       </c>
     </row>
   </sheetData>
@@ -21347,34 +21347,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.27862872981781</v>
+        <v>42.208807886976</v>
       </c>
       <c r="C2" t="n">
-        <v>30.94591995234081</v>
+        <v>30.90658649492695</v>
       </c>
       <c r="D2" t="n">
-        <v>44.06855080653686</v>
+        <v>56.63052774131589</v>
       </c>
       <c r="E2" t="n">
-        <v>44.67871089744952</v>
+        <v>42.4270690785375</v>
       </c>
       <c r="F2" t="n">
-        <v>35.89524895033764</v>
+        <v>55.59166470422981</v>
       </c>
       <c r="G2" t="n">
-        <v>48.85369959450058</v>
+        <v>30.16747272822337</v>
       </c>
       <c r="H2" t="n">
-        <v>32.04119796354473</v>
+        <v>27.34452122443817</v>
       </c>
       <c r="I2" t="n">
-        <v>42.59354939289789</v>
+        <v>46.94332233961115</v>
       </c>
       <c r="J2" t="n">
-        <v>53.90038135207311</v>
+        <v>36.48830141482818</v>
       </c>
       <c r="K2" t="n">
-        <v>37.16735627298786</v>
+        <v>42.90260468297077</v>
       </c>
     </row>
   </sheetData>
@@ -21453,34 +21453,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.86847794932363</v>
+        <v>51.9969078801936</v>
       </c>
       <c r="C2" t="n">
-        <v>50.60464902200201</v>
+        <v>48.80624934324866</v>
       </c>
       <c r="D2" t="n">
-        <v>39.01128596473039</v>
+        <v>46.83311039802502</v>
       </c>
       <c r="E2" t="n">
-        <v>47.90545018764823</v>
+        <v>34.40113573385678</v>
       </c>
       <c r="F2" t="n">
-        <v>38.25946620059525</v>
+        <v>44.53229704712641</v>
       </c>
       <c r="G2" t="n">
-        <v>43.60636880040005</v>
+        <v>35.64673439332155</v>
       </c>
       <c r="H2" t="n">
-        <v>51.46304489929579</v>
+        <v>36.08236208811939</v>
       </c>
       <c r="I2" t="n">
-        <v>54.4684130055646</v>
+        <v>42.00924991185774</v>
       </c>
       <c r="J2" t="n">
-        <v>55.35811016079654</v>
+        <v>65.50067318202021</v>
       </c>
       <c r="K2" t="n">
-        <v>40.05469802043996</v>
+        <v>47.41964448036108</v>
       </c>
     </row>
   </sheetData>
@@ -21559,34 +21559,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.15594099041661</v>
+        <v>39.00269949026888</v>
       </c>
       <c r="C2" t="n">
-        <v>35.21114375235082</v>
+        <v>48.09620760860119</v>
       </c>
       <c r="D2" t="n">
-        <v>59.2519925361592</v>
+        <v>35.6236285492549</v>
       </c>
       <c r="E2" t="n">
-        <v>38.47637595388372</v>
+        <v>33.10608431211022</v>
       </c>
       <c r="F2" t="n">
-        <v>30.88591142918647</v>
+        <v>55.14337501464468</v>
       </c>
       <c r="G2" t="n">
-        <v>44.9000405228168</v>
+        <v>24.8407129129849</v>
       </c>
       <c r="H2" t="n">
-        <v>39.54962024819621</v>
+        <v>45.41395480016617</v>
       </c>
       <c r="I2" t="n">
-        <v>37.35744915633806</v>
+        <v>56.81504955507161</v>
       </c>
       <c r="J2" t="n">
-        <v>47.80363931354105</v>
+        <v>50.8793615197066</v>
       </c>
       <c r="K2" t="n">
-        <v>34.01403165450093</v>
+        <v>38.34279019148406</v>
       </c>
     </row>
   </sheetData>
@@ -21665,34 +21665,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.82845666769917</v>
+        <v>34.35562267794691</v>
       </c>
       <c r="C2" t="n">
-        <v>35.28718450816724</v>
+        <v>55.47685485504267</v>
       </c>
       <c r="D2" t="n">
-        <v>50.18050548338578</v>
+        <v>43.33231745268643</v>
       </c>
       <c r="E2" t="n">
-        <v>41.90782418109678</v>
+        <v>44.62572617955334</v>
       </c>
       <c r="F2" t="n">
-        <v>31.45532847447097</v>
+        <v>37.54856470237311</v>
       </c>
       <c r="G2" t="n">
-        <v>42.26849737794016</v>
+        <v>44.63251384914961</v>
       </c>
       <c r="H2" t="n">
-        <v>35.12080649910915</v>
+        <v>51.61852515730368</v>
       </c>
       <c r="I2" t="n">
-        <v>34.88352150858467</v>
+        <v>38.69220311619873</v>
       </c>
       <c r="J2" t="n">
-        <v>49.81116146554098</v>
+        <v>37.13437161193936</v>
       </c>
       <c r="K2" t="n">
-        <v>41.4505620883567</v>
+        <v>48.33363348658519</v>
       </c>
     </row>
   </sheetData>
@@ -21771,34 +21771,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.35619047713361</v>
+        <v>51.11816656876152</v>
       </c>
       <c r="C2" t="n">
-        <v>49.39116439174689</v>
+        <v>42.44621920514684</v>
       </c>
       <c r="D2" t="n">
-        <v>36.88366968215102</v>
+        <v>34.78575284585926</v>
       </c>
       <c r="E2" t="n">
-        <v>26.2545370555253</v>
+        <v>31.59107291779814</v>
       </c>
       <c r="F2" t="n">
-        <v>41.46758070172487</v>
+        <v>32.32463925384028</v>
       </c>
       <c r="G2" t="n">
-        <v>42.68982376843365</v>
+        <v>34.97224789593143</v>
       </c>
       <c r="H2" t="n">
-        <v>49.35627016420461</v>
+        <v>47.9181303308177</v>
       </c>
       <c r="I2" t="n">
-        <v>34.58137208496299</v>
+        <v>40.14999922459543</v>
       </c>
       <c r="J2" t="n">
-        <v>51.99179918879942</v>
+        <v>42.73742781307568</v>
       </c>
       <c r="K2" t="n">
-        <v>53.78591857754674</v>
+        <v>37.05680057667082</v>
       </c>
     </row>
   </sheetData>
